--- a/results/cluster_ga/UAVs4_GRID13/tour/UAVs4_GRID13_1920_16_Greedy_sequences.xlsx
+++ b/results/cluster_ga/UAVs4_GRID13/tour/UAVs4_GRID13_1920_16_Greedy_sequences.xlsx
@@ -668,35 +668,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-92-93-95-96-104-105-106-108-109-122-134-135-118-129-131-132-120-121-145-146-147-148-161-156-157-158-155</t>
+          <t>77-82-109-106-129-104-90-105-145-158-157-161-108-95-156-155-93-79-80-81-96-122-135-148-132-118-131-120-147-146-134-121-92-78</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-7-8-20-18-33-11-24-37-34-19-45-46-47-48-49-59-60-62-74-70-71-86-63-76-84-85-72</t>
+          <t>34-76-89-86-88-63-37-62-74-71-24-11-8-19-45-46-47-85-84-72-70-33-7-6-20-48-49-59-60</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>89-88-97-98-99-100-101-115-127-114-110-124-125-126-113-136-137-141-154-162-149-150-151-153-140-139-163-164-166-167</t>
+          <t>5-2-29-15-3-4-43-42-54-69-65-51-38-13-1-41-28-27-26-39-55-53-68-18</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1-2-3-4-13-39-26-27-28-29-38-51-41-42-43-82-53-54-55-69-68-65-77-78-79-80-81-15</t>
+          <t>139-125-124-97-136-149-162-150-140-141-153-126-100-99-98-110-137-151-167-154-164-163-101-115-127-114-113-166</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -766,35 +766,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>85-73-86-87-88-89-115-114-100-102-98-111-112-113-99-110-123-126-154-167-164-151-152-138-163-149-166-140</t>
+          <t>110-111-83-123-112-115-102-89-88-73-163-149-151-138-71-114-113-74-87-86-85-84-72-100-99-154-152-166-167-126-140-164-98</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>58-20-7-8-11-10-9-6-5-31-32-33-34-35-36-37-24-46-45-50-49-63-62-74-72-84-71</t>
+          <t>26-13-14-54-67-64-38-25-52-51-41-55-56-29-42-30-17-16-4-1-15-28-65-66-68-70-79-12-0</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>9-8-7-58-45-46-62-49-24-37-36-33-31-32-34-35-10-11-50-63-20-6-5</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>7</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>79-81-82-83-90-103-94-95-91-105-119-129-116-117-118-122-108-121-107-144-131-132-133-134-135-142-143-120-148-161-158-157</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>81-142-143-119-134-148-120-132-144-117-157-90-107-135-122-161-158-95-82-108-121-133-105-116-118-131-129-103-91-94</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>4-1-0-12-13-14-15-16-17-25-26-38-29-30-28-41-52-51-54-42-55-56-64-65-66-67-68-70</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -864,31 +864,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>115-102-99-123-111-112-126-125-137-138-140-127-141-154-167-163-164-165-166-153</t>
+          <t>112-127-167-154-140-165-138-111-123-137-166-164-163-153-141-115-102-126-125-99</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0-3-4-12-13-15-43-18-17-28-27-38-25-26-42-66-52</t>
+          <t>12-77-78-79-52-38-25-13-28-26-15-4-3-27-66-81-42-43-17-0</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>77-78-79-81-82-95-93-90-103-107-109-122-120-121-117-129-130-131-132-133-134-142-143-144-145-146-147-148-157-158-160-161</t>
+          <t>58-72-84-83-85-86-88-74-19-23-36-21-7-24-63-87-50-76-62-71-70-45-75-61-35-48-47-34-46-33-6-18-32</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>7-6-19-21-23-24-32-33-34-35-36-45-46-47-48-50-63-61-62-58-70-71-72-74-76-75-83-84-85-86-87-88</t>
+          <t>103-117-131-129-142-143-160-161-146-130-82-93-158-145-157-144-121-95-107-109-122-134-133-132-120-148-147-90</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -962,15 +962,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>113-86-99-98-112-88-102-89-101-114-115-140-125-126-127-128-152-138-123-164-150-149-162-163-136</t>
+          <t>128-102-89-88-86-101-113-164-162-138-125-150-163-149-136-123-98-126-112-99-140-152-115-114-127</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-1-3-4-16-13-0-25-28-30-31-52-53-55-56-57-64-65-66-69-70</t>
+          <t>59-72-58-74-62-49-33-60-73-63-75-76-37-10-9-23-8-34-20-19-7-21-48-36-24-35-22-32</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -978,7 +978,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>105-80-81-82-83-106-90-77-91-103-104-94-95-107-108-109-117-130-131-132-133-134-135-157-144-158-145-155-142-147-160-161</t>
+          <t>5-57-31-82-81-28-53-30-4-1-13-0-55-66-69-56-70-83-80-65-52-64-77-25-3-16</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -986,11 +986,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>7-8-9-10-24-20-21-22-23-19-32-33-34-35-36-37-49-48-58-59-60-62-63-76-73-74-75-72</t>
+          <t>106-161-147-133-135-134-108-107-145-131-130-91-90-104-117-158-155-157-160-109-95-94-132-144-142-103-105</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>78-80-81-92-93-94-95-96-105-129-116-118-119-121-122-108-134-131-144-130-142-143-132-146-147-148-155-157-158-159</t>
+          <t>155-143-131-78-77-80-95-94-108-147-157-132-142-129-116-118-96-119-146-134-121-81-93-92-105-130-158-159-144</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1068,27 +1068,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-7-8-21-22-11-24-32-33-35-36-37-50-63-48-45-58-59-61-47-72-73-74</t>
+          <t>35-36-22-11-24-37-63-76-50-73-59-45-72-74-61-21-8-48-87-89-86-85-6-7-58-32-33-47</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>14-15-26-12-25-38-64-57-30-18-5-17-31-52-66-40-28-42-56-55-43-29-16-2</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>7</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>102-89-76-87-114-97-98-99-100-86-112-85-123-124-125-127-128-141-153-137-136-149-150-151-152-139-154-162-163-164-165-166-167</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>64-52-25-14-2-17-16-15-26-28-18-30-31-38-40-42-29-43-57-56-55-12-66-77</t>
+          <t>97-98-125-139-163-164-99-123-122-124-150-137-151-152-166-165-148-149-162-153-167-154-128-127-141-114-102-100-112-136</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-84-85-86-87-101-99-100-96-109-110-111-113-124-125-126-161-135-136-137-138-139-140-141-128-153-152-149-148-162-163-165-167</t>
+          <t>113-101-100-87-86-139-109-110-85-83-96-84-125-128-141-140-124-152-165-163-162-149-111-99-126-153-167-136-137-138</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1166,23 +1166,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>36-8-9-10-11-24-35-22-23-32-19-21-7-45-46-49-50-59-60-61-74-71-72-73-63-76-75</t>
+          <t>72-57-44-45-32-46-5-22-60-63-76-75-49-50-7-31-19-23-11-24-74-73-61-21-8-35-36-9-10-59-71</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>79-90-91-92-93-94-95-108-121-160-133-131-119-105-118-129-116-104-155-142-143-144-134-147-145-158-159-106</t>
+          <t>53-55-43-56-68-79-12-25-26-27-4-30-29-16-15-14-1-13-0-38-52-51-64-67-40-28-41-54</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-4-5-16-28-15-14-12-25-26-27-13-29-30-31-38-64-67-43-44-41-40-53-54-57-56-55-52-51-68-82</t>
+          <t>158-155-142-135-121-119-131-106-94-108-95-82-105-118-116-129-133-161-148-134-147-160-159-145-144-143-104-93-92-90-91</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -1256,15 +1256,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77-78-79-90-91-92-93-94-95-106-105-104-117-119-120-133-132-131-130-129-142-155-143-144-146-145-158-159</t>
+          <t>117-130-143-131-104-79-94-106-159-146-132-91-90-77-78-105-142-129-155-144-145-158-133-119-93-92-95-120</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-8-11-10-9-20-22-23-24-37-34-36-35-33-45-46-59-71-63-61-73-74-75-76-89</t>
+          <t>46-61-74-71-22-23-8-63-37-24-11-10-9-6-20-36-35-34-59-73-89-76-75-45-33</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>85-86-96-124-110-101-114-115-141-112-125-126-138-136-135-139-140-123-148-149-150-152-153-154-162-165-166</t>
+          <t>65-51-64-18-29-1-15-66-39-52-68-82-69-41-53-54-55-40-12-0-2-17-31-44-57</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1280,7 +1280,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>12-1-2-0-15-17-18-29-31-69-40-41-54-52-64-53-82-57-44-55-68-66-65-39-51</t>
+          <t>153-166-149-135-123-125-139-140-141-154-126-110-96-86-85-101-115-114-112-148-162-150-136-124-138-152-165</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-45-85-87-89-101-97-96-109-110-112-113-115-122-123-125-126-127-128-137-136-148-150-152-166-153-154-164-151</t>
+          <t>148-110-97-85-115-128-125-126-127-154-166-164-150-123-136-112-101-137-152-151-153-113-83-96-109-122</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1362,15 +1362,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13-12-1-14-15-16-39-25-26-38-52-51-64-53-40-17-29-42-56-43-69-67-66</t>
+          <t>48-8-22-23-36-24-11-37-61-73-60-71-58-45-72-87-89-75-74-34-50-62-59-19-7-20-46-47</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>78-79-82-91-92-93-95-106-107-116-117-118-119-143-129-130-131-155-156-144-146-133-120</t>
+          <t>67-57-44-18-5-16-1-13-14-15-17-29-56-69-43-42-40-53-66-52-39-25-12-51-64-38-26</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1378,11 +1378,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>7-8-5-18-19-20-22-23-24-11-36-37-50-46-34-47-60-44-57-58-59-48-61-62-75-72-71-74-73</t>
+          <t>119-120-133-146-144-93-107-106-118-117-131-143-155-156-129-116-130-91-79-78-92-82-95</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1452,15 +1452,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>92-95-94-93-103-104-107-109-110-119-120-121-123-149-161-134-135-136-148-160-147-146-145-142-130-155-157-144-129</t>
+          <t>163-152-164-150-99-110-100-102-101-114-126-113-127-115-128-140-139-141-125-123-111-165-166-167-154-153-151-149-136</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>21-37-10-11-8-31-32-33-5-44-45-47-62-50-60-61-48-63-70-71-72-73-74-75-115-85-87-84-19</t>
+          <t>31-44-70-80-64-28-27-39-51-77-66-53-42-29-1-17-16-40-41-55-56-82-79-65-25-12-38-54-43-30-5-2</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1468,15 +1468,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>89-88-99-100-101-102-114-113-111-125-126-139-140-127-128-141-154-153-152-151-150-163-164-165-166-167</t>
+          <t>72-71-85-89-63-50-37-11-32-45-19-33-21-61-47-73-87-74-62-48-8-10-75-88-60-84</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1-2-30-16-17-43-27-28-29-12-38-39-40-41-42-25-51-64-54-55-56-53-65-66-77-79-80-82-90-91</t>
+          <t>142-129-103-90-135-120-121-160-161-148-145-130-144-95-109-147-146-134-93-94-107-119-155-157-91-92-104</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -1550,31 +1550,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>98-84-113-100-137-109-110-111-112-99-122-123-125-126-127-128-102-139-140-148-149-151-153-152-150-161-162-163-164-166-167</t>
+          <t>98-149-162-125-102-89-88-140-152-127-128-126-110-86-87-113-112-163-150-167-153-151-164-166-139-137-100-99-111-123</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0-1-26-12-13-14-15-4-17-29-38-39-40-41-56-69-57-44-54-64-52</t>
+          <t>37-63-76-62-49-35-23-47-46-58-71-57-84-44-45-73-60-7-6-9-11-10-36-61-59-75-34-8-20</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>132-93-79-77-78-83-82-80-103-90-104-105-107-120-119-108-95-146-129-130-144-143-156-159</t>
+          <t>15-39-52-40-14-1-0-54-41-17-4-56-69-78-26-12-13-38-64-77-29</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6-7-8-9-10-11-37-23-34-20-36-35-46-45-47-49-58-71-73-63-62-59-60-61-76-75-86-87-88-89</t>
+          <t>130-129-143-93-105-104-103-90-159-144-156-108-95-83-82-79-80-107-120-122-109-119-132-146-148-161</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -1648,35 +1648,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>96-97-98-111-109-110-102-113-122-123-125-128-139-150-136-137-138-165-166-135-149-151-163-164-140-126</t>
+          <t>129-144-158-159-147-122-109-108-160-145-146-133-132-143-142-130-118-90-91-92-94-135-96-93-106-105</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0-2-14-15-16-29-41-27-39-38-25-26-66-77-52-53-54-56-43-67-51</t>
+          <t>2-0-29-16-15-41-54-66-43-56-67-77-25-26-27-53-52-51-38-39-14</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>90-91-92-108-94-93-105-106-118-129-130-132-143-142-144-158-145-133-147-160-159-146</t>
+          <t>46-47-60-32-72-86-85-74-24-50-88-73-83-44-45-35-23-34-57-70-58-84-75-49-61-20-19-18-6-33-62-37-10-36</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>137-125-126-139-138-113-111-110-97-98-102-128-140-123-136-149-151-166-165-163-164-150</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>8</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>10-6-18-19-20-23-24-32-33-34-35-36-37-44-45-46-47-49-50-62-61-60-58-57-70-72-73-74-75-84-83-88-86-85</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-92-93-94-95-103-104-106-107-108-121-118-116-129-132-133-134-135-148-143-144-160-146-142-155-157-158-145</t>
+          <t>94-95-108-148-135-160-158-107-104-142-155-129-103-90-106-118-143-144-132-134-93-92-116-145-146-157-133-121</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1754,23 +1754,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2-12-13-14-15-16-40-27-28-30-17-44-43-51-52-67-78-64-65-55-56-69-70-79-66-80-82-83</t>
+          <t>13-56-69-83-70-44-43-67-79-52-12-51-80-82-66-65-78-64-14-28-27-15-17-2-16-31-55-30-40</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>6-32-20-11-37-76-46-23-36-50-62-35-19-45-58-71-72-73-59-60-61-47-48-49-10-22-34-21</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>85-86-100-88-89-102-101-87-110-123-111-125-112-127-128-141-140-139-138-149-163-152-153-151-165-166</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>23-10-11-19-20-6-22-21-31-32-34-35-36-37-62-50-48-47-49-46-45-58-60-61-59-71-72-73-115-76</t>
+          <t>115-127-153-128-141-166-165-139-123-111-88-89-102-101-140-151-138-112-125-152-163-149-86-110-85-87-100</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -1844,23 +1844,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>105-92-104-103-129-91-94-119-132-130-142-143-156-158-159-160</t>
+          <t>156-158-159-160-119-94-91-78-92-105-103-104-129-142-143-130-132-108</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-19-33-8-21-20-50-24-23-36-17-44-45-46-47-31-58-61-62-63-70-71</t>
+          <t>45-33-19-20-23-24-8-21-47-61-63-50-36-62-89-88-71-58-46</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>85-88-89-98-97-96-109-110-111-108-112-113-114-115-127-125-124-135-138-139-140-152-149-161-162-163-164-165-166</t>
+          <t>26-39-40-41-31-4-3-13-69-56-17-5-1-38-67-80-66-68-82-70-44-42-15-14-2-28-53</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1868,11 +1868,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2-1-3-4-28-15-14-13-26-38-39-40-41-42-56-53-66-67-68-69-82-80-78</t>
+          <t>109-135-149-163-164-124-165-140-115-127-114-85-110-111-139-152-125-113-112-138-166-162-161-96-97-98</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1942,35 +1942,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>114-100-101-99-110-111-112-113-102-115-128-124-136-123-138-139-153-152-149-162-163-165-166-167</t>
+          <t>147-134-144-143-117-157-105-118-92-93-94-82-106-104-142-155-119-132-83-121-108-95-135-161-122-148-160-159</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>27-26-38-54-80-69-56-67-79-65-51-52-66-13-12-1-3-30-17-42-70-29-28</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>7</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>7-8-9-11-24-32-33-34-35-50-37-36-47-48-72-59-60-46-63-62-73-74-75-89-86-87-84</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>31-32-18-47-60-48-24-63-7-5-9-11-37-34-33-59-46-72-73-74-75-62-50-36-35-8</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>79-80-82-83-92-93-94-95-104-105-106-118-117-144-119-121-122-135-134-108-157-143-148-147-132-155-142-159-160-161</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>30-3-1-12-13-18-29-28-27-26-5-17-31-56-42-51-38-54-52-65-66-67-69-70</t>
+          <t>165-163-149-124-102-89-87-101-113-138-162-136-123-110-111-100-86-166-167-99-84-114-115-128-152-153-139-112</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-84-82-96-109-110-99-112-127-138-123-124-125-126-113-136-122-147-149-150-165-160-163-164-153-166-167</t>
+          <t>104-95-83-134-160-121-81-82-107-143-142-156-155-116-118-131-147-159-108-96-109-122-117-90-91-92-106-80-78</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2048,27 +2048,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0-1-2-3-14-12-27-16-17-15-39-41-57-43-29-44-67-53-40-52-65-51</t>
+          <t>47-59-57-8-10-11-21-48-35-50-75-86-73-76-36-37-61-6-19-32-33-44-85-89-62-49-87-84-71</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>81-80-78-90-91-92-106-95-108-107-104-116-117-118-121-134-131-143-142-155-156-159</t>
+          <t>14-27-40-39-12-0-1-41-29-43-15-3-17-16-53-52-51-65-67-2</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>99-112-126-127-102-113-110-164-153-167-166-165-163-138-125-124-123-136-149-150</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>8</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>76-48-37-11-10-8-32-33-35-19-6-21-36-47-71-59-61-62-50-49-75-73-85-86-87-89-102</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-96-87-88-89-112-100-101-109-98-122-123-124-125-126-127-128-141-136-137-138-139-140-135-148-149-150-164-166-154-167</t>
+          <t>78-92-105-104-91-103-117-116-143-156-142-108-95-155-157-159-133-119-93-80-120-106-118-144-158-160-145-130-90-77</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2146,27 +2146,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-9-10-23-36-21-34-18-31-32-44-20-22-45-46-47-48-57-70-85-59-61-71-72-74-50-75-63</t>
+          <t>36-23-21-45-32-71-72-85-87-59-48-47-34-20-46-74-75-63-50-89-88-61-22-10-9</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>77-78-80-81-64-90-91-104-93-95-56-92-105-106-130-116-117-118-119-108-120-133-142-143-144-145-155-156-157-158-159-160-103</t>
+          <t>4-3-30-44-18-5-28-15-16-66-67-83-70-57-81-65-42-29-69-43-56-31-26-0-13-25-52-64-38-40-17</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>43-4-3-13-0-26-25-38-15-29-42-30-17-16-28-40-52-65-66-67-69</t>
+          <t>122-135-96-100-140-128-127-101-126-98-125-138-139-164-166-167-137-150-149-136-148-124-154-141-112-123-109</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>80-81-82-83-91-92-94-95-69-96-103-104-105-106-107-108-109-117-118-119-121-129-130-131-133-134-135-142-155-160-147-148-145-157-158-146</t>
+          <t>117-108-82-94-107-95-80-81-83-109-135-134-133-119-121-96-106-105-160-147-146-145-131-157-118-142-158-148-122-92-78-104-91-129-103-155-130</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2244,27 +2244,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9-8-6-18-19-20-21-22-23-24-50-33-34-35-36-44-45-46-47-72-61-70-57-73-74-75-76</t>
+          <t>75-76-74-24-23-36-50-61-73-72-34-22-21-20-19-6-8-9-35-33-45-46-47</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84-86-87-88-89-98-100-110-111-112-113-114-115-138-127-126-136-122-123-153-140-139-162-149-150-164-165-167</t>
+          <t>12-26-55-69-57-30-28-40-44-31-4-18-16-1-14-27-42-70-67-66-64-38-25-0</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>40-1-0-12-25-38-26-28-42-27-14-16-4-30-31-55-67-78-64-66</t>
+          <t>127-139-138-149-111-112-113-87-110-98-136-150-167-165-164-162-140-115-114-100-89-88-86-84-123-126-153</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2334,23 +2334,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-91-95-96-104-118-107-108-109-120-106-119-134-121-147-131-130-133-116-142-145-132-156-155-157-160-161</t>
+          <t>104-90-91-109-95-96-119-131-116-118-130-142-155-157-145-147-134-161-160-120-106-107-108-121-133-132-156</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24-10-9-7-19-18-5-32-45-33-35-47-48-49-62-60-73-74-75</t>
+          <t>30-16-4-3-15-27-2-1-12-55-69-81-67-66-25-26-53-41-43-42-54-79-65-78</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>88-86-87-84-110-99-101-102-89-115-128-126-125-138-152-140-149-150-136-162-165-164-154-166-167</t>
+          <t>48-86-84-57-70-83-73-74-87-75-47-49-62-35-9-10-24-33-7-5-19-18-60-45-32</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>27-12-2-4-3-15-1-25-26-16-30-41-42-57-43-55-54-53-65-78-67-69-70-66-79-81-83</t>
+          <t>99-110-165-164-150-138-166-167-140-115-101-89-88-102-126-152-154-128-125-162-149-136</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -2432,15 +2432,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77-90-91-52-93-105-103-104-116-106-107-94-143-155-129-131-132-119-134-147-160-145-158-133-144-117</t>
+          <t>90-103-143-144-116-129-155-158-132-145-119-79-77-91-117-104-131-133-107-106-105-94-93</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-7-8-9-10-11-19-21-24-23-32-33-35-48-45-47-37-49-62-70-59-60-61-63-50-57-71-76-89</t>
+          <t>32-48-24-23-37-63-60-71-8-21-11-10-9-35-86-87-47-59-45-6-7-33-61-62-50-49-76-102-89-85-19</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -2448,19 +2448,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>85-86-87-112-98-100-102-115-127-111-97-124-122-109-110-136-135-148-150-151-152-153-166-161-162-163-164-154-167</t>
+          <t>12-26-25-67-82-70-43-69-68-81-83-80-52-2-1-13-28-40-65-66-55-31-57-41-38-39-42-44-5</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>31-28-39-38-25-12-2-1-13-26-40-41-42-43-44-55-65-66-67-68-69-79-80-81-82-83</t>
+          <t>115-98-111-150-97-109-134-162-147-167-166-152-164-100-112-124-110-122-136-160-135-151-163-161-148-153-154-127</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2530,7 +2530,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>103-90-91-106-107-108-109-116-117-130-131-118-132-133-121-135-134-143-144-145-146-147-159</t>
+          <t>130-143-144-132-118-131-145-135-109-121-108-107-106-91-90-117-133-134-159-146-147-103-116</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2538,27 +2538,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-7-19-18-31-20-21-22-24-10-32-34-35-36-37-44-45-46-48-49-50-61-63-70-71-72-73-75-76</t>
+          <t>19-20-46-45-71-32-7-6-72-73-75-37-36-49-50-63-76-61-48-34-35-21-22-10-24</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84-86-87-88-89-98-101-114-102-110-111-100-113-112-123-124-126-127-128-141-137-140-136-149-150-151-162-163-166-167</t>
+          <t>29-41-66-51-53-28-18-31-15-0-12-38-64-39-1-54-67-79-81-68-16-4-3-26-17-43-70-55-42-44-30</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>15-1-39-26-12-0-3-17-4-28-29-30-43-16-55-42-38-51-53-54-41-64-79-67-68-81-66</t>
+          <t>98-84-86-88-89-100-113-166-162-150-123-111-124-112-87-101-102-128-140-167-141-114-110-149-136-163-127-126-151-137</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2628,23 +2628,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65-77-78-79-80-81-82-90-91-104-93-94-95-92-105-106-107-108-109-117-118-132-120-133-119-130-142-145-146-155-157-159-160</t>
+          <t>77-90-146-142-133-159-160-104-105-106-107-93-94-109-108-119-118-91-80-95-82-79-92-81-120-132-155-117-130-157-145-78-65</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8-9-11-10-20-24-23-21-33-34-35-36-50-63-48-46-72-47-61-74-75-87-86-76-89</t>
+          <t>30-43-39-25-13-14-66-69-42-32-58-56-83-57-29-16-1-12-2-28-52-68-44-31-70-18-19-5-17</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>98-99-101-102-113-139-115-128-140-126-125-124-138-110-136-148-149-150-151-152-153-154-164-163-162-165-166-167</t>
+          <t>46-61-87-86-74-75-47-34-10-23-24-76-89-63-50-48-11-9-8-21-35-36-20-33-72</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -2652,11 +2652,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>39-13-1-12-25-14-16-17-18-19-2-28-29-42-58-32-5-31-30-44-57-66-52-43-56-68-69-70-83</t>
+          <t>126-140-128-139-153-154-162-148-163-150-151-152-166-167-165-164-138-124-125-113-101-102-115-99-98-110-136-149</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2726,15 +2726,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84-86-114-88-96-97-122-110-111-87-113-112-109-123-139-165-140-136-137-126-138-135-161-149-152-154-141-128-166-167</t>
+          <t>80-82-149-134-122-83-96-84-94-90-81-109-123-131-144-117-145-142-157-132-110-97-136-135-119-120-104-93-129-155-160-161-121</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18-5-7-8-9-11-6-20-21-22-23-24-35-33-34-31-45-44-71-72-47-48-61-75-36-50-63-62-59</t>
+          <t>6-20-7-11-24-23-22-8-47-87-86-62-63-50-36-21-9-34-48-35-59-72-75-61-71-45-33</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -2742,19 +2742,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>78-79-80-81-83-82-90-93-94-104-117-119-120-121-134-160-157-131-132-144-145-155-142-129</t>
+          <t>26-27-30-44-43-54-42-41-28-25-67-5-18-17-2-31-56-55-79-65-78-52-40-66-64-38-39-13-1-0-14</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-2-14-13-38-25-39-27-26-28-17-30-55-41-42-43-56-67-54-52-64-65-66-40</t>
+          <t>139-114-88-112-113-140-128-141-154-167-166-126-111-137-138-165-152</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -2824,7 +2824,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77-90-93-103-116-117-105-118-129-130-131-132-133-145-159-160-147-143-155-156-157-144-146</t>
+          <t>90-118-130-116-103-129-143-132-131-144-155-156-157-159-160-147-146-145-93-94-108-133-105-117</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2832,15 +2832,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24-11-9-23-20-32-33-37-63-46-47-49-61-60-58-45-75-73-72-86-87-89</t>
+          <t>56-30-43-17-2-0-12-27-14-1-40-53-54-66-51-77-78-65-82-69-67-26-25</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84-96-108-98-99-100-101-113-111-110-125-127-114-124-136-137-139-140-152-150-162-161-149-163-164-165-167</t>
+          <t>20-5-45-58-70-72-33-32-31-44-9-24-11-47-23-73-75-63-49-37-61-60-46</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -2848,11 +2848,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>12-1-2-5-17-14-40-25-26-27-30-44-43-70-82-94-51-53-54-78-65-66-67-69-56-31-0</t>
+          <t>98-84-96-110-111-140-167-165-161-149-124-99-100-113-101-89-87-86-139-164-162-163-150-136-137-152-127-114-125</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2922,35 +2922,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-91-92-93-94-95-106-118-117-104-129-130-131-142-143-144-145-147-160-158-157-155</t>
+          <t>157-155-142-91-106-131-118-117-129-130-144-143-145-158-147-160-121-95-94-93-90-104-92</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11-10-9-7-21-6-32-22-24-20-33-35-46-59-48-49-50-63-60-47-61-58-71-72-74-75-76</t>
+          <t>2-17-29-68-55-41-54-66-52-14-26-25-38-39-64-78-67-80-81-4</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>99-102-89-84-98-97-85-110-111-112-114-127-128-167-141-140-165-150-151-153-154-164-149-136</t>
+          <t>32-75-74-61-85-71-58-57-18-21-63-50-10-6-20-7-44-46-60-48-24-11-35-47-84-83-72-59-76-49-33-22-9</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>29-4-18-17-14-2-26-25-38-39-67-55-81-121-83-44-57-64-52-41-66-78-80-68-54</t>
+          <t>99-164-165-140-154-167-153-141-128-127-151-150-112-114-102-89-97-111-110-149-136-98</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3020,23 +3020,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-97-98-99-100-114-111-110-122-123-124-147-135-136-152-139-115-167-154-164-163-125-138</t>
+          <t>97-75-85-83-123-111-76-102-167-138-152-154-164-163-114-139-89-115-125-136-124-99-86-101-100-98-110-122</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0-1-3-4-5-6-7-14-17-32-18-30-29-25-40-41-42-58-45-69-68-66-52-54-55-67-43-44</t>
+          <t>52-65-25-14-0-1-29-42-68-64-77-79-80-67-41-54-40-3-43-55-69-81-92-90-66-78</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>64-65-77-90-79-80-81-78-92-103-104-106-120-108-133-142-130-131-132-118-129-156-160-146-144-157-158</t>
+          <t>7-32-22-24-48-34-18-45-73-62-49-61-47-58-72-71-30-44-17-4-5-6-11-10</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -3044,11 +3044,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10-11-24-22-34-47-48-49-62-61-71-72-73-76-75-89-86-85-101-102</t>
+          <t>132-118-131-130-142-156-157-129-103-104-106-108-135-120-133-147-160-146-158-144</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3118,15 +3118,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-92-95-96-103-104-105-107-109-122-120-121-117-129-130-132-133-134-135-145-146-147-148-156-157-158-159-160-161</t>
+          <t>129-130-133-121-82-81-107-132-145-157-156-158-159-160-146-147-134-120-95-79-92-77-90-103-105-104-117</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-7-11-10-8-18-20-21-23-32-33-35-36-50-45-46-47-48-49-76-74-60-88-73-58-44</t>
+          <t>58-60-46-11-21-33-49-74-72-73-45-32-47-35-36-10-23-50-76-88-87-48-20-8-7</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -3134,19 +3134,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>98-99-72-85-87-100-110-111-112-113-114-115-153-140-128-127-126-139-138-151-152-166-163-164-124</t>
+          <t>55-67-66-12-0-30-43-56-57-44-2-13-26-51-65-53-40-42-18-5-17-3-28-41</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3-2-0-12-13-51-26-40-30-28-41-17-57-43-42-55-56-53-65-77-79-66-82-81-67</t>
+          <t>110-111-126-99-100-114-115-128-96-135-161-148-138-166-152-153-140-127-113-139-112-124-122-151-164-163-85-98-109</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3216,35 +3216,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12-96-97-71-101-100-98-109-111-114-115-128-123-122-135-136-138-151-148-161-149-152-153-167-154-164-165-166-140</t>
+          <t>114-115-138-149-151-97-96-148-161-135-109-98-111-140-154-128-101-100-122-164-166-167-153-152-165-136-123</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-21-10-24-8-19-33-34-72-45-46-47-50-37-48-88-76-49-63-62-74-75-87-85-60-58</t>
+          <t>10-63-50-48-49-60-46-47-62-76-75-87-88-74-85-72-34-21-33-44-45-8-6-58-57-71-19-18-37-24</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>38-25-51-66-67-68-69-55-42-2-3-17-16-41-40-12-0-64-52-65-53</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>119-118-104-117-116-155-143-81-95-120-144-158-106-107-92-79-103-91-77-90-131-145-159-146</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>90-77-91-79-92-116-103-104-107-106-95-120-119-118-117-155-143-144-131-146-159-158-145</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0-2-3-16-17-18-25-38-40-41-65-64-51-52-53-55-57-44-42-66-67-68-69-81</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3314,35 +3314,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>97-98-88-101-110-111-112-114-115-100-123-124-125-126-127-128-136-151-140-139-148-162-137-150-163-164-165-166</t>
+          <t>97-98-111-162-123-136-128-115-140-163-150-124-110-112-126-114-86-87-88-100-127-166-164-165-139-89-101-151-125-137</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>41-2-1-0-25-12-14-15-16-17-18-7-19-4-28-29-30-31-32-6-42-43-44-56-70-69-68</t>
+          <t>33-32-46-47-35-36-11-37-50-49-63-74-75-72-58-7-6-19-9</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0-25-42-43-30-4-16-29-41-12-14-2-64-68-56-69-70-31-44-18-17-28-15-1</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>7</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>64-77-78-81-82-83-96-109-94-104-103-116-105-106-107-95-92-117-134-120-121-122-130-131-132-118-142-143-146-147-158-159-160</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>33-9-11-35-36-37-50-75-63-49-46-58-72-74-89-87-86-47</t>
+          <t>105-92-103-132-148-147-158-143-159-160-146-130-104-117-77-78-106-122-109-82-83-96-134-118-131-142-116-120-107-81-95-94-121</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3412,35 +3412,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>87-86-85-98-99-100-101-102-115-128-113-114-111-123-124-136-139-112-125-137-127-141-154-167-153-152-151-149-162-163-164-150</t>
+          <t>101-111-123-109-135-148-115-102-114-139-87-86-96-98-99-136-141-128-153-113-127-125-124-150-163-162-149-137-151-154-167-164-152-112-100-85</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4-1-0-14-15-30-17-27-25-16-55-39-40-43-57-54-53-52-56-38-64-65-66-68-69-70</t>
+          <t>27-40-57-14-25-38-30-43-16-64-78-79-65-54-39-52-15-4-17-68-56-70-69-55-82-83-80-66-53-0-1</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>78-79-80-82-83-109-96-94-93-92-103-104-105-106-90-117-118-119-156-129-130-131-132-133-134-121-142-143-145-146-148-135</t>
+          <t>19-32-5-18-49-50-37-62-60-46-59-58-47-35-36-23-11-9-22-34</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22-9-11-18-19-5-58-32-34-46-35-36-49-23-37-50-47-59-60-62</t>
+          <t>92-93-133-146-145-130-105-94-106-118-131-119-121-134-132-104-142-156-143-129-117-103-90</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84-85-86-87-88-89-101-99-100-98-109-110-112-113-114-122-123-124-127-167-154-139-140-141-163-150-151-152-138-161-148-164-136</t>
+          <t>99-86-85-98-140-141-124-122-123-161-148-109-136-110-84-112-113-100-138-139-167-163-164-150-151-152-154-127-114-101</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -3518,27 +3518,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-7-8-9-11-24-23-21-45-32-34-35-36-50-61-76-62-63-74-73-72-59</t>
+          <t>8-7-21-61-74-73-72-50-59-34-11-23-24-36-62-89-87-88-76-63-35-9</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>79-78-77-104-103-118-105-107-108-94-120-121-129-130-144-145-159-134-133-146-156-157-143</t>
+          <t>67-56-57-27-14-13-54-68-69-81-82-83-41-38-51-39-42-45-32-4-6-30-17-43-44-31-66-53-16-18-28-15-1</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4-1-13-14-15-16-17-18-27-28-30-31-38-39-41-42-43-44-66-53-54-56-57-51-67-68-69-80-81-82-83</t>
+          <t>130-159-146-133-107-80-79-78-104-77-129-144-143-156-157-121-108-94-118-145-134-120-105-103</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3608,35 +3608,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-77-78-79-93-117-104-106-107-108-120-121-132-129-142-143-144-145-147-159-158-156</t>
+          <t>104-142-117-106-120-109-122-95-108-107-93-77-78-79-121-132-145-147-143-158-159-144-156-129-90</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8-7-10-11-21-35-36-23-22-49-37-20-33-19-47-46-58-60-61-73-74-62-76</t>
+          <t>37-22-23-10-7-8-19-33-20-21-47-85-58-61-35-46-60-73-74-36-49-62-76-86-87-11</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>82-69-55-39-38-3-18-17-65-64-51-53-41-25-13-15-44-83-57-31-30-43-70-56-42-0-2-14-27</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>126-112-128-141-138-149-148-162-164-163-139-125-99-102-115-114-124-123-150-153-167-127</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>85-86-102-127-115-87-99-114-109-122-123-124-112-126-125-128-141-139-153-167-138-150-149-164-163-162-148</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0-14-25-13-2-15-17-18-3-27-30-57-44-43-41-42-39-38-51-53-55-56-31-64-65-69-70-95-82-83</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-84-85-99-96-97-98-89-100-101-102-109-110-111-112-113-114-128-125-126-124-135-136-137-140-141-150-167-154-164-165-152</t>
+          <t>84-99-162-150-165-167-140-114-89-101-128-141-154-126-113-96-98-125-102-100-85-124-110-97-112-137-136-109-135-164-152-111-83</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -3714,23 +3714,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8-7-19-9-10-22-34-31-32-36-24-37-50-63-62-46-57-58-59-61-48-47-70-71-72-73-74-75-76</t>
+          <t>13-0-27-69-82-56-43-26-38-51-39-52-42-15-3-1-40-53-68-66-77-78-65-67-41-30-64-12-25</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>91-92-108-95-107-104-105-93-103-116-117-118-119-129-130-131-132-133-134-147-145-142-143-155-156-157-160-148-162-161</t>
+          <t>58-70-72-73-19-8-7-48-50-62-76-75-36-22-10-9-34-63-37-24-47-59-57-61-74-46-31-32-71</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-3-26-13-43-30-12-27-25-38-39-40-41-42-15-52-51-68-56-67-65-66-53-78-64-77-69-82</t>
+          <t>148-161-160-147-133-105-92-118-156-155-142-129-143-157-95-108-93-107-132-119-131-145-104-117-116-103-91-130-134</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -3804,31 +3804,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84-85-87-123-110-97-98-99-100-101-89-112-113-114-115-167-127-141-165-139-166-162-163-150-136-126</t>
+          <t>85-136-163-162-99-98-126-141-127-115-89-114-165-150-166-167-139-113-101-87-86-100-84-97-110-123-112</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0-1-13-14-16-17-42-28-29-26-39-43-30-51-64-78-65-53-54-66-67-68-69-77-90-52</t>
+          <t>47-62-75-63-50-46-32-19-6-72-49-24-8-45-71-73-58-60-37-11-10-22-36-48-33-21-20</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>80-81-82-83-95-109-96-107-93-104-116-117-118-119-120-121-133-130-129-142-143-145-159-160</t>
+          <t>42-70-57-69-31-30-29-13-65-66-16-17-5-1-0-26-39-54-67-52-51-64-53-14-28-68-43</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5-6-8-10-11-37-21-36-22-24-50-32-33-20-19-45-46-47-48-49-31-57-58-60-62-63-75-71-72-73-86-70</t>
+          <t>96-81-104-130-129-142-143-145-95-121-160-159-133-119-117-116-118-120-107-93-80-82-83-109-78-90-77</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -3902,35 +3902,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>85-83-96-97-98-99-100-101-110-111-112-125-148-135-126-127-114-137-166-153-152-151-161-163-164-123</t>
+          <t>110-97-73-85-111-153-127-114-76-126-152-151-96-83-71-72-74-89-101-112-166-164-163-137-100-99-98-123-125</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>12-13-54-81-82-56-30-17-16-42-28-25-38-39-77-51-66-27-14-15-29-70-69-79-52-55-44-4-2</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>7-5-18-21-35-59-45-33-47-60-61-48-22-11-10-8-9-36-50</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>147-161-158-145-144-142-157-155-130-132-133-134-118-116-117-94-95-135-148-107-119-106-92-90-91-104-146</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>7-8-9-10-11-21-22-50-36-35-45-59-47-33-48-61-60-71-72-73-74-76-89</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>77-79-90-91-92-94-95-107-106-119-118-104-116-117-130-132-133-134-157-144-145-146-147-158-142-155</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>15-4-5-12-13-14-2-28-17-18-56-42-16-29-30-44-27-39-25-51-52-54-66-38-55-81-70-69-82</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4000,31 +4000,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>108-95-94-107-91-116-117-121-134-161-133-130-142-143-155-146-147-158-157-144-131</t>
+          <t>80-79-107-133-121-134-146-147-117-91-77-116-130-155-144-157-158-95-108-94-142-143-131-78</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-7-8-9-10-11-21-20-19-44-31-32-33-34-35-36-37-22-47-46-45-59-58-48-61-62-75-72-73-74-63-76</t>
+          <t>32-89-48-20-19-58-46-45-21-9-10-11-22-35-59-34-47-72-73-76-63-61-33-7-8-37-36-62-75-74-6</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>30-3-15-0-13-25-53-67-41-42-54-66-40-26-39-65-64-38-16-17-5-4-55-68-69-70-31-44-43</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>97-85-87-89-96-122-112-123-109-110-99-100-151-138-137-124-113-127-128-164-136-149-139-126-115-153-154-165-83</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>15-3-16-13-0-4-17-25-26-41-38-39-40-30-42-43-55-54-53-64-65-66-67-68-69-70-77-78-79-80</t>
+          <t>138-153-154-128-127-139-164-165-151-161-96-83-85-109-122-136-149-137-126-115-87-100-99-97-112-113-110-123-124</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -4098,7 +4098,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>85-86-87-88-102-99-123-97-112-113-100-126-127-141-167-154-136-150-151-152-140-163-165-166-139</t>
+          <t>112-136-150-163-167-152-140-99-113-102-100-86-87-88-141-154-165-166-151-139-127-126-123-97-85</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>59-22-9-10-11-19-20-21-8-5-31-32-45-34-33-36-37-35-47-48-49-50-24-60-62-63-75-73-74-71</t>
+          <t>9-8-21-20-34-33-31-32-45-71-59-47-35-73-74-50-48-49-36-10-24-11-37-22-60-75-62-63-5-19</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -4114,19 +4114,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>135-94-91-104-105-107-109-95-118-129-116-142-143-144-145-146-147-160-155-156-158-159-148</t>
+          <t>83-70-17-3-16-54-79-77-53-12-13-28-29-27-25-1-2-56-55-67-80-81-65-66-64-52-0-42-43</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-3-2-25-12-13-16-17-1-27-28-29-42-43-52-53-54-67-77-64-65-66-56-70-55-79-93-80-81-83</t>
+          <t>107-144-142-155-129-91-104-146-145-160-159-147-148-135-109-143-156-158-116-118-105-93-94-95</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4196,31 +4196,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77-92-93-95-96-103-104-105-107-109-122-118-119-117-131-133-145-157-144-135-148-147-146-155-156-142-159-160</t>
+          <t>133-145-144-92-93-95-147-160-159-146-104-103-90-142-155-105-119-131-157-156-117-118-107</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2-3-13-25-26-27-64-38-51-41-42-54-69-55-56-29-66-53-67-65-78-90-79-81-82-83-16</t>
+          <t>83-16-3-2-42-56-70-41-67-65-66-64-77-51-38-13-26-55-54-78-53-25-27-29-31-44-69-82-79-81</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>84-72-87-86-89-75-36-37-47-33-34-21-7-32-19-45-46-49-50-22-24-11-61-74-60</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>99-98-123-110-111-112-126-127-128-138-137-136-139-140-154-167-153-150-162-163-164-165-151</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>102-22-11-19-7-21-44-31-32-33-34-36-37-24-45-46-47-49-50-60-84-70-72-74-75-61-86-87-89</t>
+          <t>162-148-122-109-96-98-111-110-123-140-153-128-102-99-112-127-126-139-154-150-137-136-135-138-164-163-151-165-167</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -4294,35 +4294,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>96-108-95-94-93-104-92-129-118-119-120-121-122-117-130-135-134-133-143-156-157-158-159-160</t>
+          <t>143-156-120-135-122-96-95-94-118-134-121-108-93-159-160-158-157-130-133-119-92-104-129-117</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>22-9-8-6-31-18-19-34-24-11-10-36-35-48-49-61-60-58-73</t>
+          <t>26-14-15-16-28-55-52-53-67-68-81-83-70-56-44-57-43-40-66-79-65-64-38-12</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>83-84-87-88-102-99-100-101-98-110-113-114-115-167-126-125-127-138-162-149-150-151-153-154-141-164-165-123</t>
+          <t>8-6-58-9-10-24-11-36-49-48-60-19-18-31-45-73-61-34-35-22</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>12-14-15-16-28-81-68-55-45-70-57-44-43-56-38-64-65-66-67-40-52-79-53-26</t>
+          <t>84-98-110-123-149-125-138-162-165-126-114-101-115-102-88-87-100-113-127-141-167-154-153-164-151-150-99</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-84-86-87-88-97-123-124-101-110-122-137-112-99-100-126-138-135-114-127-141-163-151-153-154-167-165-150</t>
+          <t>84-124-154-126-87-100-112-150-137-151-163-123-114-127-141-153-167-165-138-88-101-86-83-97-99-110-122</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4400,7 +4400,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3-14-13-12-25-27-40-38-39-41-30-43-42-51-52-53-56-55-54-64-66-67-94-79-80-82</t>
+          <t>41-80-67-66-79-78-53-40-82-55-54-25-13-39-51-38-64-52-27-43-56-30-14-12-3-42</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -4408,15 +4408,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>92-78-91-104-103-116-118-119-105-106-107-133-129-130-131-121-134-147-146-144-143-142-155-158-159-160-161</t>
+          <t>10-23-76-63-49-35-34-20-19-57-58-44-5-8-33-45-32-46-21-9-7-47-75-73-72-62-37-11</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5-7-8-9-10-33-19-20-21-23-37-11-34-35-32-44-45-46-47-58-57-72-62-63-49-76-75-73</t>
+          <t>103-104-91-92-106-107-121-94-118-129-142-116-105-160-161-135-134-159-147-158-146-131-130-119-133-144-143-155</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -4490,31 +4490,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>104-92-93-116-103-90-105-118-94-108-134-121-119-130-131-132-129-143-155-146-160-145-157-159-147</t>
+          <t>122-92-104-157-155-143-129-105-94-108-134-131-146-160-147-121-130-119-118-81-82-109-132-159-145-116-103-90-93-96-148-161-135</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>32-20-50-36-22-9-8-45-70-46-49-61-73-84-57-7-11-10-76-74-58-5-6-19-31</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>78-79-3-4-29-1-14-40-53-16-12-51-66-77-64-52-38-39-55-56-17-42-54-41</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>8-5-4-6-7-9-10-11-22-19-20-32-31-57-45-58-46-50-36-49-61-73-74-76</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>114-86-88-89-96-109-100-98-110-111-112-84-122-123-127-140-139-136-135-148-149-150-152-154-161-162-163-164-165-166</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1-14-12-3-16-17-29-79-53-41-40-38-51-39-52-66-42-56-70-82-81-77-78-64-54-55</t>
+          <t>111-164-165-98-123-163-162-149-136-110-88-89-114-100-86-152-166-150-139-154-140-127-112</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -4588,31 +4588,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>87-88-89-101-98-97-123-96-109-112-114-99-125-126-127-128-153-154-141-140-151-137-139-162-163-164-166-167</t>
+          <t>76-101-137-123-139-167-166-140-114-112-98-97-86-88-89-154-153-164-163-162-151-126-125-99-141-128-127-87</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3-4-0-12-13-25-16-14-26-27-28-29-30-38-39-40-41-42-78-52-54-77-64-66-67-80-56-43</t>
+          <t>42-41-29-16-0-3-14-13-12-39-52-40-54-28-27-26-25-38-64-80-67-78-77-66</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>83-69-94-106-105-118-104-116-117-107-120-146-135-159-143-144-132-142-155-156-157-158-147-161</t>
+          <t>58-72-59-45-33-74-75-50-73-47-85-84-69-4-30-31-32-36-11-20-57-83-70-21-22-23-37-35-6-5-43-56</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5-6-11-36-21-20-45-31-32-33-47-50-37-23-35-22-59-58-57-70-72-73-74-75-76-86-85-84</t>
+          <t>116-104-144-156-161-159-158-157-143-155-142-118-96-109-107-94-105-120-106-135-147-146-132-117</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -4686,15 +4686,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>95-107-93-91-104-90-92-81-108-134-109-83-122-121-120-130-131-132-133-117-144-155-156-157-148-160-161</t>
+          <t>148-122-104-91-92-77-93-107-120-95-83-117-130-156-157-132-131-121-109-108-81-79-90-155-144-133-134-160</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-7-9-10-11-19-20-21-23-24-48-33-36-37-50-49-47-45-58-44-32-73-60-61-63-75-70-71-72-59-76-62-74</t>
+          <t>45-58-72-73-88-50-37-6-7-75-62-10-9-20-19-32-71-59-47-49-23-36-24-11-21-48-60-61-74-76-63-33</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>88-102-100-98-111-112-113-114-127-124-125-126-123-136-137-150-151-138-167-154-141-140-164-165-139</t>
+          <t>40-39-25-27-52-65-64-51-26-12-0-4-17-44-70-56-67-55-42-28-13-15-3-43-54-41</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-3-15-12-13-43-17-4-28-27-26-39-40-41-42-25-51-52-67-55-56-54-65-79-77-64</t>
+          <t>123-124-161-164-165-167-126-127-102-141-154-139-136-150-151-137-138-140-114-112-100-113-125-111-98</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -4784,35 +4784,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84-87-88-89-97-99-100-112-128-102-115-123-124-125-126-127-111-136-138-139-141-154-167-151-150-149-163-164-152-83</t>
+          <t>149-136-109-97-96-84-123-135-134-83-82-145-144-142-158-130-117-119-132-120-121-107-105-106-133-147</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0-1-2-3-4-29-15-14-25-26-27-12-38-28-56-43-30-52-64-51-65-66</t>
+          <t>33-7-22-24-21-20-35-48-37-47-46-44-31-32-5-6-9-34-45-57-70-74-76-59-72-75-11-10-63-50-62-61</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>77-78-79-106-90-117-105-82-96-109-107-119-132-158-147-135-121-134-120-142-144-145-133-130</t>
+          <t>4-3-2-66-79-78-77-90-64-51-65-52-15-14-0-1-12-25-38-26-28-29-27-43-30-56</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5-6-7-11-10-9-20-21-22-32-31-44-33-34-35-37-24-47-46-45-48-70-57-59-61-62-63-75-72-74-76-50</t>
+          <t>112-139-127-126-138-125-111-124-152-154-167-141-128-115-88-87-99-150-163-164-151-102-89-100</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>85-88-89-97-98-99-101-100-109-110-111-128-114-115-123-124-126-112-136-137-149-161-151-152-154-150-162-163-165-166-167</t>
+          <t>162-149-123-137-161-136-150-151-98-97-111-89-99-126-114-100-85-109-110-124-112-152-165-128-115-88-101-154-167-166-163</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-7-8-9-24-50-10-22-18-31-32-33-34-36-37-61-19-46-47-48-60-73-59-70-44-45-58-74-75</t>
+          <t>51-38-39-26-55-27-16-4-70-29-28-41-52-81-67-64-77-80-79-56-30-17-3-15-2-14-13-53-65-78</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>77-78-79-80-81-67-95-93-94-91-90-103-104-105-106-107-119-129-116-120-147-160-132-144-159-155-156-157-121-117</t>
+          <t>59-44-58-31-6-5-19-34-9-37-50-36-47-22-24-10-8-7-18-46-61-48-60-73-75-74-33-45-32</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -4906,11 +4906,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2-3-4-17-14-15-16-13-26-27-28-29-30-41-39-38-51-52-53-55-56-64-65</t>
+          <t>95-94-107-106-105-121-147-160-159-132-144-156-157-119-120-117-103-116-104-90-155-129-91-93</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>85-86-96-97-109-99-101-98-110-111-114-139-123-124-125-126-127-154-136-122-148-149-150-151-152-164-162-135</t>
+          <t>96-136-124-123-122-109-98-114-127-126-151-110-97-135-162-125-111-101-154-139-152-150-148-149-164-99-85-86</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4988,27 +4988,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-7-8-9-10-22-21-19-23-24-50-37-35-47-46-34-48-49-61-58-45-71-72-73-74-75-76-88-89</t>
+          <t>37-23-35-34-21-6-7-8-10-9-24-61-74-46-49-22-50-89-88-75-76-19-45-72-58-71-73-48-47</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>91-103-105-106-107-108-118-131-144-130-129-143-142-157-133-147-160-159-145-121</t>
+          <t>40-39-1-13-55-57-28-27-54-80-79-66-67-65-16-29-30-18-31-43-44-82-69-70-15-26-25-52-4-3</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>144-108-121-107-106-93-105-118-103-91-129-130-131-143-142-157-145-133-147-160-159</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>9</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>16-18-4-13-15-3-1-25-26-27-28-29-30-31-43-40-55-39-52-54-93-79-65-66-69-57-44-70-67-80-82</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5078,35 +5078,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-84-87-88-98-99-100-101-124-110-112-113-114-115-102-126-127-128-139-138-153-154-165-152-136-149-162-163-164-150</t>
+          <t>163-152-154-128-149-110-124-112-87-100-136-162-150-126-98-84-83-88-101-99-102-114-115-127-153-139-113-138-165-164</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>19-32-58-71-46-48-49-73-45-35-37-23-22-8-9-10-76-75-61-24-11-6-70-57-50-63-36-60-72-18-21-20-7-44-31-5</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>42-43-65-77-80-82-66-51-25-12-26-39-40-27-14-16-3-17-30-29-52-64-41-54-0-1-2-28</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>5-6-7-8-9-10-11-18-19-20-21-22-23-24-31-32-35-36-37-44-45-57-48-50-49-46-58-60-61-63-70-71-72-73-75-76</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>104-103-94-107-108-121-129-142-132-134-148-156-144-145-146-131-143-157-158-159-160</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-2-3-17-16-28-12-25-26-27-14-29-30-39-40-41-42-43-54-52-51-64-77-65-66-80-82</t>
+          <t>156-107-94-108-121-134-148-160-131-104-103-129-144-157-159-158-146-132-145-143-142</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -5176,7 +5176,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>81-82-106-93-94-95-96-104-105-109-108-92-116-117-118-119-120-146-131-142-144-145-148-122-157-158-159-161</t>
+          <t>92-78-104-117-118-106-93-142-116-146-120-77-79-131-145-159-158-157-144-94-96-82-95-81-108-119-105</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5184,23 +5184,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1-12-13-14-15-16-29-25-26-38-52-39-28-40-41-42-55-69-56-54-66-65-77-78-79</t>
+          <t>45-71-59-20-57-70-86-61-89-75-63-23-9-7-35-24-47-60-87-84-73-48-49-22-46-34-8</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>86-87-89-100-99-113-101-102-114-111-98-110-123-124-138-136-151-162-135-149-150-141-167-153-154-128-165-152</t>
+          <t>28-38-25-12-39-54-41-40-26-52-65-66-42-18-31-69-56-55-29-15-14-13-1-17-16</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22-8-31-18-20-17-7-23-24-9-49-47-45-46-34-35-48-73-59-60-61-57-70-71-84-75-63</t>
+          <t>113-100-101-102-109-111-114-136-149-162-161-148-98-99-138-154-141-128-153-152-150-135-122-124-110-123-151-165-167</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -5274,7 +5274,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-91-93-94-95-96-107-120-118-108-122-134-132-130-129-143-144-146-147-148-156-157-158-160</t>
+          <t>93-94-148-134-160-158-120-108-95-96-122-107-132-146-147-118-129-156-143-157-144-130-90-91</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5282,23 +5282,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>49-37-11-24-36-23-48-35-9-34-46-20-32-58-59-60-72-74-75-76</t>
+          <t>26-40-80-79-55-4-3-14-69-70-82-81-68-78-52-38-53-54-2-12-27-28-41-43-16-42-39</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84-85-87-100-97-98-99-89-101-102-112-113-114-128-137-125-127-115-149-123-138-152-140-141-126-151-139-154-162-164-165-166-167</t>
+          <t>31-59-46-34-5-18-6-36-48-49-9-23-76-75-37-24-11-35-20-32-74-72-60-58</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>16-3-4-2-12-14-6-5-18-31-27-28-26-38-39-40-41-42-43-52-53-54-70-69-55-68-78-79-80-81-82</t>
+          <t>125-166-165-152-115-89-87-99-97-84-113-127-140-112-123-137-151-164-162-149-98-85-100-102-101-114-154-167-141-128-126-139-138</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -5372,7 +5372,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-97-98-114-101-86-109-110-99-113-112-123-124-126-127-128-136-149-166-154-153-147-161-162-163-164-151</t>
+          <t>127-128-154-151-112-98-97-110-124-123-164-162-161-109-83-113-114-126-136-135-149-163-153-166-99-86-89-88-101</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5380,7 +5380,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>25-1-2-4-0-12-14-16-17-5-18-27-26-28-55-56-40-41-42-44-70-52-54-30-31-57-65-66-67-77-51</t>
+          <t>19-57-31-44-23-35-73-74-76-62-37-48-71-70-72-34-10-11-33-46-61-47-21-5-18-7-20</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -5388,19 +5388,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>95-80-92-93-103-104-105-106-130-116-117-118-119-120-121-133-107-131-129-143-144-157-156-146-158-160-135</t>
+          <t>42-56-55-67-54-51-65-66-52-26-25-40-16-4-17-30-1-14-27-12-0-2-28-41</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>37-10-11-23-20-21-46-47-48-35-7-19-33-34-61-74-71-72-73-62-76-89-88</t>
+          <t>77-103-116-129-117-104-105-147-158-160-118-92-80-106-107-120-95-93-119-144-157-156-130-143-146-121-133-131</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5470,23 +5470,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>96-98-99-101-109-110-111-113-114-115-122-123-138-125-126-128-135-136-124-149-150-151-152-153-154-167-166-164-165-163-162</t>
+          <t>113-87-86-85-96-109-136-163-114-128-138-125-89-101-154-153-167-166-164-165-162-135-110-124-111-99-123-98-122-149-150-151-152-126-115</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0-1-2-4-5-55-14-15-28-26-25-40-29-30-31-17-43-44-57-53-54-68-56-52-66-12</t>
+          <t>6-8-11-76-63-74-73-61-48-50-72-45-46-71-57-44-58-47-34-23-24-36-49-35-9-22-7-5-31-32-19</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>90-78-79-81-108-107-106-92-103-116-117-118-120-134-146-132-131-143-142-156-158-159-160</t>
+          <t>14-15-17-4-30-29-43-26-40-25-12-2-1-0-28-68-56-55-54-66-53-52</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -5494,11 +5494,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6-7-8-9-11-36-22-23-24-32-19-35-34-45-46-47-48-49-50-63-61-58-71-72-73-74-76-89-86-87-85</t>
+          <t>107-108-134-160-159-158-131-81-132-156-143-142-103-116-146-120-106-118-117-90-78-79-92</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5568,15 +5568,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>128-102-101-100-99-111-112-125-126-110-136-138-140-141-150-151-152-153-162-163-166-167</t>
+          <t>99-112-100-76-89-75-84-87-101-102-128-86-74-110-126-141-152-138-151-150-163-111-125-166-167-153-140-88-63</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20-7-6-19-33-21-11-34-45-58-71-59-60-61-63-50-76-75-74-84-57-83-86-87-88-89</t>
+          <t>38-80-67-1-14-16-43-56-69-68-79-78-91-65-53-54-83-81-41-40-28-51-39-27-13</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -5584,19 +5584,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>78-65-79-80-81-91-104-118-106-108-109-116-117-105-119-121-135-148-161-146-147-132-155-156-157-159-131</t>
+          <t>71-60-45-31-17-5-7-19-6-20-21-34-59-11-50-61-33-18-4-30-57-58</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>118-131-146-147-161-162-159-116-104-105-119-132-148-136-108-157-156-155-121-135-109-106-117</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>13-4-5-1-14-16-17-18-27-28-30-31-43-56-40-41-38-51-53-68-69-67-54-39</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -5666,31 +5666,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>118-92-93-94-95-83-103-105-106-107-109-96-122-121-131-130-129-132-133-155-143-144-145-146-148-135-157-158-159-160-161</t>
+          <t>148-161-131-130-143-105-106-93-92-129-155-157-146-133-145-159-160-109-95-96-94-122-121-135-118-103-144-158-132-107-83</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>50-36-24-11-7-8-21-23-9-31-32-33-49-72-44-45-46-47-48-6-5-57-58-73-76-63-37</t>
+          <t>39-29-31-0-14-42-43-3-17-44-57-28-1-15-78-80-66-55-56-30-16-2-13-26-38-51-64-12-25-27-68-53-77-65</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>123-87-88-115-100-112-111-114-102-84-97-124-140-128-127-125-137-138-150-152-139-136-162-163-164-166-167</t>
+          <t>24-37-36-47-58-45-46-21-8-9-23-50-5-6-7-33-32-72-73-76-49-63-48-11</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-2-3-12-13-14-15-16-17-25-26-27-28-29-30-64-51-42-43-38-39-55-56-68-65-66-53-77-78-80</t>
+          <t>164-136-150-84-97-112-124-100-115-140-139-167-166-128-127-125-137-123-111-87-88-102-114-152-138-162-163</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -5764,35 +5764,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>92-105-94-95-107-118-91-104-129-116-106-119-120-121-122-108-130-131-132-135-134-133-142-143-144-146-148-156-157-158-159-160</t>
+          <t>91-144-156-131-120-121-130-104-129-116-105-92-94-106-134-146-157-158-143-142-160-148-135-122-108-107-133-159-132-119-118-95</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19-8-10-11-7-21-22-24-34-35-37-45-46-47-49-50-58-59-76-63-74-72-60</t>
+          <t>46-50-76-63-49-35-7-8-21-34-19-58-45-72-74-59-60-47-37-24-11-10-22</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>83-84-85-86-87-88-89-96-97-98-99-100-101-102-141-128-115-123-149-125-127-140-166-137-138-139-114-113-124-136-152-162-150</t>
+          <t>26-27-25-43-44-42-3-17-15-28-40-38-64-78-81-79-65-51-66-68-70-69-56-54-39-13-14-4-2</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>115-113-150-137-152-166-127-128-102-88-100-99-125-139-141-140-138-123-96-97-89-87-162-149-136-124-85-86-83-84-98-114-101</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>17-3-4-13-14-15-2-25-26-27-28-38-39-40-42-43-44-56-54-51-64-65-66-68-69-70-78-79-81</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5862,7 +5862,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>114-88-89-97-98-85-111-99-127-115-123-124-126-112-136-138-140-141-152-151-150-149-162-163-153-166-167</t>
+          <t>97-149-136-162-163-166-167-140-150-151-127-153-152-114-123-111-126-141-115-89-98-88-99-85-112-138-124</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5870,27 +5870,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>14-0-12-26-38-52-39-40-41-42-29-53-67-54-65-78-64-51</t>
+          <t>53-65-78-81-67-64-52-70-57-29-14-0-12-4-41-40-54-42-30-44-31-18-5-51-38-26-39</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>116-90-92-105-94-95-96-108-107-81-109-93-117-118-120-121-129-130-131-132-134-148-147-145-155-156-158-159</t>
+          <t>24-36-35-47-60-73-75-62-50-32-19-7-72-58-33-10-11</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4-5-32-10-11-50-19-31-30-18-7-33-24-35-36-47-70-57-58-75-62-72-60-73-44</t>
+          <t>130-129-116-92-94-121-134-132-131-155-145-159-147-148-158-156-118-105-96-95-109-108-120-107-93-90-117</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5960,7 +5960,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>99-97-98-101-88-102-115-125-126-127-128-139-137-136-161-148-150-153-154-140-167-165-162</t>
+          <t>116-142-120-134-147-148-95-94-93-117-155-156-157-158-144-145-159-161-121-107-118-90-103</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -5968,7 +5968,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8-7-5-18-19-20-21-22-23-24-36-34-33-45-46-48-49-50-57-58-61-74-73-72-84</t>
+          <t>98-99-97-126-127-139-125-137-150-165-136-162-167-153-140-154-128-102-115-101-88</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -5976,7 +5976,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>67-78-79-80-94-95-107-93-81-82-103-90-116-117-118-120-121-134-159-147-145-144-155-158-157-156-142</t>
+          <t>73-61-33-45-58-57-46-18-5-8-20-74-84-72-48-49-50-24-23-36-22-21-7-19-34</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -5984,11 +5984,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>16-4-14-13-1-12-25-26-28-29-30-56-41-39-52-64-53-40</t>
+          <t>64-52-39-13-1-4-56-41-40-28-16-14-26-67-82-30-29-81-80-53-12-25-79-78</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6058,15 +6058,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-82-90-92-103-117-118-105-93-108-95-106-120-121-122-129-130-155-133-134-159-143-144-145-161-148-135-132</t>
+          <t>110-113-100-101-98-84-83-125-126-153-123-149-163-164-141-127-87-89-102-115-114-111</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-8-7-19-10-11-23-24-35-34-32-44-58-59-48-49-50-46-47-60-61-62-71-70-72-73-74-75</t>
+          <t>71-72-74-60-73-19-35-47-48-49-61-32-6-59-58-46-34-7-8-10-23-11-24-62-75-50</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -6074,19 +6074,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84-100-101-89-87-102-98-110-111-113-114-115-141-153-126-127-123-125-164-163-149</t>
+          <t>25-27-13-14-41-54-69-43-44-56-70-0-12-38-64-39-53-42-15-16-5-4-67-66-65</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>12-14-0-13-25-15-16-4-27-38-39-41-42-43-69-54-66-65-53-56-67-79-77-64</t>
+          <t>148-135-133-103-77-121-122-93-106-105-118-143-145-159-120-130-144-155-129-117-79-82-95-108-132-90-92-134-161</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -6156,31 +6156,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>106-94-93-96-107-104-90-103-117-118-121-134-129-130-131-132-122-135-142-143-144-145-146-159-161-147-157-155-160-148</t>
+          <t>90-103-129-117-145-144-131-121-107-94-130-118-96-132-159-143-160-134-146-104-93-122-135-148-147-161-157-155-142-106</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4-5-6-7-8-9-23-19-22-34-44-18-31-45-47-48-62-61-60-71-72-73-74-85-84</t>
+          <t>73-86-74-7-18-6-5-19-8-9-22-23-85-84-72-60-61-62-48-34-47-71-45-44-31</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>86-99-101-102-114-112-111-126-139-137-123-136-138-125-128-141-154-167-165-164-163-152</t>
+          <t>55-43-42-29-4-16-0-12-13-25-40-67-80-30-15-26-66-79-65-77-78-64-38-41-81-82-68-14-27</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>15-14-13-0-12-26-25-38-27-29-30-16-40-41-42-43-55-64-65-66-67-68-79-78-77-80-81-82</t>
+          <t>111-123-137-163-126-125-139-152-167-165-154-141-128-138-136-164-112-101-102-114-99</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -6254,7 +6254,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77-79-80-109-83-92-91-82-93-94-122-95-117-104-103-81-107-121-134-160-146-132-133-119-130-129-155-157-158-142</t>
+          <t>82-83-109-122-146-94-77-103-129-132-142-155-157-119-95-107-130-117-91-92-79-80-134-160-158-104-81-93-133-121</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6262,23 +6262,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>33-20-11-23-36-50-89-76-49-60-47-61-59-71-84-102-87-88-62-21</t>
+          <t>59-20-21-33-47-87-98-99-71-84-60-61-36-23-11-49-89-76-50-62-88-102-100</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>100-99-98-125-126-127-154-112-113-123-135-136-137-149-162-161-163-164-165-166-167</t>
+          <t>14-27-25-51-41-67-55-4-5-56-57-18-29-28-40-42-31-30-17-2-1-13-12-15-16-54-53</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1-2-27-25-12-13-14-15-16-17-18-5-4-28-29-30-31-42-41-40-51-53-54-55-56-57-67</t>
+          <t>167-166-163-164-137-125-112-123-149-165-154-127-113-126-136-135-161-162</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -6352,35 +6352,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>108-106-107-104-116-118-133-130-129-120-121-134-135-148-143-144-146-147-142-155-156-158-159-160-161</t>
+          <t>146-107-106-104-90-91-118-155-156-158-159-160-135-134-147-161-148-121-108-120-133-144-129-116-130-143-142</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-5-4-7-8-9-10-18-19-22-24-86-31-32-48-35-46-47-44-58-49-61-62-63-72-73-74-87</t>
+          <t>61-74-62-72-47-73-58-46-32-19-63-49-48-35-8-9-22-10-24-7-6</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>96-83-97-98-99-125-112-101-114-127-123-124-111-122-136-137-138-153-141-140-151-163</t>
+          <t>42-29-5-31-44-56-68-81-52-66-77-65-67-80-27-13-1-14-2-28-41-39-26-12-69-70-18-4-82-83-57</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1-2-14-13-12-26-27-28-29-39-41-42-52-66-65-56-57-80-67-69-70-82-68-81-90-77-91</t>
+          <t>140-153-123-122-96-97-98-86-87-125-136-163-151-141-114-101-112-99-111-137-124-138-127</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -6450,7 +6450,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>86-87-89-96-97-100-101-102-109-110-111-112-113-114-115-123-124-126-128-141-137-138-139-140-135-148-149-152-153-161-162-163-164-165-166-167</t>
+          <t>121-108-156-160-161-135-159-131-129-155-157-158-148-109-96-134-145-120-107-119-132-133-144-143-92-105-104-103-116-117-91-106</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6458,7 +6458,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-7-8-9-11-23-20-22-21-31-19-32-49-33-45-46-47-37-50-61-62-63-76-73-72</t>
+          <t>62-37-11-23-46-72-32-45-33-19-21-22-9-20-7-6-8-63-47-49-50-76-61-73</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>77-78-80-91-92-103-116-105-106-107-108-104-117-119-120-121-134-132-131-133-145-143-144-129-155-156-157-158-159-160</t>
+          <t>15-30-31-17-4-1-40-64-51-38-53-66-67-29-2-42-56-54-41-27-43-57-80-78-77-25-12-13</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -6474,11 +6474,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>27-2-1-13-12-15-41-42-4-17-30-43-57-56-40-25-38-53-54-67-51-64-66-29</t>
+          <t>138-153-140-113-128-115-102-101-100-149-137-126-111-86-89-87-124-162-163-164-166-167-141-165-152-139-114-112-97-110-123</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6548,35 +6548,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84-73-88-86-87-85-96-97-98-99-100-124-123-114-125-127-128-140-138-139-141-154-150-162-149-151-164-166-167</t>
+          <t>84-97-136-162-150-141-149-148-135-85-98-138-125-127-99-100-87-86-88-114-140-128-139-124-96-122-154-166-167-164-151-123-83</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-7-8-11-10-18-19-20-21-22-45-33-34-35-36-24-48-63-50-46-59-72-31</t>
+          <t>19-33-46-59-8-6-5-18-72-73-31-45-34-21-7-22-11-10-24-36-35-48-50-63-20</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>40-51-38-79-53-54-42-3-4-30-43-81-70-80-64-77-65-68-69-55-41-67-39-12-14-2-16-28-27-26</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>131-104-103-90-145-144-143-118-92-116-130-142-155-158-159-146-147-134-108-107-94-121-160-133</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>103-104-116-90-92-107-108-94-118-121-122-135-146-133-145-130-142-155-144-160-134-147-136-148-159-158-143-131</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2-3-4-12-14-16-26-27-28-30-43-39-40-41-42-38-51-53-54-55-64-65-67-70-69-68-77-79-80-81-83</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6646,35 +6646,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-91-92-93-134-108-131-117-118-119-120-121-129-116-105-132-130-142-143-144-145-146-147-159-158-157-160</t>
+          <t>105-92-93-147-134-95-119-129-118-117-90-91-132-144-146-145-143-130-116-142-131-121-108-120-159-157-158-160</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>39-13-3-17-29-44-57-70-83-65-79-80-67-54-53-64-77-78-25-68-42-43-56-12-14-5-31-41</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>60-74-49-62-37-9-21-7-33-22-35-24-23-46-71-58-72-73-61-86-84-85-32-20-48-88-75</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>3-5-17-31-14-12-25-29-13-39-41-42-43-44-53-54-56-57-70-68-67-65-64-77-78-79-80-83</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>95-96-97-98-99-100-101-115-111-110-122-123-125-126-139-140-141-154-152-151-150-148-161-162-163-164-165-166</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>7-9-20-21-22-23-24-32-33-35-37-46-48-71-58-72-61-62-49-60-73-74-75-88-86-85-84</t>
+          <t>110-122-125-151-162-164-150-161-148-166-140-98-97-111-96-99-115-141-154-165-101-100-163-152-126-139-123</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -6744,15 +6744,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>86-96-97-98-100-101-102-110-111-112-113-114-122-123-125-150-135-136-148-161-162-164-127-139-141-140-154-167-152</t>
+          <t>123-162-150-164-152-140-139-111-86-112-113-167-154-141-127-100-101-102-89-114-125-136-98-97-110</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0-2-3-4-18-32-5-15-16-17-6-19-27-28-29-30-57-44-45-82-43-42-41-51-52-53-12</t>
+          <t>46-32-20-11-24-23-62-73-74-75-63-49-36-35-21-22-9-47-71-50-37-34-45-19-8-6</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -6760,19 +6760,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>64-77-78-79-80-90-91-95-94-92-104-119-131-117-118-106-121-108-133-134-146-143-144-142-155-158-159-160</t>
+          <t>4-3-16-2-5-18-44-30-17-57-43-42-28-41-27-15-29-12-52-64-51-53-0</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8-9-23-20-21-22-11-24-37-36-35-34-46-71-49-50-62-63-89-75-74-73-47</t>
+          <t>78-79-91-92-108-119-94-77-90-131-118-104-155-142-144-158-143-146-148-117-106-80-82-96-95-133-121-134-122-135-160-161-159</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -6842,15 +6842,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>93-78-79-80-81-82-95-91-77-90-103-104-106-107-109-122-118-119-116-129-130-133-134-157-143-144-145-147-155-142-158-159-160</t>
+          <t>154-152-153-167-123-109-110-101-128-114-115-141-164-151-137-150-136-122-148-124-111</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-7-8-11-23-35-22-87-32-86-74-49-36-37-44-45-46-20-33-59-61-62-63-75-71-72-34-70-84-57-18</t>
+          <t>74-87-61-11-36-8-7-20-45-71-70-57-23-37-33-18-5-6-46-59-86-35-22-34-32-44-84-72-62-63-75-49</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -6858,15 +6858,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>123-110-111-114-115-101-124-137-148-151-164-136-150-152-128-141-154-167-153</t>
+          <t>42-43-66-52-68-82-81-17-30-2-4-14-1-0-28-15-38-39-40-53-80-67-69-56-54-13-12-25-26-64-77-78-79-27</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-2-4-17-30-14-15-12-25-26-13-27-52-38-39-40-42-43-28-53-54-56-64-66-67-68-69</t>
+          <t>116-90-129-142-155-145-159-158-157-160-147-106-91-103-134-133-144-143-119-118-107-95-93-104-130</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -6940,35 +6940,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77-78-81-82-83-91-92-93-95-96-103-104-105-106-107-108-109-116-117-118-119-120-121-135-132-133-147-143-131-146-145-155-157-159-160</t>
+          <t>131-117-104-132-155-143-103-116-119-106-91-107-121-133-120-92-81-95-96-105-118-93-82-108-109-135-145-157-159-160-147-146</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>64-25-0-13-14-15-17-18-6-5-30-31-43-44-57-56-55-28-67-54-66</t>
+          <t>49-63-47-18-5-6-31-57-72-45-74-37-24-23-46-83-85-71-44-32-33-34-35-48-60-87-61-75-76-62</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>78-67-55-54-43-56-15-14-13-25-0-17-30-28-66-77-64</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>10</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>97-112-102-101-113-136-123-124-125-126-127-115-140-141-139-162-149-150-151-152-167-166-137</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>167-166-152-151-150-137-136-149-162-139-127-113-101-97-123-124-112-89-102-115-126-125-140-141</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>23-24-32-33-48-49-37-45-46-47-34-35-60-61-62-75-72-71-89-63-76-85-87-74</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -7038,23 +7038,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>85-86-87-88-89-97-99-100-101-102-110-112-113-114-115-124-125-149-136-137-141-140-127-152-153-166-162-163-164-165-154</t>
+          <t>99-112-166-88-100-89-101-115-102-154-141-140-124-110-136-149-162-125-165-153-152-114-87-86-113-127-163-164-137-85-97</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0-1-2-12-14-15-16-17-25-26-28-29-80-52-39-40-41-42-43-30-55-77-64-65-66-68-56-78-79-38</t>
+          <t>59-58-19-35-50-36-11-9-21-8-60-47-45-49-76-75-62-48-61-73-74-20-32</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>103-90-91-92-93-94-95-118-106-107-108-109-122-133-119-130-116-129-120-83-145-147-134-146-144-156-157-160-161</t>
+          <t>18-5-40-52-39-38-0-15-31-30-17-28-14-41-43-42-64-65-56-68-66-55-29-16-2-26-12-25-1</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -7062,11 +7062,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>11-9-8-5-18-19-20-32-31-45-35-36-21-47-48-49-50-58-59-60-61-62-73-74-76-75</t>
+          <t>109-160-157-108-106-92-91-90-103-94-107-83-80-77-116-130-129-145-144-118-79-78-93-95-134-147-161-133-146-156-119-120-122</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -7136,35 +7136,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84-98-99-111-112-113-114-115-122-135-124-137-125-126-139-140-151-149-150-165-164-148-161-163-152-153-166</t>
+          <t>105-116-142-104-78-77-83-82-121-107-133-145-144-132-147-160-134-120-143-155-157-130-118-93-80-95</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>58-32-73-63-50-37-35-20-19-7-10-36-89-74-46-21-22-8-11-24-47-60-59</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>7-8-10-11-22-20-35-37-24-36-21-32-19-46-47-73-58-59-89-63-50-74-60</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>7</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>77-78-93-105-104-116-133-120-107-95-121-134-132-118-130-142-160-147-145-143-155-157-144</t>
+          <t>12-26-25-13-39-40-67-69-57-44-31-15-27-56-43-17-18-30-66-53-38-64-52-65-2-4-5-28</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>15-18-5-28-13-2-17-4-25-26-27-12-38-31-44-57-40-43-30-52-53-56-39-64-65-66-67-69-80-82-83</t>
+          <t>115-153-126-113-111-125-137-150-161-148-135-122-124-165-164-152-99-84-98-114-112-139-151-149-163-166-140</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -7234,31 +7234,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65-92-93-94-122-107-119-103-144-131-132-134-142-130-155-146-147-148-135-157-156-158-160-161</t>
+          <t>161-147-107-119-160-158-157-155-142-130-144-131-132-134-135-148-146-156-103-90-94-92-93</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>33-8-6-19-21-22-23-11-24-35-34-36-37-50-47-62-75-88-73-58-59</t>
+          <t>17-4-31-44-56-12-52-64-25-38-26-15-3-16-30-42-67-39-28-66-53-65-77-78-69-68-80-41-70-57-55</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84-86-99-109-96-98-100-101-102-128-127-112-113-114-115-111-124-110-162-138-140-139-137-149-150-151-152-153-154-123</t>
+          <t>59-33-36-11-22-21-34-47-8-6-19-35-50-37-24-23-62-75-73-58</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>3-4-41-42-16-17-25-26-28-30-31-15-39-12-38-64-52-53-80-68-57-44-56-66-67-55-69-70-77-78-90</t>
+          <t>115-127-140-150-114-102-88-86-96-84-109-162-137-124-112-99-113-128-154-151-138-98-111-153-152-139-100-110-122-149-123-101</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -7332,23 +7332,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65-64-78-79-94-81-92-90-103-116-105-106-104-117-118-119-120-131-143-155-157-134-147-146-159-158-132</t>
+          <t>84-122-100-87-102-101-114-138-151-111-123-148-153-139-137-150-152-165-163-110-97-85-126-128-140-112-83</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0-1-3-5-4-13-14-15-16-18-17-28-29-42-41-66-52-54-55-56-30</t>
+          <t>22-48-49-36-50-24-33-46-58-71-45-32-76-62-35-47-34-21-8-7-6-20</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>97-87-100-101-102-114-112-111-110-122-123-126-128-151-138-139-140-165-150-137-152-153-163-148</t>
+          <t>52-66-30-44-4-16-1-3-5-18-17-42-56-70-57-29-41-54-55-28-15-14-13-0</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>33-20-8-7-21-22-24-36-50-35-34-32-6-45-46-47-48-49-76-62-58-57-70-44-71-83-84-85</t>
+          <t>120-134-147-146-159-157-158-103-90-116-117-143-155-131-78-64-65-92-105-104-118-132-81-79-94-106-119</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -7430,31 +7430,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-91-92-93-94-95-96-103-105-106-107-109-117-116-118-120-129-160-161-148-135-132-144-145-157-155-143-158-159-130-131</t>
+          <t>107-94-96-148-161-120-93-92-116-158-160-135-109-95-118-130-143-155-129-131-157-145-159-106-91-105-132-144-90-117-103</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-7-10-11-18-30-19-21-22-32-33-35-37-44-45-46-47-49-57-58-83-61-62-63-70-73-72-74-75-76-60-85-86-88</t>
+          <t>2-1-65-66-55-56-54-53-67-81-78-77-79-39-30-42-40-25-27-17-4-0-14</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>127-102-115-114-139-98-123-136-137-128-141-154-150-149-162-163-164-167-166</t>
+          <t>47-49-22-7-32-5-70-72-61-33-18-19-35-45-44-57-60-46-62-37-88-63-76-75-74-73-86-85-58-21-10-11-83</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1-0-17-4-2-14-25-27-39-40-53-54-42-55-56-81-67-79-77-78-65-66</t>
+          <t>139-162-137-98-114-102-115-128-154-167-166-164-150-163-149-136-123-127-141</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -7528,7 +7528,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>102-113-85-86-87-88-96-97-98-100-83-84-111-112-109-122-123-124-125-126-127-148-135-137-128-140-141-149-150-164-161-162-152-166</t>
+          <t>82-83-148-144-143-142-160-161-135-122-96-108-118-129-116-103-93-79-105-133-120-130-131-119-95-109-104-90-117-94-134-159-147</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -7536,23 +7536,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>35-9-10-11-22-20-6-19-32-21-36-50-49-61-46-58-59-73-62-76-74-48</t>
+          <t>61-36-50-76-48-22-10-6-5-19-32-59-73-35-49-9-11-18-31-58-20-21-74-62-46-44-70</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>103-90-79-93-95-94-105-104-129-116-117-118-119-120-108-134-131-133-130-142-143-144-160-159-147</t>
+          <t>0-4-17-43-69-68-55-41-30-3-16-15-2-28-27-42-39-52-51-64-66-65-13</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-2-3-4-5-18-31-16-17-13-15-28-30-27-39-41-42-43-44-55-52-51-64-65-66-68-69-70-82</t>
+          <t>124-137-126-141-140-152-166-164-149-150-162-128-127-113-112-102-88-86-87-100-125-123-97-85-84-98-111</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -7626,7 +7626,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>78-79-80-82-91-92-104-107-108-116-117-118-142-129-130-131-132-133-121-161-148-147-146-155-156-157-159-145</t>
+          <t>78-104-130-116-129-117-79-80-91-107-155-142-156-157-131-108-121-133-147-159-132-146-145-118-92</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-19-7-24-11-10-9-8-6-31-32-33-34-37-50-47-48-45-58-59-60-62-63-76-75-71</t>
+          <t>28-42-55-25-38-51-52-16-17-29-54-67-66-64-82-31-3-2-0-13-26-5-4-14</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -7642,19 +7642,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>109-84-86-87-89-102-114-101-100-99-83-123-113-112-111-97-110-124-127-128-136-137-138-139-140-141-150-152-153-163-164-166-167</t>
+          <t>62-75-47-58-71-8-9-11-24-37-50-63-76-10-33-60-59-48-34-45-32-19-6-7</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>16-4-3-2-0-14-28-17-29-26-13-25-38-64-51-52-54-55-42-66-67</t>
+          <t>148-109-89-114-164-152-128-102-101-113-136-124-111-83-84-97-86-139-140-87-100-127-141-150-161-137-110-123-99-112-138-153-167-166-163</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>113-100-101-102-98-110-112-125-126-127-128-152-137-138-141-140-139-149-150-136-162-165-167</t>
+          <t>150-110-98-140-139-100-101-102-141-128-127-126-113-112-137-138-149-136-125-152-167-165-162</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -7732,27 +7732,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0-1-2-3-4-12-39-25-26-27-28-17-30-31-29-54-40-53-41-69-56-68-66-64</t>
+          <t>40-28-29-2-3-1-12-39-4-17-41-53-64-66-54-55-30-31-56-69-68-27-0-25-26</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>79-55-83-82-80-92-91-122-93-94-95-84-96-107-105-103-90-116-117-118-119-109-133-134-135-143-155-158-145-146-160</t>
+          <t>47-48-49-63-62-34-20-19-9-35-8-10-76-61-60-32-58-70-71-72-73-88-75-87-84-46</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>8-9-10-19-20-32-34-47-46-35-48-61-58-60-49-62-63-70-71-72-73-75-76-87-88</t>
+          <t>155-116-79-80-82-95-92-91-90-103-117-105-119-145-146-160-118-122-109-83-96-135-134-133-93-94-107-158-143</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -7822,35 +7822,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>99-97-124-110-111-112-113-114-115-102-126-127-128-137-138-139-140-141-153-150-151-152-149-161-162-164-165-167</t>
+          <t>137-150-113-167-164-165-141-128-127-102-115-153-152-162-151-138-139-126-140-114-112-110-97-149-124-111-99</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3-16-29-56-43-15-51-25-2-17-30-13-38-39-0-27-40-52-65-80-82-69-68-79-77-64-66-81-55-54</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>23-36-8-71-83-84-87-88-33-19-5-44-58-9-10-24-63-73-45-72-86-74-60-59-46-47-61</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>119-132-129-158-159-161-135-134-95-94-107-106-133-120-146-156-155-117-90-103-116-130-118-108-96</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>5-8-9-10-59-19-24-23-36-46-45-44-47-72-33-60-71-58-61-63-73-74-83-84-86-87-88</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>77-79-80-81-82-96-95-94-103-90-106-107-108-120-117-118-119-116-129-130-132-133-134-135-146-155-156-158-159</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0-2-15-13-25-16-17-3-27-29-30-43-56-55-38-51-52-54-40-39-64-65-66-68-69</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -7920,15 +7920,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>104-103-91-95-106-107-108-109-117-118-119-121-122-135-134-133-132-130-142-143-144-161-148-156-157-159-160-145</t>
+          <t>103-143-161-160-122-132-104-142-156-144-157-145-159-106-119-118-130-117-95-107-133-134-135-121-148-109-108-91</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18-6-5-8-10-23-21-7-31-32-33-34-35-36-37-63-60-57-44-45-59-72-73-75-76</t>
+          <t>43-69-42-41-39-26-53-0-1-14-12-25-38-51-79-80-81-66-64-77-78-28-29-54-56</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -7936,19 +7936,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>85-86-88-89-98-99-101-102-114-127-128-126-140-111-137-123-139-138-151-150-149-152-164-165-166-167</t>
+          <t>23-36-37-63-75-76-5-18-17-4-31-34-35-8-21-32-59-72-6-7-10-33-83-70-57-85-73-60-45-44</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>86-114-151-137-152-167-166-138-126-140-139-150-149-123-102-89-88-101-127-128-165-164-111-98-99</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>17-14-0-12-1-38-25-26-28-29-4-39-41-42-43-51-53-54-56-64-66-69-70-77-78-79-80-81-83</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -8018,23 +8018,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-91-93-94-95-159-144-118-117-116-142-129-130-143-146-145-134-109-122-135-147-148-158-156-104</t>
+          <t>130-142-116-143-145-118-78-77-80-94-95-91-79-93-146-134-109-122-135-148-156-129-90-104-117-144-158-159-147-81</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-10-11-9-24-20-22-35-18-31-32-33-44-23-37-34-47-49-84-58-59-61-62-71-72-74-75-76-57</t>
+          <t>20-22-72-84-71-6-33-58-87-75-47-59-74-49-37-24-35-62-88-76-61-23-10-11-9-34-32</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>100-88-102-115-101-87-111-112-113-126-98-137-123-125-138-139-141-154-153-165-163-150-166-167</t>
+          <t>39-26-14-15-17-4-18-44-42-41-54-56-43-66-38-52-64-13-12-1-3-31-57-68</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -8042,11 +8042,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4-3-1-13-17-15-14-12-26-38-39-41-42-43-56-54-68-81-66-64-77-78-79-80-52</t>
+          <t>101-115-126-141-153-139-154-167-166-165-150-163-123-125-138-137-111-98-102-100-112-113</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -8116,15 +8116,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>91-93-94-120-119-103-104-107-108-109-95-122-96-116-129-130-131-132-133-155-142-143-146-147-134-156-158-160-161</t>
+          <t>116-155-131-142-132-147-160-146-156-129-130-120-93-94-158-134-122-109-95-107-143-161-133-96-108-119-91-77-103-104</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-31-18-19-21-22-23-24-11-32-34-57-44-45-46-47-48-50-33-60-61-62-85-70-71-74-75-76-63-86</t>
+          <t>85-86-19-6-34-21-22-32-33-61-24-23-48-47-60-11-50-62-74-75-63-76-71-45-46</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -8132,19 +8132,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>140-101-100-99-110-136-149-151-141-128-127-102-114-124-126-152-153-154-162-163-164-165-166</t>
+          <t>57-44-31-69-70-43-5-4-29-30-41-53-55-68-51-25-28-17-18-3-2-15-39-65-64-26-0</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>152-141-128-154-153-166-163-162-149-136-164-165-151-110-124-126-101-114-127-140-102-100-99</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>17-4-3-2-15-0-25-26-39-29-30-28-41-53-51-65-77-64-55-68-69-43</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -8214,7 +8214,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-84-97-96-98-99-101-112-123-124-149-136-137-138-140-167-135-151-152-153-154-160-161-162-163-164-148</t>
+          <t>143-119-78-91-92-106-79-133-145-158-157-146-131-155-129-90-105-132-81-94-108-83-96-95-117-103</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -8222,27 +8222,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-19-11-8-7-20-21-22-24-33-35-36-37-63-50-49-48-47-58-59-60-61-62-89-76-73-72-87-115-88-45</t>
+          <t>88-50-61-89-63-76-37-24-35-49-48-47-22-21-19-45-33-59-72-73-87-84-60-6-8-11-62-36-7-20-58</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>78-103-90-91-92-94-95-79-105-106-108-119-117-129-131-132-133-146-145-143-155-157-158</t>
+          <t>69-57-30-55-53-67-68-66-3-2-1-14-42-29-27-26-65-64-38-15-5-43-56-41-25-13-16-44-18-17-54-51-28</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1-2-3-14-15-5-17-16-41-38-25-26-27-28-29-30-44-18-42-43-13-51-53-54-55-56-57-64-65-66-67-68-69-81</t>
+          <t>97-99-167-154-140-153-152-151-164-123-138-124-137-135-136-149-161-160-148-163-162-115-101-112-98</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -8312,35 +8312,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-92-94-95-120-106-119-105-129-130-131-132-144-142-155-145-146-134-158-159-156</t>
+          <t>106-105-92-90-81-80-79-146-145-131-142-155-156-144-119-108-120-159-158-134-132-94-95-130-129</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>45-32-47-74-75-73-35-48-37-24-10-6-9-22-63-76-50-44-70-83-84-86-87-58-71-72-59-46-34-21-60</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>18-5-3-16-29-55-43-42-41-52-25-12-38-51-67-53-40-39-27-13-0-1-26-2</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>8</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>5-6-9-10-18-32-21-24-22-34-35-37-63-45-46-47-48-50-76-75-60-44-58-71-72-73-74-59-70-83-84-87-86</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>101-100-96-110-108-109-111-112-113-114-151-123-124-126-127-140-154-167-152-166-148-161-162-163-153-115</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-2-3-16-13-12-25-26-41-27-38-39-40-29-43-42-55-67-53-81-80-79-52-51</t>
+          <t>110-111-113-127-140-115-114-124-163-100-101-153-154-167-151-152-166-161-162-123-109-96-148-126-112</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -8410,35 +8410,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84-86-88-115-113-101-109-110-111-112-99-114-138-122-124-127-128-154-166-139-149-151-152-137-161-162-163-164-98</t>
+          <t>111-162-163-112-98-99-113-114-101-127-138-151-137-86-88-115-128-139-152-149-164-154-166-124-110</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-7-10-24-20-18-31-32-33-34-35-36-37-50-48-47-60-49-45-57-70-44-58-73-74-75-76</t>
+          <t>15-4-16-29-28-41-53-80-81-79-51-64-30-69-82-68-42-3-26-25-12-13-1-65-38-77</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>44-45-60-73-74-76-84-70-32-18-5-31-20-6-10-35-24-36-49-48-7-33-34-37-50-75-47-58-57</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>92-143-157-161-122-108-94-107-120-133-146-129-144-158-147-109-121-106-105-118-116-155-103-90</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>103-79-80-81-82-108-107-105-90-77-116-92-106-94-118-120-121-146-133-147-155-129-143-144-157-158</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>4-3-15-12-13-25-38-26-1-16-29-30-28-41-42-53-51-64-65-68-69</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>105-91-92-93-94-95-103-104-90-106-116-117-118-119-121-146-130-143-142-129-145-133-147-155-157-159-160</t>
+          <t>121-95-78-91-90-77-118-146-157-155-142-103-105-92-104-117-119-159-145-94-93-116-129-143-130-106-133-160-147</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -8516,27 +8516,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7-5-19-11-10-21-22-23-24-36-35-49-48-46-58-59-60-61-62-63-76</t>
+          <t>60-88-87-61-59-85-58-46-48-36-35-21-22-11-24-23-63-76-62-49-10-7-19</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>128-87-88-85-99-100-125-124-123-122-111-98-151-136-137-138-139-140-141-154-149-135-148-162-164-165-166-167</t>
+          <t>80-83-70-69-30-18-44-56-14-42-57-17-5-3-16-68-40-52-65-64-26-27-66-67-54-55-81-82-25-12</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>125-166-165-164-167-140-128-99-137-151-162-136-122-135-124-100-98-111-123-148-149-138-141-154-139</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>25-12-14-16-18-17-3-26-27-52-40-42-44-30-54-55-57-70-77-65-66-67-68-69-56-64-78-80-81-82-83</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -8606,23 +8606,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>91-90-92-93-94-95-96-107-106-119-116-117-118-105-103-129-130-131-133-134-160-146-155-156-157-158-144</t>
+          <t>93-94-119-157-155-156-130-105-131-144-146-133-134-160-158-106-96-95-122-107-118-92-91-129-117-116-103-90</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>43-42-56-54-66-64-25-12-0-40-52-83-70-69-27-14-15-29-28-30-68-80-79-67</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>7</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>62-7-8-6-19-18-33-34-21-32-20-35-49-59-46-23-11-37-58-71-73-75-89</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>122-97-84-85-87-101-102-110-112-114-115-128-141-127-136-149-138-139-140-123-137-151-165-152-154-153-164-150</t>
+          <t>23-11-37-62-49-35-20-18-32-8-7-19-6-21-34-59-58-85-73-75-33-46-71-84</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -8630,11 +8630,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-12-25-15-14-27-28-29-43-56-42-30-68-67-66-64-52-54-83-69-70-79-80-40</t>
+          <t>87-102-115-152-138-150-151-165-164-149-136-101-89-114-112-123-110-97-137-153-139-127-154-141-140-128</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>79-93-91-90-103-104-105-106-107-118-119-120-121-129-130-132-147-134-133-145-143-142-155-157-158-159</t>
+          <t>107-134-147-121-132-145-159-157-158-91-106-120-133-118-143-155-142-129-130-103-90-104-105-79-93-119</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -8712,27 +8712,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23-11-10-9-20-19-33-34-35-36-37-50-63-62-59-71-72-74-76</t>
+          <t>74-34-20-23-8-9-11-10-62-87-72-71-45-19-33-35-37-36-50-63-76-59</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>83-84-86-87-97-98-99-101-102-114-149-112-109-115-45-122-123-124-125-126-128-110-137-138-135-148-165-154-151-161-150-152-162-164-141-167-8</t>
+          <t>0-12-25-26-43-30-16-15-29-41-54-53-64-66-67-65-55-68-57-69-17-4-2-28-14-1</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>15-16-2-0-12-14-1-4-17-25-26-28-29-43-30-41-53-54-69-57-64-65-66-67-68-55</t>
+          <t>126-114-102-154-167-164-135-122-123-109-97-84-83-86-98-124-110-161-152-165-151-137-148-125-101-115-112-128-141-162-149-150-138-99</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -8802,35 +8802,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>85-86-87-99-100-101-110-123-115-114-124-125-126-149-135-137-139-140-141-154-128-164-152-148-147-161-162-150-165-20</t>
+          <t>87-140-165-141-126-150-139-100-101-115-128-154-99-110-123-137-124-149-162-164-152-125-114-86-85</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>45-47-34-33-20-32-74-62-63-49-36-24-37-50-61-48-11-10-9-8-21-22-75-73</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>13-52-51-69-83-70-31-43-42-29-41-44-57-68-54-64-79-39-67-81-80-3-2-28-25-26-30-18-4-1-66-40-16</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>8-9-10-24-11-22-21-33-32-34-36-37-47-48-49-50-61-62-63-75-74-73</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>9</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>77-79-80-93-107-95-81-94-92-103-90-116-117-118-119-121-131-142-155-145-144-158-159</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2-4-3-1-13-16-40-25-26-28-29-30-31-18-44-57-45-42-43-66-51-52-54-67-64-39-41-68-69-70-83</t>
+          <t>119-147-161-148-159-158-142-117-116-93-107-94-118-131-135-121-95-145-144-155-103-92-77-90</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-85-88-89-102-97-98-99-100-101-96-109-110-111-112-113-115-122-125-123-137-139-140-141-154-153-152-162-163-165-166</t>
+          <t>157-160-146-145-132-118-117-116-103-91-120-133-119-131-143-90-78-83-96-109-80-94-161-122-107-108-144</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -8908,15 +8908,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-9-23-36-11-22-21-33-37-63-49-46-58-59-74-62-75-61-32</t>
+          <t>15-43-30-42-67-54-68-55-40-28-4-3-26-25-13-27-52-39-51-64-41-69-17-16-2-1</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>78-80-90-91-116-103-117-94-108-107-120-119-118-131-132-133-146-145-143-144-157-160-161</t>
+          <t>6-33-44-31-70-57-32-21-11-37-49-75-61-74-58-46-59-62-63-36-23-22-9</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -8924,7 +8924,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1-2-3-4-28-15-16-17-25-26-27-13-30-31-39-40-41-42-43-44-57-52-54-55-51-64-67-68-69-70</t>
+          <t>89-88-115-154-163-139-140-141-101-100-85-97-137-152-166-165-153-111-113-102-99-98-110-123-162-112-125</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -8998,35 +8998,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>96-109-99-100-102-97-110-86-111-113-114-115-126-138-125-123-135-136-137-124-139-140-141-148-149-150-151-153-161-163-164-166-167</t>
+          <t>121-108-106-78-118-132-145-158-77-90-103-116-119-133-146-157-156-155-129-130-143-144</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>21-61-36-22-8-6-7-20-72-84-86-88-75-74-73-71-23-11-49-34-32-33-58-59-60-46-47-62-76</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>30-5-69-68-42-54-82-66-28-29-16-17-41-12-0-14-25-51-27-3-4-31-44-56-57-70-80-53-26-13</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>123-138-135-148-149-139-153-163-151-114-102-115-100-126-124-137-164-140-141-113-99-111-110-96-136-125-167-166-150-161-97-109</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>5-6-7-8-11-23-21-22-20-31-36-33-34-32-44-46-47-49-88-62-61-60-59-58-70-71-72-73-74-75-76-84-57</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>90-103-116-119-106-118-129-130-132-121-108-133-158-144-145-146-157-156-155-143</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>4-3-14-13-0-12-16-17-25-26-27-28-29-42-41-54-51-53-56-69-82-68-66-77-78-80-30</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -9096,35 +9096,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-84-97-99-100-102-140-154-115-112-113-114-111-110-124-126-128-166-152-162-148-137-149-150-151-136-123-109-163-135</t>
+          <t>130-157-158-107-94-81-79-80-119-133-145-144-131-155-142-103-78-92-91-129-143-118-105-117</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32-19-6-9-21-22-23-24-48-35-58-45-46-36-11-50-62-89-73-74-87-88-71</t>
+          <t>58-45-71-35-23-24-36-50-48-46-73-74-62-11-9-21-22-32-6-19</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2-15-13-12-0-53-52-25-29-43-30-17-42-66-65-27-28-41-56-57-44-18-5-16</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>7</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>78-79-80-81-94-92-119-107-105-103-91-118-117-131-130-129-155-142-143-158-145-133-157-144</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>15-2-13-12-25-0-16-44-30-42-28-27-29-18-17-5-43-41-52-53-56-57-65-66</t>
+          <t>84-100-88-99-114-102-89-115-140-126-150-149-135-148-163-162-136-123-111-113-112-87-83-109-128-154-166-124-137-151-152-110-97</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -9194,7 +9194,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>97-99-100-101-102-85-113-114-126-123-124-135-122-136-121-149-151-139-140-141-137-150-138-153-161-162-164-165-166-167</t>
+          <t>104-121-109-122-105-143-155-145-135-161-147-160-158-146-108-95-107-156-144-131-117-129-130-118-120-133-106-90</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -9202,7 +9202,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-7-9-10-11-24-22-21-32-33-34-36-37-47-48-49-50-58-59-60-61-71-72-73-74-75-76-89-109-98-87-84</t>
+          <t>58-71-21-9-75-89-76-72-85-84-6-7-32-33-59-61-87-74-73-60-47-34-10-24-11-37-22-36-50-49-48-45</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -9210,19 +9210,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>95-90-104-105-106-107-108-120-118-117-131-130-129-143-155-156-144-146-147-160-158-145-133</t>
+          <t>70-57-0-12-38-28-27-40-53-67-65-55-56-39-25-54-43-29-4-31-18-83-82-79-66-2-15-17-30-41</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-2-25-12-27-17-18-4-15-28-29-30-45-31-38-39-40-66-65-53-54-55-56-57-43-41-67-82-79-70-83</t>
+          <t>101-114-113-137-149-150-164-153-167-165-166-141-140-151-138-126-97-123-162-136-98-99-124-139-102-100</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -9292,35 +9292,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-92-93-94-116-103-105-108-109-85-95-121-119-118-130-143-156-132-144-145-147-148-134-157-158-159-160-161</t>
+          <t>118-116-90-103-105-95-119-156-157-134-109-108-121-148-161-160-158-145-132-130-144-143-159-147-93-94-92</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10-11-22-20-32-19-34-36-37-47-45-49-50-63-60-62-89-59-71-72-73-88-76-75-61</t>
+          <t>14-31-42-66-52-39-54-68-67-78-27-15-13-3-16-29-53-51-77-79-80-81-83-69-82-56-57-4-1-0</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>10-19-32-20-73-61-76-89-75-85-60-59-71-72-45-47-34-22-37-50-36-49-63-88-62-11</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>99-98-97-110-125-127-128-102-113-123-136-137-139-140-154-151-164-149-150-166-167</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>150-137-139-127-140-149-151-164-167-166-154-113-98-110-97-123-99-102-128-125-136</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>13-0-3-4-16-14-15-1-27-29-31-69-42-51-52-39-54-56-57-68-67-66-53-77-78-79-80-81-82-83</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -9390,15 +9390,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>109-81-80-90-91-93-94-95-96-121-106-107-79-116-117-147-120-104-119-132-133-146-144-145-131-143-155-156-157-158-160-161</t>
+          <t>152-166-123-111-124-138-113-101-114-100-99-125-126-140-141-154-167-164-150-98-97-102-115-153</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-19-33-8-24-10-35-36-37-45-46-48-49-50-63-59-60-61-62-71-58-72-73-74-75-76-18</t>
+          <t>12-14-42-43-70-69-81-79-80-55-57-67-53-15-2-3-17-29-28-40-26-25-64-68-44-18-13-0</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -9406,19 +9406,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84-85-99-87-86-97-98-88-100-115-102-126-101-114-113-123-124-125-111-138-150-164-140-152-153-154-167-166-141</t>
+          <t>59-58-19-33-60-88-76-62-50-49-36-37-24-61-73-86-87-84-45-46-63-75-6-8-10-35-48-74-72-85-71</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>12-0-3-2-13-14-15-26-25-28-17-29-40-53-55-44-42-43-57-70-69-68-67-64</t>
+          <t>120-145-143-104-133-161-146-160-147-158-144-157-156-155-116-117-131-132-119-96-90-91-94-95-106-93-107-121-109</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -9488,35 +9488,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77-78-79-80-81-82-83-90-91-92-93-95-96-103-104-107-109-131-118-120-121-129-130-116-143-144-155-142-146-134-158</t>
+          <t>135-148-161-149-151-152-111-98-124-125-89-115-102-126-140-166-165-164-139-114-100-112-150-167-153-96-85-110-109</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19-32-7-8-9-10-6-18-5-20-21-23-11-24-31-46-33-34-36-37-22-72-85-58-60-62-76-75-49-50</t>
+          <t>14-13-27-25-52-40-53-70-5-4-2-16-29-83-82-31-18-28-42-30-43-68-67-66-39-15-0</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>115-89-98-124-110-111-112-114-100-102-125-148-135-139-140-126-149-150-151-152-153-161-164-165-167-166</t>
+          <t>21-34-19-6-7-9-11-24-23-46-72-58-60-62-75-76-50-37-49-33-32-8-10-36-22-20</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4-16-27-0-25-13-2-14-15-28-29-30-43-42-40-39-52-53-64-66-67-68-70</t>
+          <t>79-78-118-129-134-120-107-144-143-155-142-158-121-95-80-81-146-131-130-92-93-104-90-91-103-116-77-64</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -9586,7 +9586,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>107-79-80-81-82-83-105-91-92-93-95-96-118-104-90-77-103-119-120-121-122-135-131-134-143-130-145-146-147-148-156-157-159-160-161</t>
+          <t>83-93-92-134-160-130-156-146-120-105-79-77-90-143-131-104-91-103-118-147-121-122-96-95-107-82-119-157-145-159-161-148-135-80-81</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -9594,15 +9594,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0-1-2-3-4-5-14-26-27-28-31-44-56-42-40-39-51-52-53-68-70-43</t>
+          <t>88-86-85-45-32-20-19-33-73-61-34-47-59-21-6-7-24-37-46-60-49-35-48-76-50-9-11</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>85-86-88-101-99-110-111-114-126-127-128-136-137-138-139-140-141-150-163-151-165-166-167</t>
+          <t>5-3-4-2-70-57-31-44-14-1-0-26-39-27-28-53-68-56-43-42-40-51-52</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -9610,11 +9610,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6-7-9-11-49-35-21-48-59-20-34-33-19-57-45-46-47-24-37-50-76-60-61-73-32</t>
+          <t>110-111-101-114-136-137-150-163-151-167-166-165-140-138-141-128-127-139-126-99</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -9684,35 +9684,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>91-92-103-116-105-107-108-94-117-118-120-121-122-135-146-133-129-142-143-130-147-148-161-156-157-159-155</t>
+          <t>122-110-101-141-162-98-86-84-97-99-126-140-115-127-137-135-136-102-100-164-148-161-163-153-152-166-167-83</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18-5-9-10-11-7-19-20-21-22-24-34-33-31-45-71-72-50-57-59-84-73-62-63-76-49-61-47-58</t>
+          <t>58-72-71-62-63-49-50-61-59-24-11-10-21-19-20-7-33-45-47-22-9-76-73-34</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>99-86-98-97-110-126-101-100-102-115-127-136-137-152-153-140-163-162-164-167-166-141</t>
+          <t>57-56-31-17-18-5-3-2-67-81-68-69-55-43-28-41-66-52-12-0-15-14-27-42-29-25-51-65-64-39-53-40-16</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>29-17-3-15-14-2-16-12-25-27-28-0-39-40-41-42-64-51-52-53-55-56-43-69-66-67-68-65-78-79-81-83</t>
+          <t>103-116-146-120-121-108-155-142-156-157-159-147-133-118-105-92-91-117-130-129-143-94-107-79-78</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -9782,7 +9782,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>76-84-97-87-48-85-99-100-109-111-113-114-127-140-123-124-125-126-115-141-137-122-152-149-136-161-162-163-164-166-167</t>
+          <t>97-162-163-127-140-164-136-137-126-114-113-115-166-152-124-123-149-161-122-109-111-99-85-84-125-167-141-100-87</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -9790,27 +9790,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-7-20-9-10-8-21-37-60-73-72-59-61-62-63-49-46</t>
+          <t>60-59-46-7-21-10-37-49-48-61-63-9-8-6-20-62-76-72-73</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>103-78-65-77-90-91-92-80-95-93-105-106-116-117-118-119-120-129-143-156-132-147-146-144-155-142</t>
+          <t>30-28-29-4-3-15-2-55-68-0-1-16-26-25-38-52-39-64-65-53-18-17-41-40-27-43-69-56-44</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-2-3-4-18-16-17-15-25-26-27-28-29-40-38-39-52-41-43-44-30-56-55-53-64-79-68-69</t>
+          <t>146-144-120-95-90-77-155-156-143-142-116-103-80-93-92-91-106-132-147-119-105-118-78-79-117-129</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -9880,7 +9880,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>91-92-94-95-96-109-108-106-116-117-118-119-120-142-155-129-130-131-132-134-135-121-143-156-146-161-148-147-145-159-160-122</t>
+          <t>148-135-163-164-122-109-96-84-99-100-101-114-140-141-167-154-166-153-162-124-98-112-152-126-115-102-150-149-161</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -9888,7 +9888,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-20-8-34-18-19-7-21-22-23-24-31-32-33-10-35-48-45-46-47-37-49-61-50-63-71-73-74</t>
+          <t>7-6-74-89-87-86-85-48-34-19-46-47-35-21-20-22-23-49-61-50-37-63-73-71-45-32-33-24-10-8</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -9896,19 +9896,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84-85-86-87-100-98-99-89-101-102-115-114-112-124-126-140-141-154-153-152-150-149-162-163-164-166-167</t>
+          <t>43-18-31-15-0-4-16-70-68-54-53-28-2-65-64-66-67-56-44-5-17-13-27-41-42-55</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-13-4-15-16-17-2-27-28-41-42-43-44-56-67-66-78-77-65-53-54-68-70-55-80-79-64</t>
+          <t>129-132-119-106-94-77-78-95-108-92-79-80-118-131-156-155-145-146-160-159-130-116-91-117-134-147-121-120-143-142</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -9978,31 +9978,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-64-92-94-108-104-106-103-116-117-131-121-119-130-129-143-155-160-147-144-157-158-159-146</t>
+          <t>130-143-155-144-117-104-90-103-129-157-158-146-121-108-94-160-159-147-106-92-119-131-116</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>21-8-7-19-23-24-36-37-49-88-48-46-58-59-60-61-62-63-73-72-74-76-100-86-32</t>
+          <t>46-24-37-60-74-63-49-61-62-76-23-21-58-85-88-86-32-7-19-8-36-48-73-72-59</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>111-113-126-98-110-97-112-101-127-123-122-135-136-137-138-139-140-141-148-151-152-153-154-167-165-161</t>
+          <t>4-18-82-69-27-14-39-40-29-16-3-17-41-52-67-44-55-57-31-42-68-80-81-70-28-2-1-0-13-38-64-15-5</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-2-3-4-5-13-14-15-16-17-18-44-28-27-29-38-39-40-41-42-55-82-85-31-57-67-68-69-70-80-81-52</t>
+          <t>100-112-139-151-136-127-140-167-101-110-123-148-161-135-122-152-165-153-154-141-126-111-98-97-137-138-113</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -10076,35 +10076,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>92-93-94-106-130-116-117-118-119-120-108-133-131-142-143-145-146-155-156-157-159-160</t>
+          <t>80-93-106-146-133-160-108-94-78-79-77-142-155-143-130-157-159-145-131-156-116-119-118-117-92-120-81</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>59-22-36-10-9-7-31-32-84-72-87-75-50-37-24-89-60-33-20-6-18-83-57-44-45</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>39-53-52-38-25-51-64-30-4-17-1-13-12-26-40-55-43-16-3-2-14</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>8</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>43-31-24-10-9-7-17-4-30-6-50-22-32-20-33-36-37-44-45-18-75-59-60-72-57</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>83-84-87-89-114-113-110-112-98-109-122-135-124-125-127-128-123-136-137-138-162-148-149-151-152-153-154-139-163-164-165-167</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1-2-3-16-40-14-26-13-12-25-38-51-39-55-53-52-64-77-78-79-80-81</t>
+          <t>112-98-113-164-163-162-149-109-122-135-148-114-127-139-110-123-136-137-124-151-165-128-138-152-153-167-154-125</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -10174,7 +10174,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>106-94-91-92-93-90-103-104-81-107-108-116-117-118-119-120-129-130-133-134-144-142-155-156-157-158</t>
+          <t>108-158-157-156-142-144-120-119-129-155-90-91-92-93-107-134-133-106-118-130-117-116-103-104-94-81</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -10182,7 +10182,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-7-8-9-10-11-21-31-32-33-34-35-36-37-47-46-45-44-70-71-59-60-61-63-62-48-74-72-73-57-18</t>
+          <t>59-37-11-8-9-21-7-45-33-10-36-60-73-74-63-75-62-61-32-46-34-35-48-47-71-72</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -10190,19 +10190,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>86-85-83-96-97-98-99-111-101-102-115-100-75-114-110-135-124-126-125-127-122-137-138-152-151-141-153-161-162-163-164-165-166</t>
+          <t>30-42-43-26-51-64-41-54-68-66-25-12-27-55-3-1-2-0-14-15-28-56-70-44-5-18-31-57</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>161-162-151-164-141-127-85-83-122-138-153-166-165-114-101-115-152-99-86-98-111-110-135-97-96-125-126-100-102-137-124-163</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>12-1-3-2-0-14-15-25-26-51-27-30-28-41-42-43-54-55-56-68-66-64</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -10272,15 +10272,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77-78-79-80-82-83-96-91-92-131-130-129-116-104-105-106-107-108-109-110-71-93-119-120-103-90-118-132-133-144-156-158-159-160-53</t>
+          <t>78-90-103-105-104-116-129-130-118-119-132-133-158-159-160-96-106-120-107-156-144-131-80-79-91-77-92-93-108-109-82-83</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-8-9-10-11-24-22-33-49-37-50-47-46-35-48-61-62-87-74-75-63-76-89</t>
+          <t>22-24-37-50-49-48-46-33-71-87-89-76-63-62-35-11-10-9-8-61-75-74-47-6</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>97-100-101-102-111-115-114-112-113-124-125-126-152-137-161-149-150-166-167-154-141-153-164-165-163-135</t>
+          <t>27-28-15-51-64-53-41-1-3-17-18-16-5-43-55-54-69-42-40-52-38-2-12-25</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -10296,11 +10296,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2-1-3-5-18-17-16-15-12-25-27-28-43-42-41-40-38-51-64-52-54-55-69</t>
+          <t>126-113-101-100-150-152-153-166-165-164-149-161-163-124-110-97-135-137-154-167-141-114-115-102-125-111-112</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -10370,35 +10370,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>141-88-97-98-99-100-86-111-124-112-102-115-128-114-127-113-137-138-126-153-164-165-166-167</t>
+          <t>153-102-100-88-124-162-164-127-128-141-115-138-137-136-123-112-97-98-111-99-167-166-165-113-114-126</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>62-50-48-34-33-32-31-45-70-35-23-36-60-86-84-71-72-74-47-21</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>77-64-54-66-80-81-69-17-4-30-15-39-52-1-16-29-67-78-53-41-42-40</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>7</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1-4-15-16-30-21-23-29-17-31-32-33-34-47-60-42-45-35-36-50-48-62-84-70-71-72-74-69</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>119-95-109-121-122-123-148-162-134-135-136-146-131-155-156-157-158-160-161-132</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>39-40-41-66-53-54-67-52-64-77-78-80-81-93-103-92-90-104-105-106-118-117-116-129</t>
+          <t>95-93-105-131-156-146-118-155-103-116-119-106-161-148-132-117-92-90-104-129-157-158-160-135-109-122-134-121</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -10468,7 +10468,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>91-92-94-95-109-83-104-103-116-117-119-120-121-133-144-131-143-156-145-146-147-148-122-158-159-160-161</t>
+          <t>146-159-144-131-119-121-147-160-161-148-133-109-122-95-94-156-120-92-91-116-103-104-117-143-145-158</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -10476,27 +10476,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-21-10-11-23-24-36-35-34-32-45-47-48-59-74-62-63-71-57</t>
+          <t>13-12-38-39-66-55-43-2-15-27-42-41-65-51-64-79-67-56-29-4-30-69-77-25-26-1-0</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>127-99-86-87-88-85-101-102-89-113-114-115-124-125-110-136-162-151-152-140-165-166-163-164</t>
+          <t>21-36-62-63-10-23-48-74-59-71-57-5-32-45-47-34-35-24-11-6</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-4-2-1-12-13-15-25-26-43-29-30-38-39-41-42-56-79-77-51-64-65-66-67-69-55-27</t>
+          <t>85-86-88-99-152-151-164-162-124-101-89-102-114-115-140-113-127-166-165-163-125-136-83-110-87</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -10566,35 +10566,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>78-79-80-82-103-92-93-90-105-106-108-116-118-132-129-133-121-147-135-145-146-134-148-155-156-158-159-160-161</t>
+          <t>116-103-90-92-105-121-147-133-106-80-78-79-93-82-96-108-134-118-132-129-155-145-146-159-160-158-156</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>48-46-59-71-72-60-23-24-10-8-75-88-89-70-84-86-74-87-76-49-19-33-32</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>12-64-66-51-43-42-29-15-0-53-67-68-55-16-3-2-14-13-56-44-31-18-4-5-17-54-26-25</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>148-161-149-162-136-151-101-114-141-100-111-123-110-97-113-128-102-124-135-150-139-153-126-138-163-164-167-140-112</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>24-23-10-8-19-32-33-49-48-46-59-71-72-60-74-75-76</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>11</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>96-84-86-87-88-89-114-100-101-97-110-111-112-113-136-123-124-102-128-126-138-139-140-141-162-149-151-153-167-163-164-150</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>13-14-3-4-5-18-2-0-15-16-17-12-25-26-29-44-31-43-56-51-64-54-55-42-53-66-67-68-70</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84-111-97-99-101-102-128-114-112-153-139-140-164-137-148-135-124-123-136-149-150-126-87</t>
+          <t>111-99-97-84-87-112-124-136-149-137-150-139-140-126-89-102-128-101-114-153-164-123</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -10672,27 +10672,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18-6-7-8-11-24-10-23-21-33-34-59-45-46-49-50-35-60-71-72-73-74-76-89</t>
+          <t>78-64-65-67-68-17-18-15-1-40-13-0-39-52-83-81-82-70-69-57-30-44-31-41-27</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>71-72-76-74-73-60-46-21-23-11-24-49-50-34-33-7-6-8-10-35-45-59</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>7</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>78-93-108-95-107-104-103-116-106-92-117-118-120-121-129-130-131-132-133-134-142-143-145-146-160-156-157-158-159-147</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-13-15-17-30-44-31-40-39-41-27-52-64-65-67-83-70-57-69-81-82-68</t>
+          <t>121-134-135-104-103-92-108-148-132-142-129-130-156-143-116-117-131-133-106-95-120-147-159-145-158-157-160-146-118-93-107</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -10762,7 +10762,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>85-86-87-96-97-100-101-102-109-110-111-135-136-114-126-137-138-141-153-152-150-140-154-166-165-163</t>
+          <t>131-146-121-120-133-94-80-145-130-155-142-129-104-103-116-77-90-82-93-105-92-79-96-109-108-135-147-157-143-158-144</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -10770,7 +10770,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-7-8-9-24-10-23-21-32-34-35-36-63-47-48-50-75-61-60-73-57-71-72-45</t>
+          <t>47-48-61-60-45-32-71-72-75-73-21-34-35-36-50-63-24-9-7-6-8-10-23</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -10778,7 +10778,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>93-79-80-94-92-90-77-103-105-104-129-116-120-121-108-130-131-155-142-143-144-133-146-147-145-157-158</t>
+          <t>1-0-13-27-38-12-25-52-3-4-29-16-56-69-70-57-31-44-30-54-40-51-65-67-68-2-28</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -10786,11 +10786,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-2-3-4-16-13-12-25-27-28-56-30-31-44-54-40-51-52-38-65-82-67-68-69-70-29</t>
+          <t>110-97-111-140-153-165-166-141-154-126-102-114-100-101-87-85-86-138-137-136-150-163-152</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -10860,31 +10860,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>91-92-94-93-105-106-108-107-116-117-119-120-134-132-144-143-142-146-148-147-157-156-155-158-159-160-161</t>
+          <t>119-106-92-105-142-155-93-78-79-80-81-82-94-144-143-156-159-160-134-91-77-108-120-158-157-117-116-132-147-146-107</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>44-48-47-21-72-73-61-75-63-10-9-35-45-58-60-71-70-57-7-8-36-49-74-50-34-31-6-20-19-18</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>56-69-67-64-51-39-26-14-4-16-65-40-28-13-38-25-27-42-43-17-3-1-66-55</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>18-7-8-9-10-6-19-20-21-34-35-36-44-45-47-48-49-50-57-58-60-61-63-70-71-72-73-74-75-31</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>85-86-98-97-96-111-99-113-89-101-115-114-125-123-122-124-137-138-139-140-154-151-166-165-150</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>14-3-4-13-1-16-17-25-26-27-51-38-39-28-42-43-40-55-56-69-65-66-67-64-77-78-79-80-81-110-82</t>
+          <t>123-148-138-124-110-96-122-150-161-165-114-115-154-140-89-86-85-97-99-98-111-137-151-166-139-101-113-125</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -10958,7 +10958,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>81-90-92-93-131-104-105-129-117-118-120-121-122-109-95-132-133-134-135-143-144-157-155-156-146-159-160-161</t>
+          <t>81-95-161-135-133-93-92-90-132-134-120-109-122-121-129-131-146-159-160-143-105-118-156-155-157-144-104-117</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -10966,27 +10966,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>26-12-25-13-14-17-31-3-0-28-27-38-39-52-40-41-42-29-53-66-68-69-78-79</t>
+          <t>26-40-41-28-3-27-13-38-78-68-79-66-42-69-53-29-17-14-0-12-52-25-39</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>83-84-111-98-99-100-101-102-89-112-127-128-115-125-124-137-138-140-141-152-153-163</t>
+          <t>63-48-34-46-60-74-76-50-9-21-22-35-37-61-47-8-24-7-19-32-59-73-72-84-83-57-18-31-58-71</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>127-100-102-101-128-115-89-88-98-99-112-125-138-141-153-111-124-137-163-152-140</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>8</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>7-19-32-18-8-21-22-35-9-34-48-37-24-76-60-88-63-50-61-73-47-58-71-72-57-59-74-46</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -11056,23 +11056,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>124-98-99-100-97-109-110-112-113-114-115-101-125-126-148-135-136-138-140-141-154-153-150-151-163-149-162-128-165</t>
+          <t>99-126-153-165-125-150-163-162-149-136-110-97-112-124-98-138-151-115-128-141-154-140-114-113-101-100</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>28-0-14-3-4-2-1-26-13-12-25-38-40-41-42-43-56-53-54-66-67-68</t>
+          <t>14-3-41-2-1-4-17-43-56-54-67-68-66-53-25-38-40-42-28-26-12-13-0</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>79-80-81-93-91-103-90-92-94-95-105-121-108-122-117-118-145-120-119-131-129-142-107-146-147-155-157-158-159-160</t>
+          <t>47-71-70-72-85-89-36-35-59-60-74-87-84-83-57-34-21-33-22-11-19-58-75-76-62-37</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -11080,11 +11080,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>47-22-21-19-33-34-35-36-37-11-57-58-59-70-17-60-83-71-74-89-75-76-72-84-85-87-62</t>
+          <t>157-159-145-135-148-122-109-118-105-94-81-95-147-160-146-121-120-131-107-108-91-117-103-93-80-92-155-142-158-119-129-90-79</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -11154,35 +11154,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-91-93-107-94-106-104-103-116-142-129-130-132-134-135-121-146-145-155-156-157-159-160-161</t>
+          <t>88-101-100-112-114-115-125-136-151-153-154-102-113-111-109-96-135-124-110-138-139-87-86-85-97-83-150-164-137-99</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>74-71-58-9-10-24-37-23-8-20-21-22-49-75-61-48-35-36-73-60-5-19-33-32</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>26-38-0-27-57-70-40-55-81-56-82-80-79-78-65-77-64-66-54-25-51-52-41-67-30-2-17-3-1-14</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>91-116-129-107-121-146-160-161-159-132-145-157-156-155-130-104-90-103-142-134-94-93-106</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>30-19-20-21-8-9-10-22-23-24-37-33-35-36-60-48-49-61-58-32</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>9</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>75-73-74-96-83-85-86-87-88-71-97-99-102-101-100-109-110-111-112-113-114-115-124-150-136-137-138-139-125-154-153-151-164</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0-1-2-3-14-17-5-26-27-25-38-40-41-51-52-54-55-56-67-64-65-66-57-70-77-78-79-80-81-82</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -11252,15 +11252,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>85-83-135-109-110-113-127-122-123-114-102-137-136-161-148-160-149-151-152-154-140-163-165-166-167-98</t>
+          <t>140-163-151-149-123-110-98-85-88-102-152-167-166-165-154-114-127-113-137-136</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-8-9-10-11-19-20-21-22-24-23-36-34-45-32-59-46-47-60-58-35-50-62-88-63-76-74</t>
+          <t>50-76-62-63-36-34-8-9-11-24-23-22-6-5-32-45-21-35-60-74-47-46-20-19-58-59-10</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -11268,15 +11268,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>79-91-92-93-95-108-105-106-119-121-120-132-118-147-145-157-155-143-142-129-117-116-104</t>
+          <t>67-55-57-44-71-83-82-68-56-54-28-38-52-80-81-66-79-64-12-27-41-18-4-2-13-69-42-29-17-31</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2-4-5-12-13-55-54-27-28-29-52-38-41-42-44-31-18-17-71-57-64-66-67-68-69-56-80-82-81</t>
+          <t>155-160-135-147-122-119-118-116-117-104-105-92-91-121-109-108-95-93-106-145-120-148-161-143-132-157-129-142</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58-71-72-73-101-85-86-87-88-89-109-97-98-99-110-96-84-112-115-126-127-141-154-167-166-153-136-162-164-152-151</t>
+          <t>97-162-164-152-98-99-86-88-115-136-110-112-87-141-154-127-126-151-153-166-167-89-101-85-84</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -11358,27 +11358,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-7-8-10-11-22-21-20-19-33-34-24-37-36-49-50-63-61</t>
+          <t>50-63-37-24-33-34-58-73-61-10-11-36-49-72-71-70-22-21-20-7-19-57-31-18-6-8</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>92-80-81-95-93-78-103-104-106-108-117-118-119-121-122-129-130-131-132-133-135-160-145-156-157-158-159-147</t>
+          <t>39-53-27-28-55-56-68-43-17-29-2-15-4-42-41-65-78-52-51-38-12-14-1-0-13</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>14-15-2-4-12-13-0-1-39-38-27-28-29-18-31-43-42-41-65-51-52-53-55-17-70-57-68-56</t>
+          <t>80-81-135-131-157-159-160-147-122-96-109-95-117-92-93-119-108-121-106-103-104-118-156-129-130-158-145-133-132</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -11448,35 +11448,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-84-85-88-110-96-101-102-115-89-112-109-122-125-126-127-138-139-140-141-153-149-150-151-163-162-148-121</t>
+          <t>110-127-115-102-153-141-140-138-122-148-96-84-85-86-101-126-139-151-150-162-163-149-125-112-109</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16-2-3-1-12-25-26-27-28-29-30-54-41-40-82-56-43-55-53-51-65-66-67-79-77-64</t>
+          <t>65-66-83-70-43-27-25-40-41-55-29-53-1-2-28-51-64-57-56-54-67-79-82-44-31-30-3-16-26-12</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>89-88-75-49-24-37-50-48-23-10-22-33-20-45-32-46-47-60-61-63-76-73-71-34</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>7</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>108-93-91-92-78-90-104-103-129-116-117-131-119-120-106-118-132-133-142-143-156-145-146-159-160</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>10-24-37-23-20-31-32-33-34-47-44-45-46-22-48-49-50-57-60-61-63-70-71-73-75-76-86</t>
+          <t>159-146-131-132-108-93-106-78-90-91-118-117-103-104-92-133-121-120-119-129-116-77-142-143-156-145-160</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -11546,35 +11546,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-110-123-84-96-97-101-76-135-89-127-112-114-115-86-111-161-134-109-136-137-138-139-140-141-147-145-148-149-150-151-152-154-128-163-164-165-166-167</t>
+          <t>133-145-147-148-159-157-156-104-118-123-83-82-92-158-149-161-136-110-97-96-109-103-117-131-143-130-119-106-135-134</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-7-8-11-10-23-18-19-20-22-9-32-33-34-35-46-47-49-63-75-59-71-72-74-60-57</t>
+          <t>1-67-66-78-25-26-14-12-38-28-41-42-90-64-51-40-39-52-77-80-55-56-69-54-79-43-16-17-2-4-3-30</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>90-103-104-106-119-118-117-130-131-133-159-158-157-156-143</t>
+          <t>84-57-10-20-33-47-60-59-49-74-75-76-11-23-35-63-86-18-5-6-46-32-8-9-22-34-7-19-72-71</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>30-2-3-25-12-14-16-17-1-26-28-4-38-39-40-41-42-64-51-52-54-55-56-43-80-67-69-77-78-79-66-92-82</t>
+          <t>127-115-128-89-101-114-112-111-141-154-166-165-151-138-139-152-167-164-163-150-137-140</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -11644,31 +11644,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77-78-79-80-81-82-83-92-93-94-95-96-121-109-161-106-119-120-132-118-133-134-135-160-143-144-147-146-145-155-156-157-158-142-117</t>
+          <t>89-140-151-164-153-154-128-102-113-100-126-141-166-165-152-139-137-123-138-150-162-99-114-87-88</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1-0-2-3-4-5-12-13-15-17-18-25-26-27-28-29-30-31-44-43-41-40-54-103-51-53-69-56-57-68-65-64-38</t>
+          <t>5-6-20-22-73-86-72-75-61-46-45-60-71-44-58-57-83-32-31-21-11-10-23-62-74-85-19-35-63-50-48-34-9-8-18</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>128-102-100-113-114-99-126-154-141-140-139-138-151-165-164-137-123-150-162-152-153-166</t>
+          <t>80-68-81-15-2-17-53-65-64-77-41-13-12-0-1-43-4-3-27-28-40-26-25-51-38-54-29-82-69-30-56-79-78</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6-8-11-10-9-19-20-21-22-23-35-34-32-45-46-63-50-48-60-61-62-72-71-58-73-74-75-85-86-87-88-89</t>
+          <t>144-103-118-121-96-120-133-132-146-158-157-142-106-93-94-119-145-143-155-156-117-92-109-95-160-161-147-135-134</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -11742,35 +11742,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>115-86-93-96-97-110-100-102-99-111-112-83-122-124-126-127-128-135-137-138-140-141-154-152-153-164-163-149-166-167</t>
+          <t>100-140-126-127-137-138-135-97-96-122-110-124-99-111-128-115-154-141-153-152-166-163-149-164-167-102-86-112</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>73-62-72-70-44-31-32-20-19-71-58-45-35-36-21-6-18-60-61-47-34-33-46-11-50-37-75-22-9-23-49-83</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>21-9-11-23-22-20-6-19-32-33-34-35-36-58-45-46-47-49-50-37-60-61-62-75-72-73-71</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>7</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>77-78-90-103-92-66-105-106-107-94-116-117-118-119-120-121-133-131-129-142-143-144-145-155-156-157-158-160</t>
+          <t>15-53-51-38-52-25-12-13-1-3-4-29-69-54-41-17-16-30-55-66-40-2</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4-2-3-1-12-13-15-16-17-18-29-30-31-44-40-52-41-38-25-51-53-54-55-69-70</t>
+          <t>120-107-105-160-145-142-155-121-94-93-92-90-78-103-77-106-118-131-157-144-143-119-133-158-156-129-116-117</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -11840,35 +11840,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>45-123-82-81-83-9-90-92-94-95-103-104-117-133-106-120-109-121-122-148-130-107-134-135-144-146-157-155-132-156-143-160</t>
+          <t>132-120-134-121-92-90-103-160-146-133-157-156-155-143-144-117-104-106-130-95-94-107</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>33-20-19-7-21-34-35-11-23-24-37-50-49-48-62-76-63</t>
+          <t>72-33-35-34-20-45-19-7-9-23-48-21-11-24-49-37-50-63-62-76-89</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84-85-86-87-89-115-102-99-110-98-111-97-126-127-128-138-137-136-150-151-139-140-153-163-162-165-166</t>
+          <t>39-15-1-65-68-81-53-66-26-54-82-70-69-67-52-42-29-18-4-31-30-17-44-43-55-14-64-51-27-0-25</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-4-15-14-52-39-25-26-27-29-30-31-18-42-43-44-72-70-55-54-53-51-64-65-66-67-68-69-17</t>
+          <t>87-83-138-151-111-123-135-148-126-102-165-163-162-137-150-136-97-84-86-85-98-128-140-127-109-122-110-99-153-166-139-115</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -11938,7 +11938,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>78-77-90-91-92-93-94-95-104-103-116-106-105-117-118-142-129-130-131-132-134-119-146-155-156-157-158-159-160-135</t>
+          <t>95-132-118-105-104-129-142-116-103-91-90-155-156-157-160-134-92-93-106-117-130-131-146-159-158-119-94</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -11946,27 +11946,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>45-9-10-22-18-19-6-32-33-34-35-37-11-49-76-74-73-59-58</t>
+          <t>27-54-42-77-78-40-26-13-41-55-56-82-69-68-51-52-65-67-80-53-66-30-16-29-28-15-2-3-0-1-38</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>83-85-86-109-96-46-97-98-99-100-102-89-125-112-113-115-111-136-123-124-114-128-154-138-139-140-141-165-150-122-161-162-163-164-148-166</t>
+          <t>34-35-22-9-11-10-37-74-76-73-49-19-6-18-45-59-46-58-70-57-32-33</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>123-122-138-164-162-163-111-115-89-102-140-125-97-85-86-112-113-100-98-99-114-141-128-109-139-166-154-165-148-161-150-135-83-96-136-124</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>3</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0-1-2-3-27-15-16-26-13-28-29-30-38-51-52-53-40-41-42-54-55-56-57-68-66-67-82-69-70-80-65</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -12036,23 +12036,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>97-99-101-102-115-112-110-124-123-125-126-127-151-154-138-139-140-141-166-165-152-137-161-162-163-150-135</t>
+          <t>125-126-127-139-112-101-124-109-163-151-137-135-97-85-87-88-141-154-115-102-89-99-86-110-123-161-162-165-152-166-140-150-138</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>29-2-3-4-30-18-17-15-28-0-13-38-39-40-66-64-52-53-54-56-57-68-41-42</t>
+          <t>7-10-24-11-76-37-63-62-74-75-48-36-23-9-22-34-21-33-59-72-58-60-19-6</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>77-78-80-82-69-83-109-93-94-91-104-117-107-108-121-95-118-130-105-119-131-132-133-146-144-159-147-155-142</t>
+          <t>0-2-17-18-57-54-40-13-4-3-15-42-56-69-68-30-29-28-41-38-64-82-83-66-52-39-53</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>34-7-9-10-11-24-21-22-23-33-6-19-36-37-48-58-59-60-62-63-76-88-75-72-85-86-87-74-89</t>
+          <t>159-146-95-108-144-142-155-121-107-119-130-118-104-117-132-93-94-80-78-77-91-105-133-147-131</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -12134,7 +12134,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77-103-80-90-91-92-93-94-95-82-105-106-108-119-120-121-130-131-133-134-147-158-144-145-143-155-157-142-129</t>
+          <t>143-103-105-92-95-94-93-106-145-131-130-129-91-90-119-133-147-160-144-134-120-108-121-158-157-155-142</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -12142,27 +12142,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>26-1-0-14-28-27-16-29-4-17-30-42-56-43-65-66-53-38-52-64-51</t>
+          <t>82-43-56-17-30-16-14-28-29-4-42-70-80-65-66-52-38-27-26-1-0-51-77-64-53</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>96-97-98-99-101-114-111-112-110-122-123-154-128-126-138-148-150-151-165-152-161-160-162-163-164-135</t>
+          <t>11-37-22-8-7-6-19-32-45-20-36-50-76-74-57-58-71-59-46-34-47-48-35</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>37-11-7-6-19-20-22-32-34-35-36-8-45-46-47-48-50-59-58-57-70-71-74-76-83-84-85-87-88-89</t>
+          <t>97-83-148-162-122-123-110-99-98-126-138-151-163-164-150-161-135-84-85-111-112-165-154-96-114-89-88-87-101-128-152</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -12232,7 +12232,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>81-94-107-83-96-95-117-103-105-90-108-109-92-118-132-129-119-133-134-143-145-148-135-147-142-155-156-157-159</t>
+          <t>94-132-108-109-107-134-147-157-142-143-117-79-96-81-83-118-119-145-159-129-103-155-156-90-77-92-105-133-95</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -12240,27 +12240,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>37-11-9-21-8-6-32-34-35-23-45-46-48-50-63-60-59-72-61-75-76</t>
+          <t>34-61-86-87-75-89-76-63-37-50-35-48-60-23-8-21-11-9-32-72-59-46-45-6</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>86-87-89-113-99-100-101-102-110-111-98-124-128-114-125-127-141-136-137-123-149-150-151-153-163-164-166-167</t>
+          <t>3-2-1-16-4-17-30-65-67-70-41-26-38-51-64-39-14-13-27-15-54-55-56-43</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1-2-3-4-13-14-15-16-17-30-27-26-38-39-41-54-43-70-55-56-67-65-77-79-64-51</t>
+          <t>167-153-141-124-123-136-99-100-98-111-125-127-128-151-164-101-102-114-113-110-135-148-149-137-150-163-166</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -12330,15 +12330,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-85-86-87-88-89-96-97-98-99-100-102-110-111-112-115-122-123-124-125-127-137-138-139-140-152-151-166-153-165-150</t>
+          <t>111-124-166-140-152-139-110-99-112-83-96-97-98-85-86-88-89-102-150-165-151-125-123-122-137-115-127-153-138-100-87</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0-1-2-14-26-39-27-28-29-17-43-41-40-54-53-51-64-65-66-67-68-69-70-80-79-78-81-82</t>
+          <t>59-61-49-35-34-21-7-6-18-58-47-23-22-20-32-46-74-75-62-24-37-50-11-10-8</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -12346,15 +12346,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>147-107-93-94-91-90-119-105-118-116-129-130-131-144-155-142-143-117-133-132-146-156-157-158-160-161</t>
+          <t>29-41-67-65-79-81-68-69-43-70-80-82-54-28-27-39-53-66-78-26-2-14-40-64-51-0-1-17</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6-7-11-10-8-18-20-21-22-23-24-37-34-58-32-46-47-62-50-35-59-61-74-75-49</t>
+          <t>155-156-131-119-133-161-160-157-158-116-93-94-107-117-130-118-105-132-146-147-144-143-142-91-90-129</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -12428,35 +12428,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>97-98-99-101-110-109-136-137-123-115-141-128-126-138-139-135-148-149-150-152-153-166-165-161</t>
+          <t>128-153-138-97-99-101-139-96-123-152-166-165-161-148-86-98-83-109-110-149-135-137-150-136-126-141-115</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23-9-10-19-7-22-34-35-36-37-49-48-47-59-58-72-86-74-75-76-62</t>
+          <t>12-25-4-17-55-39-66-26-27-15-16-28-42-52-38-70-31-44-57-30-2-51-65-77-79-78-29-43-56-82-68-13</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>77-78-93-82-83-95-94-68-96-92-104-103-116-119-120-121-130-131-133-134-142-143-144-155-157-158-160</t>
+          <t>62-49-22-7-19-34-47-48-72-59-58-9-10-23-37-36-35-74-76-75</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2-4-12-13-27-39-38-25-26-15-28-29-30-31-17-16-55-43-44-57-56-42-52-51-65-66-79-70</t>
+          <t>93-103-116-130-144-134-160-158-155-143-119-95-121-120-133-157-142-131-94-92-104</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -12526,35 +12526,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>97-98-99-87-110-111-112-113-135-122-123-124-125-126-115-128-127-140-137-138-139-152-151-150-136-153-154-165</t>
+          <t>116-129-133-120-90-103-142-159-143-157-158-145-134-135-108-122-95-107-118-92-105-104</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>38-27-77-78-83-82-56-69-70-68-28-0-13-14-31-30-4-40-39-12-53-41-81-80-67-55-42-29-15</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>9-62-35-33-47-75-88-89-76-63-87-86-72-50-37-11-21</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>123-112-99-111-127-140-115-125-138-139-165-150-151-137-136-113-126-102-128-154-153-152-110-97-98-124</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>4-0-12-13-14-15-27-28-29-30-31-38-39-40-41-42-56-55-53-67-68-69-70</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>77-90-80-81-82-83-78-92-129-103-116-104-95-108-118-105-107-120-134-133-142-143-145-157-158-159</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>37-11-35-9-21-33-47-63-50-76-89-88-72-86-102-75-62</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -12624,15 +12624,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>85-83-95-96-97-99-101-102-126-110-111-113-114-115-121-108-124-122-134-135-136-137-138-140-147-149-150-161-162-164-165-166</t>
+          <t>135-122-146-147-134-95-106-92-133-161-132-131-103-90-91-129-130-119-155-156-159-157-145-107-108-121</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-7-9-22-18-19-21-10-24-36-33-34-35-50-37-49-32-57-58-61-62-63-70-71-74-75-76-87-88-89</t>
+          <t>71-18-5-57-70-58-34-36-49-75-61-74-62-37-9-10-24-35-22-21-50-76-63-32-33-7-19-6</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -12640,19 +12640,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>77-78-91-103-90-64-92-80-106-107-119-129-130-131-132-133-159-146-157-156-155-145</t>
+          <t>41-16-15-3-4-30-56-79-38-64-77-68-17-2-0-14-13-25-26-27-39-53-80-78-66-54-51-65-52</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>13-15-3-4-17-30-16-2-14-0-26-27-68-41-39-38-51-52-53-54-56-79-65-66-25</t>
+          <t>165-164-124-113-114-126-85-97-137-110-99-87-89-111-96-83-115-101-88-102-140-138-150-136-149-162-166</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -12722,35 +12722,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>96-91-93-90-105-117-118-119-120-121-122-129-130-131-133-149-148-135-144-145-159-155-156-157-161-134</t>
+          <t>155-93-122-134-121-120-105-91-131-77-79-78-90-117-157-133-119-118-96-135-148-156-144-145-161-159-130-129</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-8-18-31-20-19-23-24-11-34-33-36-44-71-47-45-99-115-75-63-62-49-60-61-76-73-84</t>
+          <t>8-34-62-63-47-33-45-73-60-71-84-75-76-61-49-36-6-19-20-24-11-23</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>87-88-89-102-101-113-112-111-125-127-128-138-151-164-152-154-153-167</t>
+          <t>16-4-3-1-13-29-44-31-17-18-66-65-64-67-53-15-14-0-38-26-28-57-56-43</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-13-3-16-1-14-15-4-17-29-28-26-38-53-43-57-56-67-65-66-64-77-78-79</t>
+          <t>151-149-111-112-127-113-99-88-87-89-102-154-153-152-164-167-128-115-101-125-138</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -12820,7 +12820,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58-83-84-98-114-102-101-88-109-110-111-112-125-96-122-123-124-113-128-126-135-136-138-139-141-154-151-152-153-148-162-164-165-167</t>
+          <t>96-109-162-152-165-167-151-141-154-128-88-101-136-135-124-138-139-98-111-110-125-126-113-102-114-112-84-123-148-164-153-122-83</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -12828,27 +12828,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-7-8-20-21-10-11-23-32-33-35-37-36-48-63-49-47-61-60-72-73-75-76</t>
+          <t>49-36-10-48-35-47-73-72-33-21-20-57-44-18-6-8-23-60-75-76-63-61-58-32-7-11-37</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>0-13-1-16-17-65-51-25-26-27-52-79-66-42-2-3-15-14-40-39-53-54-55-67-68-56-43-28</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>121-120-107-118-156-157-158-145-130-91-90-159-160-133-95-105-116-129-142-155-131-119</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>90-91-105-107-95-133-118-119-120-121-145-130-131-116-129-142-155-156-157-158-159-160</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0-1-2-3-13-14-15-16-17-18-27-26-28-55-39-40-42-43-44-57-56-53-54-79-52-51-65-66-67-68-25</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -12918,7 +12918,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>106-93-95-107-119-105-91-104-116-103-130-129-142-131-134-147-133-146-144-155-158-159</t>
+          <t>91-104-95-107-134-147-159-133-146-144-155-142-129-130-119-105-93-106-158-131-116-103</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -12926,27 +12926,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-7-5-9-11-19-21-24-23-32-47-34-35-36-37-33-45-46-48-49-60-59-63-61-58-71-72-73-74-75-89-86-85-84-87-88-76</t>
+          <t>39-65-79-66-41-15-30-43-56-54-81-69-82-68-80-29-1-3-2-26-25-38-40-53-64-52</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>37-11-21-23-24-36-72-86-85-84-71-74-61-63-76-49-48-46-58-59-60-73-34-35-47-33-7-5-75-88-89-87-9-45-32-19-6-18-44</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>4</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>122-98-112-100-101-109-110-123-97-99-124-125-126-150-137-135-138-140-141-128-154-167-153-165-161-162-149-148</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1-2-3-39-38-25-26-29-30-18-15-40-41-43-44-56-54-53-64-79-65-66-80-68-82-69-81-52</t>
+          <t>167-154-126-98-125-165-124-150-137-112-100-141-128-153-140-110-97-109-122-123-149-162-161-135-148-138-99-101</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -13016,35 +13016,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>96-94-104-105-106-107-108-122-121-118-131-130-129-132-134-147-146-142-155-157-158-159-160-161</t>
+          <t>161-134-106-118-116-129-130-131-132-146-157-158-159-160-147-121-108-107-105-104-142-155-94-96-122</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-7-23-10-11-9-20-21-22-19-33-34-35-73-45-46-47-49-37-50-76-63-62-61-74-75-59-4</t>
+          <t>20-46-74-50-37-49-62-61-7-19-45-59-58-71-84-85-87-47-22-23-10-11-76-63-89-75-73-34-33-35-9-21</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>43-4-17-56-30-29-27-13-39-51-38-26-52-40-15-16-5-68-64-77-78-65-55-69-41-2-1-57-82-83</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>162-150-137-123-151-164-166-126-128-102-99-110-98-112-113-127-125-136-163-153-154-141-115-114-138</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>116-84-85-87-123-137-99-102-71-58-110-112-98-127-89-115-125-113-114-126-141-128-138-136-150-151-153-154-162-163-164-166</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>3</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>15-2-1-13-16-17-43-27-29-30-38-39-40-41-26-51-52-65-77-64-68-55-56-57-69-78-82-83</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -13114,35 +13114,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>81-83-92-91-116-104-105-106-107-108-109-96-122-121-120-119-131-129-117-132-134-146-158-144-145-135-148-161-156-143-155</t>
+          <t>129-116-92-91-104-117-131-132-108-121-146-145-158-143-155-156-144-134-120-107-106-105-119</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-32-8-21-20-19-18-7-24-23-10-34-44-46-47-49-50-73-60-63-76-71-72-84-70-59</t>
+          <t>16-15-17-30-29-0-2-1-40-65-78-66-52-12-14-55-67-27-26-38-77-51-25-13-4-68-81-41-56-69</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>113-86-97-98-99-100-112-125-126-101-88-115-110-111-124-139-136-137-127-140-141-149-150-151-152-165-163-164-154-166-167</t>
+          <t>50-24-23-8-20-44-70-71-72-59-32-60-34-10-7-19-46-73-47-18-5-6-21-49-76-63</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-2-4-12-13-14-15-16-17-25-26-27-29-30-38-40-41-51-52-55-56-69-68-67-78-65-77-66</t>
+          <t>98-111-141-165-151-152-112-100-86-99-126-127-115-101-125-148-110-109-113-88-139-150-136-149-124-97-84-140-154-166-167-164-161-135-122-163-137-83-96</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -13212,35 +13212,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>122-90-116-103-104-105-106-107-108-109-96-119-120-121-95-129-130-131-132-133-134-135-145-144-143-147-148-156-158-159-160</t>
+          <t>104-105-77-120-109-122-144-132-147-160-158-159-119-107-106-83-121-133-145-108-82-79-96-95-103-129-156-131-143-130-116-78-80-81-135-148-134-90</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32-7-10-8-24-9-6-19-5-18-31-44-47-49-50-74-61-73-72-71-59</t>
+          <t>71-73-87-76-6-7-8-24-50-49-47-88-89-74-61-9-10-85-72-59-32-19-70</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>98-85-87-88-89-102-76-99-97-112-114-115-126-124-125-123-136-138-150-151-165-140-139-152-153-154-167-166-141</t>
+          <t>38-13-0-28-2-15-3-31-44-42-29-16-17-18-5-39-25-51-52-41-56-69-53-65-64</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-2-3-28-15-16-17-25-13-29-38-39-41-42-56-77-51-65-64-53-69-70-83-78-79-80-81-82-52</t>
+          <t>139-151-166-165-167-154-141-115-102-99-126-140-153-152-150-138-125-112-136-124-98-97-123-114</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -13310,35 +13310,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84-111-97-99-100-101-102-87-112-165-139-126-127-128-141-154-151-123-124-150-163-164-137</t>
+          <t>100-101-102-99-112-111-123-126-139-165-164-154-141-128-127-150-163-151-124-137-97-87</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>2-1-17-16-29-28-54-53-68-82-55-41-27-12-0-65-42-43-67-78-64-51-14-15</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>7</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>6-19-32-23-24-11-36-35-34-33-59-72-47-58-46-60-74-61-76-50</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>8</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70-82-94-78-91-95-96-135-104-103-106-108-109-117-118-105-144-134-122-142-143-130-145-146-158-157-156-160-161</t>
+          <t>31-34-76-72-59-74-61-46-70-58-44-57-84-60-50-36-24-11-19-32-33-47-35-23-6-5</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>28-1-2-0-12-14-15-16-42-41-27-29-31-17-5-43-44-57-68-54-55-51-64-65-67-53</t>
+          <t>108-91-103-94-122-109-95-96-134-146-156-142-143-104-105-106-118-117-130-157-144-158-160-145-161-135</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -13408,35 +13408,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>85-86-87-89-96-97-98-99-101-100-124-111-112-150-123-110-125-126-128-138-139-153-141-115-154-152-140-151-162-164-165-166-167</t>
+          <t>125-126-150-135-123-161-162-138-152-165-151-139-153-166-167-140-164-148-96-97-110-111-124-141-154-128-115-112-99-98-100-101</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>8-19-34-61-75-87-73-59-58-86-85-71-33-21-9-23-49-63-89-60-47-32-6-37-50-48</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>1-16-29-43-42-53-41-83-82-55-54-67-79-80-4-5-2-18-25-51-52-65-66-0-38-40-69-56-31-44-28-14-13</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>5-6-8-9-23-18-32-31-19-21-33-34-37-50-63-48-49-75-73-59-60-61-47-58-71-44</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>90-91-103-104-106-119-116-117-142-129-130-131-133-108-134-135-145-144-132-146-147-148-155-156-157-159-160-161</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>103-131-142-129-130-144-146-160-147-117-116-155-157-156-159-108-91-106-134-133-145-132-119-104-90</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1-2-16-4-14-13-0-40-28-29-38-25-41-42-65-51-52-53-54-55-56-43-66-67-69-79-80-82-83</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -13506,7 +13506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>86-87-88-89-98-97-99-100-101-102-141-128-114-126-113-137-136-139-140-110-149-150-152-153-166-163-164-165-167-154</t>
+          <t>149-137-136-150-154-153-152-128-126-99-98-97-139-164-166-114-102-87-86-110-113-100-89-88-101-141-167-140-165-163</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -13514,15 +13514,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-7-9-10-18-19-20-21-22-23-44-33-34-35-36-32-45-46-47-48-49-74-58-59-60-61-63-70-71-72-73-85-84-57</t>
+          <t>85-70-60-61-36-10-23-22-18-44-58-57-32-45-59-74-73-72-35-33-49-63-6-19-9-21-7-34-48-47-46-20-84-71</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>90-91-92-95-96-103-104-106-107-108-109-122-148-135-131-119-118-120-133-142-143-144-145-146-147-161-156-157-158-159-160-129</t>
+          <t>0-54-65-51-39-38-26-13-1-17-4-81-78-64-55-56-68-41-29-30-14-40-28-69-82</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -13530,11 +13530,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>13-26-1-0-14-17-4-29-28-40-38-39-65-64-51-54-55-56-41-78-68-69-82-81-30</t>
+          <t>109-108-96-95-92-143-156-145-158-159-148-135-120-119-103-104-106-107-122-161-160-147-131-118-91-90-129-142-144-157-133-146</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -13604,7 +13604,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-84-85-86-87-88-89-97-98-99-101-102-110-109-112-113-114-122-123-125-135-134-136-137-141-165-151-152-153-149-164-162-166</t>
+          <t>109-110-84-135-164-166-152-153-141-102-86-123-97-137-149-136-99-113-125-112-85-83-98-87-88-89-101-114-151-165-162-122</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -13612,23 +13612,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-19-20-7-10-23-24-37-34-58-71-74-63-62-61-60-72-59</t>
+          <t>41-15-27-26-2-1-28-39-78-79-55-56-43-82-30-53-51-77-52-66-67-81-69-16-4-3-65-38-25-54-42</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>90-91-92-93-94-95-103-104-105-106-107-108-121-133-120-117-129-130-119-132-131-142-143-144-145-147-161-159-156</t>
+          <t>59-58-57-44-5-6-19-34-20-7-37-61-60-70-71-72-74-63-62-10-24-23</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>30-2-3-4-16-15-25-26-27-28-1-38-39-41-56-43-44-57-52-53-42-55-54-51-65-66-67-69-82-77-78-79-81-70</t>
+          <t>132-95-108-134-161-147-120-119-92-91-94-107-121-133-159-156-143-117-131-144-103-90-93-106-105-104-142-130-129-145</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -13702,15 +13702,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>102-87-98-99-84-110-111-123-124-125-126-128-140-153-151-150-162-164-165-166-167</t>
+          <t>87-98-99-102-89-84-110-124-123-111-126-128-167-166-153-140-164-162-150-151-165-125</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-8-11-10-24-9-21-22-19-33-47-45-58-48-50-61-36-63-89-75-74-73</t>
+          <t>24-50-10-9-75-63-47-74-73-58-61-48-36-22-6-19-45-33-8-21-11</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -13718,19 +13718,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>90-91-92-104-105-116-117-118-119-120-122-129-155-142-135-134-144-145-146-147-148-133-157-158-159-160-161-77</t>
+          <t>12-57-56-53-64-25-55-68-66-80-70-42-69-82-81-41-38-77-65-67-79-54-28-14-1-2-30-31-43-44-17-29-16-4-18-13-0</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-2-4-12-13-14-16-17-18-57-28-38-30-31-29-44-42-43-82-95-53-54-55-56-25-64-65-66-67-68-69-70-79-80-81-41</t>
+          <t>119-133-157-159-148-146-145-155-158-118-104-95-147-122-134-120-135-161-160-92-91-90-116-129-142-144-105-117</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -13800,23 +13800,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>82-81-80-77-90-91-93-94-161-132-104-105-117-108-109-107-118-119-120-143-129-131-147-134-122-103-155-156-158-159-160-96</t>
+          <t>77-103-104-155-156-131-119-118-117-129-105-93-134-120-143-159-158-132-160-161-147-96-109-108-122-107-94-82-81-80-90-91</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-8-9-11-23-21-22-34-32-20-35-48-47-46-45-36-49-50-62-61-60-75-74-73</t>
+          <t>45-8-6-20-21-35-22-9-11-23-48-47-61-75-74-73-60-62-50-49-36-34-46-32</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84-85-98-101-88-87-99-86-100-102-113-125-114-128-153-136-162-152-141-167-139-138-123</t>
+          <t>13-52-64-51-53-16-17-15-2-0-39-38-26-27-54-29-44-18-4-5-43-42-55-56-69-57-70-31-3</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -13824,7 +13824,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-2-3-4-5-18-15-16-17-31-29-27-26-13-38-39-42-43-44-57-56-53-54-55-52-51-64-69-70</t>
+          <t>84-85-136-162-167-128-102-100-99-87-88-141-153-152-139-114-101-86-113-125-138-123-98</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -13898,7 +13898,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>82-83-110-95-96-103-106-132-142-117-93-121-122-134-135-108-120-143-155-147-148-149-146-158-159-160-161-162</t>
+          <t>112-99-100-89-141-115-111-123-149-137-140-154-128-127-151-165-152-138-163-162-150-110-98-113-114-102-153-166</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -13906,27 +13906,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>87-24-10-17-18-19-20-21-22-23-8-31-32-34-35-37-63-46-47-48-49-61-59-58-44-70-71-72-73-75-76-84-85-86</t>
+          <t>72-48-61-73-35-20-19-32-18-31-59-71-70-58-44-84-86-76-49-34-85-87-46-21-10-24-63-75-37-8-23-22-47</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>111-98-99-100-102-89-112-113-114-115-127-128-141-138-151-137-150-140-152-153-154-166-165-163-123</t>
+          <t>30-43-55-41-29-27-14-2-3-15-12-13-0-25-78-79-42-56-17-4-52-38-39-51-77-67-66-40-26-1</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-2-3-4-26-13-14-15-12-25-27-29-30-38-39-40-41-42-43-51-79-55-56-66-90-77-78-91-80-81-67-52</t>
+          <t>142-146-106-80-91-103-90-143-120-93-95-96-108-82-83-81-117-132-134-135-161-122-121-160-158-159-147-148-155</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -13996,35 +13996,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>95-81-80-78-90-91-93-94-79-106-105-104-103-116-117-129-130-131-132-159-158-156-155-143-145-146</t>
+          <t>78-79-94-106-132-131-90-95-108-80-93-81-105-104-146-155-143-116-129-117-91-103-130-145-159-158-156</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23-19-32-5-6-20-21-22-11-10-37-35-45-44-58-108-49-62-47-60-87-63-50-73-74-76</t>
+          <t>71-83-20-19-23-62-84-58-6-32-45-87-73-60-21-11-10-49-50-22-35-37-76-89-47-74-88-63</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>83-84-71-88-89-100-101-109-110-152-115-113-112-123-126-148-161-135-125-140-151-167-154-128-165-163-111</t>
+          <t>5-16-15-29-56-69-54-41-40-12-0-1-13-2-3-66-65-52-51-39-38-53-67-44</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-2-3-12-13-15-16-29-53-40-39-65-52-51-38-54-56-69-66-67-41</t>
+          <t>110-111-125-126-115-128-154-167-165-140-152-151-123-101-100-113-112-135-148-163-161-109</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -14094,15 +14094,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>116-104-107-94-80-79-105-117-129-130-118-120-146-145-155-156</t>
+          <t>146-160-145-117-116-104-77-129-118-94-107-105-130-155-156-79-80-120</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>21-22-9-35-19-20-6-7-23-24-11-48-62-37-49-47-71-43-45-59-60-61-74-63-34-33</t>
+          <t>6-7-20-33-47-34-22-35-62-74-73-60-45-71-59-61-9-11-48-37-24-23-21-49-63-19</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -14110,19 +14110,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>83-84-85-86-88-89-96-123-98-73-100-101-102-111-110-112-113-115-97-124-127-128-139-137-136-163-148-160-151-154-141-165</t>
+          <t>64-51-29-42-69-56-18-44-43-40-15-16-17-0-27-38-25-39-55-67-66-68-82-57-4-5-2-14-1-65</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>124-98-101-115-128-154-165-148-151-141-113-88-102-89-100-85-112-163-136-96-86-84-83-97-110-111-127-139-137-123</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0-1-2-4-5-18-15-16-17-14-25-27-51-38-39-40-42-44-29-55-82-67-64-77-65-66-56-68-69-57</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -14192,7 +14192,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>96-99-110-111-112-114-115-122-123-124-135-148-161-137-139-140-141-128-149-150-151-167-153-152-162-163-165-125</t>
+          <t>63-75-74-73-99-140-139-111-110-84-85-88-89-114-115-125-124-86-112-165-167-151-137-152-153-141-128-87-76</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -14200,27 +14200,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0-2-3-4-5-6-15-16-19-44-43-27-29-30-31-39-40-42-26-25-51-65-54-55-56-57-82-67-69-53</t>
+          <t>39-69-82-80-67-25-27-40-53-91-116-90-77-103-104-92-93-55-42-54-26-0-15-51-65-64</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>90-77-92-91-64-80-107-93-104-103-116-119-120-121-147-142-155-156-143-157-146-145-132</t>
+          <t>48-37-61-3-4-30-45-58-57-44-56-29-5-19-6-20-33-47-46-16-2-31-43-59-72-60-32-11-24</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>135-147-146-145-142-143-132-119-120-96-123-122-157-156-155-107-121-149-148-162-161-163-150</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>24-11-20-32-46-59-45-33-47-48-58-72-60-61-63-37-74-73-89-75-84-85-86-87-88-76</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -14290,7 +14290,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>76-87-86-100-88-89-97-99-113-84-110-112-101-115-127-126-137-125-139-152-140-153-167-165-164</t>
+          <t>99-101-89-112-137-164-165-139-125-110-87-88-76-100-113-140-153-115-127-167-152-126-86-84-97</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-7-45-19-18-31-23-24-22-33-34-35-10-49-48-47-37-50-60-59-71-62-61-74</t>
+          <t>24-10-7-6-35-34-47-48-62-60-59-33-19-45-71-18-31-5-22-49-50-74-61-23-37</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -14306,19 +14306,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>94-95-96-90-103-105-106-107-120-122-109-134-119-155-143-144-145-146-148-149-135-158-159-160-162</t>
+          <t>29-4-16-39-90-79-66-67-80-40-30-17-3-2-14-25-53-81-69-55-0-13-1-64-65-52-26-51-38</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>149-162-148-159-158-103-105-144-155-143-145-146-120-107-160-134-135-122-109-94-96-95-106-119</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>13-0-2-3-16-1-14-4-17-55-30-29-26-39-38-25-51-52-53-79-64-65-66-67-69-81-80-40</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -14388,35 +14388,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>64-78-90-103-91-93-94-95-82-105-106-107-119-116-117-118-108-121-132-133-134-147-145-143-142-155-159-160</t>
+          <t>105-78-90-93-108-82-96-121-133-106-119-107-118-159-145-134-94-122-160-147-132-143-155-142-91-83-95-103-117-116</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>59-45-33-46-47-60-85-58-44-70-71-73-48-37-24-8-19-32-86-75-89-76-63-21-35-34-62-49-36-10-9-20-18-31-72</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>30-17-4-3-42-55-26-25-12-38-51-64-53-68-67-52-40-27-15-14-13-0</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>137-149-162-161-141-154-166-127-153-138-112-151-164-163-150-124-136-123-111-97-98-99-128-114-102-101-113</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>30-3-4-0-12-14-15-27-25-26-13-38-40-53-51-52-68-55-67-42-31</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>83-85-86-96-97-98-99-101-102-114-112-113-111-122-123-138-127-128-141-137-124-136-149-150-151-153-154-164-163-162-161-166</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>24-9-10-18-19-17-20-21-8-32-33-34-37-36-35-44-45-46-47-48-49-58-59-60-62-63-70-71-72-73-76-75-89</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -14486,7 +14486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>111-110-102-87-88-89-86-97-98-99-100-96-84-83-113-114-125-161-148-135-122-137-140-141-127-154-164-149-136-163-151-166-165-167</t>
+          <t>166-154-141-167-114-113-98-135-136-161-148-122-137-111-149-151-164-165-102-89-88-87-86-125-163-140-127-100-84-96-97-99-110-83</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -14494,27 +14494,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-7-8-10-11-19-20-22-23-35-36-37-49-48-46-45-57-58-60-61-73</t>
+          <t>23-48-35-61-60-73-58-46-20-11-10-8-7-45-57-31-19-5-22-49-37-36</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>77-78-80-81-82-95-108-93-90-91-105-106-104-116-117-118-120-144-129-130-133-147-121-131-156-157-158-159-160</t>
+          <t>51-77-78-80-68-2-4-17-29-55-65-64-53-26-28-41-82-81-69-30-42-40-39-38-13-25-14-3-0-12</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-2-3-28-4-17-13-14-12-25-26-29-31-30-55-42-41-40-38-39-53-65-64-51-68-69</t>
+          <t>90-104-116-156-130-129-117-91-144-158-157-133-147-160-159-131-118-121-120-108-106-105-95-93</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -14584,15 +14584,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84-85-86-87-98-99-101-102-111-112-114-115-127-126-123-150-136-137-138-139-141-154-128-153-167-162-163-164-165-151-83</t>
+          <t>92-81-83-90-129-142-118-80-105-120-134-135-119-107-94-122-133-132-131-93-82-108-121-95-109-106-91-77-144-158-160-147-116</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-7-8-9-10-11-18-19-20-33-24-50-37-34-36-22-44-45-49-48-74-72-59-60-61-62-63-57-70-73-32</t>
+          <t>15-39-38-51-40-28-5-18-44-43-67-66-41-17-69-68-65-52-0-12-13-54-55-30-70-57-4-2-3-16</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -14600,19 +14600,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>80-81-82-105-90-91-92-93-94-108-109-107-95-118-116-106-119-120-121-122-135-131-132-133-134-129-142-144-160-158-147</t>
+          <t>8-6-19-61-49-36-48-62-63-7-20-32-45-60-74-9-22-10-11-24-37-50-34-59-73-72-33</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-2-3-4-12-13-15-16-17-43-30-40-39-51-65-77-52-38-66-28-41-54-67-68-69-55</t>
+          <t>164-154-127-138-150-163-139-112-87-102-101-114-128-85-98-141-167-151-126-115-153-165-162-136-86-99-111-137-123-84</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -14682,7 +14682,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-84-86-87-88-89-101-100-76-96-109-126-111-112-113-128-122-123-110-95-127-115-135-136-137-138-139-148-149-165-166</t>
+          <t>135-148-149-83-84-96-86-87-88-100-89-101-123-122-109-112-126-115-113-137-136-110-165-138-111-166-128-127-139</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -14690,27 +14690,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-8-9-10-31-19-20-22-23-24-37-35-34-46-45-58-71-48-36-47-60-61-62-49-63-75-74</t>
+          <t>22-9-19-6-45-63-37-76-75-74-58-71-48-62-61-60-46-47-34-49-23-36-24-10-8-35-20</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>77-90-91-92-93-94-105-103-104-107-133-119-132-131-117-145-143-144-156-155-142-158-159-160</t>
+          <t>0-15-39-53-3-5-44-69-43-30-31-40-64-66-67-51-12-25-55-70-56-13</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>15-3-5-30-0-13-25-12-39-40-43-44-55-53-51-64-79-66-67-69-70-56</t>
+          <t>103-117-145-133-132-105-77-90-155-142-104-92-94-93-107-95-131-144-156-143-91-79-119-159-158-160</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -14780,35 +14780,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-91-92-105-96-95-108-119-118-116-131-132-133-134-159-143-144-146-148-135</t>
+          <t>100-113-124-150-111-85-84-137-149-163-165-164-153-140-166-154-141-128-127-102-101-152-125-98-99</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>50-62-74-73-63-47-58-71-45-33-32-35-48-22-9-6-19-10-11-24-23</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>8</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>5-6-11-10-9-18-19-22-23-24-33-32-45-58-71-47-48-50-62-63-74-73-35</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>7</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84-85-98-99-100-101-102-111-113-124-125-127-128-141-140-137-149-150-152-153-154-166-164-165-163</t>
+          <t>14-13-26-15-17-53-79-44-70-69-68-81-83-0-12-4-5-18-65-77-51-66-56-43-29-30-27-40-42-41-67</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4-13-12-0-14-15-17-27-41-29-30-40-26-42-43-44-70-53-56-65-66-67-68-69-51-77-79-81-83</t>
+          <t>91-105-92-132-108-95-96-148-135-133-144-143-118-119-146-159-134-131-116-90</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -14878,15 +14878,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>117-118-119-143-121-122-155-129-130-132-133-135-136-138-139-123-147-124-150-152-153-154-146-157-159-161-162-164</t>
+          <t>122-109-138-152-113-124-84-83-96-100-101-102-139-97-110-136-135-123-108-121-164-150-153-154-162-161-147</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-8-9-10-21-18-19-20-11-49-36-23-33-47-34-60-73-63-62-75-87-88-101-102</t>
+          <t>11-36-23-20-19-5-18-6-10-9-8-21-34-75-62-63-87-88-73-60-47-71-58-33-49</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -14894,19 +14894,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>71-58-56-69-68-81-82-83-84-93-92-96-113-100-106-105-108-109-110-97</t>
+          <t>82-69-81-68-28-27-29-43-40-26-51-79-78-77-67-65-38-66-3-16-55-56-53-52-12-13-39</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>27-12-13-29-16-3-28-26-38-39-52-66-51-65-53-40-55-43-67-79-78-77-91-103-104</t>
+          <t>91-103-104-106-118-143-155-157-132-119-117-129-130-133-146-159-105-93-92</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -14976,35 +14976,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84-85-86-89-102-100-101-128-126-111-112-113-114-115-97-110-123-137-162-149-150-151-140-167-154-153-166-152</t>
+          <t>123-100-113-84-97-115-128-153-140-112-89-114-126-152-151-154-167-166-101-85-86-102-76-111-110-137-150</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>15-16-70-80-67-78-90-91-77-52-65-79-81-68-53-38-25-43-56-55-42-29-41-28-2-0</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>5-18-7-20-19-8-46-44-31-32-47-49-59-11-50-36-35-22-9-45-71-72-58-60-73-74-61-34-33</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>95-94-109-96-121-122-132-129-142-103-131-156-161-162-149-134-160-145-144-120-133-147-148-119-106</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>22-9-7-11-8-20-19-32-33-34-71-58-45-46-36-35-50-47-59-60-74-76-72-73-61-49</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>70-79-78-103-77-65-90-91-95-96-94-80-106-133-119-120-121-122-109-131-132-144-156-142-129-145-147-160-134-148-161</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0-2-42-15-16-41-28-29-31-5-18-44-43-38-52-53-55-56-81-67-68-25</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -15074,35 +15074,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77-78-79-103-90-91-92-93-94-95-96-81-105-106-107-108-121-143-129-130-131-144-134-120-133-158-157-155</t>
+          <t>95-93-157-144-158-155-92-105-131-134-135-148-122-108-107-106-91-90-129-130-120-94-81-103-143-133-121-96</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-7-8-10-35-34-33-75-11-37-50-47-58-45-46-59-60-61-72-71-19</t>
+          <t>27-28-2-1-3-15-16-79-78-77-64-38-51-52-66-42-67-68-55-26-25</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84-85-87-89-97-99-110-111-113-114-115-139-137-124-136-135-122-123-138-127-140-141-154-151-153-152-148-162-164-167-166-165</t>
+          <t>10-6-31-18-44-57-58-83-85-84-71-72-75-50-7-8-33-60-59-45-70-19-17-4-46-47-34-35-37-61-11</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>57-44-31-17-18-16-4-1-25-26-27-28-15-3-2-42-55-52-51-38-64-66-67-68-83-70</t>
+          <t>99-113-115-114-138-164-165-152-166-123-111-97-110-154-141-167-140-127-87-137-139-153-151-162-136-124-89</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -15172,35 +15172,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>116-92-93-106-107-91-118-144-142-129-130-131-132-119-120-145-155-156-158</t>
+          <t>107-119-158-155-144-156-130-91-93-92-82-81-109-120-145-160-131-118-106-95-96-135-132-116-129-142</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>35-22-10-9-8-19-20-21-44-31-32-33-5-18-45-58-46-48-49-47-59-70-71-73-74-75</t>
+          <t>64-65-67-53-39-38-26-13-1-2-3-29-27-40-41-68-51</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>83-84-85-86-88-96-97-98-99-100-101-114-111-124-112-113-102-115-127-123-125-136-135-109-137-140-141-165-160-151-153-154-163-150-167-95</t>
+          <t>9-21-20-32-33-46-47-59-44-43-4-18-5-19-45-48-74-73-49-22-71-84-83-70-31-8-10-35-58-56</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1-4-3-2-13-26-27-41-53-56-43-29-40-39-38-51-64-65-67-68-81-82</t>
+          <t>125-154-137-124-98-99-112-150-151-113-114-100-75-88-86-85-97-111-136-167-153-165-163-140-127-141-101-102-115-123</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -15270,7 +15270,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>116-90-92-93-95-96-107-105-106-104-108-109-83-118-119-120-121-122-135-131-132-134-130-142-143-144-146-158-159-155-157-147-148</t>
+          <t>118-155-142-105-144-157-158-148-159-143-130-92-132-120-95-122-135-134-146-119-121-107-96-83-93-106-90-104-116-131-147-109-108</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -15278,27 +15278,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18-5-7-33-8-21-22-23-24-11-63-62-76-36-74-49-50-32-46-60-61-31-58-70-71-59-73-72-35</t>
+          <t>8-21-7-32-72-73-11-24-35-74-76-49-36-23-22-61-58-46-62-63-50-60-71-59-33</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>97-86-87-88-89-85-98-99-101-102-115-126-125-124-123-149-167-154-139-140-141-127-138-153-151-162-136</t>
+          <t>51-55-42-15-27-67-66-80-31-56-68-69-70-43-18-5-17-40-52-39-25-12-0-14-26-13-3-65</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>15-14-12-13-0-3-17-25-26-27-39-65-52-51-40-42-43-56-67-66-80-68-69-55</t>
+          <t>127-154-162-136-97-86-85-98-99-88-101-115-149-123-124-126-102-87-125-138-139-151-153-140-167-141-89</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -15368,7 +15368,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-71-98-99-114-89-101-102-111-100-112-113-124-122-110-125-128-140-136-137-152-165-151-138-150-163-135</t>
+          <t>99-89-102-100-112-110-137-138-113-101-128-114-87-98-111-83-125-124-136-150-163-165-140-152-151-135-122</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -15376,7 +15376,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>31-19-6-32-21-9-23-22-20-33-36-37-49-46-45-58-60-62-63-87-73-72</t>
+          <t>58-71-45-33-9-23-36-22-20-21-6-31-19-32-46-60-63-37-49-62-73-72</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -15384,7 +15384,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>82-95-81-78-90-117-119-79-103-104-105-133-121-107-93-94-118-130-142-129-131-144-145-146-147-156-157-159</t>
+          <t>66-67-1-2-41-29-30-3-69-68-64-51-38-12-25-42-43-55-54-27-13-14-0-52-53-16-17-28</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -15392,11 +15392,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-2-3-12-13-14-16-17-29-25-38-27-28-55-41-42-43-30-54-53-52-51-64-66-67-69-68</t>
+          <t>104-93-78-90-103-130-157-133-145-121-107-95-82-94-118-131-144-156-146-147-159-117-105-79-81-119-129-142</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -15466,7 +15466,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77-79-94-108-105-103-104-92-106-93-116-117-118-130-129-131-120-132-133-134-147-143-145-157-155-142-159-160</t>
+          <t>92-133-147-159-120-94-105-117-131-130-118-106-93-132-143-129-116-104-108-134-145-142-155-157-160-103-77-79</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -15474,15 +15474,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>37-35-8-9-10-11-24-21-6-32-45-33-20-7-23-49-47-48-36-50-63-62-61-60-58-71-74-76-88</t>
+          <t>25-64-68-70-44-30-29-51-38-42-56-69-55-16-3-0-14-5-18-17-43-67-66-81-28-15-2-12-27-40</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84-85-86-113-101-102-128-112-111-110-136-123-124-97-125-126-166-154-127-138-137-161-150-151-152-139-164-162-163-148-109</t>
+          <t>7-8-20-33-45-88-62-61-35-6-32-21-10-23-9-11-24-37-63-49-50-76-74-47-36-48-60-71-58</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -15490,11 +15490,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>12-0-25-5-2-14-15-16-17-18-3-27-28-64-51-38-40-42-30-29-55-56-43-44-70-81-68-69-67-66</t>
+          <t>138-126-112-111-123-136-125-127-139-163-150-148-137-154-101-102-128-113-152-166-124-85-84-97-86-110-109-161-162-164-151</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -15564,7 +15564,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77-78-80-81-82-96-94-95-91-103-104-106-107-108-116-118-131-120-121-119-132-133-134-142-143-144-147-159-158-155</t>
+          <t>96-95-159-144-132-131-103-116-104-80-77-81-94-107-134-147-158-91-78-106-120-108-119-118-155-142-143-133-121-82</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -15572,7 +15572,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7-8-10-11-21-24-22-32-33-34-35-36-37-45-58-59-48-47-49-61-63-76-73-74-86-85-72-88-89</t>
+          <t>35-45-72-57-70-32-33-8-21-10-24-37-36-86-85-74-88-89-49-22-7-11-63-76-73-58-59-48-61-47-34</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -15580,19 +15580,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>97-99-100-101-123-110-136-149-124-125-114-113-126-138-139-140-128-162-150-153-154-167-151-164-165-166-161</t>
+          <t>67-68-56-69-41-43-14-26-18-4-30-17-39-38-25-28-15-16-2-0-13-12-52-64-66-40</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-13-25-12-2-14-15-16-17-18-4-30-28-26-38-39-40-41-43-57-70-52-64-66-67-68-69-56</t>
+          <t>150-164-151-114-101-113-167-154-140-125-126-139-165-166-136-124-138-149-161-162-110-99-100-128-153-123-97</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -15662,23 +15662,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>92-94-95-104-105-106-108-121-133-120-134-129-130-116-119-132-142-143-145-146-158-155-156-157-147-160</t>
+          <t>157-158-129-130-121-147-108-95-119-156-143-155-142-104-116-105-120-134-145-132-94-106-92-133-146-160</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>7-20-37-63-76-88-74-33-6-58-71-59-45-73-34-35-22-11-24-36-62-60-8</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>1-14-13-28-15-18-31-16-5-17-26-38-39-40-41-42-52-53-54-55-56-66-64-77-78-70-57-68-80-82</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>96-97-98-99-100-110-109-135-123-125-122-112-113-101-126-136-137-138-139-141-140-154-153-167-161-162-163-165-151</t>
+          <t>16-56-82-70-57-17-5-18-31-41-40-54-55-66-64-38-15-42-68-80-53-52-28-14-13-1-26-39-78-77</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -15686,11 +15686,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6-7-20-33-8-22-24-11-37-35-36-34-45-58-59-60-62-88-71-73-74-76-63</t>
+          <t>123-136-163-153-154-139-141-140-112-125-137-162-161-135-99-100-101-110-113-126-138-167-165-151-122-98-97-96-109</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -15760,7 +15760,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>82-83-84-86-96-97-98-113-101-102-110-125-112-99-114-167-123-124-111-135-136-137-138-139-165-166-150-153-154-160-163-148-149-122</t>
+          <t>113-138-137-122-111-124-136-135-96-83-110-150-163-98-84-97-99-112-123-148-149-102-101-86-125-139-114-165-166-167-154-153</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -15768,27 +15768,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16-1-2-3-5-18-14-15-0-12-25-26-28-41-43-29-40-27-39-53-55-56</t>
+          <t>58-73-61-36-9-11-23-45-5-18-19-33-32-6-7-21-72-60-35-62-75-76-63-37-34</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>53-64-66-65-67-55-56-43-41-40-39-25-12-26-0-1-3-16-2-29-15-14-27-28</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>9</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>108-160-158-107-94-132-157-156-144-118-130-129-104-90-78-77-103-93-82</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>8</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>67-66-65-64-77-78-93-104-103-90-94-108-107-118-130-129-132-144-156-157-158</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>19-11-23-9-21-7-6-32-33-34-35-36-37-75-58-60-61-62-63-76-73-72-45</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -15858,23 +15858,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>78-77-90-92-105-80-94-81-95-96-82-108-109-121-119-120-117-130-131-144-158-147-148-146-156-155</t>
+          <t>123-99-112-124-127-151-166-154-140-152-110-97-136-148-149-138-126-115-102-100-101-128-165-164-137</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0-1-2-3-4-5-13-14-16-17-18-30-29-27-26-25-39-40-41-42-43-56-54-53-65-66-67</t>
+          <t>7-20-44-58-85-59-8-6-10-36-50-49-34-47-46-61-60-45-57-70-71-84-88-62-63-76-75-74</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>97-99-110-101-102-100-112-123-124-137-126-127-128-136-149-138-140-115-154-152-151-164-165-166</t>
+          <t>1-2-41-0-13-40-53-65-39-25-26-69-67-42-43-30-29-17-16-14-27-66-54-56-18-5-4-3</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -15882,7 +15882,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6-7-8-10-20-34-36-44-45-46-47-49-50-74-58-59-60-61-85-84-70-69-71-88-75-76-63-62-57</t>
+          <t>90-77-94-92-80-82-95-121-108-146-131-120-130-158-147-109-96-81-78-144-156-155-117-105-119</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -15956,7 +15956,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>78-77-79-80-90-91-103-105-92-108-94-109-121-160-120-134-117-130-119-129-143-145-156-131</t>
+          <t>108-119-129-90-91-92-121-134-160-145-117-103-77-78-105-120-156-143-130-131-79-80-94</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -15964,27 +15964,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-8-9-10-11-24-23-21-36-35-33-46-47-48-50-63-62-75-74-72-73-71-59</t>
+          <t>39-38-51-64-54-18-31-56-55-69-70-12-13-25-52-65-66-67-14-15-17-4-43-57-68-30-29-2-3-16-41-27</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>96-84-111-83-97-98-99-100-101-102-86-114-127-125-126-123-136-135-149-137-150-163-151-152-153-154-128-165-167</t>
+          <t>21-8-9-6-23-36-50-35-48-72-59-33-47-46-62-75-73-71-11-10-24-63-74-32</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>32-16-4-3-27-13-12-25-14-17-18-15-2-29-30-31-43-39-41-54-51-52-38-55-56-57-64-65-66-67-68-69-70</t>
+          <t>136-149-152-153-154-167-128-102-114-101-127-165-163-151-150-137-135-111-100-86-99-98-126-125-123-109-96-97-84-83</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -16054,23 +16054,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-85-99-89-102-87-100-96-109-111-112-115-152-141-127-128-125-139-140-165-151-137-150-122-161-162-149</t>
+          <t>112-99-85-87-100-139-140-128-141-115-89-102-125-137-151-152-162-150-149-165-127-111</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0-1-3-5-18-15-17-14-25-27-26-64-39-40-42-54-51-52-53-43-31-56-67-68-70</t>
+          <t>18-33-21-8-22-63-50-47-46-5-7-6-34-59-70-72-58-45-73-74-61-37-48-9-11-24-60-32-31-19</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>77-78-79-81-82-92-91-90-93-95-108-107-118-103-117-116-130-142-131-144-145-160-147-155-156-158-146</t>
+          <t>25-39-52-26-15-42-56-68-79-64-51-54-43-27-1-14-3-17-67-78-77-53-40-0</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -16078,11 +16078,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6-7-8-9-11-34-21-22-46-32-33-19-59-58-45-47-48-50-37-24-63-61-60-72-73-74</t>
+          <t>118-145-160-161-147-146-158-156-117-93-95-83-82-91-92-122-109-96-81-107-108-131-144-116-103-90-142-155-130</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -16152,15 +16152,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-91-93-94-95-103-105-107-108-109-119-118-116-120-121-130-131-132-133-157-155-142-143-145-146-134-135-148-161-159-158</t>
+          <t>107-95-94-93-119-143-116-155-158-133-132-145-157-131-120-121-108-134-159-146-91-90-103-105-118-130-142</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-9-10-11-24-34-21-22-20-33-19-35-48-63-50-49-75-58-59-60-47-61-72-73-74-45</t>
+          <t>65-64-51-69-57-70-54-41-52-53-42-29-55-82-81-79-66-67-68-56-43-30-17-3-14-28-38-25-26</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -16168,7 +16168,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84-85-86-88-89-102-99-100-98-110-111-113-127-115-124-126-128-114-151-150-136-152-154-162-163-164-166-167</t>
+          <t>34-19-20-5-6-45-59-49-88-89-75-9-11-10-24-50-63-73-72-47-22-21-48-35-61-74-60-58-33</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -16176,11 +16176,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>43-30-17-3-26-25-14-29-28-41-42-38-51-52-53-54-55-56-57-64-65-66-67-70-69-68-79-81-82</t>
+          <t>85-86-84-100-164-166-154-162-135-136-110-109-150-161-163-151-152-115-114-102-124-148-111-99-128-167-127-126-113-98</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -16250,15 +16250,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>91-78-92-94-95-103-104-105-121-107-120-118-106-116-129-130-131-132-146-155-143-134-147-159-157-142</t>
+          <t>130-131-95-94-132-134-121-120-107-106-92-78-91-118-146-147-159-143-157-155-142-129-105-104-103-116</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-7-21-9-10-23-24-36-33-34-32-46-60-48-50-49-61-62-73-75-76-85-84-86-87-88-89</t>
+          <t>40-13-12-25-38-28-27-52-41-3-17-5-56-68-57-83-80-55-54-66-53-31-44-69-42-1</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -16266,19 +16266,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>83-98-100-102-109-110-111-113-114-115-123-124-126-127-128-135-136-137-138-139-140-141-148-149-150-151-152-153-167-162-163-164-165-166-154</t>
+          <t>10-24-60-84-85-73-86-87-61-34-23-21-48-75-89-76-62-49-36-50-88-46-33-32-6-7-9</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>135-163-114-111-98-124-136-137-164-151-150-109-123-110-127-139-126-113-128-140-141-138-162-152-153-154-102-100-115-167-166-165-148-149</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>17-31-5-28-27-1-3-13-12-25-38-40-41-80-66-52-53-54-55-56-57-44-42-69-68</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -16348,7 +16348,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>102-87-100-97-86-110-111-112-113-115-127-124-125-123-138-139-140-167-152-150-149-165-154-141</t>
+          <t>150-124-111-97-87-100-138-139-165-152-140-141-154-167-127-112-86-110-123-149-125-113-102-115</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -16356,7 +16356,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8-6-32-10-11-21-22-23-9-34-46-58-45-50-37-62-61-73-71-60-74-76</t>
+          <t>62-74-76-50-6-21-46-60-10-11-37-23-61-73-71-58-45-32-34-22-9-8</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -16364,19 +16364,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>96-83-69-81-82-79-78-91-105-90-116-118-119-120-144-129-130-131-132-134-121-146-147-161-155-156-158-159-148</t>
+          <t>1-27-40-39-68-69-57-43-31-18-15-28-26-0-13-25-12-67-53-41-17-16-29-42</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-13-12-1-15-16-17-39-25-26-27-28-29-31-18-40-41-42-43-57-67-68-53</t>
+          <t>96-130-118-105-79-91-90-78-81-121-132-144-155-116-129-119-131-156-159-158-161-148-134-146-147-120-82-83</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -16446,31 +16446,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>100-101-114-115-128-153-154-167-166-152-151-150-162-164-140</t>
+          <t>92-91-142-143-156-157-144-131-105-93-117-116-103-135-161-122-109-95-120-133-108-94-147-160-146-145</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19-18-6-7-33-21-34-46-32-22-10-36-37-24-49-57-58-60-85-73-76-84-70-87-88</t>
+          <t>40-25-38-26-14-0-15-57-56-70-81-82-68-66-64-77-80-55-43-54-53-16-3-28-30-42-39</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>80-81-109-146-91-92-93-94-82-97-95-122-110-108-105-116-103-131-117-120-136-135-144-143-142-145-161-160-156-157-147-133</t>
+          <t>34-22-7-21-46-58-32-18-19-33-60-73-76-49-37-24-36-10-6</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-14-3-15-38-25-26-28-30-16-39-40-42-43-68-54-55-56-53-66-64-77</t>
+          <t>115-87-97-84-85-88-101-114-154-167-166-164-151-162-150-136-110-100-140-152-153-128</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -16544,15 +16544,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>97-98-99-101-102-112-111-109-113-122-123-127-139-135-136-137-138-128-141-154-151-152-150-161-162-163-164-166-167</t>
+          <t>104-91-93-92-83-82-134-160-161-135-122-156-157-158-159-147-109-95-121-133-132-105-106-107-120-118-103-116</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>9-10-19-20-22-23-24-49-33-34-35-36-37-45-47-32-58-71-63-61-60-72-89-76-87-86</t>
+          <t>77-79-53-40-17-2-0-1-14-25-12-26-41-29-42-30-43-68-67-54-28-38-39-65-66-56-69-27-16</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -16560,19 +16560,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>77-79-91-92-105-103-104-93-107-106-116-118-120-121-147-133-134-132-156-157-158-159-160-95</t>
+          <t>76-63-23-24-37-10-9-35-22-45-58-32-19-20-34-36-61-47-72-71-60-49-33-31-44-70</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2-1-0-12-14-39-38-25-26-27-28-29-30-31-16-53-40-41-42-43-44-17-56-54-65-66-67-68-69-70-83-82</t>
+          <t>128-138-139-166-154-167-164-163-123-111-112-137-151-152-150-162-136-141-127-101-99-86-97-98-89-102-87-113</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -16642,35 +16642,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-91-93-94-95-106-105-104-103-116-118-120-121-147-133-131-130-143-145-146-159-158-156-157-155-129</t>
+          <t>90-103-155-143-116-81-106-156-145-146-147-133-95-93-78-77-104-105-91-129-130-157-159-158-131-94-82-121-120-118</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-8-9-10-11-24-47-45-18-31-32-33-34-35-23-21-46-49-37-50-63-62</t>
+          <t>45-46-34-33-6-32-8-10-24-37-62-74-72-21-9-11-23-50-63-49-35-47-73-76</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>72-73-74-76-83-84-85-86-87-88-96-97-109-99-102-98-111-112-115-114-122-123-126-127-128-138-139-149-151-152-154-164-167</t>
+          <t>17-4-3-1-31-18-5-66-65-38-39-13-27-70-57-44-52-26-12-25-64-53-40-28-41-68-67-14</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>152-139-86-97-88-87-99-98-127-128-167-154-102-114-115-83-96-122-109-138-111-123-149-164-151-84-85-112-126</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1-3-4-12-13-38-52-25-26-28-27-14-39-40-41-44-17-53-77-64-65-66-67-68-82-81-78-57-70</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -16740,31 +16740,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77-90-91-78-80-95-94-92-103-104-106-107-108-121-118-120-116-129-130-146-160-133-132-131-155-156-157-142</t>
+          <t>108-95-82-80-107-133-146-160-131-118-103-90-92-104-130-116-106-121-94-120-132-157-129-156-155-142-78-91-77</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-7-20-21-22-24-76-61-33-34-48-49-50-62-59-45-58-71-72-73-46</t>
+          <t>50-24-49-89-88-86-57-70-71-84-83-44-22-48-62-76-61-72-58-20-45-46-59-73-85-34-33-21-7-6</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84-85-89-88-86-97-98-111-112-114-101-100-115-128-122-123-110-135-125-127-137-139-141-148-149-150-151-154-161-162-163-164-167</t>
+          <t>54-68-56-67-65-53-52-40-14-13-0-51-64-26-25-27-30-31-17-16-43-42-29-5-4-3-2</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>16-2-3-4-5-17-14-13-0-25-26-27-44-30-31-29-42-40-64-51-52-53-65-56-57-43-54-67-68-70-82-83</t>
+          <t>111-112-101-114-128-167-154-141-163-149-135-148-161-110-97-100-125-150-123-122-137-139-127-115-162-164-151-98</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -16838,35 +16838,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>87-84-85-98-100-101-102-114-113-112-123-125-126-127-128-152-139-140-141-154-167-153-138-150-162-164-151</t>
+          <t>92-90-142-159-120-119-157-156-130-118-132-146-134-95-108-122-109-106-104-129-161-160-147-133-121-107-81-83-96-91</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>42-28-14-13-12-54-55-67-79-66-65-51-52-40-27-25-39-26-38-78-70-80-17-3-16-41</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>37-49-60-45-32-31-19-7-21-48-61-62-75-50-36-23-22-9-10-11-35-58-72-46-33-20</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>7</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>25-12-13-3-16-17-14-28-27-26-40-39-54-41-42-55-52-38-51-65-79-66-91-78</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>147-81-83-80-67-92-95-96-106-104-107-108-109-118-119-120-121-97-122-146-130-132-133-136-134-142-129-90-156-157-159-160-161</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>7-9-10-11-23-20-21-22-19-31-32-33-35-36-37-72-46-48-49-50-75-60-61-62-70-45-58</t>
+          <t>125-123-126-140-141-128-138-151-150-136-162-152-164-153-139-113-87-101-102-167-154-127-97-84-85-98-112-114-100</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -16936,7 +16936,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-91-92-95-96-131-105-107-108-109-117-118-119-132-121-122-129-130-103-145-134-161-144-120-146-147-142-155-156-157-158-159-160-148</t>
+          <t>91-157-148-147-160-161-144-131-92-105-118-103-120-108-134-121-122-109-156-155-142-107-95-96-119-130-132-117-145-159-146-158-129-90</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -16944,27 +16944,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-7-9-36-22-31-18-57-47-49-50-63-37-62-74-73-72-71-85-84-59</t>
+          <t>25-38-64-78-15-14-40-52-26-29-30-5-31-56-79-65-39-28-43-54-51-77-13-0-18-57-68-82-81-16</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>36-37-50-62-63-85-84-71-59-47-6-7-9-22-49-89-88-74-73-72</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>111-125-139-138-137-136-162-165-166-167-154-102-114-115-127-113-128-141-153-152-151-163-99-98-124-97</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>88-89-99-98-97-124-111-113-114-115-102-141-128-127-136-137-138-139-125-154-152-153-151-162-163-165-166-167</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0-13-14-15-16-43-30-28-29-51-38-39-40-26-25-52-54-56-68-82-64-77-78-79-81-65</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -17034,35 +17034,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84-87-86-97-98-99-100-102-115-113-114-112-123-124-125-127-128-136-137-139-140-149-150-164-153-151-163-162-165-166-167</t>
+          <t>96-109-123-166-165-113-100-125-99-97-137-150-149-139-151-164-162-163-135-161-84-86-98-87-102-115-112-124-136-114-140-153-167-127-128-83</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-7-8-9-10-11-19-20-21-22-23-24-32-4-35-61-45-46-48-49-50-37-62-63-71-72-74-75-76</t>
+          <t>49-75-76-48-46-45-72-71-32-19-6-9-10-24-11-21-20-50-63-62-74-61-37-8-7-22-35-23</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>105-91-79-92-93-94-120-108-95-83-96-109-104-118-119-121-161-130-132-133-135-145-144-147-146-143-155-157-117</t>
+          <t>13-26-39-40-54-42-28-43-44-30-29-17-4-15-1-0-67-53-65-51-25</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>15-1-0-13-39-25-26-40-29-30-17-28-42-43-44-67-54-53-51-77-65</t>
+          <t>119-143-155-130-145-157-144-132-118-117-94-95-120-147-146-133-121-108-77-104-91-79-92-105-93</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -17132,15 +17132,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-91-92-93-94-108-106-104-103-116-129-117-118-132-133-158-157-143-156-155-142</t>
+          <t>106-121-108-94-91-90-117-116-142-155-156-157-158-143-129-132-133-118-103-104-92-93</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11-8-21-6-18-19-20-9-23-24-59-34-35-49-48-58-57-31-46-60-75-76</t>
+          <t>77-64-53-68-81-82-43-30-14-0-12-16-29-42-55-78-66-79-39-38-25-26-67</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -17148,19 +17148,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>110-84-85-86-96-97-98-100-101-102-83-111-141-154-164-112-113-124-127-128-115-137-138-153-139-122-148-149-135-121-123-161-162-150</t>
+          <t>20-21-46-35-23-9-8-31-44-18-6-19-58-70-34-48-49-24-11-60-75-76-59-57</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>98-112-113-127-141-128-101-86-111-138-164-124-96-83-110-137-97-122-149-150-162-139-100-102-115-154-153-161-148-135-123-85-84</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>25-26-12-0-14-16-29-30-38-39-55-44-43-42-53-66-68-70-67-64-77-78-79-81-82</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -17230,35 +17230,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>87-101-102-124-112-113-114-123-122-110-139-127-138-125-164-162-149-150-151-167-154-141-140-165-152</t>
+          <t>138-151-167-84-85-113-114-127-165-102-89-101-97-110-109-96-83-87-125-124-112-123-150-164-154-141-140-139-152-162-149-135-148-122</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>14-13-66-69-17-1-26-40-39-38-51-65-25-0-12-29-42-43-56-41-27</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>45-58-44-57-9-11-50-49-23-5-18-7-33-74-63-62-73-60-59-34-35-21-46</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>7-9-21-11-23-35-34-33-44-45-46-49-50-63-57-58-59-60-62-89-73-74-83-84-85-97-5</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>91-92-93-94-96-109-107-106-105-119-121-142-129-130-131-103-51-133-135-132-144-145-146-148-155-156-158-159-160-161</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-13-12-14-17-18-29-27-26-25-38-39-40-41-42-43-56-69-66-65</t>
+          <t>144-132-145-158-146-93-92-105-103-91-142-159-160-161-121-133-131-130-155-156-119-106-94-107-129</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -17328,35 +17328,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>117-90-91-94-69-95-103-105-106-107-108-109-122-82-96-121-119-133-155-142-143-144-145-146-134-159-160</t>
+          <t>82-96-95-91-77-90-142-160-159-146-78-107-103-155-143-117-105-106-119-122-134-145-144-133-121-109-108-94</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-8-24-10-18-19-21-9-33-32-31-34-36-37-46-61-49-48-44-57-59-45-72-63-76-75-62</t>
+          <t>32-46-48-34-33-19-6-8-21-72-75-63-76-62-49-61-36-37-9-10-24-59-45</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>97-98-89-127-99-115-101-88-102-114-113-124-125-84-150-136-137-139-140-153-128-141-162-163-164-165-166</t>
+          <t>41-65-56-69-31-17-18-4-5-44-57-29-38-51-39-40-27-14-2-0-12-13-28-42-54</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>51-38-12-13-14-0-2-4-29-28-40-39-27-17-54-56-42-41-65-78-77</t>
+          <t>136-124-98-84-115-127-166-165-99-113-101-89-88-102-114-140-141-128-97-137-162-163-150-164-153-139-125</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -17426,35 +17426,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>81-82-91-92-93-106-68-96-83-107-108-109-116-117-118-119-161-121-120-130-131-132-133-142-143-144-160-148-155-158-146-110-122</t>
+          <t>148-109-122-121-119-92-93-131-133-120-106-107-96-108-132-155-142-90-91-103-116-117-118-144-158-161-130-143-146-160</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-5-4-18-30-46-23-24-8-19-33-70-58-43-44-32-47-49-35-60-63-72-84-74-75-76-34</t>
+          <t>52-66-40-2-0-25-38-51-64-78-67-39-26-4-30-15-29-43-54-81-68-82-80-65</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>88-89-101-99-97-128-115-113-114-112-125-124-136-137-138-140-154-153-150-162-164-165-166-167</t>
+          <t>18-24-35-58-70-44-46-49-23-8-19-6-5-32-72-83-84-75-74-60-76-63-47-34-33</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-2-15-25-26-51-38-39-40-29-54-52-64-65-66-67-80-78-103-90</t>
+          <t>166-167-153-140-138-124-110-97-113-137-165-164-162-125-112-99-101-88-89-115-128-154-114-150-136</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -17524,35 +17524,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>103-90-78-92-93-94-79-105-118-108-131-117-130-147-121-134-107-119-133-129-143-144-145-146-159-155-156-157-116</t>
+          <t>131-107-94-81-80-133-147-108-93-90-78-79-105-118-134-121-117-130-145-146-159-157-155-129-116-92-119-103-156-144-143</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>62-48-6-19-33-11-10-34-46-58-75-74-7-8-21-20-35-36-50-61-60-87-88-89</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>21-20-8-10-11-7-19-6-33-34-35-36-46-48-87-58-60-61-50-62-75-89-88-74</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>7</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>122-97-98-99-100-115-112-113-109-96-123-124-125-126-127-128-141-136-137-138-139-152-148-149-135-166-154-167-163-150-165-164-161</t>
+          <t>17-3-16-29-42-27-40-39-38-41-68-69-55-31-70-5-4-2-15-28-64-67-12-14</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>128-115-100-124-109-99-96-97-123-148-161-164-154-167-166-163-149-135-136-165-152-150-138-127-126-113-112-98-122-137-125-141-139</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>12-3-5-4-2-14-15-16-17-31-29-28-27-40-38-39-41-42-55-81-67-68-69-70-80-64</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -17622,35 +17622,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>91-90-92-93-94-108-107-117-116-104-120-133-131-130-129-142-143-159-155-156-157-158-146</t>
+          <t>90-104-116-146-157-129-156-131-158-159-93-107-108-133-143-155-142-130-117-78-79-92-120-94-91</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-18-20-21-32-23-22-34-35-36-37-49-47-46-45-44-57-58-61-62-63-70-71-72-75-76</t>
+          <t>61-75-102-89-85-71-84-58-47-35-23-76-63-22-34-32-45-36-37-49-62-46-72-86-88-87-20-21</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>69-82-70-43-56-0-1-27-3-16-5-2-18-57-44-30-28-53-66-52-64-65-39-40-55-54-38-81</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>139-126-127-154-153-96-109-125-112-100-99-114-165-163-122-135-136-151-152-164-161-148-123-137</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>84-85-86-87-88-89-102-99-100-96-161-148-136-122-123-114-126-112-135-137-127-139-125-151-152-153-154-165-163-164-109</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1-0-2-3-16-30-28-27-38-39-40-66-52-53-54-55-43-56-78-64-79-65-81-69-82</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -17720,7 +17720,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>79-78-80-92-93-94-95-103-104-105-106-108-121-117-130-116-129-119-133-134-145-143-159-147-155-156-157-158-146</t>
+          <t>117-155-143-130-80-108-93-146-133-145-147-134-121-95-82-94-105-103-78-92-106-79-116-129-156-158-159-157-119-104</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -17728,27 +17728,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7-6-8-11-23-22-20-32-45-59-60-47-48-49-50-61-35-46-58-72-73-76-75</t>
+          <t>59-60-48-35-11-50-76-72-45-6-32-58-73-75-61-49-22-8-20-47-23-7-46</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84-85-86-87-96-97-98-99-100-101-102-115-111-112-114-113-110-122-123-125-126-127-136-150-149-140-153-164-138-128-141-154-161-162-148-166-167</t>
+          <t>27-42-44-57-70-28-5-31-29-2-1-12-38-65-64-51-67-68-56-43-16-40-41-15-14-0-26</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-2-5-31-16-15-12-26-27-28-29-14-38-40-41-42-43-68-57-44-51-64-65-67-82-70-56</t>
+          <t>85-138-150-112-113-98-110-97-86-84-115-102-154-167-166-126-149-162-125-153-164-161-148-136-122-87-100-101-96-123-111-141-114-140-127-128-99</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -17818,31 +17818,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84-83-96-98-99-100-101-115-114-113-122-123-124-125-126-127-136-137-148-149-161-162-151-152-163-164-166</t>
+          <t>88-89-114-113-127-100-84-124-162-163-151-164-149-98-86-99-126-125-137-136-123-122-110-96-83-152-166-115-101</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0-1-2-4-5-12-13-14-16-17-18-28-38-25-26-39-40-55-69-42-66-65-52</t>
+          <t>61-46-59-73-75-76-74-49-23-11-50-63-62-7-6-18-5-33-8-24-37-47-32-70-58-45-35</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>77-79-80-81-110-108-92-93-94-95-121-107-120-132-118-91-105-130-129-142-143-131-117-144-156-147-160-145</t>
+          <t>25-12-26-1-2-13-14-28-39-52-65-77-38-0-4-17-16-42-55-69-66-40</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>6-7-8-11-23-24-37-33-35-32-45-46-47-49-50-58-70-61-62-63-73-59-74-75-76-89-88-86</t>
+          <t>132-131-130-143-144-145-148-161-95-91-105-80-81-108-121-147-120-118-92-79-94-107-160-156-142-129-117-93</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -17916,35 +17916,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77-78-81-82-93-91-103-90-106-92-105-95-107-108-118-117-116-130-132-133-134-142-143-155-146-145-158-159-160</t>
+          <t>158-159-146-108-107-95-92-78-91-142-116-117-130-105-118-143-155-160-133-103-82-81-106-93-134-145-132-90-77</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-4-0-12-13-14-16-17-18-26-27-30-31-44-54-40-41-39-51-38-53-55-57-64-65-66-68-69</t>
+          <t>19-37-49-62-34-46-45-60-73-63-75-74-24-36-48-47-59-71-20-21-11-23-22-6</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>97-86-88-84-98-99-100-101-115-102-113-114-112-122-123-124-125-126-151-137-152-139-140-141-127-135-162-163-165-166-167</t>
+          <t>12-26-40-51-38-39-69-68-55-30-17-5-0-13-14-16-54-66-65-64-53-41-57-44-31-4-18-27</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>45-6-19-20-21-22-23-24-34-36-37-11-46-47-48-49-59-60-62-63-75-73-74-71</t>
+          <t>125-140-127-141-139-124-165-166-167-162-135-137-102-86-97-122-123-163-151-152-114-88-101-115-113-100-98-99-126-112-84</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -18014,15 +18014,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-84-100-87-88-89-96-97-98-99-85-109-110-112-115-123-124-125-135-136-137-138-140-139-149-150-151-154-165-166-167</t>
+          <t>95-108-120-104-90-105-93-116-129-142-130-134-147-131-143-155-144-157-158-159-161-160-146-132-119</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>50-10-9-8-19-7-22-23-24-21-45-32-35-48-49-47-58-60-71-72-73-74-75-76</t>
+          <t>49-35-21-7-8-9-23-60-48-24-10-22-19-32-47-75-73-72-71-58-45-74-50-76</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -18030,19 +18030,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>77-90-116-104-105-95-108-120-132-119-130-131-129-155-142-143-159-146-147-134-144-157-158-160-161</t>
+          <t>82-70-69-81-57-56-67-68-40-17-44-83-43-2-0-26-77-53-39-15-31-42-13-25-27-16-4-3-64-80-55-41-28-29</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-2-3-4-13-15-16-39-25-26-27-28-29-31-17-40-41-42-43-44-53-55-56-57-80-67-68-69-70-82-81-93-64</t>
+          <t>123-149-112-88-89-138-150-135-137-167-166-154-115-139-125-140-98-110-124-165-151-136-109-96-97-85-99-87-100-84</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -18112,7 +18112,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>81-80-104-90-91-93-94-95-96-83-109-108-129-117-118-119-131-121-107-120-133-134-148-146-155-156-160</t>
+          <t>162-148-136-139-126-125-137-151-164-152-163-150-138-154-127-115-101-99-111-112-140-141-166-165-124-110</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -18120,7 +18120,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19-6-10-11-9-20-21-22-23-37-36-47-46-48-72-59-60-63-76-50-89-75-71-84-85-87-73</t>
+          <t>37-36-50-63-72-46-84-85-71-47-22-23-9-10-11-21-6-19-20-48-76-89-75-87-73-60-59</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -18128,19 +18128,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>99-101-115-127-126-125-124-110-112-111-137-136-138-139-154-141-140-166-152-151-163-162-164-165-150</t>
+          <t>14-52-65-66-70-56-42-17-4-29-57-54-68-55-15-27-39-64-51-12-13-0-1</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>14-15-39-12-13-0-1-17-42-52-51-27-4-29-56-55-70-54-64-65-66-68-57</t>
+          <t>90-104-119-146-156-117-131-121-108-109-95-81-94-93-120-107-96-83-80-91-118-160-134-133-155-129</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -18210,15 +18210,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84-88-89-102-100-99-110-112-137-125-126-115-167-154-152-151-138-141-128-140-139-161-149-136</t>
+          <t>161-159-105-120-134-107-119-104-103-129-130-145-118-117-91-90-92-109-155-143-131-135-122</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-18-7-8-9-10-11-6-20-23-22-21-32-34-35-36-46-47-48-49-50-63-59-58-62-74-73-75-76</t>
+          <t>48-63-50-49-23-62-76-74-75-9-11-10-36-35-34-21-22-59-73-47-8-7-20-6-32-46-58-5-18</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -18226,19 +18226,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>90-78-91-103-104-119-117-105-107-122-109-120-134-135-159-131-118-130-143-145-155-129</t>
+          <t>25-38-51-70-57-43-29-41-56-42-40-53-67-64-77-52-26-78-79-80-83-81-69-65-12-1-15-17-4-2</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2-1-25-12-15-17-4-56-29-43-42-41-40-26-51-52-53-38-64-77-92-67-69-70-57-65-79-80-81-83</t>
+          <t>112-152-154-141-102-115-128-167-151-138-139-140-125-126-137-136-149-110-84-89-88-100-99</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -18308,7 +18308,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84-85-86-97-96-99-100-102-109-110-111-127-113-114-115-123-124-125-126-112-152-136-137-151-140-141-139-165-162-163-135-83</t>
+          <t>109-135-139-165-152-102-141-114-100-84-97-112-99-140-115-127-113-126-151-111-124-125-163-162-136-137-123-96-85-86-110</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -18316,7 +18316,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>50-23-19-32-45-46-35-36-37-24-7-21-49-58-59-72-62-63-61-74-76-88-89</t>
+          <t>36-24-50-63-76-89-88-62-49-46-72-37-23-21-32-45-58-59-7-19-74-61-35</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -18324,19 +18324,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>116-104-105-106-94-107-119-118-131-130-129-142-143-144-146-159-157-156</t>
+          <t>69-81-41-17-31-44-43-27-26-3-30-0-14-29-52-53-70-83-82-55-42-67-40-39-38-54-66-78-80-68-56</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>14-42-41-17-29-27-26-53-30-31-44-39-40-54-43-38-52-90-77-55-56-66-80-81-69-70-82-78-67-68-3-0</t>
+          <t>116-129-105-106-118-159-146-143-156-142-130-131-104-90-77-94-107-119-144-157</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -18406,35 +18406,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>114-88-98-99-100-102-115-112-124-126-141-128-139-138-151-163-150-137-152-153-167-165-127</t>
+          <t>139-151-167-141-153-114-115-76-138-137-124-126-100-84-98-112-88-89-102-99-127-128-152-163-150-165</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>73-50-34-33-45-19-20-10-37-36-35-47-9-8-6-5-18</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>12-25-51-38-26-53-66-67-30-42-4-14-64-77-65-27-2-3-17-55-54-39-41-81-82-83-68-80-43-13-0</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>143-130-131-117-133-148-135-122-120-132-119-92-93-104-91-90-103-142-146-156-157-160-159-147</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0-2-4-3-17-26-14-13-25-12-27-41-38-51-55-42-43-39-53-54-77-64-65-66-67-68-30</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>80-81-83-82-47-84-90-103-93-92-91-104-117-119-120-122-130-131-132-133-135-142-143-146-147-148-156-157-159-160</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>5-6-8-9-10-20-19-18-33-34-35-36-37-50-76-89-73-45</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -18504,23 +18504,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-84-96-88-74-89-87-98-115-102-100-110-111-112-138-124-99-135-136-137-127-139-162-148-149-153-141-163-165-166</t>
+          <t>163-136-137-124-138-149-96-83-84-165-166-153-98-110-99-87-88-102-127-111-100-112-115-89-141-139-162</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-20-9-10-7-19-21-22-23-24-31-32-33-34-35-36-63-75-37-50-47-60-59-58-46-70-71-45</t>
+          <t>7-50-63-24-10-9-22-37-36-46-47-35-60-59-71-31-5-19-32-34-23-20-21-74-75-58-45-33</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>104-80-81-91-90-79-93-94-95-82-106-105-119-107-108-120-118-103-116-129-130-132-134-158-144-145-146-147-155-142</t>
+          <t>68-66-79-51-0-40-26-25-12-13-39-53-54-41-17-3-15-1-14-29-42-56-80-67-64-65-55-70</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -18528,11 +18528,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-14-12-13-15-3-17-25-26-29-42-41-40-39-51-64-54-68-56-53-65-66-67-55</t>
+          <t>82-95-135-148-104-103-116-130-155-158-134-146-145-90-105-94-81-142-129-118-120-119-107-108-147-132-144-106-93-91</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -18602,15 +18602,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-91-92-93-94-96-109-107-108-106-116-117-121-122-133-132-131-155-144-146-147-148-160-159-158-157-142</t>
+          <t>108-96-93-91-90-131-155-157-132-144-158-146-106-94-133-109-122-148-147-159-160-121-92-117-142-116-107</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>45-5-7-8-20-33-32-47-34-50-36-22-59-57-60-63-87-71-72-73-74-75-84-83-85-86-70</t>
+          <t>43-29-28-14-27-13-12-1-2-4-16-53-65-52-38-17-42-55-68-82-81-67-77-51-39-78-79-69-80</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -18618,19 +18618,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>126-125-112-102-115-123-124-111-114-127-128-141-140-137-149-153-154-163-162-164-165-166</t>
+          <t>60-33-32-5-45-59-87-86-36-75-63-50-20-7-8-22-70-83-72-57-71-85-74-73-84-34-47</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>16-17-2-12-13-14-1-4-27-28-29-43-55-42-38-51-52-53-39-65-67-68-69-77-78-79-80-81-82</t>
+          <t>140-154-166-153-115-102-114-126-165-164-124-125-111-112-123-137-149-162-163-141-128-127</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -18700,7 +18700,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>113-114-102-89-115-99-100-87-109-110-111-72-84-98-122-123-125-127-128-136-138-141-149-150-151-152-161-162-163-164-165-167</t>
+          <t>114-113-115-102-89-100-136-161-122-109-96-84-125-150-164-163-127-152-138-151-162-149-128-141-167-165-123-110-98-111-87-99</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -18708,27 +18708,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-7-8-22-23-11-24-37-36-35-48-34-46-60-61-74-75</t>
+          <t>2-1-28-30-70-56-57-95-80-81-82-69-64-65-78-79-54-68-42-52-40-26-16-29-3</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>93-92-90-78-105-129-117-116-160-147-108-121-96-118-144-130-142-119-134-159-143-155-156-157-145-120</t>
+          <t>11-24-23-22-46-18-5-6-7-8-34-58-72-71-60-48-74-75-61-35-37-36-20</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1-2-3-5-20-58-16-18-57-28-26-52-40-42-30-54-56-29-64-65-68-69-70-71-95-79-80-81-82</t>
+          <t>134-121-160-147-159-145-155-142-143-156-157-144-120-119-105-90-92-108-93-118-117-116-129-130</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -18798,15 +18798,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-82-91-92-93-94-96-104-105-107-121-120-119-118-116-155-142-134-135-132-146-147-148-161-159-131</t>
+          <t>159-119-94-92-91-116-104-142-155-131-118-132-146-147-134-121-82-83-96-107-93-80-79-105-120</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24-7-8-10-11-18-20-21-5-46-45-33-50-36-23-48-47-34-32-58-59-61-62-63-76</t>
+          <t>33-21-46-59-11-24-10-34-47-48-62-61-63-88-87-45-32-58-76-50-23-36-8-20-7</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -18814,19 +18814,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>125-87-88-85-100-101-102-128-114-126-124-111-123-97-136-137-138-139-162-149-150-151-166-153-141-163-165-152</t>
+          <t>25-55-69-57-15-0-14-41-54-26-51-65-64-52-53-66-68-67-29-18-5-3-1-12</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>29-15-3-0-14-1-25-12-26-53-51-52-41-57-55-54-64-65-66-67-68-69-79-80</t>
+          <t>135-163-149-148-161-162-166-165-141-102-101-100-128-153-152-139-138-97-136-111-85-124-125-126-114-151-150-137-123</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -18896,31 +18896,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>96-83-86-85-98-100-101-121-50-37-112-114-115-125-122-163-124-137-123-136-165-162-134-147-107-108-149-151-148-160-161-153-140-111</t>
+          <t>142-145-108-121-120-93-81-134-104-117-130-90-91-92-107-131-159-160-147-157-119-118-116-156-155</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0-1-2-4-3-14-13-12-26-39-27-29-41-40-51-52-55-56-67-65-64</t>
+          <t>56-55-67-41-52-65-78-64-40-14-13-26-3-4-29-27-12-0-2-1-39-51-77-79</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>81-79-78-77-90-91-92-93-104-116-117-118-119-120-145-131-130-142-155-156-157-159</t>
+          <t>70-48-49-37-22-24-11-50-63-47-46-10-9-8-7-57-58-31-20-6-32-60-62-76-61-71-59-33-19-5</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5-6-7-8-9-10-11-19-20-22-24-31-57-33-46-70-47-48-32-58-59-60-61-49-62-63-76-71</t>
+          <t>85-86-151-124-136-122-161-162-111-112-96-83-100-101-115-114-98-165-163-123-148-149-137-125-140-153</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -18994,23 +18994,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>79-92-131-130-116-103-105-107-106-109-121-120-119-118-93-81-94-95-134-147-144-145-146-160-157-156-143</t>
+          <t>130-145-160-82-93-92-106-79-81-95-109-144-146-157-156-147-134-121-94-107-120-131-105-118-119-103-116-143</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>38-40-26-14-1-28-3-5-30-43-56-54-27-16-4-18-17-44-29-41-52-67-57-69</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>24-9-8-22-19-32-34-36-62-49-48-61-59-60-58-46-71-84-85-89-102-75</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>7</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>98-99-74-110-111-112-113-114-115-123-124-125-126-127-136-137-139-140-141-154-152-153-150-162-163-164-165-166-167</t>
+          <t>71-74-75-61-59-32-19-34-46-60-48-62-49-36-9-83-84-85-89-24-22-8-58</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -19018,11 +19018,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1-3-4-5-18-16-17-14-26-27-28-29-30-41-38-40-54-44-57-43-56-52-67-83-82-69</t>
+          <t>141-166-152-124-137-163-150-136-162-165-164-153-140-114-102-115-127-113-112-111-99-98-110-125-167-154-139-126-123</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -19092,31 +19092,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>97-96-94-90-103-104-105-107-108-118-129-130-131-132-134-135-148-161-146-143-155-156-157-145</t>
+          <t>107-94-108-145-143-157-156-155-146-134-132-131-130-90-78-105-118-129-103-104</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-7-9-11-10-35-22-33-19-45-48-62-49-50-58-59-60-46-72-73-75-76</t>
+          <t>5-19-6-57-70-58-59-72-45-44-46-60-85-83-73-48-35-7-9-62-75-76-49-11-50-31-33-22-10</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>85-87-88-89-101-99-111-112-114-115-128-141-127-125-136-149-151-138-152-164-165-167-153-126</t>
+          <t>28-52-39-26-13-15-17-43-54-53-40-65-51-0-14-69-68-67-55-30-42-56-29-16-3-2-1</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-2-3-5-13-14-15-16-17-44-30-31-28-29-42-40-39-68-56-69-52-53-65-55-43-57-54-67-26-70-83-78-51</t>
+          <t>96-112-99-161-165-153-101-89-115-141-167-128-126-114-125-111-97-88-87-138-151-149-148-136-127-152-164-135</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -19190,35 +19190,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>85-86-87-88-97-98-99-100-102-115-114-112-123-125-126-127-128-140-153-149-150-151-152-141-154-162-163-164-165-167</t>
+          <t>125-164-165-141-114-99-123-150-136-149-162-151-88-102-128-126-153-97-98-85-86-87-100-112-163-154-167-152-140-127-115</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4-1-0-12-25-13-26-29-30-41-39-51-38-54-42-43-55-67-68-77-78-81-94-82-83</t>
+          <t>26-54-67-41-42-30-4-25-38-39-51-78-77-55-68-43-29-13-1-0-12</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>46-47-34-33-20-19-72-76-50-63-37-35-22-21-8-9-36-23-61-60-31-18-6-59-58-57-70</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>108-122-95-109-96-92-105-129-116-117-93-121-107-103-130-131-143-144-145-146-147-156-157-158-159-136-161</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>22-23-9-8-19-20-21-6-18-31-33-34-35-36-37-50-63-76-58-57-59-60-61-47-46-72-70</t>
+          <t>116-93-83-82-96-122-108-109-94-107-157-156-130-92-105-131-117-129-143-145-158-144-147-121-146-159-161-95-81-103</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -19288,7 +19288,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>86-85-87-89-102-114-101-112-110-98-97-123-124-125-127-128-141-137-136-149-150-164-153-154-152-167</t>
+          <t>85-101-114-153-97-110-123-136-137-124-98-125-152-154-141-167-164-150-149-112-102-128-127-86</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -19296,23 +19296,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-7-10-11-23-22-21-34-71-59-73-47-48-49-50-74-76-62-63-36-46-58-45</t>
+          <t>21-48-49-36-22-7-6-45-73-74-87-89-76-63-47-46-58-71-59-62-50-23-11-10-34</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>82-80-65-78-90-91-92-93-94-95-103-129-106-107-108-133-120-121-119-105-122-134-145-144-143-156-157-159-160</t>
+          <t>16-3-39-25-52-40-28-43-57-70-56-54-42-31-18-4-0-12-64-51-38-26-2-1-29-30-67-65-53</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-1-2-3-25-12-16-18-4-26-38-28-30-31-29-54-40-42-43-39-52-51-64-56-70-57-81-67-53</t>
+          <t>78-145-157-144-103-90-106-108-121-134-122-107-82-95-105-93-80-81-94-129-143-156-119-133-120-159-160-92-91</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -19386,7 +19386,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>102-89-85-97-110-100-88-99-111-113-126-124-115-127-128-136-138-139-140-141-149-150-152-154-162-163-165-166-167</t>
+          <t>97-127-139-165-166-154-140-100-102-113-88-85-89-136-149-163-162-150-111-99-115-126-138-152-167-141-128-124-110</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -19394,7 +19394,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>4-2-12-13-14-17-16-25-26-28-29-67-38-40-41-42-43-54-77-64-66-79-81-69-30</t>
+          <t>13-12-25-26-66-64-38-40-41-54-67-42-18-5-4-28-14-29-43-44-31-30-17-16-2-69</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -19402,19 +19402,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>135-94-93-103-90-107-96-109-133-118-119-120-121-122-105-129-116-131-134-146-143-144-130-155-156-157-158-161</t>
+          <t>11-24-48-61-73-60-7-10-37-9-33-32-46-59-74-75-76-49-22-21-19-20-63-50</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>5-7-9-10-11-22-33-20-21-18-44-31-32-19-37-24-50-48-49-46-59-60-73-74-61-75-63-76</t>
+          <t>79-131-103-105-77-90-130-129-155-143-146-121-93-81-107-133-116-156-144-158-157-161-135-94-120-118-119-134-122-96-109</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -19484,23 +19484,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84-97-98-99-100-101-102-140-113-114-138-122-124-125-126-128-115-154-165-148-135-164-153-149-161-162-163-151-111</t>
+          <t>148-149-126-151-165-164-153-154-138-124-97-84-99-125-113-87-101-100-162-163-161-122-135-128-115-102-114-140-98-111-96</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2-1-4-3-0-12-13-27-17-30-31-44-42-28-40-51-53-54-55-56-57-66-67</t>
+          <t>71-7-20-34-11-10-36-23-24-49-61-74-46-45-32-33-73-75-63-60-47-48-35-22-72</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>64-77-78-79-80-81-82-96-107-92-93-129-103-104-90-116-117-118-119-133-134-121-94-130-142-145-146-159</t>
+          <t>44-57-31-30-54-66-64-51-67-55-3-2-0-12-13-40-53-42-4-1-27-28-56-17</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -19508,11 +19508,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>20-7-22-10-11-23-24-36-35-34-33-32-45-46-47-61-48-49-75-63-71-72-73-74-87-60</t>
+          <t>116-129-90-104-119-133-134-145-142-130-94-107-93-80-81-82-118-121-146-159-103-117-92-79-77-78</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -19582,7 +19582,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77-79-103-90-91-93-94-95-80-104-105-106-107-108-117-118-119-120-121-147-145-133-142-143-156-131-129</t>
+          <t>91-103-129-133-120-93-80-121-108-79-77-90-105-147-145-156-142-118-106-94-95-107-119-143-131-117-104</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -19590,27 +19590,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7-8-9-10-11-24-20-19-23-21-32-33-34-35-36-37-50-63-62-74-73-72-59</t>
+          <t>63-50-37-36-62-74-35-34-19-32-59-73-72-21-9-7-8-23-24-11-10-20-33</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>85-98-87-101-102-96-110-148-161-122-124-126-127-139-138-149-166-141-115-140-167-153-154-151-135-123</t>
+          <t>82-83-70-69-56-66-51-15-28-54-68-27-0-16-3-2-39-40-53-42-43-4-17-31-44-57</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-2-3-15-4-16-17-42-28-27-39-44-31-43-40-51-53-54-56-57-66-68-69-83-82-70</t>
+          <t>140-127-115-102-139-154-167-166-151-141-126-85-110-122-124-138-153-149-148-161-135-123-87-101-98-96</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -19680,7 +19680,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77-78-90-92-93-95-103-105-118-129-106-117-119-130-116-132-120-134-142-143-144-146-147-156-157-158-160</t>
+          <t>77-78-92-105-90-103-118-119-134-120-143-129-142-130-146-147-160-158-132-106-93-116-144-156-157-95-117</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -19688,27 +19688,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>33-6-21-22-35-36-23-10-37-49-47-45-58-59-60-61-62-75</t>
+          <t>14-42-55-56-31-29-30-40-52-64-80-82-83-57-69-81-54-53-68-28-16-17-4-3-15-0-26-27-12-2</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>88-89-98-97-96-110-109-123-111-100-113-114-115-126-125-112-127-139-138-152-154-141-140-150-149-137-162-163-164-165</t>
+          <t>47-45-58-60-59-33-21-6-22-37-36-49-75-62-61-23-10-35</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>12-26-27-40-28-4-15-14-0-2-3-17-29-30-31-16-42-52-53-64-55-56-57-54-68-82-80-81-69-83</t>
+          <t>163-152-140-141-154-165-97-88-89-127-114-115-113-139-126-100-112-137-138-98-96-123-162-149-164-110-109-111-125-150</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -19778,15 +19778,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>101-88-89-97-98-99-87-110-111-113-114-115-141-138-137-126-139-140-152-149-150-151-123-163-164-165-166-167</t>
+          <t>137-123-111-98-99-87-88-89-114-141-140-152-164-138-126-113-139-151-163-165-166-167-110-97-149-150-101-115</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>58-7-9-11-21-35-31-18-5-16-44-45-71-60-50-37-59-47-61-62-63-72-46</t>
+          <t>52-28-14-0-1-2-30-69-67-56-55-16-3-26-12-13-25-64-65-66-80-79-91-90-77-82-41-53-54</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -19794,19 +19794,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>92-90-91-82-95-96-122-108-121-120-131-142-129-130-105-118-135-134-132-144-145-147-148-161-160-159-158</t>
+          <t>31-44-71-58-59-72-60-47-61-62-35-63-50-11-37-9-21-7-45-46-5-18</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>161-160-158-105-92-134-135-148-122-121-108-120-132-131-159-147-145-144-118-130-129-142-95-96</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>30-3-2-1-0-13-14-12-26-25-28-41-52-66-54-55-56-64-65-53-67-69-77-79-80</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -19876,35 +19876,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-91-93-94-95-120-106-107-108-117-132-121-133-131-130-104-129-142-143-144-145-146-147-155-156-157-159-160</t>
+          <t>108-106-117-159-160-120-132-147-146-133-129-144-157-145-155-156-143-142-130-131-79-93-107-121-95-94-81-80-104-77-90-91</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>14-0-13-1-15-16-17-29-27-26-39-52-65-53-55-56-64-51-77-79-81-69-80-67</t>
+          <t>8-20-19-71-84-72-62-23-45-32-47-21-22-35-60-83-61-49-63-88-75-48-59-58-34-46-6-44-70-86-73-74-76-36-9</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>13-0-15-29-16-5-18-17-69-56-27-26-39-52-53-14-1-55-67-65-64-51</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>8</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>111-98-100-101-109-110-97-112-113-114-115-154-123-124-126-127-122-135-137-139-141-128-153-150-149-151-148-161-162-164-165-166-167</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>161-148-135-151-127-115-114-101-128-154-141-153-110-109-97-124-137-165-167-139-126-113-111-98-122-123-149-150-162-164-166-112-100</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>5-6-8-32-18-19-20-21-22-23-9-34-35-36-44-45-46-47-48-61-74-59-60-49-62-63-83-71-72-73-88-75-76-86-84-70-58</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -19974,35 +19974,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>104-78-77-90-91-92-93-94-95-79-105-131-116-117-118-119-108-121-133-142-143-145-159-146-155-156</t>
+          <t>119-133-147-156-142-116-117-105-78-90-108-121-145-146-159-93-118-155-143-131-104-92-77-91-79-95-94</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-7-8-9-10-22-20-19-32-33-34-35-36-37-45-46-47-48-72-60-62-50-75-76-88-87-86</t>
+          <t>3-54-55-66-53-40-2-0-12-39-25-26-51-64-67-69-82-70-44-57-43-16-15-17-4-28-41-52-14</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>64-83-85-100-98-99-115-101-102-124-111-96-123-110-135-136-137-139-140-150-149-163-151-152-165-161-162-148-147-153-167</t>
+          <t>76-75-60-22-9-36-37-34-33-31-19-46-47-48-35-10-8-6-5-7-20-32-45-72-62-50</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>98-86-96-110-111-163-151-102-88-101-153-167-165-136-135-152-162-149-148-161-150-137-124-123-140-139-85-99-87-115-100-83</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>26-2-3-4-0-14-15-16-17-25-12-28-31-39-40-41-43-44-51-52-53-54-55-57-70-82-69-66-67</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -20072,7 +20072,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-91-92-93-94-95-96-119-104-105-107-109-131-118-103-116-155-156-144-133-120-143-142-129-145-147-148-160-159-146-122</t>
+          <t>148-120-119-118-104-94-93-91-103-129-143-156-155-159-147-133-95-105-131-144-145-142-116-90-92-107-146-160</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -20080,27 +20080,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30-4-5-3-15-16-17-43-38-27-28-14-26-40-41-25-51-52-54-55-56-64-65-66-67-68-69-70-78-79-81-83</t>
+          <t>83-70-3-30-43-16-41-81-69-56-67-54-79-68-55-15-65-78-51-52-28-4-17-14-38-64-25-40-27-26-66</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>86-87-84-110-97-98-99-100-101-102-89-111-115-149-123-124-127-128-125-137-139-138-162-150-151-152-153-140-166-167</t>
+          <t>19-21-48-60-76-75-63-49-35-24-22-10-32-45-59-72-58-47-36-37-62-73-71-46-34-8-5</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>19-10-8-21-22-45-32-34-35-36-37-24-46-47-48-71-58-59-60-62-63-49-72-73-75-76-88-85</t>
+          <t>150-122-125-140-128-127-89-102-101-115-99-139-167-166-152-123-111-124-153-151-162-149-138-137-109-110-97-84-96-98-86-100-88-87-85</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -20170,7 +20170,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84-96-86-88-89-85-97-98-99-76-101-102-110-112-114-115-122-123-124-125-126-127-150-135-151-128-141-152-153-154-161-162-163-164-165-167-132</t>
+          <t>96-86-126-141-153-151-152-150-164-163-161-98-114-101-102-112-123-135-165-154-167-127-89-99-125-124-162-122-110-97-84-85-128-115-88</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -20178,27 +20178,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-7-8-9-10-11-22-19-20-21-18-31-32-34-46-45-44-35-48-49-63-61-59-58-57-70-71-73-74</t>
+          <t>46-76-63-73-74-61-49-11-20-9-10-35-34-19-45-70-57-32-44-31-18-21-59-48-22-8-6-7-58-71</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>68-69-67-52-78-51-38-0-16-4-42-56-54-1-13-12-64-25-40-27-26</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>90-91-92-93-94-95-103-104-105-107-108-133-144-120-147-160-134-158-156-155-142-130-143-157-117-116</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0-26-25-12-13-1-4-16-27-42-40-38-51-52-64-78-54-67-68-69-56</t>
+          <t>90-103-104-116-143-142-155-156-160-147-134-144-91-92-94-95-133-132-120-105-93-107-108-158-157-130-117</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/results/cluster_ga/UAVs4_GRID13/tour/UAVs4_GRID13_1920_16_Greedy_sequences.xlsx
+++ b/results/cluster_ga/UAVs4_GRID13/tour/UAVs4_GRID13_1920_16_Greedy_sequences.xlsx
@@ -668,31 +668,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77-82-109-106-129-104-90-105-145-158-157-161-108-95-156-155-93-79-80-81-96-122-135-148-132-118-131-120-147-146-134-121-92-78</t>
+          <t>3-69-68-55-41-28-29-42-38-51-54-43-4-5-18-2-15-27-65-53-39-26-13-1</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>63-49-45-70-71-84-59-62-86-72-85-47-34-11-7-20-19-6-48-8-33-46-60-74-88-76-89-37-24</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>154-127-113-125-140-115-114-126-148-149-124-101-100-99-97-150-166-153-141-167-164-161-110-98-163-162-151-135-122-136-137-139</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>34-76-89-86-88-63-37-62-74-71-24-11-8-19-45-46-47-85-84-72-70-33-7-6-20-48-49-59-60</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>5-2-29-15-3-4-43-42-54-69-65-51-38-13-1-41-28-27-26-39-55-53-68-18</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>139-125-124-97-136-149-162-150-140-141-153-126-100-99-98-110-137-151-167-154-164-163-101-115-127-114-113-166</t>
+          <t>146-157-129-155-156-108-96-82-92-79-105-121-134-132-118-106-131-158-104-77-90-78-80-93-81-95-109-120-145-147</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -766,35 +766,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>110-111-83-123-112-115-102-89-88-73-163-149-151-138-71-114-113-74-87-86-85-84-72-100-99-154-152-166-167-126-140-164-98</t>
+          <t>26-30-4-16-17-5-29-15-1-0-12-13-14-28-41-51-52-70-31-55-56-42-68-67-54-66-65-64-25-38</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>37-63-50-10-9-8-20-72-73-71-74-24-11-46-58-45-32-6-7-35-36-62-49-34-33</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>84-148-135-122-112-99-100-102-89-98-86-114-115-154-166-140-111-110-113-126-149-163-164-167-152-87-88-151-138-123-161-83-85</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>26-13-14-54-67-64-38-25-52-51-41-55-56-29-42-30-17-16-4-1-15-28-65-66-68-70-79-12-0</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>9-8-7-58-45-46-62-49-24-37-36-33-31-32-34-35-10-11-50-63-20-6-5</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>81-142-143-119-134-148-120-132-144-117-157-90-107-135-122-161-158-95-82-108-121-133-105-116-118-131-129-103-91-94</t>
+          <t>158-134-133-121-95-108-157-132-120-79-90-103-129-116-117-118-107-94-82-105-131-144-119-81-91-142-143</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -864,31 +864,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>112-127-167-154-140-165-138-111-123-137-166-164-163-153-141-115-102-126-125-99</t>
+          <t>38-66-79-52-28-42-43-4-3-0-25-82-81-78-77-26-27-13-15-18-17-12</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>166-165-125-112-99-127-141-140-153-167-154-115-102-126-138-164-163-137-123-111</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>8</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>12-77-78-79-52-38-25-13-28-26-15-4-3-27-66-81-42-43-17-0</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>7</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>58-72-84-83-85-86-88-74-19-23-36-21-7-24-63-87-50-76-62-71-70-45-75-61-35-48-47-34-46-33-6-18-32</t>
+          <t>146-147-161-148-109-122-121-107-93-103-117-90-133-160-145-144-130-131-120-95-134-132-157-158-142-143-129</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>103-117-131-129-142-143-160-161-146-130-82-93-158-145-157-144-121-95-107-109-122-134-133-132-120-148-147-90</t>
+          <t>6-19-50-62-61-74-35-48-36-24-23-34-32-46-58-33-7-21-63-76-88-87-75-47-71-72-86-85-84-45-70-83</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -962,35 +962,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>128-102-89-88-86-101-113-164-162-138-125-150-163-149-136-123-98-126-112-99-140-152-115-114-127</t>
+          <t>107-123-150-162-158-145-132-134-161-149-163-164-155-117-144-157-142-130-131-106-133-147-160-109-136-135-108</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>4-8-9-22-10-23-35-49-48-58-33-20-32-21-24-37-36-34-19-5-31-60-30-57-72-59-7-3</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>56-81-95-65-90-77-52-16-13-25-0-1-28-82-83-70-69-66-105-91-103-104-94-80-64-53-55</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>140-88-75-62-73-74-86-99-98-102-127-115-128-114-152-138-113-112-125-126-101-89-63-76</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>59-72-58-74-62-49-33-60-73-63-75-76-37-10-9-23-8-34-20-19-7-21-48-36-24-35-22-32</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>5-57-31-82-81-28-53-30-4-1-13-0-55-66-69-56-70-83-80-65-52-64-77-25-3-16</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>106-161-147-133-135-134-108-107-145-131-130-91-90-104-117-158-155-157-160-109-95-94-132-144-142-103-105</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1060,7 +1060,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>155-143-131-78-77-80-95-94-108-147-157-132-142-129-116-118-96-119-146-134-121-81-93-92-105-130-158-159-144</t>
+          <t>131-159-158-157-144-132-146-147-134-129-116-77-105-130-143-155-121-96-95-94-81-92-93-108-80-78-119-142-118</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>35-36-22-11-24-37-63-76-50-73-59-45-72-74-61-21-8-48-87-89-86-85-6-7-58-32-33-47</t>
+          <t>89-63-35-47-22-24-11-50-37-36-33-32-58-21-6-7-8-48-73-61-59-45-72-87-85-86-74-76</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1076,19 +1076,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>14-15-26-12-25-38-64-57-30-18-5-17-31-52-66-40-28-42-56-55-43-29-16-2</t>
+          <t>102-128-154-153-124-123-149-148-97-98-125-141-127-167-166-165-164-162-163-150-137-151-152-139-136-122-100-112-99-114</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>43-18-5-17-57-56-52-38-26-14-15-2-16-31-55-66-64-25-12-40-28-29-30-42</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>97-98-125-139-163-164-99-123-122-124-150-137-151-152-166-165-148-149-162-153-167-154-128-127-141-114-102-100-112-136</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1158,7 +1158,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>113-101-100-87-86-139-109-110-85-83-96-84-125-128-141-140-124-152-165-163-162-149-111-99-126-153-167-136-137-138</t>
+          <t>142-121-108-134-93-92-104-118-105-90-91-116-129-144-133-145-159-160-119-106-94-95-147-158-155-143-131</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1166,27 +1166,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>72-57-44-45-32-46-5-22-60-63-76-75-49-50-7-31-19-23-11-24-74-73-61-21-8-35-36-9-10-59-71</t>
+          <t>124-136-163-162-161-148-149-135-101-100-99-110-96-109-137-111-113-128-141-140-125-152-165-167-153-139-126-138</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53-55-43-56-68-79-12-25-26-27-4-30-29-16-15-14-1-13-0-38-52-51-64-67-40-28-41-54</t>
+          <t>0-1-25-38-53-79-54-41-29-56-82-68-67-12-13-4-30-16-43-55-40-14-26-64-51-52-27-15-28</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>158-155-142-135-121-119-131-106-94-108-95-82-105-118-116-129-133-161-148-134-147-160-159-145-144-143-104-93-92-90-91</t>
+          <t>21-8-74-50-24-11-10-9-36-19-5-49-63-61-35-73-86-71-44-83-32-23-22-7-31-57-46-84-85-72-45-59-60-87-76-75</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>117-130-143-131-104-79-94-106-159-146-132-91-90-77-78-105-142-129-155-144-145-158-133-119-93-92-95-120</t>
+          <t>8-22-35-37-34-33-45-74-75-63-61-73-6-18-44-31-46-59-71-76-36-23-9-10-24-11-20</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1264,15 +1264,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>46-61-74-71-22-23-8-63-37-24-11-10-9-6-20-36-35-34-59-73-89-76-75-45-33</t>
+          <t>93-91-92-104-130-105-90-146-145-158-159-144-131-132-120-133-106-119-117-129-142-155-143-94-95</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>65-51-64-18-29-1-15-66-39-52-68-82-69-41-53-54-55-40-12-0-2-17-31-44-57</t>
+          <t>54-55-29-2-17-57-66-12-0-1-41-79-78-77-51-40-69-82-68-15-39-64-65-53-52</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1280,11 +1280,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>153-166-149-135-123-125-139-140-141-154-126-110-96-86-85-101-115-114-112-148-162-150-136-124-138-152-165</t>
+          <t>135-150-162-165-166-153-152-125-138-112-124-136-141-85-86-89-114-101-115-140-154-139-126-110-96-123-149-148</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1354,7 +1354,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>148-110-97-85-115-128-125-126-127-154-166-164-150-123-136-112-101-137-152-151-153-113-83-96-109-122</t>
+          <t>92-131-93-106-119-146-122-96-109-107-120-133-144-118-130-143-155-117-79-78-83-82-95-156-129-116-91</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1362,27 +1362,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>48-8-22-23-36-24-11-37-61-73-60-71-58-45-72-87-89-75-74-34-50-62-59-19-7-20-46-47</t>
+          <t>128-127-97-112-137-110-150-164-151-152-126-125-123-136-148-153-166-154-115-101-113</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>18-14-29-42-67-64-51-52-26-39-1-17-43-69-56-57-44-16-13-25-12-38-53-66-40-15-5</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>67-57-44-18-5-16-1-13-14-15-17-29-56-69-43-42-40-53-66-52-39-25-12-51-64-38-26</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>119-120-133-146-144-93-107-106-118-117-131-143-155-156-129-116-130-91-79-78-92-82-95</t>
+          <t>75-62-50-37-24-89-74-61-8-7-19-20-47-60-59-34-46-87-73-36-23-11-22-48-72-71-58-45-85</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>163-152-164-150-99-110-100-102-101-114-126-113-127-115-128-140-139-141-125-123-111-165-166-167-154-153-151-149-136</t>
+          <t>56-55-77-64-25-12-38-66-65-43-44-30-31-5-29-1-2-17-16-27-51-39-41-54-53-79-80-40-28-82-70-42</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1460,15 +1460,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>31-44-70-80-64-28-27-39-51-77-66-53-42-29-1-17-16-40-41-55-56-82-79-65-25-12-38-54-43-30-5-2</t>
+          <t>130-144-129-120-147-148-161-160-95-94-91-92-104-90-93-107-119-121-134-135-109-146-145-157-142-155-103</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>72-71-85-89-63-50-37-11-32-45-19-33-21-61-47-73-87-74-62-48-8-10-75-88-60-84</t>
+          <t>60-74-87-84-73-85-50-63-37-21-32-48-61-88-89-75-62-19-47-45-72-71-10-11-8-33</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>142-129-103-90-135-120-121-160-161-148-145-130-144-95-109-147-146-134-93-94-107-119-155-157-91-92-104</t>
+          <t>127-114-140-154-141-153-136-149-152-151-113-102-128-115-101-99-111-100-126-125-110-123-163-150-164-165-167-166-139</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -1550,35 +1550,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>98-149-162-125-102-89-88-140-152-127-128-126-110-86-87-113-112-163-150-167-153-151-164-166-139-137-100-99-111-123</t>
+          <t>38-64-54-15-26-13-0-1-4-17-29-40-52-39-69-56-41-14-12</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>20-45-71-61-62-63-76-7-6-9-36-60-86-73-44-57-58-75-89-88-87-47-35-23-10-11-37-49-59-84-46-34-8</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>37-63-76-62-49-35-23-47-46-58-71-57-84-44-45-73-60-7-6-9-11-10-36-61-59-75-34-8-20</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>15-39-52-40-14-1-0-54-41-17-4-56-69-78-26-12-13-38-64-77-29</t>
+          <t>102-113-98-99-111-125-139-127-153-166-167-128-140-152-100-112-126-137-149-150-151-163-148-164-161-162-123-122-110-109</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>130-129-143-93-105-104-103-90-159-144-156-108-95-83-82-79-80-107-120-122-109-119-132-146-148-161</t>
+          <t>80-107-93-108-120-132-119-103-143-156-129-104-105-144-159-146-83-82-95-90-130-77-78-79</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -1648,35 +1648,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>129-144-158-159-147-122-109-108-160-145-146-133-132-143-142-130-118-90-91-92-94-135-96-93-106-105</t>
+          <t>60-62-61-75-88-140-128-102-49-37-50-24-36-85-98-126-113-86-74-73</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>132-133-105-118-158-149-150-136-122-147-106-123-163-151-164-166-139-165-159-145-135-111-125-138-108-94-110-109-146-144-129-137-142-143-130-97-96-160</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>15-53-77-92-93-54-29-27-25-38-51-52-26-0-14-39-66-67-91-90-41-2-16</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2-0-29-16-15-41-54-66-43-56-67-77-25-26-27-53-52-51-38-39-14</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>46-47-60-32-72-86-85-74-24-50-88-73-83-44-45-35-23-34-57-70-58-84-75-49-61-20-19-18-6-33-62-37-10-36</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>137-125-126-139-138-113-111-110-97-98-102-128-140-123-136-149-151-166-165-163-164-150</t>
+          <t>83-84-70-33-20-19-45-44-56-43-58-57-72-47-35-34-23-10-6-32-18-46</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1746,7 +1746,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>94-95-108-148-135-160-158-107-104-142-155-129-103-90-106-118-143-144-132-134-93-92-116-145-146-157-133-121</t>
+          <t>61-76-88-87-71-20-6-32-45-60-48-62-47-22-35-10-23-11-36-50-37-49-59-72-85-73-86-58-46-19-21-34</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13-56-69-83-70-44-43-67-79-52-12-51-80-82-66-65-78-64-14-28-27-15-17-2-16-31-55-30-40</t>
+          <t>67-79-66-65-78-83-82-69-17-2-15-14-12-13-16-28-55-43-44-31-40-52-56-70-30-27-51-64-80</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -1762,19 +1762,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>6-32-20-11-37-76-46-23-36-50-62-35-19-45-58-71-72-73-59-60-61-47-48-49-10-22-34-21</t>
+          <t>142-103-90-116-132-145-158-160-135-121-93-92-106-133-146-157-155-143-144-134-148-118-129-104-94-107-108-95</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>115-127-153-128-141-166-165-139-123-111-88-89-102-101-140-151-138-112-125-152-163-149-86-110-85-87-100</t>
+          <t>123-149-151-163-152-139-140-101-89-102-115-127-128-141-153-166-165-100-112-138-110-111-125</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -1844,35 +1844,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>156-158-159-160-119-94-91-78-92-105-103-104-129-142-143-130-132-108</t>
+          <t>127-152-161-160-162-97-139-140-166-165-163-164-125-138-113-98-111-124-149-135-109-110-96-112-114-115</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>45-33-19-20-23-24-8-21-47-61-63-50-36-62-89-88-71-58-46</t>
+          <t>13-1-42-40-53-38-66-68-67-82-69-56-44-70-17-31-5-3-39-41-28-4-2-15-14-26</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26-39-40-41-31-4-3-13-69-56-17-5-1-38-67-80-66-68-82-70-44-42-15-14-2-28-53</t>
+          <t>104-105-132-130-156-143-158-159-142-129-103-78-91-92-80-94-108-119</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>109-135-149-163-164-124-165-140-115-127-114-85-110-111-139-152-125-113-112-138-166-162-161-96-97-98</t>
+          <t>58-85-71-45-50-24-23-8-19-33-47-46-62-63-89-88-61-36-21-20</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -1942,35 +1942,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>147-134-144-143-117-157-105-118-92-93-94-82-106-104-142-155-119-132-83-121-108-95-135-161-122-148-160-159</t>
+          <t>104-155-106-95-108-135-122-121-134-94-92-93-144-157-159-147-160-161-148-119-132-142-143-117-118-105</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>27-26-38-54-80-69-56-67-79-65-51-52-66-13-12-1-3-30-17-42-70-29-28</t>
+          <t>82-69-56-30-18-31-27-26-66-67-54-13-12-65-52-79-70-51-38-1-3-28-80-29-17-5-42-83</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31-32-18-47-60-48-24-63-7-5-9-11-37-34-33-59-46-72-73-74-75-62-50-36-35-8</t>
+          <t>111-99-110-123-167-128-115-153-138-124-136-84-101-112-139-163-162-149-165-166-152-86-87-89-102-114-113-100</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>165-163-149-124-102-89-87-101-113-138-162-136-123-110-111-100-86-166-167-99-84-114-115-128-152-153-139-112</t>
+          <t>46-47-34-50-11-9-8-7-24-37-36-63-62-75-48-35-73-60-74-72-59-32-33</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>104-95-83-134-160-121-81-82-107-143-142-156-155-116-118-131-147-159-108-96-109-122-117-90-91-92-106-80-78</t>
+          <t>147-160-83-84-138-150-163-164-165-127-167-166-153-112-149-136-123-124-110-96-99-113-125-126-109-122</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2048,27 +2048,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>47-59-57-8-10-11-21-48-35-50-75-86-73-76-36-37-61-6-19-32-33-44-85-89-62-49-87-84-71</t>
+          <t>53-65-39-52-51-12-0-14-15-3-16-17-29-2-1-41-40-27-43-67</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>14-27-40-39-12-0-1-41-29-43-15-3-17-16-53-52-51-65-67-2</t>
+          <t>6-19-32-11-37-49-87-86-73-61-76-50-89-102-75-85-59-21-8-10-36-48-62-35-71-57-44-47-33</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>99-112-126-127-102-113-110-164-153-167-166-165-163-138-125-124-123-136-149-150</t>
+          <t>104-90-116-118-81-82-108-121-134-95-80-78-91-92-107-106-159-156-142-155-143-131-117</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>78-92-105-104-91-103-117-116-143-156-142-108-95-155-157-159-133-119-93-80-120-106-118-144-158-160-145-130-90-77</t>
+          <t>57-43-42-81-80-65-64-66-69-67-40-26-13-17-5-4-15-38-0-25-52-28-3-16-29-83-70-44-18-30-31-56</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -2146,27 +2146,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>36-23-21-45-32-71-72-85-87-59-48-47-34-20-46-74-75-63-50-89-88-61-22-10-9</t>
+          <t>91-90-77-103-117-130-133-95-93-78-105-106-120-160-159-108-119-158-145-157-156-143-142-155-116-144-118-92-104</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>98-138-137-150-164-166-167-154-141-125-109-122-96-101-128-139-126-112-124-123-136-148-135-149-127-140-100</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>71-45-32-9-75-87-89-88-63-61-48-34-47-46-20-22-21-10-23-36-50-74-85-72-59</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>4-3-30-44-18-5-28-15-16-66-67-83-70-57-81-65-42-29-69-43-56-31-26-0-13-25-52-64-38-40-17</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>122-135-96-100-140-128-127-101-126-98-125-138-139-164-166-167-137-150-149-136-148-124-154-141-112-123-109</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2236,15 +2236,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>117-108-82-94-107-95-80-81-83-109-135-134-133-119-121-96-106-105-160-147-146-145-131-157-118-142-158-148-122-92-78-104-91-129-103-155-130</t>
+          <t>127-114-126-139-149-162-113-115-167-165-164-150-86-84-110-136-111-112-98-100-88-89-87-123-153-138-140</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>75-76-74-24-23-36-50-61-73-72-34-22-21-20-19-6-8-9-35-33-45-46-47</t>
+          <t>1-16-4-27-26-14-40-30-42-28-25-38-64-55-69-67-66-78-12-0</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -2252,15 +2252,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12-26-55-69-57-30-28-40-44-31-4-18-16-1-14-27-42-70-67-66-64-38-25-0</t>
+          <t>119-91-103-92-94-106-107-80-81-96-83-109-108-121-134-118-157-155-158-146-133-135-122-148-160-147-145-142-130-131-117-129-104-105-95-82</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>127-139-138-149-111-112-113-87-110-98-136-150-167-165-164-162-140-115-114-100-89-88-86-84-123-126-153</t>
+          <t>31-70-33-21-9-22-35-36-19-18-34-45-61-76-75-73-46-44-57-74-8-23-24-50-72-47-20-6</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -2334,15 +2334,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>104-90-91-109-95-96-119-131-116-118-130-142-155-157-145-147-134-161-160-120-106-107-108-121-133-132-156</t>
+          <t>110-84-83-120-121-109-96-95-108-133-134-147-160-149-162-150-164-161-136</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>30-16-4-3-15-27-2-1-12-55-69-81-67-66-25-26-53-41-43-42-54-79-65-78</t>
+          <t>119-79-66-65-91-90-78-67-81-107-145-157-104-116-130-142-131-118-156-155-132-106</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -2350,19 +2350,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48-86-84-57-70-83-73-74-87-75-47-49-62-35-9-10-24-33-7-5-19-18-60-45-32</t>
+          <t>87-74-73-140-165-138-86-99-102-89-88-115-128-154-167-166-152-125-126-101-75-49-62</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>99-110-165-164-150-138-166-167-140-115-101-89-88-102-126-152-154-128-125-162-149-136</t>
+          <t>43-54-42-41-30-57-69-70-35-10-9-47-60-45-33-19-18-16-55-53-2-1-3-7-24-48-32-5-4-15-12-25-26-27</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2432,35 +2432,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-103-143-144-116-129-155-158-132-145-119-79-77-91-117-104-131-133-107-106-105-94-93</t>
+          <t>124-110-98-85-97-136-166-167-152-151-150-162-163-164-154-153-115-112-127-100-89-102-87-86-111</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32-48-24-23-37-63-60-71-8-21-11-10-9-35-86-87-47-59-45-6-7-33-61-62-50-49-76-102-89-85-19</t>
+          <t>94-117-155-143-161-134-107-109-122-135-148-160-158-144-145-105-90-91-104-131-132-106-119-103-116-129-147-133-93</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12-26-25-67-82-70-43-69-68-81-83-80-52-2-1-13-28-40-65-66-55-31-57-41-38-39-42-44-5</t>
+          <t>13-52-65-77-79-42-43-55-68-44-31-1-12-25-40-28-26-38-39-41-69-82-81-80-66-67-70-57-83-2</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>115-98-111-150-97-109-134-162-147-167-166-152-164-100-112-124-110-122-136-160-135-151-163-161-148-153-154-127</t>
+          <t>33-71-59-48-24-37-23-11-10-9-8-6-7-21-62-61-49-35-60-45-32-5-19-50-63-76-47</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2530,23 +2530,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>130-143-144-132-118-131-145-135-109-121-108-107-106-91-90-117-133-134-159-146-147-103-116</t>
+          <t>116-117-131-146-133-132-107-106-108-121-134-135-147-159-143-103-90-91-118-145-144-130</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19-20-46-45-71-32-7-6-72-73-75-37-36-49-50-63-76-61-48-34-35-21-22-10-24</t>
+          <t>28-15-26-12-1-0-16-30-81-67-79-66-53-38-51-64-42-68-54-39-29-3-4-17-43-55-41</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29-41-66-51-53-28-18-31-15-0-12-38-64-39-1-54-67-79-81-68-16-4-3-26-17-43-70-55-42-44-30</t>
+          <t>140-151-162-149-163-166-124-126-113-100-112-110-150-127-102-137-136-123-109-89-87-86-88-111-84-98-114-101-128-141-167</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -2554,7 +2554,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>98-84-86-88-89-100-113-166-162-150-123-111-124-112-87-101-102-128-140-167-141-114-110-149-136-163-127-126-151-137</t>
+          <t>18-45-44-31-70-72-73-37-24-22-36-21-7-49-75-76-63-50-10-20-19-6-32-46-61-71-34-35-48</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -2628,35 +2628,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77-90-146-142-133-159-160-104-105-106-107-93-94-109-108-119-118-91-80-95-82-79-92-81-120-132-155-117-130-157-145-78-65</t>
+          <t>46-23-9-74-86-61-36-34-35-48-75-89-63-50-11-24-10-21-47-87-76-72-58-20-8-33</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>12-25-17-18-31-32-30-39-52-68-70-69-57-42-29-16-2-13-14-1-5-19-44-43-56-28</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>148-162-138-152-151-139-101-102-115-166-165-128-113-126-99-98-125-136-163-164-149-150-153-167-154-140-124-110</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>93-77-90-81-94-80-106-119-92-130-142-117-155-157-145-160-159-146-133-104-91-66-79-78-65-83-95-82-109-108-120-107-132-118-105</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>30-43-39-25-13-14-66-69-42-32-58-56-83-57-29-16-1-12-2-28-52-68-44-31-70-18-19-5-17</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>46-61-87-86-74-75-47-34-10-23-24-76-89-63-50-48-11-9-8-21-35-36-20-33-72</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>126-140-128-139-153-154-162-148-163-150-151-152-166-167-165-164-138-124-125-113-101-102-115-99-98-110-136-149</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -2726,35 +2726,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>80-82-149-134-122-83-96-84-94-90-81-109-123-131-144-117-145-142-157-132-110-97-136-135-119-120-104-93-129-155-160-161-121</t>
+          <t>35-21-20-7-33-34-36-63-47-45-71-72-59-61-50-22-8-6-75-62-48-24-9-11-23</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6-20-7-11-24-23-22-8-47-87-86-62-63-50-36-21-9-34-48-35-59-72-75-61-71-45-33</t>
+          <t>119-132-157-144-145-134-121-94-82-81-80-93-120-160-131-79-78-104-155-142-129-117-90</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>25-39-52-67-42-56-54-55-40-26-38-65-64-66-41-27-14-0-13-28-30-2-1-17-31-43-44-18-5</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>26-27-30-44-43-54-42-41-28-25-67-5-18-17-2-31-56-55-79-65-78-52-40-66-64-38-39-13-1-0-14</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>139-114-88-112-113-140-128-141-154-167-166-126-111-137-138-165-152</t>
+          <t>84-83-97-113-114-88-109-96-139-140-154-141-128-111-123-135-167-165-166-126-87-86-122-110-112-138-152-161-149-137-136</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -2824,15 +2824,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-118-130-116-103-129-143-132-131-144-155-156-157-159-160-147-146-145-93-94-108-133-105-117</t>
+          <t>116-118-108-94-131-129-143-157-145-159-160-146-147-133-132-130-117-78-93-144-156-155-90-77-103-105</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>56-30-43-17-2-0-12-27-14-1-40-53-54-66-51-77-78-65-82-69-67-26-25</t>
+          <t>9-49-72-58-46-45-61-73-87-86-75-89-24-11-23-37-63-60-47-33-20-32</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -2840,19 +2840,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20-5-45-58-70-72-33-32-31-44-9-24-11-47-23-73-75-63-49-37-61-60-46</t>
+          <t>162-164-111-124-149-137-84-125-113-101-114-139-163-136-150-165-152-167-140-127-99-110-100-98-96-161</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>5-17-43-40-51-25-14-27-26-53-65-66-56-31-44-30-70-82-69-67-54-1-0-12-2</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>98-84-96-110-111-140-167-165-161-149-124-99-100-113-101-89-87-86-139-164-162-163-150-136-137-152-127-114-125</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -2922,35 +2922,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>157-155-142-91-106-131-118-117-129-130-144-143-145-158-147-160-121-95-94-93-90-104-92</t>
+          <t>71-74-61-48-35-7-33-49-75-63-50-76-32-57-84-83-46-60-11-10-24-9-22-21-20-18-44-85-72-47-6-59-58</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>129-142-157-158-147-160-144-143-155-130-117-118-131-145-95-93-121-106-91-90-94-92-104</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>7</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>2-17-29-68-55-41-54-66-52-14-26-25-38-39-64-78-67-80-81-4</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>8</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>32-75-74-61-85-71-58-57-18-21-63-50-10-6-20-7-44-46-60-48-24-11-35-47-84-83-72-59-76-49-33-22-9</t>
+          <t>114-127-165-164-151-153-140-150-136-149-111-98-97-110-89-128-167-154-141-112-99-102</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>99-164-165-140-154-167-153-141-128-127-151-150-112-114-102-89-97-111-110-149-136-98</t>
+          <t>14-41-54-55-39-38-52-80-81-68-67-66-78-64-26-25-2-4-17-29</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3020,35 +3020,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>97-75-85-83-123-111-76-102-167-138-152-154-164-163-114-139-89-115-125-136-124-99-86-101-100-98-110-122</t>
+          <t>6-5-3-41-40-29-14-25-52-54-42-17-1-0-4-30-43-68-67-69-45-18-32-44-55-7</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>52-65-25-14-0-1-29-42-68-64-77-79-80-67-41-54-40-3-43-55-69-81-92-90-66-78</t>
+          <t>110-147-136-123-111-125-114-139-152-138-124-154-167-164-163-160-122-135-97-98</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>7-32-22-24-48-34-18-45-73-62-49-61-47-58-72-71-30-44-17-4-5-6-11-10</t>
+          <t>79-92-158-157-146-120-108-80-65-81-106-90-103-118-133-132-131-130-129-104-66-64-77-78-142-144-156</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>132-118-131-130-142-156-157-129-103-104-106-108-135-120-133-147-160-146-158-144</t>
+          <t>48-71-83-34-47-85-99-101-100-102-115-76-89-86-61-62-75-49-22-11-73-72-58-10-24</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3118,35 +3118,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>129-130-133-121-82-81-107-132-145-157-156-158-159-160-146-147-134-120-95-79-92-77-90-103-105-104-117</t>
+          <t>48-47-60-73-85-46-32-20-7-11-49-76-88-87-50-10-21-74-72-58-45-33-8-35-23-36</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>58-60-46-11-21-33-49-74-72-73-45-32-47-35-36-10-23-50-76-88-87-48-20-8-7</t>
+          <t>100-114-113-139-153-166-164-163-151-110-111-99-98-126-127-115-128-140-152-138-124-112</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>9</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>56-43-44-17-3-12-13-2-0-28-30-41-53-67-55-57-40-26-51-65-66-42-5-18</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>55-67-66-12-0-30-43-56-57-44-2-13-26-51-65-53-40-42-18-5-17-3-28-41</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>110-111-126-99-100-114-115-128-96-135-161-148-138-166-152-153-140-127-113-139-112-124-122-151-164-163-85-98-109</t>
+          <t>122-109-157-129-77-103-79-81-107-134-135-148-120-133-145-158-156-130-104-90-92-105-121-117-132-159-146-147-160-161-95-82-96</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -3216,31 +3216,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>114-115-138-149-151-97-96-148-161-135-109-98-111-140-154-128-101-100-122-164-166-167-153-152-165-136-123</t>
+          <t>19-8-72-57-44-45-46-34-48-62-60-74-75-76-63-50-49-37-24-10-21-6-58-71-47-33-18</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10-63-50-48-49-60-46-47-62-76-75-87-88-74-85-72-34-21-33-44-45-8-6-58-57-71-19-18-37-24</t>
+          <t>91-131-143-144-158-145-120-146-159-161-148-135-107-95-106-119-104-103-116-117-155-118-92-90</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38-25-51-66-67-68-69-55-42-2-3-17-16-41-40-12-0-64-52-65-53</t>
+          <t>25-38-69-68-81-66-41-42-16-2-0-40-53-55-67-79-64-77-51-52-65-12-3-17</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>119-118-104-117-116-155-143-81-95-120-144-158-106-107-92-79-103-91-77-90-131-145-159-146</t>
+          <t>140-87-85-96-109-97-122-114-115-128-154-165-164-151-101-88-100-111-98-123-136-149-138-152-166-167-153</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -3314,15 +3314,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>97-98-111-162-123-136-128-115-140-163-150-124-110-112-126-114-86-87-88-100-127-166-164-165-139-89-101-151-125-137</t>
+          <t>19-17-16-15-0-14-42-43-31-6-2-12-25-4-32-44-56-41-30-18-1-28-29-70-69-68</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>33-32-46-47-35-36-11-37-50-49-63-74-75-72-58-7-6-19-9</t>
+          <t>63-50-75-74-86-72-58-87-89-88-49-37-11-9-7-33-46-47-35-36</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -3330,15 +3330,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0-25-42-43-30-4-16-29-41-12-14-2-64-68-56-69-70-31-44-18-17-28-15-1</t>
+          <t>160-147-121-106-77-64-78-103-118-105-82-81-95-94-92-104-107-120-146-132-158-159-116-117-142-130-143-131-134</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>105-92-103-132-148-147-158-143-159-160-146-130-104-117-77-78-106-122-109-82-83-96-134-118-131-142-116-120-107-81-95-94-121</t>
+          <t>140-137-123-128-115-100-98-111-97-112-126-125-136-148-122-110-101-83-96-109-124-139-162-163-150-164-151-166-165-114-127</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -3412,15 +3412,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>101-111-123-109-135-148-115-102-114-139-87-86-96-98-99-136-141-128-153-113-127-125-124-150-163-162-149-137-151-154-167-164-152-112-100-85</t>
+          <t>16-38-40-54-66-53-64-65-52-39-27-0-25-55-68-69-43-56-30-17-4-1-14-15</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>27-40-57-14-25-38-30-43-16-64-78-79-65-54-39-52-15-4-17-68-56-70-69-55-82-83-80-66-53-0-1</t>
+          <t>136-149-123-125-139-154-167-115-102-128-127-150-135-164-163-137-152-114-101-100-111-124-162-148-141-153-151-113-112-98-99</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -3428,19 +3428,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19-32-5-18-49-50-37-62-60-46-59-58-47-35-36-23-11-9-22-34</t>
+          <t>92-131-130-129-156-143-146-133-145-117-119-93-106-109-96-82-94-80-79-78-103-118-105-121-134-132-142-104-90</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>92-93-133-146-145-130-105-94-106-118-131-119-121-134-132-104-142-156-143-129-117-103-90</t>
+          <t>11-36-87-86-83-85-47-23-37-50-49-62-58-34-9-5-32-46-57-18-19-22-35-60-59-70</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -3510,7 +3510,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>99-86-85-98-140-141-124-122-123-161-148-109-136-110-84-112-113-100-138-139-167-163-164-150-151-152-154-127-114-101</t>
+          <t>6-32-45-89-36-24-11-72-84-85-87-88-86-62-63-76-50-35-8-21-23-9-34-61-74-73-59-7</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -3518,15 +3518,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8-7-21-61-74-73-72-50-59-34-11-23-24-36-62-89-87-88-76-63-35-9</t>
+          <t>113-127-140-139-100-98-152-161-148-122-109-123-136-124-110-138-151-150-163-164-154-167-141-112-99-101-114</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>67-56-57-27-14-13-54-68-69-81-82-83-41-38-51-39-42-45-32-4-6-30-17-43-44-31-66-53-16-18-28-15-1</t>
+          <t>15-4-16-17-30-56-69-51-39-53-66-41-28-83-82-80-54-42-13-1-27-14-43-31-18-44-81-68-67-38-57</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -3534,11 +3534,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>130-159-146-133-107-80-79-78-104-77-129-144-143-156-157-121-108-94-118-145-134-120-105-103</t>
+          <t>133-121-108-94-79-78-130-156-143-129-104-118-144-157-159-145-120-134-146-107-105-103-77</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3608,35 +3608,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>104-142-117-106-120-109-122-95-108-107-93-77-78-79-121-132-145-147-143-158-159-144-156-129-90</t>
+          <t>117-104-122-121-120-107-93-106-108-95-90-129-143-142-156-144-132-145-158-159-148-147-109</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>58-46-21-22-11-10-7-8-23-37-62-73-60-61-49-36-76-74-47-35-20-19-33</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>14-77-78-64-51-65-79-82-57-56-15-0-25-39-83-44-31-41-55-30-3-17-18-2-13-38-53-69-70-42-43-27</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>86-87-102-127-126-167-153-138-125-124-112-114-115-128-141-150-162-149-85-99-139-164-163-123</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>37-22-23-10-7-8-19-33-20-21-47-85-58-61-35-46-60-73-74-36-49-62-76-86-87-11</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>82-69-55-39-38-3-18-17-65-64-51-53-41-25-13-15-44-83-57-31-30-43-70-56-42-0-2-14-27</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>126-112-128-141-138-149-148-162-164-163-139-125-99-102-115-114-124-123-150-153-167-127</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -3706,35 +3706,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84-99-162-150-165-167-140-114-89-101-128-141-154-126-113-96-98-125-102-100-85-124-110-97-112-137-136-109-135-164-152-111-83</t>
+          <t>92-133-134-108-132-145-160-147-143-117-105-104-103-116-91-93-95-107-119-118-130-129-142-155-156-157-131</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>24-7-19-31-57-83-72-59-46-32-62-63-50-10-34-74-61-73-84-58-71-70-48-36-37-9-22-8-47-85-75-89-76</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>13-0-27-69-82-56-43-26-38-51-39-52-42-15-3-1-40-53-68-66-77-78-65-67-41-30-64-12-25</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>58-70-72-73-19-8-7-48-50-62-76-75-36-22-10-9-34-63-37-24-47-59-57-61-74-46-31-32-71</t>
+          <t>152-140-126-114-128-167-136-97-99-100-113-101-102-154-165-137-96-110-148-124-125-111-98-164-162-161-150-135-109-112-141</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>148-161-160-147-133-105-92-118-156-155-142-129-143-157-95-108-93-107-132-119-131-145-104-117-116-103-91-130-134</t>
+          <t>0-12-38-51-52-53-67-30-42-78-77-64-65-39-25-13-26-40-41-27-3-15-43-66-82-68-69-56-1</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -3804,31 +3804,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>85-136-163-162-99-98-126-141-127-115-89-114-165-150-166-167-139-113-101-87-86-100-84-97-110-123-112</t>
+          <t>46-22-49-10-8-6-19-20-50-36-87-89-63-73-85-47-48-21-11-24-37-32-45-58-71-84-60-57-70-72-86-75-62-33</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>47-62-75-63-50-46-32-19-6-72-49-24-8-45-71-73-58-60-37-11-10-22-36-48-33-21-20</t>
+          <t>51-64-52-65-66-53-39-0-26-54-67-68-69-30-17-16-5-31-42-43-1-13-14-28-29</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>42-70-57-69-31-30-29-13-65-66-16-17-5-1-0-26-39-54-67-52-51-64-53-14-28-68-43</t>
+          <t>112-165-163-162-136-123-97-99-100-113-150-139-141-167-166-127-115-101-114-126-110-98</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>96-81-104-130-129-142-143-145-95-121-160-159-133-119-117-116-118-120-107-93-80-82-83-109-78-90-77</t>
+          <t>116-129-130-117-80-83-82-96-109-107-119-142-143-90-78-77-120-121-93-95-81-104-118-133-160-159-145</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -3902,35 +3902,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>110-97-73-85-111-153-127-114-76-126-152-151-96-83-71-72-74-89-101-112-166-164-163-137-100-99-98-123-125</t>
+          <t>135-146-130-118-106-119-133-134-107-92-91-90-104-132-158-145-161-95-94-157-155-142-117-116-144-147-148</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12-13-54-81-82-56-30-17-16-42-28-25-38-39-77-51-66-27-14-15-29-70-69-79-52-55-44-4-2</t>
+          <t>110-85-99-112-98-97-111-163-164-151-123-137-152-166-153-126-125-114-89-127-101-100-83-96</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>7-5-18-21-35-59-45-33-47-60-61-48-22-11-10-8-9-36-50</t>
+          <t>7-48-61-74-73-71-70-59-76-50-45-5-18-44-33-47-60-72-35-22-10-36-11-21-9-8</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>147-161-158-145-144-142-157-155-130-132-133-134-118-116-117-94-95-135-148-107-119-106-92-90-91-104-146</t>
+          <t>12-77-66-28-51-52-25-27-54-79-82-81-30-4-17-29-42-69-56-55-39-38-2-16-15-14-13</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4000,23 +4000,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>80-79-107-133-121-134-146-147-117-91-77-116-130-155-144-157-158-95-108-94-142-143-131-78</t>
+          <t>66-53-67-65-64-15-13-0-41-55-54-68-69-70-31-43-44-17-5-4-30-40-26-42-16-3-38-25-39</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32-89-48-20-19-58-46-45-21-9-10-11-22-35-59-34-47-72-73-76-63-61-33-7-8-37-36-62-75-74-6</t>
+          <t>72-74-34-21-8-7-6-20-32-33-45-47-48-63-62-89-75-73-36-10-11-9-35-61-59-46-19-22-37-76-58</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30-3-15-0-13-25-53-67-41-42-54-66-40-26-39-65-64-38-16-17-5-4-55-68-69-70-31-44-43</t>
+          <t>79-78-77-130-142-131-144-157-133-146-147-155-143-91-116-117-94-95-108-121-158-134-107-80</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -4024,11 +4024,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>138-153-154-128-127-139-164-165-151-161-96-83-85-109-122-136-149-137-126-115-87-100-99-97-112-113-110-123-124</t>
+          <t>151-164-85-87-139-153-165-138-100-154-115-128-127-112-83-96-97-109-137-136-161-149-122-99-110-123-126-113-124</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -4098,35 +4098,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>112-136-150-163-167-152-140-99-113-102-100-86-87-88-141-154-165-166-151-139-127-126-123-97-85</t>
+          <t>116-144-146-145-143-129-118-105-104-91-93-95-135-148-147-160-159-158-155-142-156-107-94</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>35-36-63-50-24-34-47-5-45-71-59-33-9-11-10-8-37-49-48-62-73-60-32-20-19-74-75-22-21</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>141-154-166-167-163-136-152-139-151-165-140-126-127-102-85-97-123-109-112-113-99-86-87-88-100-150</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>9-8-21-20-34-33-31-32-45-71-59-47-35-73-74-50-48-49-36-10-24-11-37-22-60-75-62-63-5-19</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>83-70-17-3-16-54-79-77-53-12-13-28-29-27-25-1-2-56-55-67-80-81-65-66-64-52-0-42-43</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>107-144-142-155-129-91-104-146-145-160-159-147-148-135-109-143-156-158-116-118-105-93-94-95</t>
+          <t>25-64-66-67-80-42-2-3-17-81-53-52-77-79-83-70-55-43-31-16-29-1-13-65-54-56-28-0-27-12</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4196,15 +4196,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>133-145-144-92-93-95-147-160-159-146-104-103-90-142-155-105-119-131-157-156-117-118-107</t>
+          <t>38-64-92-79-93-65-77-90-78-29-44-16-2-3-41-81-54-66-55-67-51-53-69-42-13-27-70-95-82-96-83-56-26-25</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>83-16-3-2-42-56-70-41-67-65-66-64-77-51-38-13-26-55-54-78-53-25-27-29-31-44-69-82-79-81</t>
+          <t>11-24-61-74-60-34-22-75-89-37-7-33-32-19-31-45-46-49-50-36-47-72-84-87-86-21</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -4212,19 +4212,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84-72-87-86-89-75-36-37-47-33-34-21-7-32-19-45-46-49-50-22-24-11-61-74-60</t>
+          <t>137-138-111-110-98-112-99-126-151-150-140-128-102-127-139-123-136-164-165-167-154-153-163-162</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>162-148-122-109-96-98-111-110-123-140-153-128-102-99-112-127-126-139-154-150-137-136-135-138-164-163-151-165-167</t>
+          <t>159-160-147-122-109-135-148-107-105-104-103-117-145-146-133-131-157-156-155-142-119-118-144</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4294,35 +4294,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>143-156-120-135-122-96-95-94-118-134-121-108-93-159-160-158-157-130-133-119-92-104-129-117</t>
+          <t>44-57-43-55-68-56-70-83-81-67-16-15-26-14-28-40-65-64-52-12-38-79-66-53-31</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>150-123-110-84-88-114-115-102-100-98-138-162-149-165-167-141-154-153-164-151-126-127-125-113-101-87-99</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>26-14-15-16-28-55-52-53-67-68-81-83-70-56-44-57-43-40-66-79-65-64-38-12</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>58-73-48-61-49-36-24-10-11-8-6-34-60-35-22-9-19-18-45</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>9</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>8-6-58-9-10-24-11-36-49-48-60-19-18-31-45-73-61-34-35-22</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>84-98-110-123-149-125-138-162-165-126-114-101-115-102-88-87-100-113-127-141-167-154-153-164-151-150-99</t>
+          <t>143-129-119-108-134-135-159-160-133-95-96-122-121-120-94-93-92-117-104-118-130-157-158-156</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4392,35 +4392,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84-124-154-126-87-100-112-150-137-151-163-123-114-127-141-153-167-165-138-88-101-86-83-97-99-110-122</t>
+          <t>141-127-126-138-167-153-165-163-135-161-100-112-123-110-99-87-154-124-84-97-122-150-151-137-86-88-101-114</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>41-80-67-66-79-78-53-40-82-55-54-25-13-39-51-38-64-52-27-43-56-30-14-12-3-42</t>
+          <t>41-14-27-12-51-79-80-40-3-42-30-57-82-83-56-13-38-25-53-54-66-67-55-44-43-39-64-78-52</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>72-33-21-8-20-19-5-7-9-10-23-47-34-58-45-32-35-76-63-37-11-75-49-62-73-46</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>10-23-76-63-49-35-34-20-19-57-58-44-5-8-33-45-32-46-21-9-7-47-75-73-72-62-37-11</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>103-104-91-92-106-107-121-94-118-129-142-116-105-160-161-135-134-159-147-158-146-131-130-119-133-144-143-155</t>
+          <t>105-92-94-107-106-159-160-146-155-142-158-144-143-130-129-116-103-118-133-147-134-121-119-131-104-91</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4490,31 +4490,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>122-92-104-157-155-143-129-105-94-108-134-131-146-160-147-121-130-119-118-81-82-109-132-159-145-116-103-90-93-96-148-161-135</t>
+          <t>3-1-42-82-81-70-55-66-57-56-40-12-16-14-54-79-78-77-52-64-53-39-51-38-41-29-4-17</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32-20-50-36-22-9-8-45-70-46-49-61-73-84-57-7-11-10-76-74-58-5-6-19-31</t>
+          <t>20-6-5-31-58-45-7-8-22-19-61-73-74-76-9-10-11-36-50-49-46-32</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>78-79-3-4-29-1-14-40-53-16-12-51-66-77-64-52-38-39-55-56-17-42-54-41</t>
+          <t>135-161-160-122-121-134-157-131-118-92-105-143-155-129-116-104-159-147-109-96-108-94-93-119-132-146-145-130-103-90-148</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>111-164-165-98-123-163-162-149-136-110-88-89-114-100-86-152-166-150-139-154-140-127-112</t>
+          <t>88-100-86-98-112-127-140-89-114-165-154-166-162-149-111-139-152-164-163-150-136-123-110-84</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -4588,35 +4588,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>76-101-137-123-139-167-166-140-114-112-98-97-86-88-89-154-153-164-163-162-151-126-125-99-141-128-127-87</t>
+          <t>39-38-25-0-12-26-13-41-42-20-21-28-40-16-5-6-33-45-32-31-3-14-27-29-4-30-43</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42-41-29-16-0-3-14-13-12-39-52-40-54-28-27-26-25-38-64-80-67-78-77-66</t>
+          <t>87-74-75-11-97-137-112-98-73-114-101-128-59-47-22-23-36-37-35-153-154-167-166-139-125-89-141-86-99-72-88-50-76-126-164-84-85-123-140-127-151</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>106-107-83-58-70-109-96-57-56-66-52-64-77-94-69-54-67-80-78</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>8</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>58-72-59-45-33-74-75-50-73-47-85-84-69-4-30-31-32-36-11-20-57-83-70-21-22-23-37-35-6-5-43-56</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>116-104-144-156-161-159-158-157-143-155-142-118-96-109-107-94-105-120-106-135-147-146-132-117</t>
+          <t>142-155-158-159-132-120-135-162-163-161-147-146-143-117-105-104-116-118-144-157-156</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4686,35 +4686,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>148-122-104-91-92-77-93-107-120-95-83-117-130-156-157-132-131-121-109-108-81-79-90-155-144-133-134-160</t>
+          <t>72-71-73-75-76-24-63-88-62-36-21-9-20-45-58-6-7-48-50-37-11-10-23-60-59-74-61-49-33-47-32-19</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>45-58-72-73-88-50-37-6-7-75-62-10-9-20-19-32-71-59-47-49-23-36-24-11-21-48-60-61-74-76-63-33</t>
+          <t>131-132-160-134-133-120-121-144-157-155-156-130-117-104-107-108-95-92-90-91-93</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>40-39-25-27-52-65-64-51-26-12-0-4-17-44-70-56-67-55-42-28-13-15-3-43-54-41</t>
+          <t>70-39-25-12-77-64-65-56-83-67-79-51-40-3-4-17-0-13-52-28-42-43-27-26-15-54-41-55-81-44</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>123-124-161-164-165-167-126-127-102-141-154-139-136-150-151-137-138-140-114-112-100-113-125-111-98</t>
+          <t>148-161-164-126-138-127-139-150-165-167-154-141-140-98-111-112-100-102-124-122-136-137-151-125-114-113-123-109</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4784,7 +4784,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>149-136-109-97-96-84-123-135-134-83-82-145-144-142-158-130-117-119-132-120-121-107-105-106-133-147</t>
+          <t>3-2-65-64-51-38-25-66-79-77-90-78-30-29-26-52-27-0-1-12-14-15-28-56-43-4</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4792,27 +4792,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>33-7-22-24-21-20-35-48-37-47-46-44-31-32-5-6-9-34-45-57-70-74-76-59-72-75-11-10-63-50-62-61</t>
+          <t>100-127-141-128-115-154-167-138-164-163-124-99-87-111-112-150-151-139-152-125-126-102-89-88</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>84-83-105-117-82-109-158-145-144-132-147-123-136-149-135-121-120-106-133-134-97-96-107-142-130-119</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>34-62-48-37-50-32-46-59-44-57-74-75-76-63-61-72-70-31-6-22-11-24-21-45-33-35-47-7-5-20-9-10</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>4-3-2-66-79-78-77-90-64-51-65-52-15-14-0-1-12-25-38-26-28-29-27-43-30-56</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>112-139-127-126-138-125-111-124-152-154-167-141-128-115-88-87-99-150-163-164-151-102-89-100</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>162-149-123-137-161-136-150-151-98-97-111-89-99-126-114-100-85-109-110-124-112-152-165-128-115-88-101-154-167-166-163</t>
+          <t>65-64-79-81-119-103-156-159-132-77-90-80-120-121-107-93-94-95-106-105-144-157-91-78-116-129-155-117-104</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -4890,27 +4890,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>51-38-39-26-55-27-16-4-70-29-28-41-52-81-67-64-77-80-79-56-30-17-3-15-2-14-13-53-65-78</t>
+          <t>29-55-44-5-31-30-16-18-56-67-41-27-52-53-39-51-38-26-14-13-17-4-3-2-15-28</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>59-44-58-31-6-5-19-34-9-37-50-36-47-22-24-10-8-7-18-46-61-48-60-73-75-74-33-45-32</t>
+          <t>101-114-128-154-167-152-98-115-100-97-110-149-162-161-160-147-166-165-151-163-124-112-99-126-136-123-109-111-150-137</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>95-94-107-106-105-121-147-160-159-132-144-156-157-119-120-117-103-116-104-90-155-129-91-93</t>
+          <t>59-46-32-58-19-6-34-50-37-75-89-88-74-8-7-45-47-48-24-9-33-60-22-10-36-61-73-85-70</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -4980,23 +4980,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>96-136-124-123-122-109-98-114-127-126-151-110-97-135-162-125-111-101-154-139-152-150-148-149-164-99-85-86</t>
+          <t>96-110-123-148-122-99-111-124-109-149-136-135-162-164-126-86-85-98-125-150-151-152-139-154-127-114-101-97</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>37-23-35-34-21-6-7-8-10-9-24-61-74-46-49-22-50-89-88-75-76-19-45-72-58-71-73-48-47</t>
+          <t>105-93-118-131-130-129-142-159-145-144-106-107-121-108-133-147-160-157-143-103-91</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>40-39-1-13-55-57-28-27-54-80-79-66-67-65-16-29-30-18-31-43-44-82-69-70-15-26-25-52-4-3</t>
+          <t>29-39-40-65-79-67-82-80-66-25-1-15-28-27-54-55-16-3-18-4-31-70-69-52-26-13-30-44-57-43</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -5004,11 +5004,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>144-108-121-107-106-93-105-118-103-91-129-130-131-143-142-157-145-133-147-160-159</t>
+          <t>34-35-49-6-7-45-73-74-21-8-9-22-58-71-47-48-61-50-37-46-72-75-89-88-76-10-23-24-19</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5078,35 +5078,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>163-152-154-128-149-110-124-112-87-100-136-162-150-126-98-84-83-88-101-99-102-114-115-127-153-139-113-138-165-164</t>
+          <t>156-143-157-145-132-131-104-103-129-146-134-121-108-94-107-158-160-148-159-144-142</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19-32-58-71-46-48-49-73-45-35-37-23-22-8-9-10-76-75-61-24-11-6-70-57-50-63-36-60-72-18-21-20-7-44-31-5</t>
+          <t>113-101-100-87-88-124-110-138-150-164-163-165-114-128-115-102-154-153-152-162-149-136-99-98-84-127-139-112-126</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>65-51-0-64-77-41-18-5-57-42-2-27-1-14-28-30-66-83-70-44-31-16-29-17-3-12-25-26-52-54-40-39-43-82-80</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>3</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>42-43-65-77-80-82-66-51-25-12-26-39-40-27-14-16-3-17-30-29-52-64-41-54-0-1-2-28</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>156-107-94-108-121-134-148-160-131-104-103-129-144-157-159-158-146-132-145-143-142</t>
+          <t>24-46-60-72-73-76-37-23-22-8-50-49-36-20-6-19-7-21-63-75-61-48-35-71-58-32-45-9-11-10</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5176,15 +5176,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>92-78-104-117-118-106-93-142-116-146-120-77-79-131-145-159-158-157-144-94-96-82-95-81-108-119-105</t>
+          <t>38-25-13-17-16-15-40-39-77-66-78-65-55-42-29-28-41-54-69-56-14-1-52-79-26-12</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>45-71-59-20-57-70-86-61-89-75-63-23-9-7-35-24-47-60-87-84-73-48-49-22-46-34-8</t>
+          <t>92-93-94-106-120-145-116-104-118-96-109-108-122-135-148-159-146-161-95-131-117-157-158-142-144-119-105-81-82</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -5192,15 +5192,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28-38-25-12-39-54-41-40-26-52-65-66-42-18-31-69-56-55-29-15-14-13-1-17-16</t>
+          <t>61-75-63-24-22-8-7-20-18-31-46-34-60-84-70-57-45-59-71-73-35-47-49-48-23-9</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>113-100-101-102-109-111-114-136-149-162-161-148-98-99-138-154-141-128-153-152-150-135-122-124-110-123-151-165-167</t>
+          <t>89-102-99-123-136-111-128-153-152-149-162-150-151-165-167-154-141-98-110-124-86-87-100-101-114-138-113</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -5274,31 +5274,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>93-94-148-134-160-158-120-108-95-96-122-107-132-146-147-118-129-156-143-157-144-130-90-91</t>
+          <t>85-99-100-102-75-76-89-101-74-60-84-87-48-35-23-37-49-24-11-36-59-72-98-112-113-114-141-128-115-127</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>26-40-80-79-55-4-3-14-69-70-82-81-68-78-52-38-53-54-2-12-27-28-41-43-16-42-39</t>
+          <t>2-3-32-46-58-70-34-20-9-6-18-5-4-43-31-16</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31-59-46-34-5-18-6-36-48-49-9-23-76-75-37-24-11-35-20-32-74-72-60-58</t>
+          <t>143-144-132-157-148-96-120-134-146-158-160-137-126-167-166-165-152-138-108-123-122-147-162-149-97-125-151-164-154-140-139-156</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>125-166-165-152-115-89-87-99-97-84-113-127-140-112-123-137-151-164-162-149-98-85-100-102-101-114-154-167-141-128-126-139-138</t>
+          <t>14-41-40-28-12-26-38-39-52-42-79-80-94-95-107-69-27-54-53-55-68-82-81-78-93-118-91-130-129-90</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -5372,31 +5372,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>127-128-154-151-112-98-97-110-124-123-164-162-161-109-83-113-114-126-136-135-149-163-153-166-99-86-89-88-101</t>
+          <t>146-158-157-144-156-143-131-129-130-104-103-77-92-160-147-120-93-80-95-118-119-133-121-107-106-117-116-105</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19-57-31-44-23-35-73-74-76-62-37-48-71-70-72-34-10-11-33-46-61-47-21-5-18-7-20</t>
+          <t>51-12-27-1-14-25-26-41-40-54-55-30-42-28-16-4-5-18-2-0-52-65-66-17-31-44-56-67</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>42-56-55-67-54-51-65-66-52-26-25-40-16-4-17-30-1-14-27-12-0-2-28-41</t>
+          <t>19-33-88-86-74-47-71-72-20-34-7-37-62-73-76-89-61-83-70-57-46-48-35-21-23-11-10</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>77-103-116-129-117-104-105-147-158-160-118-92-80-106-107-120-95-93-119-144-157-156-130-143-146-121-133-131</t>
+          <t>114-113-112-126-127-128-98-123-135-110-124-136-162-163-151-97-109-161-164-153-154-166-149-99-101</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -5470,35 +5470,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>113-87-86-85-96-109-136-163-114-128-138-125-89-101-154-153-167-166-164-165-162-135-110-124-111-99-123-98-122-149-150-151-152-126-115</t>
+          <t>99-98-123-110-165-152-153-154-115-101-114-126-138-125-150-167-166-164-163-151-162-149-136-124-111-113-128</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>160-159-143-158-109-122-135-134-146-120-132-142-156-118-106-108-107-103-116-117-131-90-92-96</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>6-7-61-74-89-76-23-24-11-9-22-48-34-45-32-46-58-49-36-35-5-31-44-57-85-72-71-86-87-73-63-50-47-19-8</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>6-8-11-76-63-74-73-61-48-50-72-45-46-71-57-44-58-47-34-23-24-36-49-35-9-22-7-5-31-32-19</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>14-15-17-4-30-29-43-26-40-25-12-2-1-0-28-68-56-55-54-66-53-52</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>107-108-134-160-159-158-131-81-132-156-143-142-103-116-146-120-106-118-117-90-78-79-92</t>
+          <t>53-55-54-43-56-81-79-78-66-25-40-28-15-68-30-29-2-17-4-0-12-1-14-26-52</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5568,35 +5568,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>99-112-100-76-89-75-84-87-101-102-128-86-74-110-126-141-152-138-151-150-163-111-125-166-167-153-140-88-63</t>
+          <t>50-11-45-84-83-57-43-33-7-19-6-5-4-17-18-58-60-61-34-21-20-71-59-31-30</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>38-80-67-1-14-16-43-56-69-68-79-78-91-65-53-54-83-81-41-40-28-51-39-27-13</t>
+          <t>108-106-119-131-132-118-157-156-155-147-148-135-161-162-136-109-121-159-146-105-117-116-104</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>71-60-45-31-17-5-7-19-6-20-21-34-59-11-50-61-33-18-4-30-57-58</t>
+          <t>63-74-99-110-151-150-128-141-102-89-101-112-111-125-138-86-87-88-75-100-163-166-167-152-153-140-126-76</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>65-53-67-80-81-68-41-16-1-14-28-27-39-13-38-51-69-56-78-91-79-54-40</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>118-131-146-147-161-162-159-116-104-105-119-132-148-136-108-157-156-155-121-135-109-106-117</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -5666,35 +5666,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>148-161-131-130-143-105-106-93-92-129-155-157-146-133-145-159-160-109-95-96-94-122-121-135-118-103-144-158-132-107-83</t>
+          <t>65-56-57-43-55-38-39-28-16-5-3-14-12-25-0-27-26-1-15-29-42-53-64-66-51-13-2-17-30-31-44-68</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>103-129-143-132-160-159-158-145-157-144-133-106-118-155-130-131-77-105-93-80-94-107-146-121-95-78-92</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>21-9-23-36-11-24-49-87-88-76-63-47-46-45-8-7-6-32-33-58-73-72-48-37-50</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>83-96-109-111-112-127-152-128-167-163-162-135-114-102-115-166-140-150-123-138-125-100-84-97-137-136-148-161-164-139-124-122</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>39-29-31-0-14-42-43-3-17-44-57-28-1-15-78-80-66-55-56-30-16-2-13-26-38-51-64-12-25-27-68-53-77-65</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>24-37-36-47-58-45-46-21-8-9-23-50-5-6-7-33-32-72-73-76-49-63-48-11</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>164-136-150-84-97-112-124-100-115-140-139-167-166-128-127-125-137-123-111-87-88-102-114-152-138-162-163</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5764,31 +5764,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>91-144-156-131-120-121-130-104-129-116-105-92-94-106-134-146-157-158-143-142-160-148-135-122-108-107-133-159-132-119-118-95</t>
+          <t>19-7-34-24-37-60-74-72-58-59-49-50-76-63-22-11-10-21-8-35-47-46-45</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>65-66-42-56-69-81-38-51-79-78-64-39-13-2-3-28-27-68-44-70-54-40-25-26-4-14-15-17-43</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>149-162-136-137-138-140-139-114-100-87-125-86-85-84-83-98-99-101-123-97-96-150-124-113-141-127-115-102-88-89-128-152-166</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>46-50-76-63-49-35-7-8-21-34-19-58-45-72-74-59-60-47-37-24-11-10-22</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>26-27-25-43-44-42-3-17-15-28-40-38-64-78-81-79-65-51-66-68-70-69-56-54-39-13-14-4-2</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>115-113-150-137-152-166-127-128-102-88-100-99-125-139-141-140-138-123-96-97-89-87-162-149-136-124-85-86-83-84-98-114-101</t>
+          <t>157-158-133-146-122-94-91-105-132-121-108-95-134-159-160-148-131-118-106-119-143-142-130-129-144-156-116-104-92-120-107-135</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -5862,23 +5862,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>97-149-136-162-163-166-167-140-150-151-127-153-152-114-123-111-126-141-115-89-98-88-99-85-112-138-124</t>
+          <t>151-141-114-115-98-97-85-124-149-162-163-150-138-123-111-112-99-88-89-127-126-152-153-167-166-140-136</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>53-65-78-81-67-64-52-70-57-29-14-0-12-4-41-40-54-42-30-44-31-18-5-51-38-26-39</t>
+          <t>130-131-120-108-95-109-96-94-107-105-129-116-117-145-158-148-147-121-134-93-92-118-155-156-159-132</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>24-36-35-47-60-73-75-62-50-32-19-7-72-58-33-10-11</t>
+          <t>0-14-40-53-39-51-52-90-65-78-64-38-26-29-54-81-67-42-41-12</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -5886,11 +5886,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>130-129-116-92-94-121-134-132-131-155-145-159-147-148-158-156-118-105-96-95-109-108-120-107-93-90-117</t>
+          <t>32-33-24-11-10-35-72-70-58-44-57-60-75-62-50-36-5-4-47-73-18-30-31-19-7</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5960,35 +5960,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>116-142-120-134-147-148-95-94-93-117-155-156-157-158-144-145-159-161-121-107-118-90-103</t>
+          <t>16-29-53-67-56-30-4-28-14-13-26-64-52-39-41-40-25-12-1</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>98-99-97-126-127-139-125-137-150-165-136-162-167-153-140-154-128-102-115-101-88</t>
+          <t>18-5-8-22-49-50-58-73-74-36-23-24-21-34-19-7-20-33-84-72-61-48-46-57-45</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>73-61-33-45-58-57-46-18-5-8-20-74-84-72-48-49-50-24-23-36-22-21-7-19-34</t>
+          <t>126-128-140-139-136-150-162-165-167-154-153-125-137-97-98-99-88-101-102-115-127</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>64-52-39-13-1-4-56-41-40-28-16-14-26-67-82-30-29-81-80-53-12-25-79-78</t>
+          <t>95-121-145-157-156-158-161-159-147-148-120-107-94-93-78-79-81-80-103-116-155-142-144-118-117-90-134-82</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6058,35 +6058,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>110-113-100-101-98-84-83-125-126-153-123-149-163-164-141-127-87-89-102-115-114-111</t>
+          <t>106-95-121-134-145-159-133-132-118-130-144-120-108-92-90-103-155-143-129-117-105-93</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>42-16-4-43-82-69-56-15-14-0-13-25-12-27-41-54-66-77-39-38-65-64-79-67-53</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>7</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>71-72-74-60-73-19-35-47-48-49-61-32-6-59-58-46-34-7-8-10-23-11-24-62-75-50</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25-27-13-14-41-54-69-43-44-56-70-0-12-38-64-39-53-42-15-16-5-4-67-66-65</t>
+          <t>83-122-149-163-110-148-123-111-100-115-141-153-127-126-113-101-89-87-102-114-98-84-135-161-164-125</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>148-135-133-103-77-121-122-93-106-105-118-143-145-159-120-130-144-155-129-117-79-82-95-108-132-90-92-134-161</t>
+          <t>19-70-71-74-73-46-32-44-59-72-58-10-11-50-75-61-60-48-62-34-47-35-8-24-49-23-7-6-5</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6156,15 +6156,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-103-129-117-145-144-131-121-107-94-130-118-96-132-159-143-160-134-146-104-93-122-135-148-147-161-157-155-142-106</t>
+          <t>6-8-73-74-62-47-44-45-60-48-61-34-22-23-9-19-31-30-18-4-5-72-71-84-7</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>73-86-74-7-18-6-5-19-8-9-22-23-85-84-72-60-61-62-48-34-47-71-45-44-31</t>
+          <t>14-13-12-25-90-77-64-38-0-15-16-27-26-40-68-81-55-42-29-43-82-67-66-65-78-79-80-41</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -6172,19 +6172,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>55-43-42-29-4-16-0-12-13-25-40-67-80-30-15-26-66-79-65-77-78-64-38-41-81-82-68-14-27</t>
+          <t>165-125-85-96-123-136-137-164-163-138-126-154-152-139-112-114-102-101-86-111-99-128-141-167</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>111-123-137-163-126-125-139-152-167-165-154-141-128-138-136-164-112-101-102-114-99</t>
+          <t>145-159-130-155-157-144-131-106-104-117-93-94-107-134-122-121-135-148-161-160-142-129-103-132-146-147-118-143</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>82-83-109-122-146-94-77-103-129-132-142-155-157-119-95-107-130-117-91-92-79-80-134-160-158-104-81-93-133-121</t>
+          <t>121-133-82-95-91-77-103-107-83-109-134-94-119-130-142-155-158-157-160-146-79-92-93-132-81-80-104-129-117</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6262,15 +6262,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>59-20-21-33-47-87-98-99-71-84-60-61-36-23-11-49-89-76-50-62-88-102-100</t>
+          <t>21-20-47-49-11-23-36-50-76-102-89-88-60-59-84-87-62-61-71-33</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>14-27-25-51-41-67-55-4-5-56-57-18-29-28-40-42-31-30-17-2-1-13-12-15-16-54-53</t>
+          <t>13-55-67-29-14-51-25-12-1-16-4-5-18-17-57-42-56-30-31-54-40-53-41-27-28-15-2</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -6278,11 +6278,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>167-166-163-164-137-125-112-123-149-165-154-127-113-126-136-135-161-162</t>
+          <t>99-100-112-126-113-137-136-166-165-135-123-122-161-163-167-154-127-149-162-164-125-98</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6352,35 +6352,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>146-107-106-104-90-91-118-155-156-158-159-160-135-134-147-161-148-121-108-120-133-144-129-116-130-143-142</t>
+          <t>65-77-90-91-67-56-39-12-13-27-41-68-82-81-80-70-69-42-2-1-14-28-29-66-52-26</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>61-74-62-72-47-73-58-46-32-19-63-49-48-35-8-9-22-10-24-7-6</t>
+          <t>111-137-138-151-153-141-127-114-140-87-83-96-98-99-112-125-163-136-122-123-124-97-86-101</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>42-29-5-31-44-56-68-81-52-66-77-65-67-80-27-13-1-14-2-28-41-39-26-12-69-70-18-4-82-83-57</t>
+          <t>120-121-108-107-144-143-148-135-134-158-159-155-156-147-160-161-146-133-104-106-118-129-142-130-116</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>140-153-123-122-96-97-98-86-87-125-136-163-151-141-114-101-112-99-111-137-124-138-127</t>
+          <t>24-48-35-57-18-6-10-9-7-8-22-49-63-62-74-72-58-32-44-31-4-5-19-47-73-61-46</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6450,23 +6450,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>121-108-156-160-161-135-159-131-129-155-157-158-148-109-96-134-145-120-107-119-132-133-144-143-92-105-104-103-116-117-91-106</t>
+          <t>133-120-161-160-157-158-148-134-132-119-106-91-92-105-117-145-131-143-159-144-156-129-116-155-103-104-135-121-108-96-109-107</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>62-37-11-23-46-72-32-45-33-19-21-22-9-20-7-6-8-63-47-49-50-76-61-73</t>
+          <t>43-78-77-51-38-25-40-54-42-29-17-30-4-2-1-13-64-80-56-67-15-27-66-53-41-12</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>15-30-31-17-4-1-40-64-51-38-53-66-67-29-2-42-56-54-41-27-43-57-80-78-77-25-12-13</t>
+          <t>62-63-76-61-23-22-20-46-72-47-21-9-11-8-19-6-7-32-33-73-57-45-31-49-37-50</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -6474,7 +6474,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>138-153-140-113-128-115-102-101-100-149-137-126-111-86-89-87-124-162-163-164-166-167-141-165-152-139-114-112-97-110-123</t>
+          <t>149-163-165-153-164-138-124-123-111-100-114-113-126-152-166-167-141-140-101-112-86-87-89-115-128-102-97-137-110-139-162</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -6548,7 +6548,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84-97-136-162-150-141-149-148-135-85-98-138-125-127-99-100-87-86-88-114-140-128-139-124-96-122-154-166-167-164-151-123-83</t>
+          <t>134-160-133-108-81-107-131-143-144-145-146-158-130-103-118-147-159-142-155-116-80-79-121-96-94-77-90-104-92</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6556,27 +6556,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19-33-46-59-8-6-5-18-72-73-31-45-34-21-7-22-11-10-24-36-35-48-50-63-20</t>
+          <t>24-10-11-7-8-50-88-59-20-6-21-46-35-22-36-48-34-45-33-19-83-70-84-87-63-72-85-73-86</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>40-51-38-79-53-54-42-3-4-30-43-81-70-80-64-77-65-68-69-55-41-67-39-12-14-2-16-28-27-26</t>
+          <t>12-39-28-14-2-3-4-16-69-68-67-41-42-40-26-38-51-64-65-54-55-43-31-18-5-30-53-27</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>131-104-103-90-145-144-143-118-92-116-130-142-155-158-159-146-147-134-108-107-94-121-160-133</t>
+          <t>141-128-139-164-125-99-98-123-136-122-162-167-154-140-127-138-150-149-124-100-114-97-135-148-151-166</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6646,7 +6646,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>105-92-93-147-134-95-119-129-118-117-90-91-132-144-146-145-143-130-116-142-131-121-108-120-159-157-158-160</t>
+          <t>90-65-25-13-12-41-42-53-77-64-67-43-56-3-29-54-68-93-79-80-14-39-78-92-91</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -6654,15 +6654,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>39-13-3-17-29-44-57-70-83-65-79-80-67-54-53-64-77-78-25-68-42-43-56-12-14-5-31-41</t>
+          <t>100-99-111-123-122-97-96-165-166-125-115-126-110-85-86-88-101-141-139-152-151-164-140-98-84-83-162-163-150-154</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60-74-49-62-37-9-21-7-33-22-35-24-23-46-71-58-72-73-61-86-84-85-32-20-48-88-75</t>
+          <t>119-160-161-148-121-159-146-120-132-144-117-105-118-108-95-134-147-145-143-157-158-131-130-129-142-116</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -6670,11 +6670,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>110-122-125-151-162-164-150-161-148-166-140-98-97-111-96-99-115-141-154-165-101-100-163-152-126-139-123</t>
+          <t>46-5-7-9-22-61-58-32-33-20-17-62-75-71-70-72-73-74-48-49-21-35-37-24-23-60-31-44-57</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6744,15 +6744,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>123-162-150-164-152-140-139-111-86-112-113-167-154-141-127-100-101-102-89-114-125-136-98-97-110</t>
+          <t>150-152-135-148-162-100-114-127-140-139-125-113-164-161-136-123-167-154-141-96-97-110-98-86-102-101-112-111-122</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>46-32-20-11-24-23-62-73-74-75-63-49-36-35-21-22-9-47-71-50-37-34-45-19-8-6</t>
+          <t>41-42-30-17-16-18-32-44-43-19-5-6-53-52-51-12-0-2-15-28-3-4-45-57-29-27</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -6760,7 +6760,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>4-3-16-2-5-18-44-30-17-57-43-42-28-41-27-15-29-12-52-64-51-53-0</t>
+          <t>20-21-22-35-49-74-89-50-63-37-36-23-34-47-46-62-75-73-71-9-24-11-8</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -6768,11 +6768,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>78-79-91-92-108-119-94-77-90-131-118-104-155-142-144-158-143-146-148-117-106-80-82-96-95-133-121-134-122-135-160-161-159</t>
+          <t>78-82-108-94-106-118-104-77-79-80-64-90-91-92-131-146-160-158-159-143-142-155-144-133-119-117-121-134-95</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -6842,35 +6842,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>154-152-153-167-123-109-110-101-128-114-115-141-164-151-137-150-136-122-148-124-111</t>
+          <t>34-8-22-11-37-61-71-44-45-57-32-5-18-20-7-75-49-35-6-23-36-74-62-63-72-59-46-33</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>74-87-61-11-36-8-7-20-45-71-70-57-23-37-33-18-5-6-46-59-86-35-22-34-32-44-84-72-62-63-75-49</t>
+          <t>107-157-130-116-104-90-91-93-118-119-133-106-103-129-142-155-143-158-145-144-159-147-134-160-95</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>153-154-128-141-115-87-123-122-124-110-84-109-148-164-150-137-136-111-86-101-114-151-152-167</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>77-64-52-39-14-13-80-79-67-54-53-40-30-2-1-0-4-15-43-17-70-81-78-38-25-66-69-56-28-12-26-27-42-68-82</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>42-43-66-52-68-82-81-17-30-2-4-14-1-0-28-15-38-39-40-53-80-67-69-56-54-13-12-25-26-64-77-78-79-27</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>116-90-129-142-155-145-159-158-157-160-147-106-91-103-134-133-144-143-119-118-107-95-93-104-130</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -6940,31 +6940,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>131-117-104-132-155-143-103-116-119-106-91-107-121-133-120-92-81-95-96-105-118-93-82-108-109-135-145-157-159-160-147-146</t>
+          <t>47-60-35-23-49-48-46-34-33-72-74-62-63-89-87-85-71-45-32-61-37-24-76-75</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>49-63-47-18-5-6-31-57-72-45-74-37-24-23-46-83-85-71-44-32-33-34-35-48-60-87-61-75-76-62</t>
+          <t>150-136-137-151-127-115-102-101-123-149-162-124-125-152-140-141-113-97-112-126-139-166-167</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>78-67-55-54-43-56-15-14-13-25-0-17-30-28-66-77-64</t>
+          <t>117-106-120-132-143-155-104-119-147-146-157-93-105-133-145-118-91-78-77-103-92-81-107-96-121-135-160-159-109-83-82-108-95-131-116</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>167-166-152-151-150-137-136-149-162-139-127-113-101-97-123-124-112-89-102-115-126-125-140-141</t>
+          <t>5-6-17-14-15-28-30-43-56-67-66-64-31-18-44-57-55-54-13-25-0</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -7038,23 +7038,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>99-112-166-88-100-89-101-115-102-154-141-140-124-110-136-149-162-125-165-153-152-114-87-86-113-127-163-164-137-85-97</t>
+          <t>35-11-36-9-5-31-32-60-74-61-62-76-75-49-48-50-47-58-45-59-73-20-19-18-8-21</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>152-166-162-136-124-87-86-100-101-154-153-125-112-89-102-165-164-163-149-97-110-137-140-141-99-113-114-115-127-88-85</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>59-58-19-35-50-36-11-9-21-8-60-47-45-49-76-75-62-48-61-73-74-20-32</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18-5-40-52-39-38-0-15-31-30-17-28-14-41-43-42-64-65-56-68-66-55-29-16-2-26-12-25-1</t>
+          <t>14-26-40-55-42-41-68-56-80-77-78-25-12-38-30-43-17-29-52-64-65-0-15-79-66-39-28-16-2-1</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -7062,11 +7062,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>109-160-157-108-106-92-91-90-103-94-107-83-80-77-116-130-129-145-144-118-79-78-93-95-134-147-161-133-146-156-119-120-122</t>
+          <t>83-118-130-116-90-103-92-93-120-108-94-95-122-109-157-156-146-133-106-129-145-144-134-147-161-160-107-119-91</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -7136,7 +7136,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>105-116-142-104-78-77-83-82-121-107-133-145-144-132-147-160-134-120-143-155-157-130-118-93-80-95</t>
+          <t>83-66-78-64-77-39-38-25-26-13-4-17-2-27-52-53-67-82-69-80-30-28-15-40-65-12-43-56</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -7144,7 +7144,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>58-32-73-63-50-37-35-20-19-7-10-36-89-74-46-21-22-8-11-24-47-60-59</t>
+          <t>152-115-114-113-149-148-161-135-122-126-153-166-164-165-139-140-125-98-111-150-163-151-137-124-112-99</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -7152,7 +7152,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12-26-25-13-39-40-67-69-57-44-31-15-27-56-43-17-18-30-66-53-38-64-52-65-2-4-5-28</t>
+          <t>57-74-73-84-24-11-46-58-44-7-21-8-10-36-63-89-37-50-22-35-60-47-59-20-5-18-19-32-31</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -7160,11 +7160,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>115-153-126-113-111-125-137-150-161-148-135-122-124-165-164-152-99-84-98-114-112-139-151-149-163-166-140</t>
+          <t>147-160-133-132-105-104-116-118-142-155-157-120-121-134-107-95-93-130-143-144-145</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -7234,7 +7234,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>161-147-107-119-160-158-157-155-142-130-144-131-132-134-135-148-146-156-103-90-94-92-93</t>
+          <t>96-94-119-146-148-149-162-147-144-131-130-156-158-161-160-135-109-122-134-157-155-142-132-107</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -7242,7 +7242,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17-4-31-44-56-12-52-64-25-38-26-15-3-16-30-42-67-39-28-66-53-65-77-78-69-68-80-41-70-57-55</t>
+          <t>15-41-42-16-38-25-12-52-93-80-68-56-69-92-78-90-77-103-64-65-26-3-28-55-67-66-53-39</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -7250,19 +7250,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>59-33-36-11-22-21-34-47-8-6-19-35-50-37-24-23-62-75-73-58</t>
+          <t>30-44-70-57-58-6-34-35-50-37-8-19-4-17-31-33-62-59-73-21-22-36-24-11-23-47</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>115-127-140-150-114-102-88-86-96-84-109-162-137-124-112-99-113-128-154-151-138-98-111-153-152-139-100-110-122-149-123-101</t>
+          <t>128-115-114-98-84-124-113-75-88-102-151-123-110-111-86-99-100-137-127-112-101-150-139-138-152-154-153-140</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -7332,35 +7332,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>84-122-100-87-102-101-114-138-151-111-123-148-153-139-137-150-152-165-163-110-97-85-126-128-140-112-83</t>
+          <t>105-106-118-131-94-120-147-146-132-119-134-143-155-158-157-159-78-92-79-90-103-116-117-104</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>22-48-49-36-50-24-33-46-58-71-45-32-76-62-35-47-34-21-8-7-6-20</t>
+          <t>42-5-4-18-17-13-1-3-0-14-16-15-55-66-41-54-56-83-57-44-30-29-28-52-64-65-70-81</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>52-66-30-44-4-16-1-3-5-18-17-42-56-70-57-29-41-54-55-28-15-14-13-0</t>
+          <t>138-126-100-114-151-165-163-150-148-137-112-111-123-153-140-139-152-128-102-101-97-110-122</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>120-134-147-146-159-157-158-103-90-116-117-143-155-131-78-64-65-92-105-104-118-132-81-79-94-106-119</t>
+          <t>76-33-45-32-20-22-35-34-48-58-87-50-36-24-85-84-71-46-21-6-7-8-47-49-62</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -7430,35 +7430,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>107-94-96-148-161-120-93-92-116-158-160-135-109-95-118-130-143-155-129-131-157-145-159-106-91-105-132-144-90-117-103</t>
+          <t>42-55-57-44-5-30-18-67-66-53-39-25-0-4-17-2-40-1-14-27-56-70-83-65-54</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2-1-65-66-55-56-54-53-67-81-78-77-79-39-30-42-40-25-27-17-4-0-14</t>
+          <t>72-32-58-21-7-45-19-49-10-35-47-46-60-33-22-11-37-62-63-76-75-85-86-102-88-74-61-73</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>94-95-96-129-130-159-155-143-144-158-132-120-81-107-116-103-77-91-118-117-131-145-157-78-79-90-105-106-92-93</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>136-114-115-128-141-154-167-127-164-150-137-109-98-123-135-161-160-162-149-148-163-166-139</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>47-49-22-7-32-5-70-72-61-33-18-19-35-45-44-57-60-46-62-37-88-63-76-75-74-73-86-85-58-21-10-11-83</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>139-162-137-98-114-102-115-128-154-167-166-164-150-163-149-136-123-127-141</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -7528,31 +7528,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>82-83-148-144-143-142-160-161-135-122-96-108-118-129-116-103-93-79-105-133-120-130-131-119-95-109-104-90-117-94-134-159-147</t>
+          <t>129-116-131-159-160-94-95-105-104-117-93-79-119-144-143-130-142-118-120-133-134-147-108-90-103</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>48-11-10-35-58-32-19-9-22-36-49-62-76-50-6-46-20-21-59-73-74-61</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>124-85-87-102-88-86-97-123-149-164-152-162-111-112-125-127-128-141-140-166-126-150-137-98-100-113-122-135-148-161-109-84-83-96</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>61-36-50-76-48-22-10-6-5-19-32-59-73-35-49-9-11-18-31-58-20-21-74-62-46-44-70</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0-4-17-43-69-68-55-41-30-3-16-15-2-28-27-42-39-52-51-64-66-65-13</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>124-137-126-141-140-152-166-164-149-150-162-128-127-113-112-102-88-86-87-100-125-123-97-85-84-98-111</t>
+          <t>18-17-16-27-13-0-28-41-55-39-52-66-69-70-82-68-65-64-51-2-3-15-4-42-30-43-31-44-5</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -7626,35 +7626,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>78-104-130-116-129-117-79-80-91-107-155-142-156-157-131-108-121-133-147-159-132-146-145-118-92</t>
+          <t>59-47-60-34-33-19-7-8-9-37-50-45-71-58-75-62-63-76-48-24-11-10-6-32</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>84-83-86-110-111-113-140-128-100-114-87-101-89-102-99-112-137-166-167-153-163-164-150-97-136-139-141-127-152-138-124-109-123</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>157-155-117-78-79-91-131-118-146-161-148-133-130-129-142-156-145-147-108-121-116-104-92-80-107-132-159</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0-26-16-17-4-5-82-67-54-51-52-64-55-31-29-42-66-13-25-38-28-14-2-3</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>28-42-55-25-38-51-52-16-17-29-54-67-66-64-82-31-3-2-0-13-26-5-4-14</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>62-75-47-58-71-8-9-11-24-37-50-63-76-10-33-60-59-48-34-45-32-19-6-7</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>148-109-89-114-164-152-128-102-101-113-136-124-111-83-84-97-86-139-140-87-100-127-141-150-161-137-110-123-99-112-138-153-167-166-163</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -7724,35 +7724,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>150-110-98-140-139-100-101-102-141-128-127-126-113-112-137-138-149-136-125-152-167-165-162</t>
+          <t>2-1-29-54-64-26-12-0-40-53-66-3-4-17-30-31-69-68-55-56-25-39-27-41-28</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>70-60-62-10-19-34-35-75-88-76-63-49-61-73-46-47-20-48-9-8-32-58-72-87-84-71</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>93-94-83-96-135-146-134-133-91-103-118-119-105-90-117-116-143-155-158-82-80-95-107-109-122-160-145-92-79</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>136-138-150-162-149-112-98-125-165-167-141-140-127-128-126-113-102-101-100-110-137-139-152</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>40-28-29-2-3-1-12-39-4-17-41-53-64-66-54-55-30-31-56-69-68-27-0-25-26</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>47-48-49-63-62-34-20-19-9-35-8-10-76-61-60-32-58-70-71-72-73-88-75-87-84-46</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>155-116-79-80-82-95-92-91-90-103-117-105-119-145-146-160-118-122-109-83-96-135-134-133-93-94-107-158-143</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -7822,7 +7822,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>137-150-113-167-164-165-141-128-127-102-115-153-152-162-151-138-139-126-140-114-112-110-97-149-124-111-99</t>
+          <t>64-81-80-68-82-55-56-30-0-13-2-3-16-79-65-39-69-43-15-27-25-38-51-52-40-29-17-54-66-77</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -7830,15 +7830,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3-16-29-56-43-15-51-25-2-17-30-13-38-39-0-27-40-52-65-80-82-69-68-79-77-64-66-81-55-54</t>
+          <t>130-129-156-155-119-118-117-132-146-158-134-120-107-95-96-108-94-106-90-103-116-133-159</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23-36-8-71-83-84-87-88-33-19-5-44-58-9-10-24-63-73-45-72-86-74-60-59-46-47-61</t>
+          <t>112-99-138-137-162-150-152-139-127-114-102-115-128-140-141-167-165-164-113-126-151-153-111-97-135-161-149-124-110</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -7846,11 +7846,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>119-132-129-158-159-161-135-134-95-94-107-106-133-120-146-156-155-117-90-103-116-130-118-108-96</t>
+          <t>63-61-60-73-72-58-46-33-5-19-59-74-87-88-36-23-47-71-84-86-83-8-9-10-24-45-44</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -7920,31 +7920,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>103-143-161-160-122-132-104-142-156-144-157-145-159-106-119-118-130-117-95-107-133-134-135-121-148-109-108-91</t>
+          <t>57-32-33-21-31-6-7-8-37-36-35-89-76-75-63-60-59-44-18-5-72-85-83-70-73-88-86-45-34-23-10</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43-69-42-41-39-26-53-0-1-14-12-25-38-51-79-80-81-66-64-77-78-28-29-54-56</t>
+          <t>148-109-98-140-139-152-151-111-123-137-138-165-150-164-167-166-114-102-127-126-128-101-99-135-122-149-161</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>23-36-37-63-75-76-5-18-17-4-31-34-35-8-21-32-59-72-6-7-10-33-83-70-57-85-73-60-45-44</t>
+          <t>95-108-106-103-119-143-144-130-132-133-134-121-118-117-104-91-159-145-142-156-157-160-107</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>86-114-151-137-152-167-166-138-126-140-139-150-149-123-102-89-88-101-127-128-165-164-111-98-99</t>
+          <t>25-38-1-4-17-29-79-66-41-28-42-43-56-54-69-80-81-77-78-12-0-14-26-39-53-51-64</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -8018,15 +8018,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>130-142-116-143-145-118-78-77-80-94-95-91-79-93-146-134-109-122-135-148-156-129-90-104-117-144-158-159-147-81</t>
+          <t>95-91-116-144-146-147-134-143-130-129-142-156-145-159-158-118-117-104-78-90-77-93-80-79-94-81</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20-22-72-84-71-6-33-58-87-75-47-59-74-49-37-24-35-62-88-76-61-23-10-11-9-34-32</t>
+          <t>123-109-84-115-102-166-165-163-150-153-141-126-138-125-111-98-101-113-112-135-122-148-137-139-154-167-100</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -8034,19 +8034,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39-26-14-15-17-4-18-44-42-41-54-56-43-66-38-52-64-13-12-1-3-31-57-68</t>
+          <t>54-15-1-12-26-38-52-39-64-66-4-3-17-44-68-56-57-31-18-43-41-13-14-42</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>101-115-126-141-153-139-154-167-166-165-150-163-123-125-138-137-111-98-102-100-112-113</t>
+          <t>74-75-87-88-59-71-72-61-37-23-9-34-47-33-32-58-20-6-11-24-10-22-49-76-62-35</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -8116,15 +8116,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>116-155-131-142-132-147-160-146-156-129-130-120-93-94-158-134-122-109-95-107-143-161-133-96-108-119-91-77-103-104</t>
+          <t>33-46-34-21-24-23-63-50-62-61-75-100-101-45-47-60-71-74-86-85-99-102-76-48-22-11</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>85-86-19-6-34-21-22-32-33-61-24-23-48-47-60-11-50-62-74-75-63-76-71-45-46</t>
+          <t>3-18-17-28-69-53-39-25-26-41-65-64-51-43-70-57-68-55-44-19-5-31-4-6-32-30-29-0-2-15</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -8132,7 +8132,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>57-44-31-69-70-43-5-4-29-30-41-53-55-68-51-25-28-17-18-3-2-15-39-65-64-26-0</t>
+          <t>119-156-133-96-109-95-93-94-107-120-134-132-130-104-77-103-129-143-158-160-147-122-108-131-91-116-155-142-146</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -8140,11 +8140,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>152-141-128-154-153-166-163-162-149-136-164-165-151-110-124-126-101-114-127-140-102-100-99</t>
+          <t>140-154-141-165-162-149-161-163-164-151-124-110-136-152-166-153-126-114-127-128</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -8214,15 +8214,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>143-119-78-91-92-106-79-133-145-158-157-146-131-155-129-90-105-132-81-94-108-83-96-95-117-103</t>
+          <t>91-79-78-119-145-160-146-106-143-155-158-117-94-83-81-105-92-95-96-108-131-157-133-132-103-90-129</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>88-50-61-89-63-76-37-24-35-49-48-47-22-21-19-45-33-59-72-73-87-84-60-6-8-11-62-36-7-20-58</t>
+          <t>72-84-73-76-89-61-6-7-21-22-47-87-63-88-45-58-33-19-20-8-49-37-36-48-24-11-50-62-35-60-59</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -8230,19 +8230,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69-57-30-55-53-67-68-66-3-2-1-14-42-29-27-26-65-64-38-15-5-43-56-41-25-13-16-44-18-17-54-51-28</t>
+          <t>137-124-98-99-123-161-162-149-148-135-163-152-164-136-101-97-112-153-167-154-115-140-151-138</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>3-2-27-66-64-51-25-13-14-65-38-68-42-30-17-16-28-5-18-69-54-67-57-56-44-55-43-26-1-53-41-29-15</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>97-99-167-154-140-153-152-151-164-123-138-124-137-135-136-149-161-160-148-163-162-115-101-112-98</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -8312,35 +8312,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>106-105-92-90-81-80-79-146-145-131-142-155-156-144-119-108-120-159-158-134-132-94-95-130-129</t>
+          <t>58-84-74-75-37-24-22-86-87-76-50-48-59-71-46-45-6-21-32-44-83-70-47-10-9-35-34-73-72-63-60</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>52-55-43-18-42-29-16-5-2-0-25-38-51-53-40-39-27-3-1-13-12-26-41-67</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>112-110-163-161-123-109-96-111-124-113-126-140-127-115-101-100-114-152-148-162-166-154-167-153-151</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>45-32-47-74-75-73-35-48-37-24-10-6-9-22-63-76-50-44-70-83-84-86-87-58-71-72-59-46-34-21-60</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>18-5-3-16-29-55-43-42-41-52-25-12-38-51-67-53-40-39-27-13-0-1-26-2</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>110-111-113-127-140-115-114-124-163-100-101-153-154-167-151-152-166-161-162-123-109-96-148-126-112</t>
+          <t>95-81-105-142-155-158-145-156-129-90-80-79-92-132-159-144-131-130-119-106-94-120-146-134-108</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -8410,23 +8410,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>111-162-163-112-98-99-113-114-101-127-138-151-137-86-88-115-128-139-152-149-164-154-166-124-110</t>
+          <t>3-4-16-15-28-42-69-68-30-29-41-80-82-81-53-12-26-1-13-64-51-65-38-25-79-77</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>101-86-88-115-127-112-111-110-98-113-99-138-162-163-164-139-152-128-114-166-154-151-149-137-124</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>15-4-16-29-28-41-53-80-81-79-51-64-30-69-82-68-42-3-26-25-12-13-1-65-38-77</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>44-45-60-73-74-76-84-70-32-18-5-31-20-6-10-35-24-36-49-48-7-33-34-37-50-75-47-58-57</t>
+          <t>76-75-60-70-58-45-35-36-7-20-32-57-18-5-31-44-6-33-47-34-49-50-37-24-10-48-84-73-74</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -8434,7 +8434,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>92-143-157-161-122-108-94-107-120-133-146-129-144-158-147-109-121-106-105-118-116-155-103-90</t>
+          <t>90-103-105-118-146-161-122-121-120-107-106-94-109-108-144-157-129-143-116-133-147-158-155-92</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -8508,7 +8508,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>121-95-78-91-90-77-118-146-157-155-142-103-105-92-104-117-119-159-145-94-93-116-129-143-130-106-133-160-147</t>
+          <t>14-66-67-80-55-42-56-30-17-5-18-40-52-64-65-16-3-26-69-70-83-68-82-81-54-44-57-27-25-12</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -8516,27 +8516,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>60-88-87-61-59-85-58-46-48-36-35-21-22-11-24-23-63-76-62-49-10-7-19</t>
+          <t>162-141-154-167-166-164-124-100-125-137-136-123-135-148-149-165-128-140-139-151-138-99-98-111-122</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>103-117-142-129-118-121-95-94-78-77-90-91-104-105-93-119-106-92-155-157-146-133-147-160-159-145-130-143-116</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>22-10-11-24-21-19-7-46-59-62-63-76-35-48-36-23-49-87-88-61-60-85-58</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>80-83-70-69-30-18-44-56-14-42-57-17-5-3-16-68-40-52-65-64-26-27-66-67-54-55-81-82-25-12</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>125-166-165-164-167-140-128-99-137-151-162-136-122-135-124-100-98-111-123-148-149-138-141-154-139</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -8606,35 +8606,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>93-94-119-157-155-156-130-105-131-144-146-133-134-160-158-106-96-95-122-107-118-92-91-129-117-116-103-90</t>
+          <t>32-46-59-73-85-84-71-58-34-23-11-8-7-33-19-18-35-37-49-62-75-21-20-6</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>153-165-164-149-150-136-137-151-123-114-102-115-127-112-97-110-138-141-128-140-154-152-139-101-87-89</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>43-42-56-54-66-64-25-12-0-40-52-83-70-69-27-14-15-29-28-30-68-80-79-67</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>28-15-29-70-83-68-67-54-42-43-56-79-80-69-66-64-52-27-14-12-25-0-40-30</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>7</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>23-11-37-62-49-35-20-18-32-8-7-19-6-21-34-59-58-85-73-75-33-46-71-84</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>87-102-115-152-138-150-151-165-164-149-136-101-89-114-112-123-110-97-137-153-139-127-154-141-140-128</t>
+          <t>119-118-116-117-96-95-106-93-94-122-134-146-157-107-133-131-129-130-105-92-91-90-103-160-158-155-156-144</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -8704,7 +8704,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>107-134-147-121-132-145-159-157-158-91-106-120-133-118-143-155-142-129-130-103-90-104-105-79-93-119</t>
+          <t>20-33-72-71-8-9-23-11-76-62-36-10-34-35-37-50-63-74-59-45-19</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -8712,27 +8712,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>74-34-20-23-8-9-11-10-62-87-72-71-45-19-33-35-37-36-50-63-76-59</t>
+          <t>147-159-134-121-107-93-79-105-130-129-103-90-104-118-145-158-133-157-132-119-106-143-155-142-91-120</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0-12-25-26-43-30-16-15-29-41-54-53-64-66-67-65-55-68-57-69-17-4-2-28-14-1</t>
+          <t>126-141-152-151-138-164-109-122-123-150-165-154-167-128-125-110-149-162-135-86-87-101-114-124-83-84-98-99-102-115-112-137-148-161-97</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>126-114-102-154-167-164-135-122-123-109-97-84-83-86-98-124-110-161-152-165-151-137-148-125-101-115-112-128-141-162-149-150-138-99</t>
+          <t>15-29-43-68-69-57-55-41-26-25-14-0-1-16-17-4-2-12-53-54-30-66-64-65-67-28</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -8802,35 +8802,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>87-140-165-141-126-150-139-100-101-115-128-154-99-110-123-137-124-149-162-164-152-125-114-86-85</t>
+          <t>29-57-69-70-41-13-1-25-64-68-43-4-16-42-83-81-66-52-51-26-40-67-44-30-18-31-28-39-54-80-3-2</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>45-47-34-33-20-32-74-62-63-49-36-24-37-50-61-48-11-10-9-8-21-22-75-73</t>
+          <t>101-114-140-162-135-148-137-126-128-125-110-85-87-154-165-164-152-139-100-124-123-149-161-150-99-86-115-141</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>48-49-73-45-32-8-22-36-62-75-63-50-37-11-10-24-9-21-47-61-74-34-33-20</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>7</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>13-52-51-69-83-70-31-43-42-29-41-44-57-68-54-64-79-39-67-81-80-3-2-28-25-26-30-18-4-1-66-40-16</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>119-147-161-148-159-158-142-117-116-93-107-94-118-131-135-121-95-145-144-155-103-92-77-90</t>
+          <t>93-94-121-147-144-142-155-145-159-158-131-117-118-119-116-77-90-103-92-79-95-107</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -8900,31 +8900,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>157-160-146-145-132-118-117-116-103-91-120-133-119-131-143-90-78-83-96-109-80-94-161-122-107-108-144</t>
+          <t>131-90-91-103-116-117-94-107-119-108-96-109-122-145-146-132-161-160-144-143-157-133-120-118</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>15-43-30-42-67-54-68-55-40-28-4-3-26-25-13-27-52-39-51-64-41-69-17-16-2-1</t>
+          <t>111-98-137-153-154-141-140-97-85-89-115-102-100-99-112-139-166-165-152-125-163-162-123-110-88-101-113</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>6-33-44-31-70-57-32-21-11-37-49-75-61-74-58-46-59-62-63-36-23-22-9</t>
+          <t>58-63-62-61-59-74-75-46-33-21-9-22-11-36-49-37-23-6-32</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>89-88-115-154-163-139-140-141-101-100-85-97-137-152-166-165-153-111-113-102-99-98-110-123-162-112-125</t>
+          <t>43-69-83-68-67-55-41-28-16-13-1-15-2-70-42-54-26-27-40-64-52-39-25-51-78-80-4-3-31-17-30-44-57</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -8998,35 +8998,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>121-108-106-78-118-132-145-158-77-90-103-116-119-133-146-157-156-155-129-130-143-144</t>
+          <t>153-166-141-114-102-126-138-161-148-136-167-140-84-110-123-124-137-151-125-113-99-150-135-86-100-88-115-139-164-163-149-109-111-97-96</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>21-61-36-22-8-6-7-20-72-84-86-88-75-74-73-71-23-11-49-34-32-33-58-59-60-46-47-62-76</t>
+          <t>51-54-80-69-70-82-53-77-78-57-68-12-13-26-0-14-16-17-4-3-31-56-30-44-41-66-27-29-42-28-25</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30-5-69-68-42-54-82-66-28-29-16-17-41-12-0-14-25-51-27-3-4-31-44-56-57-70-80-53-26-13</t>
+          <t>62-49-36-8-21-23-22-20-73-74-75-76-61-72-60-47-33-32-58-71-59-46-34-5-7-6-11</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>123-138-135-148-149-139-153-163-151-114-102-115-100-126-124-137-164-140-141-113-99-111-110-96-136-125-167-166-150-161-97-109</t>
+          <t>133-118-130-129-103-90-116-155-157-156-143-144-145-132-121-108-119-106-146-158</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -9096,31 +9096,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>130-157-158-107-94-81-79-80-119-133-145-144-131-155-142-103-78-92-91-129-143-118-105-117</t>
+          <t>117-142-143-144-131-130-103-91-94-92-105-133-145-158-157-155-129-118-119-107</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>9</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>13-27-15-16-17-30-43-56-41-66-81-78-65-52-53-28-0-2-29-42-80-79-25-12</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>7</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>58-45-71-35-23-24-36-50-48-46-73-74-62-11-9-21-22-32-6-19</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>8</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2-15-13-12-0-53-52-25-29-43-30-17-42-66-65-27-28-41-56-57-44-18-5-16</t>
+          <t>62-50-36-23-24-6-32-45-57-58-71-46-35-22-9-11-21-18-19-5-44-48-74-73</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>84-100-88-99-114-102-89-115-140-126-150-149-135-148-163-162-136-123-111-113-112-87-83-109-128-154-166-124-137-151-152-110-97</t>
+          <t>87-113-112-124-149-163-152-140-126-83-84-99-97-123-114-115-128-137-150-151-166-154-135-162-148-136-111-89-102-110-109-100-88</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -9194,35 +9194,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>104-121-109-122-105-143-155-145-135-161-147-160-158-146-108-95-107-156-144-131-117-129-130-118-120-133-106-90</t>
+          <t>72-60-47-61-6-9-48-85-73-71-84-87-89-76-50-37-24-49-36-32-33-34-74-75-21-7-22-10-11-45-58-59</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>58-71-21-9-75-89-76-72-85-84-6-7-32-33-59-61-87-74-73-60-47-34-10-24-11-37-22-36-50-49-48-45</t>
+          <t>104-117-130-156-155-143-144-158-146-147-160-95-108-121-133-118-105-106-90-107-120-145-131-129</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>70-57-0-12-38-28-27-40-53-67-65-55-56-39-25-54-43-29-4-31-18-83-82-79-66-2-15-17-30-41</t>
+          <t>27-4-2-0-28-15-31-57-56-79-65-38-39-40-54-55-70-18-29-17-30-41-25-12-43-83-82-67-66-53</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>101-114-113-137-149-150-164-153-167-165-166-141-140-151-138-126-97-123-162-136-98-99-124-139-102-100</t>
+          <t>122-135-161-123-101-100-126-140-141-102-114-151-150-162-136-149-109-97-139-165-166-167-153-164-99-98-124-113-138-137</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -9292,35 +9292,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>118-116-90-103-105-95-119-156-157-134-109-108-121-148-161-160-158-145-132-130-144-143-159-147-93-94-92</t>
+          <t>82-83-57-31-16-3-1-0-13-27-39-77-51-68-67-66-42-53-52-78-79-80-54-15-14-29-4-56-81-69</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>98-150-166-164-151-167-154-102-128-127-140-125-113-110-137-139-149-136-123-99-97</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>63-75-61-36-22-62-76-88-73-60-32-45-71-85-89-72-59-47-10-11-20-19-34-49-50-37</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>147-148-134-158-159-144-116-103-105-94-145-157-156-132-121-109-108-95-93-92-90-130-143-118-119-160-161</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>14-31-42-66-52-39-54-68-67-78-27-15-13-3-16-29-53-51-77-79-80-81-83-69-82-56-57-4-1-0</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>10-19-32-20-73-61-76-89-75-85-60-59-71-72-45-47-34-22-37-50-36-49-63-88-62-11</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>150-137-139-127-140-149-151-164-167-166-154-113-98-110-97-123-99-102-128-125-136</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -9390,35 +9390,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>152-166-123-111-124-138-113-101-114-100-99-125-126-140-141-154-167-164-150-98-97-102-115-153</t>
+          <t>86-88-113-126-125-97-84-98-111-150-123-124-100-87-85-99-141-140-164-166-167-154-114-101-102-115-153-152-138</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>29-42-44-57-28-79-80-67-64-53-70-81-68-69-26-40-55-14-2-0-13-17-43-15-25-12-3-18</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>94-117-116-155-131-158-160-161-119-90-104-91-93-147-120-133-144-157-143-156-145-146-132-121-106-107-109-96-95</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>24-37-60-73-72-71-59-45-58-8-6-19-33-35-10-36-63-75-74-61-62-49-50-76-48-46</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>12-14-42-43-70-69-81-79-80-55-57-67-53-15-2-3-17-29-28-40-26-25-64-68-44-18-13-0</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>59-58-19-33-60-88-76-62-50-49-36-37-24-61-73-86-87-84-45-46-63-75-6-8-10-35-48-74-72-85-71</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>120-145-143-104-133-161-146-160-147-158-144-157-156-155-116-117-131-132-119-96-90-91-94-95-106-93-107-121-109</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -9488,7 +9488,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>135-148-161-149-151-152-111-98-124-125-89-115-102-126-140-166-165-164-139-114-100-112-150-167-153-96-85-110-109</t>
+          <t>140-102-115-153-166-167-152-164-150-124-96-83-85-98-114-126-139-111-151-165-125-112-100-110-135-149-161-148-109</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -9496,27 +9496,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>14-13-27-25-52-40-53-70-5-4-2-16-29-83-82-31-18-28-42-30-43-68-67-66-39-15-0</t>
+          <t>103-134-121-95-81-80-92-91-104-118-107-120-79-64-78-82-93-130-129-143-155-142-90-77-131-158-146-144-116</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>20-19-32-36-49-34-33-72-58-46-60-76-89-75-62-24-11-23-21-8-9-6-7-10-22-37-50</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>21-34-19-6-7-9-11-24-23-46-72-58-60-62-75-76-50-37-49-33-32-8-10-36-22-20</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>79-78-118-129-134-120-107-144-143-155-142-158-121-95-80-81-146-131-130-92-93-104-90-91-103-116-77-64</t>
+          <t>39-25-0-14-28-29-30-31-18-5-43-42-70-68-66-67-53-16-4-15-2-13-27-40-52</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -9586,35 +9586,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>83-93-92-134-160-130-156-146-120-105-79-77-90-143-131-104-91-103-118-147-121-122-96-95-107-82-119-157-145-159-161-148-135-80-81</t>
+          <t>9-6-7-48-61-76-35-34-33-20-32-45-19-21-47-73-59-46-60-49-24-11-37-50</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>88-86-85-45-32-20-19-33-73-61-34-47-59-21-6-7-24-37-46-60-49-35-48-76-50-9-11</t>
+          <t>137-136-163-150-165-167-166-138-110-111-85-86-114-140-141-151-139-128-127-126-99-88-101</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5-3-4-2-70-57-31-44-14-1-0-26-39-27-28-53-68-56-43-42-40-51-52</t>
+          <t>96-119-145-134-122-81-93-92-91-103-105-131-143-159-135-148-79-107-104-130-156-157-77-90-118-146-147-161-160-121-82-83-95-120-80</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>110-111-101-114-136-137-150-163-151-167-166-165-140-138-141-128-127-139-126-99</t>
+          <t>70-56-68-42-57-5-4-43-53-2-3-1-0-27-40-28-51-52-39-26-14-31-44</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -9684,23 +9684,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>122-110-101-141-162-98-86-84-97-99-126-140-115-127-137-135-136-102-100-164-148-161-163-153-152-166-167-83</t>
+          <t>41-28-53-79-40-67-68-81-69-42-25-27-39-66-78-65-51-64-52-29-3-14-12-0-2-15-17-16-55-56-43</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>58-72-71-62-63-49-50-61-59-24-11-10-21-19-20-7-33-45-47-22-9-76-73-34</t>
+          <t>110-136-152-140-115-102-101-99-126-100-137-167-166-153-164-163-162-141-127-98-97</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>57-56-31-17-18-5-3-2-67-81-68-69-55-43-28-41-66-52-12-0-15-14-27-42-29-25-51-65-64-39-53-40-16</t>
+          <t>61-22-9-49-62-63-50-24-34-47-45-59-72-21-11-10-7-20-5-31-33-19-18-58-84-83-57-71-73-76-86</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -9708,7 +9708,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>103-116-146-120-121-108-155-142-156-157-159-147-133-118-105-92-91-117-130-129-143-94-107-79-78</t>
+          <t>156-142-155-143-129-130-92-105-157-159-161-147-94-107-118-116-117-91-103-120-133-146-148-135-121-122-108</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -9782,35 +9782,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>97-162-163-127-140-164-136-137-126-114-113-115-166-152-124-123-149-161-122-109-111-99-85-84-125-167-141-100-87</t>
+          <t>65-77-129-143-146-95-93-91-116-117-118-132-120-119-92-80-106-105-103-142-155-156-144-64-79-78-90</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>55-68-41-40-28-29-30-43-69-56-2-0-26-1-3-15-27-52-53-18-17-39-25-38-16-4-44</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>20-6-8-7-9-37-10-61-60-46-62-63-76-87-73-72-59-48-49-21</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>163-164-127-152-137-123-122-109-111-84-97-124-136-162-113-100-85-115-114-140-141-167-166-147-161-149-125-126-99</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>60-59-46-7-21-10-37-49-48-61-63-9-8-6-20-62-76-72-73</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>30-28-29-4-3-15-2-55-68-0-1-16-26-25-38-52-39-64-65-53-18-17-41-40-27-43-69-56-44</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>146-144-120-95-90-77-155-156-143-142-116-103-80-93-92-91-106-132-147-119-105-118-78-79-117-129</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -9880,15 +9880,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>148-135-163-164-122-109-96-84-99-100-101-114-140-141-167-154-166-153-162-124-98-112-152-126-115-102-150-149-161</t>
+          <t>146-145-156-147-148-161-160-159-134-79-77-78-80-109-122-143-117-129-155-142-116-130-92-94-95-96-120-108-135-106-119-132-118-131-121-91</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7-6-74-89-87-86-85-48-34-19-46-47-35-21-20-22-23-49-61-50-37-63-73-71-45-32-33-24-10-8</t>
+          <t>5-18-54-65-64-66-67-27-41-31-16-2-4-17-70-43-44-56-55-42-28-13-0-15-53-68</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -9896,19 +9896,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>43-18-31-15-0-4-16-70-68-54-53-28-2-65-64-66-67-56-44-5-17-13-27-41-42-55</t>
+          <t>162-149-163-166-167-153-141-154-126-152-164-150-140-115-102-101-114-100-112-98-99-124</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>129-132-119-106-94-77-78-95-108-92-79-80-118-131-156-155-145-146-160-159-130-116-91-117-134-147-121-120-143-142</t>
+          <t>32-10-24-8-7-20-19-6-35-37-49-86-87-63-89-74-71-34-22-21-33-47-46-61-73-84-85-48-50-23-45</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -9978,35 +9978,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>130-143-155-144-117-104-90-103-129-157-158-146-121-108-94-160-159-147-106-92-119-131-116</t>
+          <t>8-60-48-24-23-21-37-49-74-86-85-59-63-76-88-62-36-61-73-72-58-7-46-32-19</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>135-160-147-121-119-158-161-122-108-94-90-116-103-155-143-129-117-104-130-144-157-159-131-92-106-146-148</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>111-100-101-113-139-151-136-110-123-137-140-153-141-165-152-138-97-98-127-154-167-126-112</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>7</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>46-24-37-60-74-63-49-61-62-76-23-21-58-85-88-86-32-7-19-8-36-48-73-72-59</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>4-18-82-69-27-14-39-40-29-16-3-17-41-52-67-44-55-57-31-42-68-80-81-70-28-2-1-0-13-38-64-15-5</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>100-112-139-151-136-127-140-167-101-110-123-148-161-135-122-152-165-153-154-141-126-111-98-97-137-138-113</t>
+          <t>16-4-5-18-31-44-69-82-70-57-55-28-15-14-39-38-13-0-1-2-3-52-64-40-27-42-29-17-81-80-67-68-41</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -10076,35 +10076,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>80-93-106-146-133-160-108-94-78-79-77-142-155-143-130-157-159-145-131-156-116-119-118-117-92-120-81</t>
+          <t>113-114-127-149-164-151-138-148-135-136-137-98-109-122-123-110-112-124-125-139-154-165-163-162-152-153-167-128</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>59-22-36-10-9-7-31-32-84-72-87-75-50-37-24-89-60-33-20-6-18-83-57-44-45</t>
+          <t>57-44-24-37-36-59-60-89-87-75-32-31-6-7-9-10-22-20-18-45-72-84-83-50-33</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39-53-52-38-25-51-64-30-4-17-1-13-12-26-40-55-43-16-3-2-14</t>
+          <t>108-160-159-117-142-155-130-143-116-77-92-78-79-118-145-157-156-146-133-131-106-80-94-93-119-120-81</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>112-98-113-164-163-162-149-109-122-135-148-114-127-139-110-123-136-137-124-151-165-128-138-152-153-167-154-125</t>
+          <t>55-13-1-2-14-26-38-64-51-52-40-53-39-25-12-43-30-17-16-3-4</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -10174,35 +10174,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>108-158-157-156-142-144-120-119-129-155-90-91-92-93-107-134-133-106-118-130-117-116-103-104-94-81</t>
+          <t>97-99-152-164-163-161-165-151-166-126-110-98-114-127-115-153-141-102-101-100-122-96-111-124-125-138-137-162-135</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>28-41-42-56-44-31-30-43-54-64-51-0-15-5-18-3-2-1-26-27-14-12-25-66-68-55</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>104-92-106-81-93-116-129-142-155-156-117-130-119-108-94-107-120-91-90-103-144-133-134-158-157-118</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>59-37-11-8-9-21-7-45-33-10-36-60-73-74-63-75-62-61-32-46-34-35-48-47-71-72</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>30-42-43-26-51-64-41-54-68-66-25-12-27-55-3-1-2-0-14-15-28-56-70-44-5-18-31-57</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>161-162-151-164-141-127-85-83-122-138-153-166-165-114-101-115-152-99-86-98-111-110-135-97-96-125-126-100-102-137-124-163</t>
+          <t>45-32-57-46-74-75-63-21-34-33-59-71-86-73-60-61-62-9-11-10-37-48-35-36-8-7-47-72-85-70-83</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -10272,7 +10272,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>78-90-103-105-104-116-129-130-118-119-132-133-158-159-160-96-106-120-107-156-144-131-80-79-91-77-92-93-108-109-82-83</t>
+          <t>166-165-164-150-161-135-111-124-154-167-114-125-112-113-101-100-102-115-153-141-126-110-97-163-149-137-152</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -10280,15 +10280,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>22-24-37-50-49-48-46-33-71-87-89-76-63-62-35-11-10-9-8-61-75-74-47-6</t>
+          <t>16-2-1-27-12-38-64-51-17-18-28-5-3-25-52-43-69-55-54-53-40-41-42-15</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>27-28-15-51-64-53-41-1-3-17-18-16-5-43-55-54-69-42-40-52-38-2-12-25</t>
+          <t>6-9-8-22-11-10-24-37-50-62-63-87-71-46-33-61-75-49-48-35-47-74-89-76</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -10296,11 +10296,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>126-113-101-100-150-152-153-166-165-164-149-161-163-124-110-97-135-137-154-167-141-114-115-102-125-111-112</t>
+          <t>77-105-132-82-83-96-107-156-130-118-131-120-108-79-91-103-116-104-90-78-92-133-160-144-119-106-93-80-109-159-158-129</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -10370,35 +10370,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>153-102-100-88-124-162-164-127-128-141-115-138-137-136-123-112-97-98-111-99-167-166-165-113-114-126</t>
+          <t>80-67-42-41-40-15-52-64-81-70-30-31-17-29-39-66-53-1-16-4-54-69</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>62-50-48-34-33-32-31-45-70-35-23-36-60-86-84-71-72-74-47-21</t>
+          <t>92-78-103-131-132-146-118-77-90-104-117-129-155-156-116-106-119-157-158-160-134-121-105-95-93</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>148-136-135-137-99-138-126-113-100-166-127-114-115-102-112-111-124-141-153-167-128-98-97-109-164-165-123-122-162-161</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>33-21-48-47-72-71-45-32-34-23-35-50-36-60-84-86-74-88-62</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>8</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>77-64-54-66-80-81-69-17-4-30-15-39-52-1-16-29-67-78-53-41-42-40</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>95-93-105-131-156-146-118-155-103-116-119-106-161-148-132-117-92-90-104-129-157-158-160-135-109-122-134-121</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -10468,15 +10468,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>146-159-144-131-119-121-147-160-161-148-133-109-122-95-94-156-120-92-91-116-103-104-117-143-145-158</t>
+          <t>86-113-127-140-101-87-125-166-152-151-124-136-163-165-164-114-115-102-89-88-99-85-110</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13-12-38-39-66-55-43-2-15-27-42-41-65-51-64-79-67-56-29-4-30-69-77-25-26-1-0</t>
+          <t>15-0-38-51-65-39-26-1-2-27-66-77-79-69-29-41-13-12-25-64-67-56-43-55-42-30-4</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -10484,19 +10484,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21-36-62-63-10-23-48-74-59-71-57-5-32-45-47-34-35-24-11-6</t>
+          <t>91-103-104-143-116-94-92-117-95-119-131-158-159-147-122-120-144-156-145-133-146-160-162-148-161-109-121-83</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>63-62-74-47-71-57-45-59-48-32-5-6-11-24-36-35-34-23-10-21</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>85-86-88-99-152-151-164-162-124-101-89-102-114-115-140-113-127-166-165-163-125-136-83-110-87</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -10566,15 +10566,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>116-103-90-92-105-121-147-133-106-80-78-79-93-82-96-108-134-118-132-129-155-145-146-159-160-158-156</t>
+          <t>96-123-110-97-101-167-153-114-102-128-141-140-138-113-126-151-150-111-124-135-161-149-139-100-112-136-162-163-164-148</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>48-46-59-71-72-60-23-24-10-8-75-88-89-70-84-86-74-87-76-49-19-33-32</t>
+          <t>49-23-19-32-8-33-46-74-88-48-60-59-70-71-86-87-75-76-89-72-84-24-10</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -10582,19 +10582,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12-64-66-51-43-42-29-15-0-53-67-68-55-16-3-2-14-13-56-44-31-18-4-5-17-54-26-25</t>
+          <t>129-155-132-92-79-118-156-133-108-121-147-134-82-80-93-106-105-145-159-158-160-146-78-90-116-103</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>148-161-149-162-136-151-101-114-141-100-111-123-110-97-113-128-102-124-135-150-139-153-126-138-163-164-167-140-112</t>
+          <t>12-31-5-4-17-18-42-54-53-64-51-26-15-16-56-55-43-44-3-2-29-66-67-68-13-25-14-0</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -10664,31 +10664,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>111-99-97-84-87-112-124-136-149-137-150-139-140-126-89-102-128-101-114-153-164-123</t>
+          <t>107-134-135-121-95-108-131-145-146-133-160-148-147-117-142-130-93-106-120-132-159-158-156-129-143-157-116-104-118-103-92</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>126-128-140-153-139-149-137-124-112-111-84-97-123-99-87-102-89-101-114-164-150-136</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>7</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>78-64-65-67-68-17-18-15-1-40-13-0-39-52-83-81-82-70-69-57-30-44-31-41-27</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>72-71-45-18-7-6-34-60-73-76-50-10-11-23-33-31-46-59-74-49-8-21-24-35</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>71-72-76-74-73-60-46-21-23-11-24-49-50-34-33-7-6-8-10-35-45-59</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>121-134-135-104-103-92-108-148-132-142-129-130-156-143-116-117-131-133-106-95-120-147-159-145-158-157-160-146-118-93-107</t>
+          <t>70-30-57-67-78-64-15-17-44-40-41-68-82-81-52-65-39-1-27-13-0-69-83</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -10762,23 +10762,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>131-146-121-120-133-94-80-145-130-155-142-129-104-103-116-77-90-82-93-105-92-79-96-109-108-135-147-157-143-158-144</t>
+          <t>111-110-109-136-150-137-100-86-85-87-101-102-126-166-154-141-165-163-135-96-97-114-152-153-140-138</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>47-48-61-60-45-32-71-72-75-73-21-34-35-36-50-63-24-9-7-6-8-10-23</t>
+          <t>65-52-38-51-0-1-13-12-68-79-77-80-67-70-82-69-56-30-3-4-16-28-25-40-27-2-29-54</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1-0-13-27-38-12-25-52-3-4-29-16-56-69-70-57-31-44-30-54-40-51-65-67-68-2-28</t>
+          <t>61-73-47-6-7-21-35-50-63-48-23-34-31-32-75-60-71-72-57-44-45-8-9-10-24-36</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -10786,7 +10786,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>110-97-111-140-153-165-166-141-154-126-102-114-100-101-87-85-86-138-137-136-150-163-152</t>
+          <t>104-116-144-157-158-120-105-130-129-143-145-146-147-133-131-155-142-121-108-94-92-93-103-90</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -10860,35 +10860,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>119-106-92-105-142-155-93-78-79-80-81-82-94-144-143-156-159-160-134-91-77-108-120-158-157-117-116-132-147-146-107</t>
+          <t>48-35-36-50-49-47-45-57-71-19-20-21-34-18-58-60-61-74-72-70-44-31-4-17-6-7-8-9-10-73-63-75</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>44-48-47-21-72-73-61-75-63-10-9-35-45-58-60-71-70-57-7-8-36-49-74-50-34-31-6-20-19-18</t>
+          <t>137-151-166-154-140-165-123-110-99-98-125-124-150-139-138-113-85-86-115-101-89-114-111-97-96</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>56-69-67-64-51-39-26-14-4-16-65-40-28-13-38-25-27-42-43-17-3-1-66-55</t>
+          <t>69-82-91-92-66-27-14-13-26-25-80-81-56-43-3-42-65-78-77-28-16-1-39-51-64-38-79-67-55-40</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>155-143-158-157-144-117-116-107-108-148-147-120-134-93-94-122-161-160-132-105-106-119-146-159-156-142</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>123-148-138-124-110-96-122-150-161-165-114-115-154-140-89-86-85-97-99-98-111-137-151-166-139-101-113-125</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -10958,7 +10958,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>81-95-161-135-133-93-92-90-132-134-120-109-122-121-129-131-146-159-160-143-105-118-156-155-157-144-104-117</t>
+          <t>131-146-133-81-93-132-120-157-144-159-156-143-117-118-155-129-90-104-92-105-95-109-121-161-134-135-160-122</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -10966,15 +10966,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>26-40-41-28-3-27-13-38-78-68-79-66-42-69-53-29-17-14-0-12-52-25-39</t>
+          <t>42-3-0-53-41-40-66-79-78-52-26-13-14-39-38-25-12-27-28-29-17-68-69</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>63-48-34-46-60-74-76-50-9-21-22-35-37-61-47-8-24-7-19-32-59-73-72-84-83-57-18-31-58-71</t>
+          <t>83-84-76-63-9-8-46-59-57-58-18-19-47-74-73-60-72-71-61-34-7-21-22-37-50-48-24-35-32-31</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -10982,7 +10982,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>127-100-102-101-128-115-89-88-98-99-112-125-138-141-153-111-124-137-163-152-140</t>
+          <t>88-102-115-141-153-152-112-99-100-101-128-140-127-124-98-111-125-137-163-138-89</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -11056,35 +11056,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>99-126-153-165-125-150-163-162-149-136-110-97-112-124-98-138-151-115-128-141-154-140-114-113-101-100</t>
+          <t>109-110-124-98-101-138-150-165-153-154-128-114-126-140-112-113-99-136-163-149-125-151-141-115-100-97-135-148-162-122</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>14-3-41-2-1-4-17-43-56-54-67-68-66-53-25-38-40-42-28-26-12-13-0</t>
+          <t>90-118-129-142-157-159-146-119-107-121-93-94-147-160-120-131-155-103-117-108-92-91-79-81-80-145-158-105-95</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>2-13-28-26-25-38-12-0-1-40-67-66-53-14-68-56-54-41-42-43-17-4-3</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>8</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>47-71-70-72-85-89-36-35-59-60-74-87-84-83-57-34-21-33-22-11-19-58-75-76-62-37</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>157-159-145-135-148-122-109-118-105-94-81-95-147-160-146-121-120-131-107-108-91-117-103-93-80-92-155-142-158-119-129-90-79</t>
+          <t>34-21-37-36-59-60-47-22-35-11-19-33-76-89-87-71-57-70-83-85-72-62-74-75-84-58</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -11154,7 +11154,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>88-101-100-112-114-115-125-136-151-153-154-102-113-111-109-96-135-124-110-138-139-87-86-85-97-83-150-164-137-99</t>
+          <t>107-94-93-80-77-82-145-156-142-103-104-116-78-121-160-157-146-159-155-132-134-81-106-129-130-90-91-79</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -11162,7 +11162,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>74-71-58-9-10-24-37-23-8-20-21-22-49-75-61-48-35-36-73-60-5-19-33-32</t>
+          <t>22-10-24-23-20-33-60-73-75-49-36-71-58-32-21-35-37-74-61-48-19-5-8-9</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -11170,19 +11170,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>26-38-0-27-57-70-40-55-81-56-82-80-79-78-65-77-64-66-54-25-51-52-41-67-30-2-17-3-1-14</t>
+          <t>55-30-17-67-66-65-38-2-14-25-27-3-1-0-51-64-40-26-41-54-56-57-70-52</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>91-116-129-107-121-146-160-161-159-132-145-157-156-155-130-104-90-103-142-134-94-93-106</t>
+          <t>110-97-111-100-113-139-153-154-164-125-114-85-83-96-86-112-150-138-151-136-135-161-124-87-99-88-101-115-102-137-109</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -11252,23 +11252,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>140-163-151-149-123-110-98-85-88-102-152-167-166-165-154-114-127-113-137-136</t>
+          <t>8-74-60-47-9-35-20-6-71-45-22-11-76-63-50-24-10-21-19-5-18-32-31-23-36-62-58-59-46-34</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>136-123-149-152-127-102-88-85-98-110-163-165-166-167-151-137-113-114-140-154</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>7</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>50-76-62-63-36-34-8-9-11-24-23-22-6-5-32-45-21-35-60-74-47-46-20-19-58-59-10</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>67-55-57-44-71-83-82-68-56-54-28-38-52-80-81-66-79-64-12-27-41-18-4-2-13-69-42-29-17-31</t>
+          <t>91-118-132-108-122-109-95-106-129-143-155-145-147-161-148-121-120-119-135-160-157-116-104-117-142-105-92-93</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -11276,7 +11276,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>155-160-135-147-122-119-118-116-117-104-105-92-91-121-109-108-95-93-106-145-120-148-161-143-132-157-129-142</t>
+          <t>79-82-83-12-13-27-80-67-28-29-44-4-2-17-57-68-81-66-52-41-54-56-69-55-42-38-64</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>97-162-164-152-98-99-86-88-115-136-110-112-87-141-154-127-126-151-153-166-167-89-101-85-84</t>
+          <t>85-86-115-141-153-152-164-167-166-154-101-112-98-84-162-151-136-110-127-126-89-88-87-99-97</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -11358,27 +11358,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>50-63-37-24-33-34-58-73-61-10-11-36-49-72-71-70-22-21-20-7-19-57-31-18-6-8</t>
+          <t>6-34-73-72-61-49-37-24-22-36-50-63-58-71-19-33-20-21-11-10-8-7</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>39-53-27-28-55-56-68-43-17-29-2-15-4-42-41-65-78-52-51-38-12-14-1-0-13</t>
+          <t>0-15-68-41-13-14-31-18-4-17-29-53-52-51-65-70-57-56-43-55-42-28-12-38-39-27-2-1</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>80-81-135-131-157-159-160-147-122-96-109-95-117-92-93-119-108-121-106-103-104-118-156-129-130-158-145-133-132</t>
+          <t>78-103-104-132-147-106-81-108-119-160-135-109-95-159-133-145-158-157-117-131-93-80-92-129-156-130-118-121-96-122</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -11448,31 +11448,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>110-127-115-102-153-141-140-138-122-148-96-84-85-86-101-126-139-151-150-162-163-149-125-112-109</t>
+          <t>86-46-47-49-34-45-84-37-10-75-89-102-85-71-73-63-101-88-61-48-33-20-32-60-22-23-24-50-76</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>116-104-117-92-118-132-156-143-133-121-146-159-145-131-91-142-129-93-108-120-119-106-79-90-103-78-77</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>65-66-83-70-43-27-25-40-41-55-29-53-1-2-28-51-64-57-56-54-67-79-82-44-31-30-3-16-26-12</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>89-88-75-49-24-37-50-48-23-10-22-33-20-45-32-46-47-60-61-63-76-73-71-34</t>
+          <t>138-162-163-127-115-141-153-125-112-110-122-148-160-139-140-126-109-96-149-150-151</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>159-146-131-132-108-93-106-78-90-91-118-117-103-104-92-133-121-120-119-129-116-77-142-143-156-145-160</t>
+          <t>27-41-57-56-55-54-51-65-66-53-64-12-25-26-1-3-2-28-40-29-30-44-31-16-43-70-82-83-67</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -11546,15 +11546,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>133-145-147-148-159-157-156-104-118-123-83-82-92-158-149-161-136-110-97-96-109-103-117-131-143-130-119-106-135-134</t>
+          <t>6-19-86-72-46-34-33-20-10-23-11-9-22-8-7-32-35-49-60-47-74-63-75-76-89-71-59-84</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1-67-66-78-25-26-14-12-38-28-41-42-90-64-51-40-39-52-77-80-55-56-69-54-79-43-16-17-2-4-3-30</t>
+          <t>54-66-52-56-18-30-28-14-12-51-26-16-4-3-2-1-39-40-41-42-57-83-82-25-38-64-69-55-67-43-5-17</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -11562,19 +11562,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>84-57-10-20-33-47-60-59-49-74-75-76-11-23-35-63-86-18-5-6-46-32-8-9-22-34-7-19-72-71</t>
+          <t>77-78-118-143-157-131-145-119-133-147-134-159-158-156-130-117-106-104-103-90-92-80-79</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>127-115-128-89-101-114-112-111-141-154-166-165-151-138-139-152-167-164-163-150-137-140</t>
+          <t>135-123-151-165-164-161-148-111-110-109-96-136-150-137-138-128-115-127-167-166-154-139-152-114-101-97-112-140-141-163-149</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -11644,35 +11644,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>89-140-151-164-153-154-128-102-113-100-126-141-166-165-152-139-137-123-138-150-162-99-114-87-88</t>
+          <t>126-141-113-100-99-114-128-102-140-139-164-152-165-166-153-154-151-162-123-137-138-150</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-6-20-22-73-86-72-75-61-46-45-60-71-44-58-57-83-32-31-21-11-10-23-62-74-85-19-35-63-50-48-34-9-8-18</t>
+          <t>161-160-156-142-118-79-80-93-109-120-132-145-143-157-158-147-144-117-78-92-83-95-121-134-135-146-133-119-96-81-106-94-82-155-103-77</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>69-54-41-27-15-3-17-53-25-26-1-29-56-68-65-64-12-40-28-4-2-13-0-38-51-30-43</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>44-6-31-21-5-18-20-8-11-23-86-61-63-62-50-35-22-34-19-32-57-58-71-85-87-73-46-60-74-72-75-89-88-48-10-9-45</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>80-68-81-15-2-17-53-65-64-77-41-13-12-0-1-43-4-3-27-28-40-26-25-51-38-54-29-82-69-30-56-79-78</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>144-103-118-121-96-120-133-132-146-158-157-142-106-93-94-119-145-143-155-156-117-92-109-95-160-161-147-135-134</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -11742,7 +11742,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>100-140-126-127-137-138-135-97-96-122-110-124-99-111-128-115-154-141-153-152-166-163-149-164-167-102-86-112</t>
+          <t>31-45-19-6-18-9-34-32-20-33-46-70-83-71-72-60-47-50-73-86-75-62-61-49-37-23-11-36-21-22-35-58-44</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -11750,23 +11750,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>73-62-72-70-44-31-32-20-19-71-58-45-35-36-21-6-18-60-61-47-34-33-46-11-50-37-75-22-9-23-49-83</t>
+          <t>17-54-69-55-52-38-53-66-51-25-12-3-2-40-41-30-29-13-1-15-16-4</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>15-53-51-38-52-25-12-13-1-3-4-29-69-54-41-17-16-30-55-66-40-2</t>
+          <t>138-152-127-128-115-154-141-112-126-140-124-110-137-163-164-166-167-153-102-96-111-100-99-135-149-122-97</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>120-107-105-160-145-142-155-121-94-93-92-90-78-103-77-106-118-131-157-144-143-119-133-158-156-129-116-117</t>
+          <t>105-116-131-118-119-107-92-93-103-144-145-143-129-117-120-133-121-94-156-157-142-155-158-160-106-90-77-78</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -11840,35 +11840,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>132-120-134-121-92-90-103-160-146-133-157-156-155-143-144-117-104-106-130-95-94-107</t>
+          <t>150-162-163-166-139-126-138-102-87-85-84-97-110-123-111-98-99-86-136-127-165-151-137-128-115-89-140-153</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>72-33-35-34-20-45-19-7-9-23-48-21-11-24-49-37-50-63-62-76-89</t>
+          <t>0-51-64-68-67-69-17-30-31-54-52-53-27-43-44-70-83-82-81-18-4-14-25-26-39-65-66-55-42-29-15-1</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>21-11-24-23-37-50-76-62-48-63-49-34-35-33-20-7-19-45-72-9</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>8</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>39-15-1-65-68-81-53-66-26-54-82-70-69-67-52-42-29-18-4-31-30-17-44-43-55-14-64-51-27-0-25</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>4</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>87-83-138-151-111-123-135-148-126-102-165-163-162-137-150-136-97-84-86-85-98-128-140-127-109-122-110-99-153-166-139-115</t>
+          <t>144-130-143-155-156-157-146-160-134-106-120-122-135-148-92-104-132-117-103-90-94-109-95-107-121-133</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -11938,35 +11938,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>95-132-118-105-104-129-142-116-103-91-90-155-156-157-160-134-92-93-106-117-130-131-146-159-158-119-94</t>
+          <t>122-135-96-109-112-99-139-161-97-98-111-124-162-148-164-165-113-114-123-136-163-150-138-140-141-128-125-154-166-102-115-100</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>53-40-56-68-82-70-42-2-15-28-41-54-69-83-57-55-27-3-18-16-0-26-13-1-51-38-52-65-29-80-66-67-30</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>106-95-134-160-142-156-118-131-105-94-93-92-146-159-130-116-129-117-132-119-78-90-103-158-157-155-91-104-77</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>4</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>6-46-73-59-58-45-19-32-34-22-35-9-10-11-76-89-86-85-33-74-49-37</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>27-54-42-77-78-40-26-13-41-55-56-82-69-68-51-52-65-67-80-53-66-30-16-29-28-15-2-3-0-1-38</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>34-35-22-9-11-10-37-74-76-73-49-19-6-18-45-59-46-58-70-57-32-33</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>123-122-138-164-162-163-111-115-89-102-140-125-97-85-86-112-113-100-98-99-114-141-128-109-139-166-154-165-148-161-150-135-83-96-136-124</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -12036,15 +12036,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>125-126-127-139-112-101-124-109-163-151-137-135-97-85-87-88-141-154-115-102-89-99-86-110-123-161-162-165-152-166-140-150-138</t>
+          <t>108-95-83-82-109-147-159-132-130-117-93-80-131-118-119-94-91-107-121-133-146-144-155-142-105-104-77-78</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7-10-24-11-76-37-63-62-74-75-48-36-23-9-22-34-21-33-59-72-58-60-19-6</t>
+          <t>2-28-42-57-69-68-54-66-64-39-13-0-29-56-30-17-18-4-3-15-41-38-52-53-40</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -12052,7 +12052,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0-2-17-18-57-54-40-13-4-3-15-42-56-69-68-30-29-28-41-38-64-82-83-66-52-39-53</t>
+          <t>11-24-37-33-59-86-74-75-60-88-76-63-87-85-6-7-19-9-10-22-58-72-21-34-48-62-89-36-23</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -12060,11 +12060,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>159-146-95-108-144-142-155-121-107-119-130-118-104-117-132-93-94-80-78-77-91-105-133-147-131</t>
+          <t>126-152-165-154-127-140-139-151-150-138-101-141-166-161-137-124-110-135-162-163-123-97-125-112-99-102-115</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -12134,35 +12134,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>143-103-105-92-95-94-93-106-145-131-130-129-91-90-119-133-147-160-144-134-120-108-121-158-157-155-142</t>
+          <t>57-45-8-48-76-36-37-11-7-19-47-88-89-50-74-70-58-20-22-35-34-6-46-59-83-84-87-85-71-32</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>82-43-56-17-30-16-14-28-29-4-42-70-80-65-66-52-38-27-26-1-0-51-77-64-53</t>
+          <t>134-108-82-92-105-120-106-119-90-77-95-121-147-145-158-143-157-130-131-142-129-155-103-91-93-80-94-133-144-160</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>11-37-22-8-7-6-19-32-45-20-36-50-76-74-57-58-71-59-46-34-47-48-35</t>
+          <t>123-150-138-114-110-122-135-163-162-161-151-128-101-99-96-97-111-98-112-126-148-164-165-154-152</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>56-65-66-52-64-51-38-27-14-0-1-26-42-28-4-16-29-17-30-43-53</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>8</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>97-83-148-162-122-123-110-99-98-126-138-151-163-164-150-161-135-84-85-111-112-165-154-96-114-89-88-87-101-128-152</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -12232,15 +12232,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>94-132-108-109-107-134-147-157-142-143-117-79-96-81-83-118-119-145-159-129-103-155-156-90-77-92-105-133-95</t>
+          <t>14-15-30-17-43-54-41-55-67-65-38-51-39-64-26-27-13-1-56-70-4-3-2-16</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>34-61-86-87-75-89-76-63-37-50-35-48-60-23-8-21-11-9-32-72-59-46-45-6</t>
+          <t>59-8-11-6-32-46-45-72-60-61-34-21-9-48-35-50-76-89-63-37-23-75-86-87</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -12248,15 +12248,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>3-2-1-16-4-17-30-65-67-70-41-26-38-51-64-39-14-13-27-15-54-55-56-43</t>
+          <t>164-149-150-124-111-98-102-114-113-127-99-100-101-141-128-125-136-137-151-167-166-153-135-148-123-110-83-96-109-163</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>167-153-141-124-123-136-99-100-98-111-125-127-128-151-164-101-102-114-113-110-135-148-149-137-150-163-166</t>
+          <t>103-117-143-129-119-142-156-155-157-145-159-147-133-118-108-94-132-134-81-95-107-105-90-77-79-92</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -12330,35 +12330,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>111-124-166-140-152-139-110-99-112-83-96-97-98-85-86-88-89-102-150-165-151-125-123-122-137-115-127-153-138-100-87</t>
+          <t>119-146-133-142-129-90-105-118-132-117-116-91-94-93-107-161-147-160-156-155-143-157-158-131-144-130</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>59-61-49-35-34-21-7-6-18-58-47-23-22-20-32-46-74-75-62-24-37-50-11-10-8</t>
+          <t>43-54-40-26-14-39-79-81-70-17-2-1-0-27-41-69-68-67-53-80-82-83-78-64-51-65-66-29-28</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29-41-67-65-79-81-68-69-43-70-80-82-54-28-27-39-53-66-78-26-2-14-40-64-51-0-1-17</t>
+          <t>11-24-22-34-35-20-18-7-6-47-49-50-23-37-10-8-21-61-75-62-74-58-59-46-32</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>155-156-131-119-133-161-160-157-158-116-93-94-107-117-130-118-105-132-146-147-144-143-142-91-90-129</t>
+          <t>87-97-98-122-137-150-124-138-166-165-110-123-127-125-112-99-86-102-115-89-85-96-111-151-139-140-152-153-100-88</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -12428,35 +12428,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>128-153-138-97-99-101-139-96-123-152-166-165-161-148-86-98-83-109-110-149-135-137-150-136-126-141-115</t>
+          <t>155-144-131-120-96-109-135-161-133-160-157-158-130-119-95-94-92-104-142-143-116-103-93-134-148-121</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>7-9-19-58-59-49-48-74-72-47-34-23-36-37-76-75-62-35-10-22</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>98-86-97-110-166-153-152-150-123-137-136-149-138-165-99-101-115-128-141-139-126</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>51-25-26-29-42-31-17-13-12-68-83-82-43-15-28-39-66-77-38-27-57-56-44-30-16-2-4-70-55-52-78-79-65</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>12-25-4-17-55-39-66-26-27-15-16-28-42-52-38-70-31-44-57-30-2-51-65-77-79-78-29-43-56-82-68-13</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>62-49-22-7-19-34-47-48-72-59-58-9-10-23-37-36-35-74-76-75</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>9</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>93-103-116-130-144-134-160-158-155-143-119-95-121-120-133-157-142-131-94-92-104</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -12526,35 +12526,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>116-129-133-120-90-103-142-159-143-157-158-145-134-135-108-122-95-107-118-92-105-104</t>
+          <t>87-63-50-37-35-47-72-86-33-21-9-11-62-75-76-89-88</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>10</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>41-40-39-53-67-31-30-15-27-55-83-69-82-78-77-38-29-56-70-28-68-81-80-14-13-12-0-42-4</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>112-151-137-123-110-111-127-128-153-154-140-139-126-113-102-115-165-152-125-99-98-97-124-138-150-136</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>7</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>38-27-77-78-83-82-56-69-70-68-28-0-13-14-31-30-4-40-39-12-53-41-81-80-67-55-42-29-15</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>9-62-35-33-47-75-88-89-76-63-87-86-72-50-37-11-21</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>9</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>123-112-99-111-127-140-115-125-138-139-165-150-151-137-136-113-126-102-128-154-153-152-110-97-98-124</t>
+          <t>120-142-129-143-116-90-118-103-104-105-92-133-145-157-158-159-134-108-95-107-122-135</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -12624,35 +12624,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>135-122-146-147-134-95-106-92-133-161-132-131-103-90-91-129-130-119-155-156-159-157-145-107-108-121</t>
+          <t>18-19-61-49-37-24-10-34-35-36-22-21-7-33-74-75-71-58-5-6-9-50-76-63-62-32</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>71-18-5-57-70-58-34-36-49-75-61-74-62-37-9-10-24-35-22-21-50-76-63-32-33-7-19-6</t>
+          <t>51-64-65-39-38-26-4-3-2-15-16-30-70-79-77-27-14-0-17-57-68-78-54-53-13-25-52-41-56-80-66</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>41-16-15-3-4-30-56-79-38-64-77-68-17-2-0-14-13-25-26-27-39-53-80-78-66-54-51-65-52</t>
+          <t>97-87-113-88-89-102-115-124-126-140-166-165-164-114-101-99-85-96-83-111-138-137-149-150-162-136-110</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>165-164-124-113-114-126-85-97-137-110-99-87-89-111-96-83-115-101-88-102-140-138-150-136-149-162-166</t>
+          <t>130-132-147-161-133-134-146-159-157-156-155-119-131-107-95-106-108-121-122-135-91-90-103-92-145-129</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -12722,35 +12722,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>155-93-122-134-121-120-105-91-131-77-79-78-90-117-157-133-119-118-96-135-148-156-144-145-161-159-130-129</t>
+          <t>75-87-60-33-45-71-73-88-89-76-63-34-47-8-11-24-23-49-36-20-61-62</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8-34-62-63-47-33-45-73-60-71-84-75-76-61-49-36-6-19-20-24-11-23</t>
+          <t>157-156-155-129-90-77-64-65-121-134-133-93-120-119-130-117-118-145-159-144-131-105-79-91-78</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>99-128-115-102-84-122-111-113-138-164-149-96-151-167-154-127-101-112-125-153-152-161-148-135</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>15-29-66-53-38-26-13-0-1-43-57-44-17-16-67-56-28-3-4-18-6-19-31-14</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>16-4-3-1-13-29-44-31-17-18-66-65-64-67-53-15-14-0-38-26-28-57-56-43</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>151-149-111-112-127-113-99-88-87-89-102-154-153-152-164-167-128-115-101-125-138</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -12820,23 +12820,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>96-109-162-152-165-167-151-141-154-128-88-101-136-135-124-138-139-98-111-110-125-126-113-102-114-112-84-123-148-164-153-122-83</t>
+          <t>18-44-57-3-28-40-14-13-39-25-0-2-1-27-53-68-43-56-55-54-67-79-16-42-66-51-65-52-26-15-17</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>49-36-10-48-35-47-73-72-33-21-20-57-44-18-6-8-23-60-75-76-63-61-58-32-7-11-37</t>
+          <t>131-118-129-130-133-121-120-119-107-95-145-156-155-142-116-90-91-105-159-160-158-157</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0-13-1-16-17-65-51-25-26-27-52-79-66-42-2-3-15-14-40-39-53-54-55-67-68-56-43-28</t>
+          <t>73-58-32-6-20-8-23-36-37-11-10-35-60-75-88-48-7-21-33-47-49-63-76-61-72</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -12844,11 +12844,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>121-120-107-118-156-157-158-145-130-91-90-159-160-133-95-105-116-129-142-155-131-119</t>
+          <t>96-84-98-114-141-128-154-167-165-123-111-151-153-126-139-113-102-101-112-83-135-125-164-152-138-162-148-124-136-110-109-122</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -12918,23 +12918,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>91-104-95-107-134-147-159-133-146-144-155-142-129-130-119-105-93-106-158-131-116-103</t>
+          <t>144-158-159-93-91-104-103-142-130-131-155-129-116-106-107-95-134-147-133-119-105-146</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>39-65-79-66-41-15-30-43-56-54-81-69-82-68-80-29-1-3-2-26-25-38-40-53-64-52</t>
+          <t>38-39-81-69-80-52-29-30-44-82-54-41-1-15-3-43-56-68-53-25-26-40-65-64-79-66-18-5-2</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37-11-21-23-24-36-72-86-85-84-71-74-61-63-76-49-48-46-58-59-60-73-34-35-47-33-7-5-75-88-89-87-9-45-32-19-6-18-44</t>
+          <t>19-6-7-88-74-24-37-63-75-87-86-59-60-47-36-11-9-21-34-23-35-48-33-46-32-45-71-85-49-76-89-61-73-72-84-58</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -12942,7 +12942,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>167-154-126-98-125-165-124-150-137-112-100-141-128-153-140-110-97-109-122-123-149-162-161-135-148-138-99-101</t>
+          <t>123-98-99-135-149-162-161-125-100-101-167-140-165-150-137-109-97-110-112-126-153-154-141-128-138-124-148-122</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -13016,15 +13016,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>161-134-106-118-116-129-130-131-132-146-157-158-159-160-147-121-108-107-105-104-142-155-94-96-122</t>
+          <t>107-121-122-131-158-159-146-130-105-94-108-96-106-160-161-147-132-157-142-155-129-118-134-116-104</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20-46-74-50-37-49-62-61-7-19-45-59-58-71-84-85-87-47-22-23-10-11-76-63-89-75-73-34-33-35-9-21</t>
+          <t>38-51-64-52-27-26-13-4-17-2-30-43-56-68-78-39-15-1-57-83-82-69-29-16-55-41-40-65-77</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -13032,7 +13032,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>43-4-17-56-30-29-27-13-39-51-38-26-52-40-15-16-5-68-64-77-78-65-55-69-41-2-1-57-82-83</t>
+          <t>71-85-59-46-35-49-50-63-76-62-75-33-45-58-61-74-73-5-7-10-11-37-23-22-19-20-21-9-34-47-84</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -13040,11 +13040,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>162-150-137-123-151-164-166-126-128-102-99-110-98-112-113-127-125-136-163-153-154-141-115-114-138</t>
+          <t>102-115-114-110-98-164-151-138-150-153-141-128-113-125-123-112-99-87-127-166-154-163-162-136-137-126-89</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -13114,15 +13114,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>129-116-92-91-104-117-131-132-108-121-146-145-158-143-155-156-144-134-120-107-106-105-119</t>
+          <t>27-17-18-69-68-56-66-65-13-1-4-5-29-40-12-0-2-14-15-16-30-41-55-67-52-25-26-51-38</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>16-15-17-30-29-0-2-1-40-65-78-66-52-12-14-55-67-27-26-38-77-51-25-13-4-68-81-41-56-69</t>
+          <t>100-101-115-165-152-125-111-124-137-113-112-163-164-136-135-161-148-109-96-151-140-141-127-166-154-167-97-98-99-110-150-149-139-126-122</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -13130,19 +13130,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>50-24-23-8-20-44-70-71-72-59-32-60-34-10-7-19-46-73-47-18-5-6-21-49-76-63</t>
+          <t>108-81-77-116-129-144-145-156-155-143-146-107-106-119-132-158-104-92-78-91-121-134-120-105-117-131</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>98-111-141-165-151-152-112-100-86-99-126-127-115-101-125-148-110-109-113-88-139-150-136-149-124-97-84-140-154-166-167-164-161-135-122-163-137-83-96</t>
+          <t>72-60-10-23-24-7-71-70-44-19-20-6-8-21-47-34-32-46-73-86-63-88-84-83-76-50-49-59</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -13212,15 +13212,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>104-105-77-120-109-122-144-132-147-160-158-159-119-107-106-83-121-133-145-108-82-79-96-95-103-129-156-131-143-130-116-78-80-81-135-148-134-90</t>
+          <t>80-81-90-78-52-51-65-39-28-29-16-3-15-42-56-64-77-79-69-53-41-2-13-0-25-38</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>71-73-87-76-6-7-8-24-50-49-47-88-89-74-61-9-10-85-72-59-32-19-70</t>
+          <t>85-166-167-165-151-138-153-152-126-99-87-89-102-88-76-136-97-98-112-139-114-115-154-141-140-124-150-125-123</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -13228,19 +13228,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>38-13-0-28-2-15-3-31-44-42-29-16-17-18-5-39-25-51-52-41-56-69-53-65-64</t>
+          <t>109-96-95-131-145-143-129-103-116-147-160-133-107-104-130-156-144-158-159-132-120-82-108-121-134-148-135-122-105-106-119</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>139-151-166-165-167-154-141-115-102-99-126-140-153-152-150-138-125-112-136-124-98-97-123-114</t>
+          <t>59-47-49-61-18-19-17-5-7-8-6-32-71-83-70-72-73-74-50-24-10-9-31-44</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -13310,35 +13310,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>100-101-102-99-112-111-123-126-139-165-164-154-141-128-127-150-163-151-124-137-97-87</t>
+          <t>5-17-29-55-43-57-44-31-54-68-82-70-42-27-15-28-67-41-53-65-64-51-0-12-1-14-2-16</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2-1-17-16-29-28-54-53-68-82-55-41-27-12-0-65-42-43-67-78-64-51-14-15</t>
+          <t>109-122-135-161-126-100-128-112-101-102-97-137-150-139-154-141-127-165-163-164-151-124-99-123-111-84-96</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>60-47-46-32-6-19-33-34-35-58-72-59-61-11-23-36-76-50-24-74-87</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>7</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>31-34-76-72-59-74-61-46-70-58-44-57-84-60-50-36-24-11-19-32-33-47-35-23-6-5</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>108-91-103-94-122-109-95-96-134-146-156-142-143-104-105-106-118-117-130-157-144-158-160-145-161-135</t>
+          <t>105-146-134-144-143-156-157-130-108-94-95-106-91-78-104-103-117-142-158-160-145-118</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -13408,35 +13408,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>125-126-150-135-123-161-162-138-152-165-151-139-153-166-167-140-164-148-96-97-110-111-124-141-154-128-115-112-99-98-100-101</t>
+          <t>141-115-128-139-164-165-166-154-167-153-112-97-123-110-125-150-138-162-151-96-98-86-100-101-99-87-89-126-140-152-124-111</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8-19-34-61-75-87-73-59-58-86-85-71-33-21-9-23-49-63-89-60-47-32-6-37-50-48</t>
+          <t>80-41-28-38-40-54-42-55-67-52-51-13-25-53-65-43-56-29-4-2-16-0-1-14-69-82-66-79</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1-16-29-43-42-53-41-83-82-55-54-67-79-80-4-5-2-18-25-51-52-65-66-0-38-40-69-56-31-44-28-14-13</t>
+          <t>23-19-6-5-18-44-32-31-58-83-59-85-47-21-34-49-63-60-73-75-50-37-33-8-9-48-61-71</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>103-131-142-129-130-144-146-160-147-117-116-155-157-156-159-108-91-106-134-133-145-132-119-104-90</t>
+          <t>108-144-156-155-142-157-146-132-119-117-103-129-130-104-131-133-148-159-145-134-135-147-160-161-116-90-91-106</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -13506,7 +13506,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>149-137-136-150-154-153-152-128-126-99-98-97-139-164-166-114-102-87-86-110-113-100-89-88-101-141-167-140-165-163</t>
+          <t>30-44-57-70-28-4-17-55-56-82-68-54-26-1-13-0-38-51-64-40-14-39-69-81-78-65-41-29-18</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -13514,7 +13514,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>85-70-60-61-36-10-23-22-18-44-58-57-32-45-59-74-73-72-35-33-49-63-6-19-9-21-7-34-48-47-46-20-84-71</t>
+          <t>101-100-149-148-165-166-152-128-114-113-126-139-98-97-137-150-110-96-135-136-140-154-153-141-167-122-109-161-163-164-99-102</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -13522,19 +13522,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0-54-65-51-39-38-26-13-1-17-4-81-78-64-55-56-68-41-29-30-14-40-28-69-82</t>
+          <t>46-71-59-60-89-74-85-72-33-19-7-6-21-48-63-87-32-9-23-49-73-86-88-10-36-61-35-45-58-84-47-34-22-20</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>109-108-96-95-92-143-156-145-158-159-148-135-120-119-103-104-106-107-122-161-160-147-131-118-91-90-129-142-144-157-133-146</t>
+          <t>146-133-147-160-159-129-142-156-143-120-107-157-144-104-90-118-106-108-95-92-91-103-119-131-145-158</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -13604,35 +13604,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>109-110-84-135-164-166-152-153-141-102-86-123-97-137-149-136-99-113-125-112-85-83-98-87-88-89-101-114-151-165-162-122</t>
+          <t>6-7-20-23-37-62-63-61-70-83-58-57-44-72-59-60-19-34-10-24-74-71-5</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>55-69-54-67-15-27-39-51-65-78-77-66-28-79-81-82-56-16-41-53-52-38-25-26-4-30-1-2-3-43-42</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>141-84-99-89-102-87-162-136-123-110-97-98-86-85-112-88-113-125-137-149-165-151-164-152-101-114-153-166</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>93-117-103-142-156-131-130-104-120-135-122-94-106-91-92-119-105-107-95-145-159-161-109-108-121-147-134-133-132-144-129-143-90</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>41-15-27-26-2-1-28-39-78-79-55-56-43-82-30-53-51-77-52-66-67-81-69-16-4-3-65-38-25-54-42</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>59-58-57-44-5-6-19-34-20-7-37-61-60-70-71-72-74-63-62-10-24-23</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>7</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>132-95-108-134-161-147-120-119-92-91-94-107-121-133-159-156-143-117-131-144-103-90-93-106-105-104-142-130-129-145</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -13702,15 +13702,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>87-98-99-102-89-84-110-124-123-111-126-128-167-166-153-140-164-162-150-151-165-125</t>
+          <t>118-157-155-142-95-120-129-117-104-105-92-91-90-116-144-145-159-147-119-133-134-160-158-146-161-148-135-122</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24-50-10-9-75-63-47-74-73-58-61-48-36-22-6-19-45-33-8-21-11</t>
+          <t>164-162-98-110-111-99-128-102-125-126-167-153-166-165-140-151-124-123-150</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -13718,19 +13718,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12-57-56-53-64-25-55-68-66-80-70-42-69-82-81-41-38-77-65-67-79-54-28-14-1-2-30-31-43-44-17-29-16-4-18-13-0</t>
+          <t>48-61-74-87-89-75-47-8-21-6-19-22-33-58-84-45-10-9-36-50-73-63-24-11</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>25-13-14-81-68-16-4-17-1-30-44-41-28-12-2-0-29-31-18-43-56-42-65-64-77-54-55-66-67-69-70-57-82-79-80-53-38</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>119-133-157-159-148-146-145-155-158-118-104-95-147-122-134-120-135-161-160-92-91-90-116-129-142-144-105-117</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -13800,23 +13800,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77-103-104-155-156-131-119-118-117-129-105-93-134-120-143-159-158-132-160-161-147-96-109-108-122-107-94-82-81-80-90-91</t>
+          <t>0-13-2-15-27-53-39-38-26-69-56-16-3-17-4-29-54-55-43-42-51-77-64-52</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>45-8-6-20-21-35-22-9-11-23-48-47-61-75-74-73-60-62-50-49-36-34-46-32</t>
+          <t>84-100-139-141-102-101-99-136-125-113-88-75-123-138-152-167-153-128-114-87-74-86-85-98</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>13-52-64-51-53-16-17-15-2-0-39-38-26-27-54-29-44-18-4-5-43-42-55-56-69-57-70-31-3</t>
+          <t>57-70-44-18-5-32-46-34-20-9-21-23-11-62-48-61-35-47-60-73-31-6-8-22-36-50-49-45</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -13824,11 +13824,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>84-85-136-162-167-128-102-100-99-87-88-141-153-152-139-114-101-86-113-125-138-123-98</t>
+          <t>82-93-91-104-117-159-147-94-80-90-118-119-132-143-156-131-108-109-162-161-134-120-107-81-96-122-158-160-155-129-103-105</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -13898,15 +13898,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>112-99-100-89-141-115-111-123-149-137-140-154-128-127-151-165-152-138-163-162-150-110-98-113-114-102-153-166</t>
+          <t>44-35-19-8-10-22-21-31-58-46-49-23-24-86-73-59-85-72-48-47-84-71-70-32-18-20-34-61-76-63-37-75</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>72-48-61-73-35-20-19-32-18-31-59-71-70-58-44-84-86-76-49-34-85-87-46-21-10-24-63-75-37-8-23-22-47</t>
+          <t>132-146-160-147-149-135-161-159-82-108-96-83-103-143-158-142-91-93-106-120-134-121-95-122-162-148-155-117</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -13914,19 +13914,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>30-43-55-41-29-27-14-2-3-15-12-13-0-25-78-79-42-56-17-4-52-38-39-51-77-67-66-40-26-1</t>
+          <t>78-90-27-14-29-43-17-4-52-39-40-25-26-12-13-2-0-1-66-80-41-3-15-67-79-56-42-30-55-81-77-51-38</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>142-146-106-80-91-103-90-143-120-93-95-96-108-82-83-81-117-132-134-135-161-122-121-160-158-159-147-148-155</t>
+          <t>87-89-102-99-111-110-98-128-127-138-151-152-153-140-113-115-166-141-137-150-123-100-114-154-165-163-112</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -13996,7 +13996,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>78-79-94-106-132-131-90-95-108-80-93-81-105-104-146-155-143-116-129-117-91-103-130-145-159-158-156</t>
+          <t>93-95-158-81-80-91-155-143-156-145-106-108-94-90-116-129-146-159-132-131-130-117-103-78-79-104-105</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -14004,27 +14004,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>71-83-20-19-23-62-84-58-6-32-45-87-73-60-21-11-10-49-50-22-35-37-76-89-47-74-88-63</t>
+          <t>167-154-152-151-125-126-113-112-110-101-100-140-128-115-111-135-161-148-83-84-109-123-163-165</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5-16-15-29-56-69-54-41-40-12-0-1-13-2-3-66-65-52-51-39-38-53-67-44</t>
+          <t>16-5-44-41-40-53-13-0-12-38-65-54-56-69-3-1-2-15-29-67-66-52-51-39</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>110-111-125-126-115-128-154-167-165-140-152-151-123-101-100-113-112-135-148-163-161-109</t>
+          <t>35-37-50-63-49-11-23-10-47-62-22-20-32-87-74-76-89-88-73-21-6-19-45-71-58-60</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -14094,31 +14094,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>146-160-145-117-116-104-77-129-118-94-107-105-130-155-156-79-80-120</t>
+          <t>102-128-89-88-101-100-84-97-83-96-86-85-112-154-163-148-136-127-115-141-111-98-113-139-165-151-124-137-123-110</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>48-49-37-21-20-19-22-23-11-24-9-7-6-35-61-73-62-63-74-59-71-45-60-47-34-33</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>7</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>6-7-20-33-47-34-22-35-62-74-73-60-45-71-59-61-9-11-48-37-24-23-21-49-63-19</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>64-51-29-42-69-56-18-44-43-40-15-16-17-0-27-38-25-39-55-67-66-68-82-57-4-5-2-14-1-65</t>
+          <t>118-155-156-160-146-145-130-120-105-117-129-116-104-77-107-80-79-94</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>124-98-101-115-128-154-165-148-151-141-113-88-102-89-100-85-112-163-136-96-86-84-83-97-110-111-127-139-137-123</t>
+          <t>56-43-42-29-14-27-40-25-38-39-55-66-69-44-57-5-4-17-18-2-1-82-67-68-64-16-15-0-51-65</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -14192,15 +14192,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>63-75-74-73-99-140-139-111-110-84-85-88-89-114-115-125-124-86-112-165-167-151-137-152-153-141-128-87-76</t>
+          <t>4-15-31-30-16-26-27-55-42-57-29-40-51-0-2-5-19-43-56-69-54-67-53-39-25-82-44-32-6-3</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>39-69-82-80-67-25-27-40-53-91-116-90-77-103-104-92-93-55-42-54-26-0-15-51-65-64</t>
+          <t>156-142-116-143-145-157-146-121-107-80-65-90-104-92-91-93-132-119-120-64-77-103-155</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -14208,19 +14208,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>48-37-61-3-4-30-45-58-57-44-56-29-5-19-6-20-33-47-46-16-2-31-43-59-72-60-32-11-24</t>
+          <t>63-76-87-84-72-99-85-86-60-47-20-59-58-45-48-61-75-88-89-74-73-46-33-37-11-24</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>135-147-146-145-142-143-132-119-120-96-123-122-157-156-155-107-121-149-148-162-161-163-150</t>
+          <t>139-141-167-137-96-115-114-123-111-112-125-153-124-135-110-122-150-151-162-161-147-148-149-163-165-128-140-152</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -14290,7 +14290,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>99-101-89-112-137-164-165-139-125-110-87-88-76-100-113-140-153-115-127-167-152-126-86-84-97</t>
+          <t>115-101-89-100-88-113-162-149-110-97-99-84-137-164-153-167-165-152-139-125-112-87-86-126-140-127</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -14298,7 +14298,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>24-10-7-6-35-34-47-48-62-60-59-33-19-45-71-18-31-5-22-49-50-74-61-23-37</t>
+          <t>107-106-94-122-134-103-90-105-80-79-81-96-109-95-160-146-119-120-135-148-159-158-145-143-155-144</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -14306,19 +14306,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>29-4-16-39-90-79-66-67-80-40-30-17-3-2-14-25-53-81-69-55-0-13-1-64-65-52-26-51-38</t>
+          <t>25-38-0-29-17-30-4-5-16-3-2-18-31-69-64-52-66-53-40-67-55-65-51-1-14-26-39-13</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>149-162-148-159-158-103-105-144-155-143-145-146-120-107-160-134-135-122-109-94-96-95-106-119</t>
+          <t>22-37-50-19-45-6-7-74-76-62-48-61-60-71-59-33-34-35-47-49-23-24-10</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -14388,31 +14388,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>105-78-90-93-108-82-96-121-133-106-119-107-118-159-145-134-94-122-160-147-132-143-155-142-91-83-95-103-117-116</t>
+          <t>40-27-42-4-13-12-25-26-0-14-38-52-78-53-30-17-3-15-67-64-51-68-55</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>90-93-106-105-107-95-108-96-83-147-159-161-160-145-143-142-155-117-121-133-134-122-94-82-118-116-103-91-119-132</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>47-86-76-37-20-31-19-59-33-21-36-35-60-75-73-71-85-70-44-34-48-32-18-45-58-46-8-9-24-10-63-49-62-72</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>59-45-33-46-47-60-85-58-44-70-71-73-48-37-24-8-19-32-86-75-89-76-63-21-35-34-62-49-36-10-9-20-18-31-72</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>30-17-4-3-42-55-26-25-12-38-51-64-53-68-67-52-40-27-15-14-13-0</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>9</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>137-149-162-161-141-154-166-127-153-138-112-151-164-163-150-124-136-123-111-97-98-99-128-114-102-101-113</t>
+          <t>97-136-151-164-154-166-153-141-128-127-111-98-99-114-101-89-102-113-124-149-150-163-162-123-137-138-112</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -14486,7 +14486,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>166-154-141-167-114-113-98-135-136-161-148-122-137-111-149-151-164-165-102-89-88-87-86-125-163-140-127-100-84-96-97-99-110-83</t>
+          <t>91-93-105-129-116-122-121-81-95-106-158-159-156-157-144-131-133-135-96-148-160-161-147-130-118-108-120-117-104-90-80-82-83</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -14494,15 +14494,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>23-48-35-61-60-73-58-46-20-11-10-8-7-45-57-31-19-5-22-49-37-36</t>
+          <t>125-149-136-110-111-113-140-164-163-97-84-87-98-99-88-86-89-102-154-151-137-114-127-141-165-166-167-100</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>51-77-78-80-68-2-4-17-29-55-65-64-53-26-28-41-82-81-69-30-42-40-39-38-13-25-14-3-0-12</t>
+          <t>0-2-29-3-14-40-77-78-65-55-30-17-4-28-68-64-51-12-26-39-38-25-13-53-42-69-41</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -14510,7 +14510,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>90-104-116-156-130-129-117-91-144-158-157-133-147-160-159-131-118-121-120-108-106-105-95-93</t>
+          <t>10-23-48-61-36-11-5-7-8-20-31-45-58-57-46-35-37-49-73-60-19-22</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -14584,35 +14584,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>92-81-83-90-129-142-118-80-105-120-134-135-119-107-94-122-133-132-131-93-82-108-121-95-109-106-91-77-144-158-160-147-116</t>
+          <t>19-5-7-6-18-11-24-37-48-34-72-45-8-9-10-33-20-22-50-36-49-59-73-74-60-61-62-63-32</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>105-91-90-116-94-108-134-121-118-131-132-142-158-133-122-147-160-135-144-129-95-93-92-106-107-109-120-119</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>67-83-82-57-43-51-13-12-2-30-44-41-15-3-4-55-68-69-70-40-0-38-66-81-17-16-28-54-80-77-65-52-39</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>15-39-38-51-40-28-5-18-44-43-67-66-41-17-69-68-65-52-0-12-13-54-55-30-70-57-4-2-3-16</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>8-6-19-61-49-36-48-62-63-7-20-32-45-60-74-9-22-10-11-24-37-50-34-59-73-72-33</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>164-154-127-138-150-163-139-112-87-102-101-114-128-85-98-141-167-151-126-115-153-165-162-136-86-99-111-137-123-84</t>
+          <t>126-139-127-101-87-102-141-153-165-163-162-136-150-154-167-164-123-137-115-128-114-151-138-84-111-112-99-86-85-98</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -14682,35 +14682,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>135-148-149-83-84-96-86-87-88-100-89-101-123-122-109-112-126-115-113-137-136-110-165-138-111-166-128-127-139</t>
+          <t>109-122-136-112-101-113-87-89-88-86-84-83-96-110-123-137-149-135-166-138-165-127-128-115-139-126-100-111</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>160-148-133-107-119-105-132-145-144-131-117-103-104-143-142-155-156-158-159</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>11</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>76-63-49-60-45-44-58-46-35-34-22-24-37-23-31-5-6-71-47-19-9-10-8-20-36-48-61-74-75-62</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>56-67-95-93-40-12-25-53-43-55-66-51-77-91-94-92-70-69-90-79-64-0-39-13-3-15-30</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>22-9-19-6-45-63-37-76-75-74-58-71-48-62-61-60-46-47-34-49-23-36-24-10-8-35-20</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>6</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>0-15-39-53-3-5-44-69-43-30-31-40-64-66-67-51-12-25-55-70-56-13</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>103-117-145-133-132-105-77-90-155-142-104-92-94-93-107-95-131-144-156-143-91-79-119-159-158-160</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -14780,23 +14780,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>100-113-124-150-111-85-84-137-149-163-165-164-153-140-166-154-141-128-127-102-101-152-125-98-99</t>
+          <t>0-12-13-67-66-53-40-27-14-15-56-69-68-43-30-29-41-42-17-4-26-65-51</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>90-116-143-144-119-91-81-134-159-132-131-92-105-118-133-146-148-135-108-95-96-83-79-77</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>50-62-74-73-63-47-58-71-45-33-32-35-48-22-9-6-19-10-11-24-23</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>8</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>14-13-26-15-17-53-79-44-70-69-68-81-83-0-12-4-5-18-65-77-51-66-56-43-29-30-27-40-42-41-67</t>
+          <t>5-50-24-10-11-23-22-32-18-44-45-58-73-84-71-74-63-62-19-6-70-85-47-9-33-48-35</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -14804,7 +14804,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>91-105-92-132-108-95-96-148-135-133-144-143-118-119-146-159-134-131-116-90</t>
+          <t>101-102-137-125-100-113-98-99-111-124-149-150-163-164-152-153-140-141-128-154-165-166-127</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -14878,7 +14878,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>122-109-138-152-113-124-84-83-96-100-101-102-139-97-110-136-135-123-108-121-164-150-153-154-162-161-147</t>
+          <t>13-12-38-28-40-65-79-77-78-81-67-66-82-68-55-53-39-56-69-27-26-3-16-51-52-43-29</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -14886,27 +14886,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11-36-23-20-19-5-18-6-10-9-8-21-34-75-62-63-87-88-73-60-47-71-58-33-49</t>
+          <t>20-18-8-21-47-71-58-73-60-62-63-75-49-36-23-34-33-6-5-19-9-10-11</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>7</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>110-97-109-83-96-84-87-88-101-102-113-124-135-162-138-139-154-153-164-150-152-100-161-136-123-122</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>82-69-81-68-28-27-29-43-40-26-51-79-78-77-67-65-38-66-3-16-55-56-53-52-12-13-39</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>91-103-104-106-118-143-155-157-132-119-117-129-130-133-146-159-105-93-92</t>
+          <t>129-155-104-92-91-103-105-118-106-108-121-119-132-133-146-147-159-143-157-130-117-93</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -14976,35 +14976,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>123-100-113-84-97-115-128-153-140-112-89-114-126-152-151-154-167-166-101-85-86-102-76-111-110-137-150</t>
+          <t>43-56-67-79-81-80-91-78-90-77-65-68-55-38-52-25-0-2-15-16-41-53-28-29-42</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>33-8-18-70-84-71-45-31-5-7-46-85-76-50-49-36-35-44-74-73-72-58-59-32-34-11-22-9-19-20-60-47-61</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>15-16-70-80-67-78-90-91-77-52-65-79-81-68-53-38-25-43-56-55-42-29-41-28-2-0</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>7</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>5-18-7-20-19-8-46-44-31-32-47-49-59-11-50-36-35-22-9-45-71-72-58-60-73-74-61-34-33</t>
+          <t>110-97-113-154-153-128-126-152-151-150-137-123-111-101-102-114-112-100-86-89-115-167-166-140</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>95-94-109-96-121-122-132-129-142-103-131-156-161-162-149-134-160-145-144-120-133-147-148-119-106</t>
+          <t>147-134-161-160-122-109-96-106-119-132-103-131-148-133-144-156-142-129-162-149-121-95-94-120-145</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -15074,35 +15074,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>95-93-157-144-158-155-92-105-131-134-135-148-122-108-107-106-91-90-129-130-120-94-81-103-143-133-121-96</t>
+          <t>94-107-134-121-122-110-108-81-42-27-67-95-97-85-72-57-55-83-96-84-71-70-68</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>27-28-2-1-3-15-16-79-78-77-64-38-51-52-66-42-67-68-55-26-25</t>
+          <t>151-164-87-99-166-165-135-136-137-113-140-141-153-152-139-127-114-89-115-111-124-123-148-162-138-167-154</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>10-6-31-18-44-57-58-83-85-84-71-72-75-50-7-8-33-60-59-45-70-19-17-4-46-47-34-35-37-61-11</t>
+          <t>133-158-106-66-79-92-25-26-38-51-77-90-103-155-129-130-52-78-64-93-91-120-131-105-143-157-144</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>10-11-50-47-34-6-19-33-7-8-35-31-17-18-58-59-37-75-60-61-4-3-2-1-28-16-44-15-46-45</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>99-113-115-114-138-164-165-152-166-123-111-97-110-154-141-167-140-127-87-137-139-153-151-162-136-124-89</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -15172,35 +15172,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>107-119-158-155-144-156-130-91-93-92-82-81-109-120-145-160-131-118-106-95-96-135-132-116-129-142</t>
+          <t>86-85-98-151-150-163-101-102-153-167-165-124-140-137-125-127-88-100-97-96-111-112-113-114-154-141-115-135-136-123-109-99</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>64-65-67-53-39-38-26-13-1-2-3-29-27-40-41-68-51</t>
+          <t>160-144-129-142-130-132-120-106-92-131-156-155-91-116-118-119-93-95-82-81-107-145-158</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>9-21-20-32-33-46-47-59-44-43-4-18-5-19-45-48-74-73-49-22-71-84-83-70-31-8-10-35-58-56</t>
+          <t>65-68-56-43-53-67-40-41-29-4-13-1-39-26-27-3-2-38-64-51</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>125-154-137-124-98-99-112-150-151-113-114-100-75-88-86-85-97-111-136-167-153-165-163-140-127-141-101-102-115-123</t>
+          <t>31-45-74-49-35-21-8-20-5-32-46-58-70-71-59-47-75-48-22-33-19-9-10-83-84-73-44-18</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -15270,35 +15270,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>118-155-142-105-144-157-158-148-159-143-130-92-132-120-95-122-135-134-146-119-121-107-96-83-93-106-90-104-116-131-147-109-108</t>
+          <t>159-132-118-107-108-95-121-120-106-92-144-157-158-143-155-131-134-146-119-105-130-142-116-90-104-93-147</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>71-46-22-8-7-33-35-24-50-36-60-59-32-21-62-61-88-63-49-11-23-85-87-74-72-86-73-76-89-58</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>8-21-7-32-72-73-11-24-35-74-76-49-36-23-22-61-58-46-62-63-50-60-71-59-33</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>55-68-52-51-39-56-43-31-69-42-27-40-14-15-3-17-18-5-70-83-80-66-65-67-12-25-0-13-26</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>102-115-141-140-127-139-153-154-167-148-149-136-125-124-99-97-122-109-96-123-135-162-151-138-126-101-98</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>51-55-42-15-27-67-66-80-31-56-68-69-70-43-18-5-17-40-52-39-25-12-0-14-26-13-3-65</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>127-154-162-136-97-86-85-98-99-88-101-115-149-123-124-126-102-87-125-138-139-151-153-140-167-141-89</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -15368,31 +15368,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>99-89-102-100-112-110-137-138-113-101-128-114-87-98-111-83-125-124-136-150-163-165-140-152-151-135-122</t>
+          <t>58-46-33-21-9-6-19-72-60-36-23-37-63-62-49-22-20-31-32-45-71-83-73</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>100-113-112-137-124-136-151-152-165-140-102-101-98-110-125-150-163-138-128-114-111-99-89-87</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>58-71-45-33-9-23-36-22-20-21-6-31-19-32-46-60-63-37-49-62-73-72</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>8</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>66-67-1-2-41-29-30-3-69-68-64-51-38-12-25-42-43-55-54-27-13-14-0-52-53-16-17-28</t>
+          <t>121-122-135-146-133-147-159-104-105-90-107-118-131-119-93-103-117-130-145-144-156-157-142-129-94-95</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>104-93-78-90-103-130-157-133-145-121-107-95-82-94-118-131-144-156-146-147-159-117-105-79-81-119-129-142</t>
+          <t>38-51-54-2-1-0-27-29-43-17-3-16-28-67-53-25-12-14-41-69-68-81-82-79-64-13-42-30-55-78-66-52</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -15466,7 +15466,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>92-133-147-159-120-94-105-117-131-130-118-106-93-132-143-129-116-104-108-134-145-142-155-157-160-103-77-79</t>
+          <t>27-67-44-69-81-68-66-40-12-0-2-15-28-16-17-3-18-5-30-55-70-56-29-14-25-38-51-64-42-43</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -15474,15 +15474,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>25-64-68-70-44-30-29-51-38-42-56-69-55-16-3-0-14-5-18-17-43-67-66-81-28-15-2-12-27-40</t>
+          <t>136-162-123-125-124-137-127-86-85-97-111-84-109-163-154-126-112-113-139-102-88-110-138-166-164-128-101-152-150-151-148-161</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>7-8-20-33-45-88-62-61-35-6-32-21-10-23-9-11-24-37-63-49-50-76-74-47-36-48-60-71-58</t>
+          <t>133-118-129-103-77-117-157-159-160-147-132-145-134-120-94-93-79-104-105-92-116-130-131-106-108-155-142-143</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -15490,11 +15490,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>138-126-112-111-123-136-125-127-139-163-150-148-137-154-101-102-128-113-152-166-124-85-84-97-86-110-109-161-162-164-151</t>
+          <t>35-9-24-37-50-49-48-21-33-32-45-60-71-58-23-11-76-63-36-74-62-61-47-10-6-7-8-20</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -15564,15 +15564,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>96-95-159-144-132-131-103-116-104-80-77-81-94-107-134-147-158-91-78-106-120-108-119-118-155-142-143-133-121-82</t>
+          <t>56-43-81-67-38-77-78-52-41-39-64-80-82-70-28-15-0-25-40-26-2-69-68-66-16-4-17-57-18-30-12-13-14</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>35-45-72-57-70-32-33-8-21-10-24-37-36-86-85-74-88-89-49-22-7-11-63-76-73-58-59-48-61-47-34</t>
+          <t>128-138-164-162-149-165-166-113-100-110-123-124-125-126-140-153-151-150-136-99-97-139-154-167-114-101</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -15580,15 +15580,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>67-68-56-69-41-43-14-26-18-4-30-17-39-38-25-28-15-16-2-0-13-12-52-64-66-40</t>
+          <t>142-131-143-118-107-95-106-119-158-144-132-133-120-147-161-96-94-108-121-134-159-155-104-103-116-91</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>150-164-151-114-101-113-167-154-140-125-126-139-165-166-136-124-138-149-161-162-110-99-100-128-153-123-97</t>
+          <t>34-61-89-76-49-48-74-73-85-45-58-59-88-63-24-21-33-35-36-22-8-47-72-86-32-7-10-11-37</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -15662,7 +15662,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>157-158-129-130-121-147-108-95-119-156-143-155-142-104-116-105-120-134-145-132-94-106-92-133-146-160</t>
+          <t>5-6-33-34-37-35-62-73-60-88-7-20-45-8-22-11-24-36-63-76-74-59-57-58-71-70-18-31</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -15670,7 +15670,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7-20-37-63-76-88-74-33-6-58-71-59-45-73-34-35-22-11-24-36-62-60-8</t>
+          <t>116-106-119-120-94-92-104-105-130-142-155-158-145-132-143-156-133-147-146-134-121-95-108-160-157-129</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -15678,15 +15678,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16-56-82-70-57-17-5-18-31-41-40-54-55-66-64-38-15-42-68-80-53-52-28-14-13-1-26-39-78-77</t>
+          <t>39-26-13-14-15-41-28-16-17-56-40-1-42-68-80-78-82-66-64-77-53-54-55-52-38</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>123-136-163-153-154-139-141-140-112-125-137-162-161-135-99-100-101-110-113-126-138-167-165-151-122-98-97-96-109</t>
+          <t>109-123-112-113-126-153-140-141-154-167-100-101-122-136-151-165-163-139-125-138-137-97-96-98-99-110-135-162-161</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -15760,15 +15760,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>113-138-137-122-111-124-136-135-96-83-110-150-163-98-84-97-99-112-123-148-149-102-101-86-125-139-114-165-166-167-154-153</t>
+          <t>41-56-43-29-3-15-1-0-25-12-27-39-40-2-16-14-26-53-66-67-65-64-78-77-55-28</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>58-73-61-36-9-11-23-45-5-18-19-33-32-6-7-21-72-60-35-62-75-76-63-37-34</t>
+          <t>135-148-130-129-118-122-160-157-156-144-158-132-107-108-83-94-104-103-90-93-82-96</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -15776,19 +15776,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>53-64-66-65-67-55-56-43-41-40-39-25-12-26-0-1-3-16-2-29-15-14-27-28</t>
+          <t>97-84-98-112-113-138-163-149-124-101-102-125-139-166-167-154-153-114-111-136-137-165-150-110-123-99-86</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>108-160-158-107-94-132-157-156-144-118-130-129-104-90-78-77-103-93-82</t>
+          <t>60-34-7-21-35-45-58-32-19-9-6-5-18-33-62-75-76-37-11-23-36-63-61-72-73</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -15858,15 +15858,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>123-99-112-124-127-151-166-154-140-152-110-97-136-148-149-138-126-115-102-100-101-128-165-164-137</t>
+          <t>136-110-112-101-152-164-137-151-149-124-97-99-100-154-166-127-102-128-115-126-140-165-138-123-148</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7-20-44-58-85-59-8-6-10-36-50-49-34-47-46-61-60-45-57-70-71-84-88-62-63-76-75-74</t>
+          <t>0-13-56-30-18-43-29-42-70-57-44-67-40-41-54-66-53-69-2-3-1-14-27-65-39-25-26-4-5-17-16</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -15874,7 +15874,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1-2-41-0-13-40-53-65-39-25-26-69-67-42-43-30-29-17-16-14-27-66-54-56-18-5-4-3</t>
+          <t>75-62-49-10-7-6-8-50-63-36-46-45-20-34-47-58-59-74-61-60-76-88-85-71-84</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -15882,7 +15882,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>90-77-94-92-80-82-95-121-108-146-131-120-130-158-147-109-96-81-78-144-156-155-117-105-119</t>
+          <t>92-81-80-96-121-146-155-156-130-90-77-95-82-108-147-158-117-78-105-131-144-119-120-109-94</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -15956,7 +15956,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>108-119-129-90-91-92-121-134-160-145-117-103-77-78-105-120-156-143-130-131-79-80-94</t>
+          <t>105-121-94-92-117-91-90-103-129-130-145-160-134-135-120-109-108-96-83-143-156-131-119</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -15964,7 +15964,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>39-38-51-64-54-18-31-56-55-69-70-12-13-25-52-65-66-67-14-15-17-4-43-57-68-30-29-2-3-16-41-27</t>
+          <t>64-77-68-41-13-12-25-38-27-15-16-30-29-43-55-69-67-78-51-52-66-80-54-65-79-57-70-56-17-4-14-2-3-39</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -15972,19 +15972,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21-8-9-6-23-36-50-35-48-72-59-33-47-46-62-75-73-71-11-10-24-63-74-32</t>
+          <t>59-73-72-31-46-33-48-35-24-6-18-71-75-63-11-23-9-10-36-50-62-74-47-8-21-32</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>136-149-152-153-154-167-128-102-114-101-127-165-163-151-150-137-135-111-100-86-99-98-126-125-123-109-96-97-84-83</t>
+          <t>111-114-101-98-128-127-153-167-154-126-125-136-84-97-151-152-165-163-150-149-137-123-100-102-86-99</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -16054,31 +16054,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>112-99-85-87-100-139-140-128-141-115-89-102-125-137-151-152-162-150-149-165-127-111</t>
+          <t>42-43-3-17-68-78-64-25-26-79-67-56-54-77-51-39-53-52-40-15-1-14-0-27</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>89-85-111-151-152-165-128-115-112-99-100-102-127-141-140-139-162-149-150-137-125-87</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>7</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>18-33-21-8-22-63-50-47-46-5-7-6-34-59-70-72-58-45-73-74-61-37-48-9-11-24-60-32-31-19</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25-39-52-26-15-42-56-68-79-64-51-54-43-27-1-14-3-17-67-78-77-53-40-0</t>
+          <t>156-107-82-83-109-96-122-161-160-92-81-95-108-147-146-117-103-116-130-142-90-93-91-118-131-145-144-158-155</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>118-145-160-161-147-146-158-156-117-93-95-83-82-91-92-122-109-96-81-107-108-131-144-116-103-90-142-155-130</t>
+          <t>32-18-6-7-8-11-24-37-59-45-73-74-63-61-60-19-5-31-46-48-47-72-70-58-22-9-34-33-50-21</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -16152,7 +16152,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>107-95-94-93-119-143-116-155-158-133-132-145-157-131-120-121-108-134-159-146-91-90-103-105-118-130-142</t>
+          <t>130-142-155-132-121-120-143-157-158-159-145-146-133-134-95-91-94-108-107-105-93-103-90-116-118-119-131</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -16160,15 +16160,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>65-64-51-69-57-70-54-41-52-53-42-29-55-82-81-79-66-67-68-56-43-30-17-3-14-28-38-25-26</t>
+          <t>33-86-72-45-5-6-19-11-10-9-22-49-88-75-74-61-35-20-58-48-21-34-47-84-85-89-50-24-63-60-73-59</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>34-19-20-5-6-45-59-49-88-89-75-9-11-10-24-50-63-73-72-47-22-21-48-35-61-74-60-58-33</t>
+          <t>152-154-115-102-150-114-113-100-98-109-111-136-162-163-164-151-126-99-110-148-161-135-124-128-127-167-166</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -16176,11 +16176,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>85-86-84-100-164-166-154-162-135-136-110-109-150-161-163-151-152-115-114-102-124-148-111-99-128-167-127-126-113-98</t>
+          <t>3-43-69-55-28-41-57-70-82-67-66-64-26-14-30-68-54-53-65-51-38-25-52-79-81-42-56-29-17</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -16250,35 +16250,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>130-131-95-94-132-134-121-120-107-106-92-78-91-118-146-147-159-143-157-155-142-129-105-104-103-116</t>
+          <t>73-76-75-50-24-9-23-10-5-6-7-21-36-49-33-32-46-34-48-61-62-60</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>40-13-12-25-38-28-27-52-41-3-17-5-56-68-57-83-80-55-54-66-53-31-44-69-42-1</t>
+          <t>152-136-138-124-102-89-88-137-164-154-167-166-141-111-110-135-148-149-127-140-115-113-126-87-84-100-153-114-128-139-151-162-165-150-163-109-86-85-98-123</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>83-69-31-17-3-42-27-28-66-54-68-25-1-40-55-56-57-44-41-53-80-78-12-13-38-52</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>107-94-92-105-120-134-159-146-157-143-142-116-103-131-155-132-104-91-106-121-147-130-129-118-95</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>10-24-60-84-85-73-86-87-61-34-23-21-48-75-89-76-62-49-36-50-88-46-33-32-6-7-9</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>135-163-114-111-98-124-136-137-164-151-150-109-123-110-127-139-126-113-128-140-141-138-162-152-153-154-102-100-115-167-166-165-148-149</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -16348,15 +16348,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>150-124-111-97-87-100-138-139-165-152-140-141-154-167-127-112-86-110-123-149-125-113-102-115</t>
+          <t>130-155-156-118-116-129-105-119-120-121-134-132-146-147-148-161-159-91-90-131-144-158</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>62-74-76-50-6-21-46-60-10-11-37-23-61-73-71-58-45-32-34-22-9-8</t>
+          <t>83-96-140-127-152-165-167-154-141-113-87-102-115-139-124-125-138-150-149-123-110-97-86-112-100-111</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -16364,19 +16364,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1-27-40-39-68-69-57-43-31-18-15-28-26-0-13-25-12-67-53-41-17-16-29-42</t>
+          <t>39-40-53-67-28-29-17-41-25-26-78-79-68-43-16-15-1-0-12-13-27-42-69-81-82</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>96-130-118-105-79-91-90-78-81-121-132-144-155-116-129-119-131-156-159-158-161-148-134-146-147-120-82-83</t>
+          <t>37-11-74-76-62-73-46-61-22-9-21-34-45-60-71-32-58-57-18-31-6-8-10-23-50</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -16446,23 +16446,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>92-91-142-143-156-157-144-131-105-93-117-116-103-135-161-122-109-95-120-133-108-94-147-160-146-145</t>
+          <t>114-100-101-115-128-140-151-164-136-110-97-150-161-162-153-154-167-166-152</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>40-25-38-26-14-0-15-57-56-70-81-82-68-66-64-77-80-55-43-54-53-16-3-28-30-42-39</t>
+          <t>57-70-84-58-33-46-87-73-18-6-7-19-32-37-49-85-60-88-76-36-34-22-24-10-21</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>34-22-7-21-46-58-32-18-19-33-60-73-76-49-37-24-36-10-6</t>
+          <t>26-25-38-40-39-64-53-15-16-30-56-68-55-43-3-66-54-42-28-14-0</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -16470,11 +16470,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>115-87-97-84-85-88-101-114-154-167-166-164-151-162-150-136-110-100-140-152-153-128</t>
+          <t>80-92-91-77-103-116-117-93-105-131-142-144-160-147-120-133-146-145-94-81-109-108-143-156-157-122-135-82-95</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -16544,15 +16544,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>104-91-93-92-83-82-134-160-161-135-122-156-157-158-159-147-109-95-121-133-132-105-106-107-120-118-103-116</t>
+          <t>69-70-56-31-17-16-29-28-2-14-26-27-66-65-38-39-1-0-67-43-44-30-53-41-42-12-25-40-54-68</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>77-79-53-40-17-2-0-1-14-25-12-26-41-29-42-30-43-68-67-54-28-38-39-65-66-56-69-27-16</t>
+          <t>104-156-157-158-132-133-134-147-160-159-107-92-79-83-82-95-93-106-103-91-105-135-109-122-121-120-77-116-118</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -16560,7 +16560,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>76-63-23-24-37-10-9-35-22-45-58-32-19-20-34-36-61-47-72-71-60-49-33-31-44-70</t>
+          <t>60-49-63-24-37-23-22-36-34-35-33-20-45-58-32-19-9-10-76-89-86-87-61-47-71-72</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -16568,11 +16568,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>128-138-139-166-154-167-164-163-123-111-112-137-151-152-150-162-136-141-127-101-99-86-97-98-89-102-87-113</t>
+          <t>139-151-152-154-141-128-102-112-113-99-127-167-166-164-162-163-150-136-97-98-101-138-137-161-123-111</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -16642,35 +16642,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-103-155-143-116-81-106-156-145-146-147-133-95-93-78-77-104-105-91-129-130-157-159-158-131-94-82-121-120-118</t>
+          <t>49-63-76-33-46-72-74-73-32-45-6-21-35-11-24-50-62-47-34-37-23-10-9-8</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>45-46-34-33-6-32-8-10-24-37-62-74-72-21-9-11-23-50-63-49-35-47-73-76</t>
+          <t>96-97-115-128-88-102-85-84-123-149-138-111-83-98-86-99-112-126-139-164-151-167-154-127-152-114-87-122-109</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>131-118-105-106-94-78-77-93-104-91-90-103-143-158-147-95-121-120-133-146-159-130-116-129-155-156-157-145</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>17-4-3-1-31-18-5-66-65-38-39-13-27-70-57-44-52-26-12-25-64-53-40-28-41-68-67-14</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>152-139-86-97-88-87-99-98-127-128-167-154-102-114-115-83-96-122-109-138-111-123-149-164-151-84-85-112-126</t>
+          <t>3-5-44-70-82-68-66-65-13-12-18-31-57-81-67-64-52-25-38-41-53-39-4-17-14-28-27-40-26-1</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -16740,31 +16740,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>108-95-82-80-107-133-146-160-131-118-103-90-92-104-130-116-106-121-94-120-132-157-129-156-155-142-78-91-77</t>
+          <t>80-67-54-16-27-14-2-3-82-68-40-53-52-26-13-0-25-29-42-65-77-51-64-78</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>50-24-49-89-88-86-57-70-71-84-83-44-22-48-62-76-61-72-58-20-45-46-59-73-85-34-33-21-7-6</t>
+          <t>30-43-57-48-50-49-24-33-45-58-84-71-59-73-72-70-56-44-31-34-7-5-61-62-85-83-46-22-21-6-4-17-20</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>54-68-56-67-65-53-52-40-14-13-0-51-64-26-25-27-30-31-17-16-43-42-29-5-4-3-2</t>
+          <t>110-125-139-137-151-150-162-154-141-101-112-98-86-97-149-163-164-167-128-115-127-88-100-111-123-114-89-76</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>111-112-101-114-128-167-154-141-163-149-135-148-161-110-97-100-125-150-123-122-137-139-127-115-162-164-151-98</t>
+          <t>104-130-129-142-131-121-118-116-156-155-157-132-160-122-135-148-94-91-103-90-146-161-133-106-108-95-107-120-92</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -16838,35 +16838,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>92-90-142-159-120-119-157-156-130-118-132-146-134-95-108-122-109-106-104-129-161-160-147-133-121-107-81-83-96-91</t>
+          <t>51-38-26-40-41-54-67-66-79-78-65-52-42-55-27-39-13-12-25-14-16-3-17-28</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>42-28-14-13-12-54-55-67-79-66-65-51-52-40-27-25-39-26-38-78-70-80-17-3-16-41</t>
+          <t>9-7-20-45-46-33-87-75-48-32-31-19-72-85-84-60-21-36-37-50-62-61-70-58-49-35-10-11-23-22</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>37-49-60-45-32-31-19-7-21-48-61-62-75-50-36-23-22-9-10-11-35-58-72-46-33-20</t>
+          <t>162-164-136-154-167-140-152-139-151-138-150-125-112-101-102-114-127-153-141-128-126-123-100-98-113-97</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>125-123-126-140-141-128-138-151-150-136-162-152-164-153-139-113-87-101-102-167-154-127-97-84-85-98-112-114-100</t>
+          <t>104-90-118-130-156-157-122-108-134-132-142-159-146-133-129-80-83-96-121-147-160-161-91-92-107-120-119-106-81-95-109</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -16936,35 +16936,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>91-157-148-147-160-161-144-131-92-105-118-103-120-108-134-121-122-109-156-155-142-107-95-96-119-130-132-117-145-159-146-158-129-90</t>
+          <t>115-154-166-167-141-128-114-127-125-153-165-151-138-139-152-163-137-111-162-136-124-113-102</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>5-18-31-15-0-13-28-79-81-82-56-30-16-26-40-52-78-77-64-65-39-14-25-38-51-54-29-43-68</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>7-9-22-36-37-50-63-49-73-72-85-84-57-97-71-59-47-98-99-88-74-89-62-6</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>7</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>108-146-144-130-157-156-145-148-161-158-155-129-132-119-121-122-147-160-95-105-117-118-103-107-90-91-92-131-142-159-134-120-96-109</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>4</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>25-38-64-78-15-14-40-52-26-29-30-5-31-56-79-65-39-28-43-54-51-77-13-0-18-57-68-82-81-16</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>36-37-50-62-63-85-84-71-59-47-6-7-9-22-49-89-88-74-73-72</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>8</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>111-125-139-138-137-136-162-165-166-167-154-102-114-115-127-113-128-141-153-152-151-163-99-98-124-97</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -17034,35 +17034,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>96-109-123-166-165-113-100-125-99-97-137-150-149-139-151-164-162-163-135-161-84-86-98-87-102-115-112-124-136-114-140-153-167-127-128-83</t>
+          <t>123-149-163-162-137-98-125-139-165-164-166-167-140-127-99-86-84-97-112-100-87-102-128-115-113-114-136-150-153-151-124</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>49-75-76-48-46-45-72-71-32-19-6-9-10-24-11-21-20-50-63-62-74-61-37-8-7-22-35-23</t>
+          <t>13-28-4-17-30-25-26-51-77-79-67-53-40-39-65-54-42-44-43-29-15-1-0</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>8</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>120-145-157-155-143-144-161-147-146-119-83-93-95-121-132-118-130-117-104-91-92-105-94-108-96-109-135-133</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>13-26-39-40-54-42-28-43-44-30-29-17-4-15-1-0-67-53-65-51-25</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>9</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>119-143-155-130-145-157-144-132-118-117-94-95-120-147-146-133-121-108-77-104-91-79-92-105-93</t>
+          <t>21-7-45-35-49-50-37-63-72-71-61-75-76-74-48-62-22-8-9-11-24-23-10-19-6-20-32-46</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -17132,15 +17132,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>106-121-108-94-91-90-117-116-142-155-156-157-158-143-129-132-133-118-103-104-92-93</t>
+          <t>6-24-48-49-23-60-58-21-9-8-11-34-35-20-19-42-29-44-43-57-70-59-46-31-18-30-16</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>77-64-53-68-81-82-43-30-14-0-12-16-29-42-55-78-66-79-39-38-25-26-67</t>
+          <t>122-137-149-133-132-158-156-157-161-164-150-124-97-84-108-121-135-148-162-123-83-96-110</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -17148,19 +17148,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>20-21-46-35-23-9-8-31-44-18-6-19-58-70-34-48-49-24-11-60-75-76-59-57</t>
+          <t>26-142-129-90-117-106-118-64-77-104-143-155-116-103-79-92-91-68-66-78-67-38-81-55-14-12-0-82-94-93-39-53-25</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>98-112-113-127-141-128-101-86-111-138-164-124-96-83-110-137-97-122-149-150-162-139-100-102-115-154-153-161-148-135-123-85-84</t>
+          <t>101-127-139-138-112-100-113-86-98-85-111-153-154-141-128-102-115-76-75</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -17230,23 +17230,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>138-151-167-84-85-113-114-127-165-102-89-101-97-110-109-96-83-87-125-124-112-123-150-164-154-141-140-139-152-162-149-135-148-122</t>
+          <t>14-43-17-5-18-29-39-25-26-13-40-27-66-42-41-69-56-1-0-12-38-51-65</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>7</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>130-92-93-96-135-133-145-160-159-142-129-131-121-122-109-94-107-106-105-161-148-156-155-158-146-119-132-144-103-91</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>14-13-66-69-17-1-26-40-39-38-51-65-25-0-12-29-42-43-56-41-27</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>7</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>45-58-44-57-9-11-50-49-23-5-18-7-33-74-63-62-73-60-59-34-35-21-46</t>
+          <t>114-127-123-110-97-112-124-125-150-151-167-154-102-140-139-152-138-149-162-164-165-141-101-113</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -17254,11 +17254,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>144-132-145-158-146-93-92-105-103-91-142-159-160-161-121-133-131-130-155-156-119-106-94-107-129</t>
+          <t>7-21-35-62-49-33-73-85-87-89-74-63-23-9-45-44-58-57-83-84-60-50-11-34-59-46</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -17328,7 +17328,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>82-96-95-91-77-90-142-160-159-146-78-107-103-155-143-117-105-106-119-122-134-145-144-133-121-109-108-94</t>
+          <t>84-72-59-33-21-6-19-34-49-8-9-36-10-46-48-75-88-89-61-37-24-63-76-62-45-32</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -17336,23 +17336,23 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>32-46-48-34-33-19-6-8-21-72-75-63-76-62-49-61-36-37-9-10-24-59-45</t>
+          <t>125-128-141-140-153-124-97-162-163-164-114-113-99-98-136-150-165-166-102-101-115-127-139-137</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>41-65-56-69-31-17-18-4-5-44-57-29-38-51-39-40-27-14-2-0-12-13-28-42-54</t>
+          <t>44-17-40-12-39-51-65-42-56-57-18-5-4-31-29-2-14-38-13-0-27-28-41-54-69</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>136-124-98-84-115-127-166-165-99-113-101-89-88-102-114-140-141-128-97-137-162-163-150-164-153-139-125</t>
+          <t>94-95-96-105-90-103-117-106-119-107-142-155-143-144-160-146-145-133-108-122-109-121-134-159-91-78-77-82</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -17426,7 +17426,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>148-109-122-121-119-92-93-131-133-120-106-107-96-108-132-155-142-90-91-103-116-117-118-144-158-161-130-143-146-160</t>
+          <t>142-144-121-133-155-143-119-108-81-82-93-80-92-118-117-158-160-146-120-132-131-91-90-78-107-106-103-116-130</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -17434,15 +17434,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>52-66-40-2-0-25-38-51-64-78-67-39-26-4-30-15-29-43-54-81-68-82-80-65</t>
+          <t>70-84-83-72-60-58-33-47-89-88-75-76-63-24-46-35-23-8-6-19-5-18-44-32-34-49-74</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>18-24-35-58-70-44-46-49-23-8-19-6-5-32-72-83-84-75-74-60-76-63-47-34-33</t>
+          <t>137-122-97-110-162-161-148-164-114-115-101-128-154-167-166-165-138-125-124-136-109-96-99-112-140-153-150-113</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -17450,11 +17450,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>166-167-153-140-138-124-110-97-113-137-165-164-162-125-112-99-101-88-89-115-128-154-114-150-136</t>
+          <t>4-30-43-67-66-38-64-65-29-15-0-25-26-40-68-54-52-51-39-2</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -17524,7 +17524,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>131-107-94-81-80-133-147-108-93-90-78-79-105-118-134-121-117-130-145-146-159-157-155-129-116-92-119-103-156-144-143</t>
+          <t>117-129-103-90-105-146-145-155-156-118-130-116-143-157-144-108-134-147-159-133-121-92-94-107-93-78-79-119-131</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -17532,15 +17532,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>62-48-6-19-33-11-10-34-46-58-75-74-7-8-21-20-35-36-50-61-60-87-88-89</t>
+          <t>167-154-141-127-166-139-124-109-98-113-137-123-96-97-135-136-163-165-164-152-138-122-148-150-99-125-126-149-161-112-100-115-128</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>17-3-16-29-42-27-40-39-38-41-68-69-55-31-70-5-4-2-15-28-64-67-12-14</t>
+          <t>10-34-21-20-19-6-7-58-87-74-89-88-11-36-62-75-61-48-60-46-33-8-35-50</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -17548,11 +17548,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>128-115-100-124-109-99-96-97-123-148-161-164-154-167-166-163-149-135-136-165-152-150-138-127-126-113-112-98-122-137-125-141-139</t>
+          <t>16-29-41-39-80-40-12-4-5-3-28-14-38-27-64-68-69-70-55-31-17-42-67-81-15-2</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -17622,35 +17622,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>90-104-116-146-157-129-156-131-158-159-93-107-108-133-143-155-142-130-117-78-79-92-120-94-91</t>
+          <t>122-109-107-130-131-116-117-92-91-129-155-142-93-94-96-133-146-157-161-148-108-135-120-104-90-143-156-158-159</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>70-45-32-5-20-23-35-72-85-84-61-46-71-58-86-88-87-62-34-49-63-37-36-75-76-89-47-21-22-18-57-44</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>82-81-64-52-38-40-53-43-56-66-79-65-78-39-16-2-27-55-30-3-1-0-28-54-69</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>6</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>61-75-102-89-85-71-84-58-47-35-23-76-63-22-34-32-45-36-37-49-62-46-72-86-88-87-20-21</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>69-82-70-43-56-0-1-27-3-16-5-2-18-57-44-30-28-53-66-52-64-65-39-40-55-54-38-81</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>139-126-127-154-153-96-109-125-112-100-99-114-165-163-122-135-136-151-152-164-161-148-123-137</t>
+          <t>151-164-125-112-99-100-102-114-127-153-154-126-139-152-165-163-136-123-137</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -17720,31 +17720,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>117-155-143-130-80-108-93-146-133-145-147-134-121-95-82-94-105-103-78-92-106-79-116-129-156-158-159-157-119-104</t>
+          <t>108-96-110-123-136-150-162-161-159-158-148-138-166-164-149-147-146-134-133-145-157-121-122</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>59-60-48-35-11-50-76-72-45-6-32-58-73-75-61-49-22-8-20-47-23-7-46</t>
+          <t>78-64-79-93-92-105-143-156-155-129-94-82-95-104-103-116-130-117-119-106-80-67-65-51</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>27-42-44-57-70-28-5-31-29-2-1-12-38-65-64-51-67-68-56-43-16-40-41-15-14-0-26</t>
+          <t>0-15-2-28-41-68-70-29-43-56-58-44-31-42-1-26-40-38-12-14-27-5-20-7-32-57-45-8-6-16</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>85-138-150-112-113-98-110-97-86-84-115-102-154-167-166-126-149-162-125-153-164-161-148-136-122-87-100-101-96-123-111-141-114-140-127-128-99</t>
+          <t>11-50-102-115-128-99-86-87-140-154-141-127-112-111-22-23-49-61-73-100-85-98-76-35-47-72-48-59-46-75-101-84-113-114-126-153-167-125-97-60</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -17818,15 +17818,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>88-89-114-113-127-100-84-124-162-163-151-164-149-98-86-99-126-125-137-136-123-122-110-96-83-152-166-115-101</t>
+          <t>12-16-17-42-28-18-66-65-52-26-13-2-1-0-14-4-5-69-55-40-39-38-25</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>61-46-59-73-75-76-74-49-23-11-50-63-62-7-6-18-5-33-8-24-37-47-32-70-58-45-35</t>
+          <t>7-23-24-75-62-89-88-76-63-50-47-45-46-33-32-58-70-6-11-37-59-73-86-61-74-49-35-8</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -17834,15 +17834,15 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25-12-26-1-2-13-14-28-39-52-65-77-38-0-4-17-16-42-55-69-66-40</t>
+          <t>105-118-147-160-121-120-92-79-77-91-108-95-81-93-80-130-143-142-117-129-131-145-156-144-132-107-94</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>132-131-130-143-144-145-148-161-95-91-105-80-81-108-121-147-120-118-92-79-94-107-160-156-142-129-117-93</t>
+          <t>164-166-126-115-114-127-136-110-148-161-137-162-149-163-151-152-113-101-100-124-99-98-125-123-122-83-84-96</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -17916,35 +17916,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>158-159-146-108-107-95-92-78-91-142-116-117-130-105-118-143-155-160-133-103-82-81-106-93-134-145-132-90-77</t>
+          <t>98-97-112-125-114-126-127-139-166-167-115-141-140-152-165-151-123-124-84-100-113-102-101-88-137-162-163-99-86</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19-37-49-62-34-46-45-60-73-63-75-74-24-36-48-47-59-71-20-21-11-23-22-6</t>
+          <t>18-19-45-60-57-71-75-36-63-62-73-59-31-44-46-11-24-23-37-49-74-47-48-21-22-34-20-5-6</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>12-26-40-51-38-39-69-68-55-30-17-5-0-13-14-16-54-66-65-64-53-41-57-44-31-4-18-27</t>
+          <t>66-54-78-53-0-16-4-17-30-55-69-68-41-40-39-14-27-26-13-12-38-65-51-64-77</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>125-140-127-141-139-124-165-166-167-162-135-137-102-86-97-122-123-163-151-152-114-88-101-115-113-100-98-99-126-112-84</t>
+          <t>105-130-142-155-143-118-90-103-91-93-92-159-160-134-122-107-108-135-81-82-95-132-145-158-117-116-133-146-106</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -18014,35 +18014,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>95-108-120-104-90-105-93-116-129-142-130-134-147-131-143-155-144-157-158-159-161-160-146-132-119</t>
+          <t>71-84-83-58-7-21-45-19-31-85-75-50-48-35-8-10-23-22-57-70-72-73-60-49-24-76-74-47-9-32-44</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>49-35-21-7-8-9-23-60-48-24-10-22-19-32-47-75-73-72-71-58-45-74-50-76</t>
+          <t>4-3-16-29-42-43-81-82-41-0-13-25-27-26-39-64-77-80-68-67-53-40-17-2-15-28-55-69-56</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>82-70-69-81-57-56-67-68-40-17-44-83-43-2-0-26-77-53-39-15-31-42-13-25-27-16-4-3-64-80-55-41-28-29</t>
+          <t>104-116-144-134-147-132-158-131-130-105-90-129-159-160-161-135-146-157-142-155-143-119-120-95-108-93</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>123-149-112-88-89-138-150-135-137-167-166-154-115-139-125-140-98-110-124-165-151-136-109-96-97-85-99-87-100-84</t>
+          <t>100-115-154-167-110-97-136-149-150-124-112-99-139-165-166-140-87-123-137-151-138-125-89-88-98-96-109</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -18112,7 +18112,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>162-148-136-139-126-125-137-151-164-152-163-150-138-154-127-115-101-99-111-112-140-141-166-165-124-110</t>
+          <t>93-94-96-83-95-108-81-80-91-133-155-156-117-129-90-104-118-119-120-121-134-146-131-160-109-107</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -18120,27 +18120,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>37-36-50-63-72-46-84-85-71-47-22-23-9-10-11-21-6-19-20-48-76-89-75-87-73-60-59</t>
+          <t>70-73-60-63-50-72-71-85-87-75-89-76-11-37-36-48-47-22-21-20-59-57-19-6-46-9-10-23-84</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>14-52-65-66-70-56-42-17-4-29-57-54-68-55-15-27-39-64-51-12-13-0-1</t>
+          <t>12-64-51-65-52-55-29-56-68-66-54-42-4-17-15-39-27-14-13-1-0</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>136-151-150-125-112-115-101-99-110-111-124-137-164-166-165-152-139-138-154-141-140-127-126-162-163-148</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>90-104-119-146-156-117-131-121-108-109-95-81-94-93-120-107-96-83-80-91-118-160-134-133-155-129</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -18210,35 +18210,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>161-159-105-120-134-107-119-104-103-129-130-145-118-117-91-90-92-109-155-143-131-135-122</t>
+          <t>112-110-151-152-138-140-154-167-139-149-136-137-125-126-100-88-84-99-89-102-128-141-115</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>48-63-50-49-23-62-76-74-75-9-11-10-36-35-34-21-22-59-73-47-8-7-20-6-32-46-58-5-18</t>
+          <t>41-56-43-17-4-2-29-42-67-69-53-40-52-51-64-65-26-15-1-12-25-38</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25-38-51-70-57-43-29-41-56-42-40-53-67-64-77-52-26-78-79-80-83-81-69-65-12-1-15-17-4-2</t>
+          <t>104-119-120-135-122-134-131-143-145-155-129-91-103-117-118-107-159-161-105-78-77-90-130-109-83-79-80-81-92</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>112-152-154-141-102-115-128-167-151-138-139-140-125-126-137-136-149-110-84-89-88-100-99</t>
+          <t>6-5-18-35-34-21-32-73-76-50-36-23-22-8-70-58-20-9-10-11-49-63-46-59-57-47-48-74-75-62-7</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -18308,35 +18308,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>109-135-139-165-152-102-141-114-100-84-97-112-99-140-115-127-113-126-151-111-124-125-163-162-136-137-123-96-85-86-110</t>
+          <t>7-72-61-89-76-63-62-59-46-74-88-37-50-49-35-23-24-36-21</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>8</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>58-32-41-40-53-27-0-38-39-26-69-68-80-67-54-43-44-45-31-19-3-17-14-52-55-29-30-42-81-66-83-82-70-56</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>36-24-50-63-76-89-88-62-49-46-72-37-23-21-32-45-58-59-7-19-74-61-35</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>7</v>
-      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>69-81-41-17-31-44-43-27-26-3-30-0-14-29-52-53-70-83-82-55-42-67-40-39-38-54-66-78-80-68-56</t>
+          <t>119-159-157-144-142-116-78-77-104-90-105-131-118-130-143-129-156-146-107-94-106</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>116-129-105-106-118-159-146-143-156-142-130-131-104-90-77-94-107-119-144-157</t>
+          <t>99-125-113-114-115-140-151-123-97-110-84-100-112-126-139-127-141-85-86-102-137-152-165-96-109-136-163-162-135-124-111</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -18406,7 +18406,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>139-151-167-141-153-114-115-76-138-137-124-126-100-84-98-112-88-89-102-99-127-128-152-163-150-165</t>
+          <t>157-147-130-142-146-159-120-135-148-160-132-131-133-122-103-90-92-82-83-81-93-91-80-119-104-117-143-156</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -18414,27 +18414,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>73-50-34-33-45-19-20-10-37-36-35-47-9-8-6-5-18</t>
+          <t>153-152-163-124-150-151-139-141-128-114-126-112-100-89-99-98-84-88-167-165-137-138-102-115-127</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>43-55-42-25-13-0-27-54-53-67-68-14-12-38-51-66-77-65-39-64-26-41-17-4-2-3-30</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>6</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>45-73-76-50-37-36-34-33-47-20-19-8-35-10-9-6-5-18</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>9</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>12-25-51-38-26-53-66-67-30-42-4-14-64-77-65-27-2-3-17-55-54-39-41-81-82-83-68-80-43-13-0</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>143-130-131-117-133-148-135-122-120-132-119-92-93-104-91-90-103-142-146-156-157-160-159-147</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -18504,7 +18504,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>163-136-137-124-138-149-96-83-84-165-166-153-98-110-99-87-88-102-127-111-100-112-115-89-141-139-162</t>
+          <t>70-71-21-7-19-35-36-24-50-63-37-23-10-9-33-45-31-46-32-5-20-59-60-47-34-22-75-74-58</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -18512,15 +18512,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>7-50-63-24-10-9-22-37-36-46-47-35-60-59-71-31-5-19-32-34-23-20-21-74-75-58-45-33</t>
+          <t>41-40-64-51-65-12-25-14-15-3-17-1-26-0-13-39-53-66-67-55-68-42-54-56-29</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>68-66-79-51-0-40-26-25-12-13-39-53-54-41-17-3-15-1-14-29-42-56-80-67-64-65-55-70</t>
+          <t>88-87-111-112-100-99-110-136-162-149-163-124-137-84-98-127-115-102-166-139-138-165-153-141-89</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -18528,7 +18528,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>82-95-135-148-104-103-116-130-155-158-134-146-145-90-105-94-81-142-129-118-120-119-107-108-147-132-144-106-93-91</t>
+          <t>81-103-79-90-106-95-132-155-142-129-130-116-93-82-83-108-107-120-145-135-148-96-94-134-147-146-158-144-119-118-105-104-91-80</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -18602,7 +18602,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>108-96-93-91-90-131-155-157-132-144-158-146-106-94-133-109-122-148-147-159-160-121-92-117-142-116-107</t>
+          <t>131-142-155-106-94-93-117-116-144-158-159-90-91-92-109-96-122-121-147-160-148-108-107-133-132-157-146</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -18610,7 +18610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>43-29-28-14-27-13-12-1-2-4-16-53-65-52-38-17-42-55-68-82-81-67-77-51-39-78-79-69-80</t>
+          <t>36-20-33-72-85-84-32-5-7-8-60-86-71-59-57-70-83-45-34-47-22-63-75-87-73-74-50</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -18618,19 +18618,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60-33-32-5-45-59-87-86-36-75-63-50-20-7-8-22-70-83-72-57-71-85-74-73-84-34-47</t>
+          <t>163-137-149-162-164-165-140-102-115-128-126-123-124-125-112-111-114-127-153-141-154-166</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>140-154-166-153-115-102-114-126-165-164-124-125-111-112-123-137-149-162-163-141-128-127</t>
+          <t>1-27-55-69-82-81-68-29-13-78-65-42-43-28-53-67-16-17-4-2-80-79-77-51-12-52-39-38-14</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -18700,31 +18700,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>114-113-115-102-89-100-136-161-122-109-96-84-125-150-164-163-127-152-138-151-162-149-128-141-167-165-123-110-98-111-87-99</t>
+          <t>56-40-28-29-30-16-26-1-2-3-5-35-36-24-11-37-23-22-20-7-8-6-58-57-48-34-61-60-72-71-46-42-18</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2-1-28-30-70-56-57-95-80-81-82-69-64-65-78-79-54-68-42-52-40-26-16-29-3</t>
+          <t>145-119-118-130-129-155-143-116-90-64-65-52-79-78-92-105-117-142-156-157-159-144</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>11-24-23-22-46-18-5-6-7-8-34-58-72-71-60-48-74-75-61-35-37-36-20</t>
+          <t>125-87-113-98-111-99-74-75-89-115-114-127-100-138-152-167-164-136-162-151-149-150-163-165-141-128-102</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>134-121-160-147-159-145-155-142-143-156-157-144-120-119-105-90-92-108-93-118-117-116-129-130</t>
+          <t>93-95-96-84-68-81-122-123-110-109-121-134-108-82-69-70-54-80-147-160-161-120</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -18798,7 +18798,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>159-119-94-92-91-116-104-142-155-131-118-132-146-147-134-121-82-83-96-107-93-80-79-105-120</t>
+          <t>3-29-67-80-79-53-41-14-1-15-55-54-57-69-68-66-52-26-25-51-64-65-12-0</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -18806,7 +18806,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>33-21-46-59-11-24-10-34-47-48-62-61-63-88-87-45-32-58-76-50-23-36-8-20-7</t>
+          <t>85-97-123-149-162-163-138-124-125-139-126-152-153-166-102-114-128-141-165-150-137-136-111-151-100-101-88-87</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -18814,19 +18814,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>25-55-69-57-15-0-14-41-54-26-51-65-64-52-53-66-68-67-29-18-5-3-1-12</t>
+          <t>82-119-142-116-83-96-94-120-118-155-104-131-132-159-146-105-91-135-134-147-161-148-121-107-93-92</t>
         </is>
       </c>
       <c r="G2" t="n">
+        <v>5</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>32-46-47-62-63-76-50-24-11-10-23-33-45-58-59-18-7-48-61-36-34-21-8-20-5</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>7</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>135-163-149-148-161-162-166-165-141-102-101-100-128-153-152-139-138-97-136-111-85-124-125-126-114-151-150-137-123</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -18896,35 +18896,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>142-145-108-121-120-93-81-134-104-117-130-90-91-92-107-131-159-160-147-157-119-118-116-156-155</t>
+          <t>108-92-134-121-93-90-142-155-156-157-159-120-107-131-117-116-130-145-160-147-119-118-104-91</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>56-55-67-41-52-65-78-64-40-14-13-26-3-4-29-27-12-0-2-1-39-51-77-79</t>
+          <t>85-112-153-140-101-100-86-83-96-136-148-161-162-151-165-163-125-137-149-111-98-122-123-124-115-114</t>
         </is>
       </c>
       <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>4-41-40-26-13-12-14-1-0-27-56-67-39-52-51-65-78-77-64-79-81-55-29-2-3</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>7</v>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>70-48-49-37-22-24-11-50-63-47-46-10-9-8-7-57-58-31-20-6-32-60-62-76-61-71-59-33-19-5</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>5</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>85-86-151-124-136-122-161-162-111-112-96-83-100-101-115-114-98-165-163-123-148-149-137-125-140-153</t>
+          <t>76-62-37-20-19-5-6-8-22-7-10-49-61-60-71-70-57-59-48-47-46-32-58-63-50-24-9-11-33-31</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -18994,35 +18994,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>130-145-160-82-93-92-106-79-81-95-109-144-146-157-156-147-134-121-94-107-120-131-105-118-119-103-116-143</t>
+          <t>126-113-111-112-127-115-85-98-99-102-89-139-125-140-153-166-154-167-141-114-75-62-74</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>38-40-26-14-1-28-3-5-30-43-56-54-27-16-4-18-17-44-29-41-52-67-57-69</t>
+          <t>82-107-119-121-67-52-38-79-93-131-103-116-130-146-144-92-94-95-118-143-157-156-145-120-106-105-81</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>71-74-75-61-59-32-19-34-46-60-48-62-49-36-9-83-84-85-89-24-22-8-58</t>
+          <t>40-27-8-59-18-36-24-9-48-60-32-43-57-83-69-54-41-3-16-29-58-22-46-14-17-4-5-44-19-34-61-49-71-84-56-30-28-1-26</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>141-166-152-124-137-163-150-136-162-165-164-153-140-114-102-115-127-113-112-111-99-98-110-125-167-154-139-126-123</t>
+          <t>136-160-147-134-123-137-124-109-110-152-150-164-165-163-162</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
     </row>
   </sheetData>
@@ -19092,23 +19092,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>107-94-108-145-143-157-156-155-146-134-132-131-130-90-78-105-118-129-103-104</t>
+          <t>6-44-45-58-83-73-75-49-50-59-60-19-5-22-10-35-46-33-7-48-72-57-70-31-62-76-11-9</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>5-19-6-57-70-58-59-72-45-44-46-60-85-83-73-48-35-7-9-62-75-76-49-11-50-31-33-22-10</t>
+          <t>26-13-14-15-3-1-2-42-43-30-16-17-56-69-55-0-51-40-39-65-78-67-54-68-29-28-53-52</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>28-52-39-26-13-15-17-43-54-53-40-65-51-0-14-69-68-67-55-30-42-56-29-16-3-2-1</t>
+          <t>145-129-103-105-104-107-108-94-146-131-132-118-90-134-135-148-161-155-156-157-143-130</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -19116,11 +19116,11 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>96-112-99-161-165-153-101-89-115-141-167-128-126-114-125-111-97-88-87-138-151-149-148-136-127-152-164-135</t>
+          <t>164-151-126-111-112-87-88-89-85-99-127-114-128-115-101-141-125-149-96-97-136-165-153-167-152-138</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -19190,31 +19190,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>125-164-165-141-114-99-123-150-136-149-162-151-88-102-128-126-153-97-98-85-86-87-100-112-163-154-167-152-140-127-115</t>
+          <t>47-61-35-9-23-37-19-18-31-46-33-72-60-59-58-50-63-76-36-34-6-8-22-21-20</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>6</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>96-109-122-95-121-157-146-145-144-143-130-103-116-131-158-156-129-117-92-107-108-94-93-105-159-161-147</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>6</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>164-150-149-87-100-154-167-140-127-86-99-88-115-141-163-165-153-162-85-97-136-123-98-125-112-102-128-114-126-151-152</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>4</v>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>26-54-67-41-42-30-4-25-38-39-51-78-77-55-68-43-29-13-1-0-12</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>46-47-34-33-20-19-72-76-50-63-37-35-22-21-8-9-36-23-61-60-31-18-6-59-58-57-70</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>116-93-83-82-96-122-108-109-94-107-157-156-130-92-105-131-117-129-143-145-158-144-147-121-146-159-161-95-81-103</t>
+          <t>26-38-54-41-0-12-51-81-83-70-67-68-82-39-25-77-78-13-1-4-30-42-55-57-43-29</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -19288,31 +19288,31 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>85-101-114-153-97-110-123-136-137-124-98-125-152-154-141-167-164-150-149-112-102-128-127-86</t>
+          <t>82-103-143-157-144-108-121-107-94-80-81-93-92-91-78-90-105-120-133-129-156-160-159-145-106-119-134-122-95</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>21-48-49-36-22-7-6-45-73-74-87-89-76-63-47-46-58-71-59-62-50-23-11-10-34</t>
+          <t>64-51-38-28-42-57-43-53-54-67-39-52-56-70-30-18-4-12-1-2-16-31-65-25-0-26-3-29-40</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16-3-39-25-52-40-28-43-57-70-56-54-42-31-18-4-0-12-64-51-38-26-2-1-29-30-67-65-53</t>
+          <t>58-71-59-74-63-76-62-49-50-36-48-47-73-46-45-6-7-34-23-11-10-22-21</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>78-145-157-144-103-90-106-108-121-134-122-107-82-95-105-93-80-81-94-129-143-156-119-133-120-159-160-92-91</t>
+          <t>124-136-137-150-149-164-114-89-101-86-85-110-125-154-167-102-127-128-141-153-152-123-112-87-98-97</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -19386,7 +19386,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>97-127-139-165-166-154-140-100-102-113-88-85-89-136-149-163-162-150-111-99-115-126-138-152-167-141-128-124-110</t>
+          <t>99-113-136-162-154-167-138-140-165-166-141-128-115-126-127-88-100-150-149-163-139-152-111-124-102-89-97-110</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -19394,7 +19394,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13-12-25-26-66-64-38-40-41-54-67-42-18-5-4-28-14-29-43-44-31-30-17-16-2-69</t>
+          <t>69-42-81-77-64-41-29-28-12-26-25-38-67-79-66-54-40-2-4-17-30-13-14-16-43</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -19402,19 +19402,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>11-24-48-61-73-60-7-10-37-9-33-32-46-59-74-75-76-49-22-21-19-20-63-50</t>
+          <t>157-144-131-122-96-109-94-93-158-161-146-130-116-129-90-103-143-156-155-119-120-121-134-135-107-105-118-133</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>79-131-103-105-77-90-130-129-155-143-146-121-93-81-107-133-116-156-144-158-157-161-135-94-120-118-119-134-122-96-109</t>
+          <t>7-33-20-9-24-50-48-61-60-32-19-22-10-21-46-44-18-31-59-63-49-75-74-73-85-76-37-11-5</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -19484,23 +19484,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>148-149-126-151-165-164-153-154-138-124-97-84-99-125-113-87-101-100-162-163-161-122-135-128-115-102-114-140-98-111-96</t>
+          <t>153-154-100-138-165-151-124-111-84-99-113-115-102-101-128-114-126-140-125-162-149-163-164-148-161-135-98-97-96-122</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>71-7-20-34-11-10-36-23-24-49-61-74-46-45-32-33-73-75-63-60-47-48-35-22-72</t>
+          <t>71-45-33-34-61-74-75-87-72-73-63-36-23-11-22-20-7-32-46-60-47-35-10-24-49-48</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>44-57-31-30-54-66-64-51-67-55-3-2-0-12-13-40-53-42-4-1-27-28-56-17</t>
+          <t>1-3-54-53-42-31-44-57-27-2-4-17-30-56-55-0-12-13-40-51-66-67-28</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -19508,7 +19508,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>116-129-90-104-119-133-134-145-142-130-94-107-93-80-81-82-118-121-146-159-103-117-92-79-77-78</t>
+          <t>107-121-133-82-81-80-94-92-93-129-159-146-145-130-117-64-79-78-77-90-104-142-116-103-119-118-134</t>
         </is>
       </c>
       <c r="I2" t="n">
@@ -19582,35 +19582,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>91-103-129-133-120-93-80-121-108-79-77-90-105-147-145-156-142-118-106-94-95-107-119-143-131-117-104</t>
+          <t>135-102-115-166-167-154-140-141-139-124-123-87-101-127-126-85-98-110-122-149-148-138-151-153-161</t>
         </is>
       </c>
       <c r="C2" t="n">
+        <v>5</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>44-31-17-4-16-2-69-83-70-57-82-68-28-42-51-54-53-66-15-3-40-27-0-39-43-56</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>19-21-9-10-50-62-63-24-11-36-74-73-72-59-32-23-37-35-34-33-20-8-7</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>8</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>106-91-104-105-118-93-95-96-108-107-80-79-103-90-77-94-121-133-143-142-129-117-119-156-131-145-147-120</t>
+        </is>
+      </c>
+      <c r="I2" t="n">
         <v>6</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>63-50-37-36-62-74-35-34-19-32-59-73-72-21-9-7-8-23-24-11-10-20-33</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>7</v>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>82-83-70-69-56-66-51-15-28-54-68-27-0-16-3-2-39-40-53-42-43-4-17-31-44-57</t>
-        </is>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>140-127-115-102-139-154-167-166-151-141-126-85-110-122-124-138-153-149-148-161-135-123-87-101-98-96</t>
-        </is>
-      </c>
-      <c r="I2" t="n">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -19680,35 +19680,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>77-78-92-105-90-103-118-119-134-120-143-129-142-130-146-147-160-158-132-106-93-116-144-156-157-95-117</t>
+          <t>158-147-157-116-119-132-146-160-162-149-134-120-106-105-118-103-117-144-143-130-129-142-156</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>14-42-55-56-31-29-30-40-52-64-80-82-83-57-69-81-54-53-68-28-16-17-4-3-15-0-26-27-12-2</t>
+          <t>55-56-57-58-83-82-69-68-54-53-64-92-109-96-95-93-80-78-90-77-52-81</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>47-45-58-60-59-33-21-6-22-37-36-49-75-62-61-23-10-35</t>
+          <t>110-59-47-36-22-35-62-88-100-113-127-154-112-97-138-163-140-141-89-23-10-61-114-126-164-137-123-111-139-165-75-49-37-60-98-125-150-115-152</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>163-152-140-141-154-165-97-88-89-127-114-115-113-139-126-100-112-137-138-98-96-123-162-149-164-110-109-111-125-150</t>
+          <t>27-14-17-4-6-33-45-21-31-30-42-29-28-2-3-16-15-40-12-0-26</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -19778,7 +19778,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>137-123-111-98-99-87-88-89-114-141-140-152-164-138-126-113-139-151-163-165-166-167-110-97-149-150-101-115</t>
+          <t>28-31-44-56-5-18-16-41-55-66-52-12-25-1-0-13-64-65-69-30-2-3-26-14-53-67-54</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -19786,27 +19786,27 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>52-28-14-0-1-2-30-69-67-56-55-16-3-26-12-13-25-64-65-66-80-79-91-90-77-82-41-53-54</t>
+          <t>46-45-58-71-72-59-47-62-37-50-35-21-60-61-87-88-89-63-11-9-7</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>31-44-71-58-59-72-60-47-61-62-35-63-50-11-37-9-21-7-45-46-5-18</t>
+          <t>108-121-90-77-134-160-147-159-132-131-145-144-158-142-105-91-92-120-96-79-80-95-82-118-129-130</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>161-160-158-105-92-134-135-148-122-121-108-120-132-131-159-147-145-144-118-130-129-142-95-96</t>
+          <t>161-148-164-165-115-141-166-138-152-113-150-163-151-98-114-101-140-139-137-149-135-123-110-97-111-99-126-167-122</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -19876,35 +19876,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>108-106-117-159-160-120-132-147-146-133-129-144-157-145-155-156-143-142-130-131-79-93-107-121-95-94-81-80-104-77-90-91</t>
+          <t>81-55-17-16-15-29-39-14-13-0-1-26-27-56-53-65-51-52-77-79-90-91-80-67-64-69</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8-20-19-71-84-72-62-23-45-32-47-21-22-35-60-83-61-49-63-88-75-48-59-58-34-46-6-44-70-86-73-74-76-36-9</t>
+          <t>84-63-62-34-32-18-6-20-35-36-46-70-73-75-88-19-5-21-8-9-22-49-23-76-74-45-44-72-47-60-86-59-61-48-58-71-83</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>13-0-15-29-16-5-18-17-69-56-27-26-39-52-53-14-1-55-67-65-64-51</t>
+          <t>122-109-94-104-120-133-147-121-107-93-117-156-157-144-130-132-145-129-142-155-106-108-95-148-135-146-131-143-159-160-161</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>161-148-135-151-127-115-114-101-128-154-141-153-110-109-97-124-137-165-167-139-126-113-111-98-122-123-149-150-162-164-166-112-100</t>
+          <t>98-97-110-123-124-137-128-154-167-165-162-164-127-101-100-111-112-113-114-115-141-153-166-126-139-151-150-149</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -19974,15 +19974,15 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>119-133-147-156-142-116-117-105-78-90-108-121-145-146-159-93-118-155-143-131-104-92-77-91-79-95-94</t>
+          <t>4-3-16-17-43-69-54-67-41-0-2-12-26-66-53-39-64-52-51-28-14-25-40-55-15</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3-54-55-66-53-40-2-0-12-39-25-26-51-64-67-69-82-70-44-57-43-16-15-17-4-28-41-52-14</t>
+          <t>133-121-108-95-82-94-119-131-92-91-104-105-117-142-143-147-159-146-118-79-93-77-78-90-116-155-156-145</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -19990,19 +19990,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>76-75-60-22-9-36-37-34-33-31-19-46-47-48-35-10-8-6-5-7-20-32-45-72-62-50</t>
+          <t>110-161-163-162-135-123-136-137-101-102-115-140-167-153-100-87-86-83-96-98-149-148-139-165-152-150-151-88-99-124-111-85</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>98-86-96-110-111-163-151-102-88-101-153-167-165-136-135-152-162-149-148-161-150-137-124-123-140-139-85-99-87-115-100-83</t>
+          <t>31-70-72-48-35-33-32-45-44-57-46-20-62-76-75-60-47-36-10-9-5-6-34-50-37-22-8-7-19</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -20072,7 +20072,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>148-120-119-118-104-94-93-91-103-129-143-156-155-159-147-133-95-105-131-144-145-142-116-90-92-107-146-160</t>
+          <t>155-156-159-145-107-119-120-146-160-143-144-93-95-94-92-105-104-118-147-131-133-91-90-103-129-142-116</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -20080,7 +20080,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>83-70-3-30-43-16-41-81-69-56-67-54-79-68-55-15-65-78-51-52-28-4-17-14-38-64-25-40-27-26-66</t>
+          <t>97-98-153-128-127-166-167-148-149-138-140-139-152-150-151-115-102-101-96-122-109-123-124-125-99-111-100-137-162-110</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -20088,19 +20088,19 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>19-21-48-60-76-75-63-49-35-24-22-10-32-45-59-72-58-47-36-37-62-73-71-46-34-8-5</t>
+          <t>59-58-36-37-34-21-8-85-86-72-84-75-76-88-89-49-62-63-35-10-22-48-47-46-60-71-45-32-19-24-87-73</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>150-122-125-140-128-127-89-102-101-115-99-139-167-166-152-123-111-124-153-151-162-149-138-137-109-110-97-84-96-98-86-100-88-87-85</t>
+          <t>55-68-79-78-65-38-25-51-64-67-54-4-5-56-30-17-26-40-41-43-70-83-69-81-16-3-28-27-14-15-52-66</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -20170,35 +20170,35 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>96-86-126-141-153-151-152-150-164-163-161-98-114-101-102-112-123-135-165-154-167-127-89-99-125-124-162-122-110-97-84-85-128-115-88</t>
+          <t>31-44-57-84-70-45-11-10-19-18-59-49-76-63-73-61-34-48-35-21-6-8-22-9-7-20-85-74-71-58-46-32</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>46-76-63-73-74-61-49-11-20-9-10-35-34-19-45-70-57-32-44-31-18-21-59-48-22-8-6-7-58-71</t>
+          <t>163-150-153-115-89-99-112-96-110-97-122-123-152-167-154-141-102-101-126-125-124-135-162-114-128-127-88-86-98-161-165-151-164</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>68-69-67-52-78-51-38-0-16-4-42-56-54-1-13-12-64-25-40-27-26</t>
+          <t>1-12-64-78-52-51-25-38-27-56-69-68-42-4-16-54-67-40-26-13-0</t>
         </is>
       </c>
       <c r="G2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>90-103-104-116-143-142-155-156-160-147-134-144-91-92-94-95-133-132-120-105-93-107-108-158-157-130-117</t>
+          <t>93-103-116-117-130-147-160-158-133-132-142-155-143-156-120-108-92-91-104-90-107-94-95-134-157-144-105</t>
         </is>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
